--- a/workspaces/example_new_calculations/input/input.xlsx
+++ b/workspaces/example_new_calculations/input/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKL\Documents\Github\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9AABB1-8C0C-43A9-B9D2-267F6B69BDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0624654-91F0-4134-87DE-988E2AA5D3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-180" windowWidth="29040" windowHeight="17520" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
+    <workbookView xWindow="38280" yWindow="-165" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
   </bookViews>
   <sheets>
     <sheet name="Vakken" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="Ondergrondscenarios" sheetId="3" r:id="rId3"/>
     <sheet name="Overzicht_variabelen" sheetId="2" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Ondergrondscenarios!$A$1:$O$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="209">
   <si>
     <t>M_van</t>
   </si>
@@ -687,7 +690,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -697,6 +700,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -713,13 +722,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -827,7 +838,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{ECE0F829-0060-4D7E-94D4-430EA87FED82}" name="Tabel12" displayName="Tabel12" ref="A2:P55" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{ECE0F829-0060-4D7E-94D4-430EA87FED82}" name="Tabel12" displayName="Tabel12" ref="A2:P69" headerRowCount="0" totalsRowShown="0">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P55">
     <sortCondition ref="D2:D55" customList="Input,Input,can also be calculated,Constant,Calculated"/>
     <sortCondition ref="A2:A55"/>
@@ -1172,21 +1183,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C253AA-AAA1-47E5-9332-CA169F978D7A}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.25" customWidth="1"/>
-    <col min="2" max="2" width="32.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.25" customWidth="1"/>
-    <col min="5" max="5" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.375" customWidth="1"/>
+    <col min="1" max="1" width="8.19921875" customWidth="1"/>
+    <col min="2" max="2" width="32.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.19921875" customWidth="1"/>
+    <col min="5" max="5" width="8.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.3984375" customWidth="1"/>
     <col min="10" max="10" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>180</v>
       </c>
@@ -1211,19 +1222,19 @@
       <c r="H1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="4" t="str">
-        <f>LEFT(H1,LEN(H1)-5)&amp;VLOOKUP(LEFT(H1,LEN(H1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+      <c r="I1" s="6" t="str">
+        <f>LEFT(H1,LEN(H1)-5)&amp;VLOOKUP(LEFT(H1,LEN(H1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>c_voorland_stdev</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="4" t="str">
-        <f>LEFT(J1,LEN(J1)-5)&amp;VLOOKUP(LEFT(J1,LEN(J1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+      <c r="K1" s="6" t="str">
+        <f>LEFT(J1,LEN(J1)-5)&amp;VLOOKUP(LEFT(J1,LEN(J1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>c_achterland_vc</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1258,7 +1269,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1293,7 +1304,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1328,7 +1339,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1363,7 +1374,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1398,7 +1409,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1433,7 +1444,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1468,7 +1479,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1503,7 +1514,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1549,25 +1560,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB77777-746E-45C0-BE11-D138C11C003A}">
   <dimension ref="A1:T103"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.375" customWidth="1"/>
+    <col min="1" max="1" width="7.3984375" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.8984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.25" customWidth="1"/>
-    <col min="11" max="11" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.19921875" customWidth="1"/>
+    <col min="11" max="11" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.8984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="17.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>180</v>
       </c>
@@ -1613,26 +1624,26 @@
       <c r="O1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="4" t="str">
-        <f>LEFT(O1,LEN(O1)-5)&amp;VLOOKUP(LEFT(O1,LEN(O1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+      <c r="P1" s="6" t="str">
+        <f>LEFT(O1,LEN(O1)-5)&amp;VLOOKUP(LEFT(O1,LEN(O1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>modelfactor_u_stdev</v>
       </c>
       <c r="Q1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="4" t="str">
-        <f>LEFT(Q1,LEN(Q1)-5)&amp;VLOOKUP(LEFT(Q1,LEN(Q1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+      <c r="R1" s="6" t="str">
+        <f>LEFT(Q1,LEN(Q1)-5)&amp;VLOOKUP(LEFT(Q1,LEN(Q1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>modelfactor_h_stdev</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="4" t="str">
-        <f>LEFT(S1,LEN(S1)-5)&amp;VLOOKUP(LEFT(S1,LEN(S1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+      <c r="T1" s="6" t="str">
+        <f>LEFT(S1,LEN(S1)-5)&amp;VLOOKUP(LEFT(S1,LEN(S1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>modelfactor_p_stdev</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1694,7 +1705,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>3</v>
       </c>
@@ -1756,7 +1767,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>4</v>
       </c>
@@ -1818,7 +1829,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1880,7 +1891,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1942,7 +1953,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2004,7 +2015,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5</v>
       </c>
@@ -2066,7 +2077,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5</v>
       </c>
@@ -2128,7 +2139,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>5</v>
       </c>
@@ -2190,7 +2201,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>5</v>
       </c>
@@ -2252,7 +2263,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>5</v>
       </c>
@@ -2314,7 +2325,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>5</v>
       </c>
@@ -2376,7 +2387,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>5</v>
       </c>
@@ -2438,7 +2449,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>5</v>
       </c>
@@ -2500,7 +2511,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>5</v>
       </c>
@@ -2562,7 +2573,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>6</v>
       </c>
@@ -2624,7 +2635,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>6</v>
       </c>
@@ -2686,7 +2697,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>6</v>
       </c>
@@ -2748,7 +2759,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>6</v>
       </c>
@@ -2810,7 +2821,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>6</v>
       </c>
@@ -2872,7 +2883,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>6</v>
       </c>
@@ -2934,7 +2945,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>6</v>
       </c>
@@ -2996,7 +3007,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>6</v>
       </c>
@@ -3058,7 +3069,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>6</v>
       </c>
@@ -3120,7 +3131,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>7</v>
       </c>
@@ -3182,7 +3193,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>7</v>
       </c>
@@ -3244,7 +3255,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>7</v>
       </c>
@@ -3306,7 +3317,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>7</v>
       </c>
@@ -3368,7 +3379,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>7</v>
       </c>
@@ -3430,7 +3441,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>7</v>
       </c>
@@ -3492,7 +3503,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>7</v>
       </c>
@@ -3554,7 +3565,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>7</v>
       </c>
@@ -3616,7 +3627,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>7</v>
       </c>
@@ -3678,7 +3689,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>7</v>
       </c>
@@ -3740,7 +3751,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>7</v>
       </c>
@@ -3802,7 +3813,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>7</v>
       </c>
@@ -3864,7 +3875,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>7</v>
       </c>
@@ -3926,7 +3937,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>7</v>
       </c>
@@ -3988,7 +3999,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>7</v>
       </c>
@@ -4050,7 +4061,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>8</v>
       </c>
@@ -4112,7 +4123,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>8</v>
       </c>
@@ -4174,7 +4185,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>8</v>
       </c>
@@ -4236,7 +4247,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
@@ -4298,7 +4309,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
@@ -4360,7 +4371,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>8</v>
       </c>
@@ -4422,7 +4433,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>8</v>
       </c>
@@ -4484,7 +4495,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>8</v>
       </c>
@@ -4546,7 +4557,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>8</v>
       </c>
@@ -4608,7 +4619,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>8</v>
       </c>
@@ -4670,7 +4681,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>8</v>
       </c>
@@ -4732,7 +4743,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>8</v>
       </c>
@@ -4794,7 +4805,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>8</v>
       </c>
@@ -4856,7 +4867,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
@@ -4918,7 +4929,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>8</v>
       </c>
@@ -4980,7 +4991,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>8</v>
       </c>
@@ -5042,7 +5053,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>8</v>
       </c>
@@ -5104,7 +5115,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>8</v>
       </c>
@@ -5166,7 +5177,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>8</v>
       </c>
@@ -5228,7 +5239,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>8</v>
       </c>
@@ -5290,7 +5301,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>8</v>
       </c>
@@ -5352,7 +5363,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>8</v>
       </c>
@@ -5414,7 +5425,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>8</v>
       </c>
@@ -5476,7 +5487,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>8</v>
       </c>
@@ -5538,7 +5549,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>8</v>
       </c>
@@ -5600,7 +5611,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>8</v>
       </c>
@@ -5662,7 +5673,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>8</v>
       </c>
@@ -5724,7 +5735,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>8</v>
       </c>
@@ -5786,7 +5797,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>8</v>
       </c>
@@ -5848,7 +5859,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>8</v>
       </c>
@@ -5910,7 +5921,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>8</v>
       </c>
@@ -5972,7 +5983,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>8</v>
       </c>
@@ -6034,7 +6045,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>8</v>
       </c>
@@ -6096,7 +6107,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>8</v>
       </c>
@@ -6158,7 +6169,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>8</v>
       </c>
@@ -6220,7 +6231,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>8</v>
       </c>
@@ -6282,7 +6293,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>8</v>
       </c>
@@ -6344,7 +6355,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>8</v>
       </c>
@@ -6406,7 +6417,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>8</v>
       </c>
@@ -6468,7 +6479,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>8</v>
       </c>
@@ -6530,7 +6541,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>9</v>
       </c>
@@ -6592,7 +6603,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>9</v>
       </c>
@@ -6654,7 +6665,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>9</v>
       </c>
@@ -6716,7 +6727,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>9</v>
       </c>
@@ -6778,7 +6789,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>9</v>
       </c>
@@ -6840,7 +6851,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>9</v>
       </c>
@@ -6902,7 +6913,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>9</v>
       </c>
@@ -6964,7 +6975,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>9</v>
       </c>
@@ -7026,7 +7037,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>9</v>
       </c>
@@ -7088,7 +7099,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>9</v>
       </c>
@@ -7150,7 +7161,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>9</v>
       </c>
@@ -7212,7 +7223,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>9</v>
       </c>
@@ -7274,7 +7285,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>9</v>
       </c>
@@ -7336,7 +7347,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>9</v>
       </c>
@@ -7398,7 +7409,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>9</v>
       </c>
@@ -7460,7 +7471,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>9</v>
       </c>
@@ -7522,7 +7533,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>9</v>
       </c>
@@ -7584,7 +7595,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>9</v>
       </c>
@@ -7646,7 +7657,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>9</v>
       </c>
@@ -7708,7 +7719,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>9</v>
       </c>
@@ -7770,7 +7781,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>9</v>
       </c>
@@ -7832,7 +7843,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>9</v>
       </c>
@@ -7894,7 +7905,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>9</v>
       </c>
@@ -7967,23 +7978,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3ED9FF6-8968-4FA6-BAEC-B95365AA2886}">
   <dimension ref="A1:O55"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="8.19921875" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.69921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="23.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.59765625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.25" customWidth="1"/>
+    <col min="12" max="12" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>180</v>
       </c>
@@ -7999,29 +8010,29 @@
       <c r="E1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="4" t="str">
-        <f>LEFT(E1,LEN(E1)-5)&amp;VLOOKUP(LEFT(E1,LEN(E1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+      <c r="F1" s="6" t="str">
+        <f>LEFT(E1,LEN(E1)-5)&amp;VLOOKUP(LEFT(E1,LEN(E1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>top_zand</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="4" t="str">
-        <f>LEFT(G1,LEN(G1)-5)&amp;VLOOKUP(LEFT(G1,LEN(G1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+      <c r="H1" s="6" t="str">
+        <f>LEFT(G1,LEN(G1)-5)&amp;VLOOKUP(LEFT(G1,LEN(G1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>gamma_sat_deklaag_stdev</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="4" t="str">
-        <f>LEFT(I1,LEN(I1)-5)&amp;VLOOKUP(LEFT(I1,LEN(I1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+      <c r="J1" s="6" t="str">
+        <f>LEFT(I1,LEN(I1)-5)&amp;VLOOKUP(LEFT(I1,LEN(I1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>D_wvp_stdev</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="4" t="str">
-        <f>LEFT(K1,LEN(K1)-5)&amp;VLOOKUP(LEFT(K1,LEN(K1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+      <c r="L1" s="6" t="str">
+        <f>LEFT(K1,LEN(K1)-5)&amp;VLOOKUP(LEFT(K1,LEN(K1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>kD_wvp_vc</v>
       </c>
       <c r="M1" s="4" t="s">
@@ -8030,12 +8041,12 @@
       <c r="N1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="4" t="str">
-        <f>LEFT(N1,LEN(N1)-5)&amp;VLOOKUP(LEFT(N1,LEN(N1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+      <c r="O1" s="6" t="str">
+        <f>LEFT(N1,LEN(N1)-5)&amp;VLOOKUP(LEFT(N1,LEN(N1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>d70_vc</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -8082,7 +8093,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8129,7 +8140,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -8167,7 +8178,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -8200,7 +8211,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
@@ -8233,7 +8244,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
@@ -8266,7 +8277,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2</v>
       </c>
@@ -8313,7 +8324,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2</v>
       </c>
@@ -8360,7 +8371,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2</v>
       </c>
@@ -8398,7 +8409,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2</v>
       </c>
@@ -8431,7 +8442,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
@@ -8464,7 +8475,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
@@ -8497,7 +8508,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>3</v>
       </c>
@@ -8544,7 +8555,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>3</v>
       </c>
@@ -8591,7 +8602,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>3</v>
       </c>
@@ -8629,7 +8640,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>3</v>
       </c>
@@ -8662,7 +8673,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>3</v>
       </c>
@@ -8695,7 +8706,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
@@ -8728,7 +8739,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>4</v>
       </c>
@@ -8775,7 +8786,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>4</v>
       </c>
@@ -8822,7 +8833,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>4</v>
       </c>
@@ -8860,7 +8871,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>4</v>
       </c>
@@ -8893,7 +8904,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>4</v>
       </c>
@@ -8926,7 +8937,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>4</v>
       </c>
@@ -8959,7 +8970,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>5</v>
       </c>
@@ -9006,7 +9017,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>5</v>
       </c>
@@ -9053,7 +9064,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>5</v>
       </c>
@@ -9091,7 +9102,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>5</v>
       </c>
@@ -9124,7 +9135,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>5</v>
       </c>
@@ -9157,7 +9168,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>5</v>
       </c>
@@ -9190,7 +9201,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>6</v>
       </c>
@@ -9237,7 +9248,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>6</v>
       </c>
@@ -9284,7 +9295,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>6</v>
       </c>
@@ -9322,7 +9333,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>6</v>
       </c>
@@ -9355,7 +9366,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>6</v>
       </c>
@@ -9388,7 +9399,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
@@ -9421,7 +9432,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>7</v>
       </c>
@@ -9468,7 +9479,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>7</v>
       </c>
@@ -9515,7 +9526,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>7</v>
       </c>
@@ -9553,7 +9564,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
@@ -9586,7 +9597,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
@@ -9619,7 +9630,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
@@ -9652,7 +9663,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
@@ -9699,7 +9710,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
@@ -9746,7 +9757,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>8</v>
       </c>
@@ -9784,7 +9795,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>8</v>
       </c>
@@ -9817,7 +9828,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>8</v>
       </c>
@@ -9850,7 +9861,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>8</v>
       </c>
@@ -9883,7 +9894,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>9</v>
       </c>
@@ -9930,7 +9941,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>9</v>
       </c>
@@ -9977,7 +9988,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>9</v>
       </c>
@@ -10015,7 +10026,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>9</v>
       </c>
@@ -10048,7 +10059,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>9</v>
       </c>
@@ -10081,7 +10092,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
@@ -10115,36 +10126,38 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O1" xr:uid="{A3ED9FF6-8968-4FA6-BAEC-B95365AA2886}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B7A8CE-63DA-4EEA-9A88-5E62FD2B5E40}">
-  <dimension ref="A1:R55"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:R69"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="17.19921875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.19921875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="47.625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.25" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="47.59765625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.19921875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>192</v>
       </c>
@@ -10197,7 +10210,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -10234,7 +10247,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>99</v>
       </c>
@@ -10262,7 +10275,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -10293,7 +10306,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>88</v>
       </c>
@@ -10313,7 +10326,7 @@
         <v>57</v>
       </c>
       <c r="I5" s="2">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
         <v>60</v>
@@ -10325,7 +10338,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>93</v>
       </c>
@@ -10348,7 +10361,7 @@
         <v>1.4999999999999999E-4</v>
       </c>
       <c r="J6" s="1">
-        <v>5.0000000000000001E-4</v>
+        <v>5</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>70</v>
@@ -10360,7 +10373,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>71</v>
       </c>
@@ -10380,7 +10393,7 @@
         <v>57</v>
       </c>
       <c r="I7" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2">
         <v>22</v>
@@ -10389,7 +10402,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -10409,7 +10422,7 @@
         <v>59</v>
       </c>
       <c r="I8" s="2">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2">
         <v>4000</v>
@@ -10430,7 +10443,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -10465,7 +10478,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -10498,7 +10511,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -10534,7 +10547,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -10572,7 +10585,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>105</v>
       </c>
@@ -10606,7 +10619,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>106</v>
       </c>
@@ -10640,7 +10653,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>102</v>
       </c>
@@ -10674,7 +10687,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -10696,8 +10709,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A17" t="s">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="s">
         <v>19</v>
       </c>
       <c r="B17" t="s">
@@ -10709,15 +10722,11 @@
       <c r="D17" t="s">
         <v>53</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I17" s="2">
-        <v>-4</v>
-      </c>
-      <c r="J17" s="2">
-        <v>15</v>
-      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
         <v>55</v>
       </c>
@@ -10725,7 +10734,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -10759,8 +10768,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A19" t="s">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
         <v>67</v>
       </c>
       <c r="B19" t="s">
@@ -10772,7 +10781,7 @@
       <c r="D19" t="s">
         <v>53</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="7" t="s">
         <v>69</v>
       </c>
       <c r="I19" s="2">
@@ -10788,7 +10797,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>130</v>
       </c>
@@ -10817,7 +10826,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>115</v>
       </c>
@@ -10842,7 +10851,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>132</v>
       </c>
@@ -10870,7 +10879,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>138</v>
       </c>
@@ -10899,7 +10908,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>81</v>
       </c>
@@ -10922,7 +10931,7 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>178</v>
       </c>
@@ -10942,7 +10951,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>108</v>
       </c>
@@ -10976,7 +10985,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>174</v>
       </c>
@@ -10996,7 +11005,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>176</v>
       </c>
@@ -11016,7 +11025,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>111</v>
       </c>
@@ -11045,7 +11054,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>127</v>
       </c>
@@ -11074,7 +11083,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>135</v>
       </c>
@@ -11103,7 +11112,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>75</v>
       </c>
@@ -11125,7 +11134,7 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -11149,7 +11158,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>146</v>
       </c>
@@ -11169,7 +11178,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>142</v>
       </c>
@@ -11189,7 +11198,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>140</v>
       </c>
@@ -11209,7 +11218,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>170</v>
       </c>
@@ -11229,7 +11238,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>172</v>
       </c>
@@ -11249,7 +11258,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>168</v>
       </c>
@@ -11269,7 +11278,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>122</v>
       </c>
@@ -11289,7 +11298,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>144</v>
       </c>
@@ -11309,7 +11318,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>90</v>
       </c>
@@ -11330,7 +11339,7 @@
       </c>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>158</v>
       </c>
@@ -11350,7 +11359,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>125</v>
       </c>
@@ -11370,7 +11379,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>156</v>
       </c>
@@ -11390,7 +11399,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>162</v>
       </c>
@@ -11410,7 +11419,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>160</v>
       </c>
@@ -11430,7 +11439,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>120</v>
       </c>
@@ -11456,7 +11465,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>117</v>
       </c>
@@ -11476,7 +11485,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>166</v>
       </c>
@@ -11496,7 +11505,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>164</v>
       </c>
@@ -11516,7 +11525,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>154</v>
       </c>
@@ -11542,7 +11551,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>150</v>
       </c>
@@ -11562,7 +11571,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>152</v>
       </c>
@@ -11582,7 +11591,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>148</v>
       </c>
@@ -11602,9 +11611,93 @@
         <v>119</v>
       </c>
     </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="K56" s="2"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="K57" s="2"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="K58" s="2"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K59" s="2"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="K60" s="2"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="K61" s="2"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="K62" s="2"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="K63" s="2"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="K64" s="2"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K65" s="2"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="K66" s="2"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="K67" s="2"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="K68" s="2"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>185</v>
+      </c>
+      <c r="K69" s="2"/>
+    </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2 F3:F55" xr:uid="{0C4D3287-2227-4749-A999-A3EC2866277F}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F55" xr:uid="{0C4D3287-2227-4749-A999-A3EC2866277F}">
       <formula1>$R$1:$R$2</formula1>
     </dataValidation>
   </dataValidations>

--- a/workspaces/example_new_calculations/input/input.xlsx
+++ b/workspaces/example_new_calculations/input/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKL\Documents\Github\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0624654-91F0-4134-87DE-988E2AA5D3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739F3ADB-FA47-4B04-95F8-99A8E64F4571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-165" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
   </bookViews>
   <sheets>
     <sheet name="Vakken" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Overzicht_variabelen" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Ondergrondscenarios!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Ondergrondscenarios!$A$1:$N$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="207">
   <si>
     <t>M_van</t>
   </si>
@@ -182,9 +182,6 @@
     <t>kD_wvp_mean</t>
   </si>
   <si>
-    <t>k_wvp_mean</t>
-  </si>
-  <si>
     <t>d70_mean</t>
   </si>
   <si>
@@ -345,9 +342,6 @@
   </si>
   <si>
     <t>Weerstand van de deklaag in het achterland</t>
-  </si>
-  <si>
-    <t>Input, can also be calculated</t>
   </si>
   <si>
     <t>modelfactor_u</t>
@@ -815,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9844274D-7B34-420F-9662-89C5C9A298BD}" name="Tabel10" displayName="Tabel10" ref="A2:O55" headerRowCount="0" totalsRowShown="0">
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9844274D-7B34-420F-9662-89C5C9A298BD}" name="Tabel10" displayName="Tabel10" ref="A2:N55" headerRowCount="0" totalsRowShown="0">
+  <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{849DD8E4-53A6-4E3D-B1F9-91F33ED43571}" name="Kolom1"/>
     <tableColumn id="2" xr3:uid="{E80206AD-C5FD-4475-B5E4-08A08DA66E4A}" name="Kolom2"/>
     <tableColumn id="3" xr3:uid="{1769008F-0E39-48C3-B6C5-959D62F52592}" name="Kolom3"/>
@@ -829,7 +823,6 @@
     <tableColumn id="10" xr3:uid="{30E95029-7E84-4404-97EA-CC899B222DC3}" name="Kolom10"/>
     <tableColumn id="11" xr3:uid="{21D2E504-CBB5-45F7-9119-E1DA7B53C2D5}" name="Kolom11"/>
     <tableColumn id="12" xr3:uid="{FF7176FB-923E-4ECE-83AA-046E768AD06C}" name="Kolom12"/>
-    <tableColumn id="13" xr3:uid="{F65A6039-B474-4D50-AEEB-0C9E748E2BE5}" name="Kolom13"/>
     <tableColumn id="14" xr3:uid="{4E1A767E-8059-4EF5-B52B-A1637577AFDF}" name="Kolom14" headerRowDxfId="5" dataDxfId="4"/>
     <tableColumn id="15" xr3:uid="{E12738E9-E3E4-4A5D-81C1-E333D11489B2}" name="Kolom15"/>
   </tableColumns>
@@ -1183,26 +1176,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C253AA-AAA1-47E5-9332-CA169F978D7A}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8.19921875" customWidth="1"/>
-    <col min="2" max="2" width="32.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.19921875" customWidth="1"/>
-    <col min="5" max="5" width="8.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.8984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.09765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.3984375" customWidth="1"/>
+    <col min="1" max="1" width="8.25" customWidth="1"/>
+    <col min="2" max="2" width="32.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.25" customWidth="1"/>
+    <col min="5" max="5" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.375" customWidth="1"/>
     <col min="10" max="10" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.69921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>0</v>
@@ -1211,7 +1204,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>2</v>
@@ -1234,7 +1227,7 @@
         <v>c_achterland_vc</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1269,7 +1262,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1304,7 +1297,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1339,7 +1332,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1374,7 +1367,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1409,7 +1402,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1444,7 +1437,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1479,7 +1472,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1514,7 +1507,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1560,45 +1553,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB77777-746E-45C0-BE11-D138C11C003A}">
   <dimension ref="A1:T103"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="7.3984375" customWidth="1"/>
+    <col min="1" max="1" width="7.375" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.8984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.8984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.19921875" customWidth="1"/>
-    <col min="11" max="11" width="19.19921875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.09765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="17.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.25" customWidth="1"/>
+    <col min="11" max="11" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="17.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>188</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>15</v>
@@ -1610,7 +1603,7 @@
         <v>17</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>18</v>
@@ -1640,10 +1633,10 @@
       </c>
       <c r="T1" s="6" t="str">
         <f>LEFT(S1,LEN(S1)-5)&amp;VLOOKUP(LEFT(S1,LEN(S1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
-        <v>modelfactor_p_stdev</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+        <v>modelfactor_p</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1705,7 +1698,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>3</v>
       </c>
@@ -1767,7 +1760,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>4</v>
       </c>
@@ -1829,7 +1822,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1891,7 +1884,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1953,7 +1946,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2015,7 +2008,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>5</v>
       </c>
@@ -2077,7 +2070,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>5</v>
       </c>
@@ -2139,7 +2132,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>5</v>
       </c>
@@ -2201,7 +2194,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>5</v>
       </c>
@@ -2263,7 +2256,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>5</v>
       </c>
@@ -2325,7 +2318,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>5</v>
       </c>
@@ -2387,7 +2380,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>5</v>
       </c>
@@ -2449,7 +2442,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>5</v>
       </c>
@@ -2511,7 +2504,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>5</v>
       </c>
@@ -2573,7 +2566,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>6</v>
       </c>
@@ -2635,7 +2628,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>6</v>
       </c>
@@ -2697,7 +2690,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>6</v>
       </c>
@@ -2759,7 +2752,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>6</v>
       </c>
@@ -2821,7 +2814,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>6</v>
       </c>
@@ -2883,7 +2876,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>6</v>
       </c>
@@ -2945,7 +2938,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>6</v>
       </c>
@@ -3007,7 +3000,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>6</v>
       </c>
@@ -3069,7 +3062,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>6</v>
       </c>
@@ -3131,7 +3124,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>7</v>
       </c>
@@ -3193,7 +3186,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>7</v>
       </c>
@@ -3255,7 +3248,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>7</v>
       </c>
@@ -3317,7 +3310,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>7</v>
       </c>
@@ -3379,7 +3372,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>7</v>
       </c>
@@ -3441,7 +3434,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>7</v>
       </c>
@@ -3503,7 +3496,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>7</v>
       </c>
@@ -3565,7 +3558,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>7</v>
       </c>
@@ -3627,7 +3620,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>7</v>
       </c>
@@ -3689,7 +3682,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>7</v>
       </c>
@@ -3751,7 +3744,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>7</v>
       </c>
@@ -3813,7 +3806,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>7</v>
       </c>
@@ -3875,7 +3868,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>7</v>
       </c>
@@ -3937,7 +3930,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>7</v>
       </c>
@@ -3999,7 +3992,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>7</v>
       </c>
@@ -4061,7 +4054,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>8</v>
       </c>
@@ -4123,7 +4116,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>8</v>
       </c>
@@ -4185,7 +4178,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>8</v>
       </c>
@@ -4247,7 +4240,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>8</v>
       </c>
@@ -4309,7 +4302,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>8</v>
       </c>
@@ -4371,7 +4364,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>8</v>
       </c>
@@ -4433,7 +4426,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>8</v>
       </c>
@@ -4495,7 +4488,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>8</v>
       </c>
@@ -4557,7 +4550,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>8</v>
       </c>
@@ -4619,7 +4612,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>8</v>
       </c>
@@ -4681,7 +4674,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>8</v>
       </c>
@@ -4743,7 +4736,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>8</v>
       </c>
@@ -4805,7 +4798,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>8</v>
       </c>
@@ -4867,7 +4860,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>8</v>
       </c>
@@ -4929,7 +4922,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>8</v>
       </c>
@@ -4991,7 +4984,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>8</v>
       </c>
@@ -5053,7 +5046,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>8</v>
       </c>
@@ -5115,7 +5108,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>8</v>
       </c>
@@ -5177,7 +5170,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>8</v>
       </c>
@@ -5239,7 +5232,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>8</v>
       </c>
@@ -5301,7 +5294,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>8</v>
       </c>
@@ -5363,7 +5356,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A62">
         <v>8</v>
       </c>
@@ -5425,7 +5418,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A63">
         <v>8</v>
       </c>
@@ -5487,7 +5480,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A64">
         <v>8</v>
       </c>
@@ -5549,7 +5542,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A65">
         <v>8</v>
       </c>
@@ -5611,7 +5604,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A66">
         <v>8</v>
       </c>
@@ -5673,7 +5666,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A67">
         <v>8</v>
       </c>
@@ -5735,7 +5728,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A68">
         <v>8</v>
       </c>
@@ -5797,7 +5790,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A69">
         <v>8</v>
       </c>
@@ -5859,7 +5852,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A70">
         <v>8</v>
       </c>
@@ -5921,7 +5914,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A71">
         <v>8</v>
       </c>
@@ -5983,7 +5976,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A72">
         <v>8</v>
       </c>
@@ -6045,7 +6038,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A73">
         <v>8</v>
       </c>
@@ -6107,7 +6100,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A74">
         <v>8</v>
       </c>
@@ -6169,7 +6162,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A75">
         <v>8</v>
       </c>
@@ -6231,7 +6224,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A76">
         <v>8</v>
       </c>
@@ -6293,7 +6286,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A77">
         <v>8</v>
       </c>
@@ -6355,7 +6348,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A78">
         <v>8</v>
       </c>
@@ -6417,7 +6410,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A79">
         <v>8</v>
       </c>
@@ -6479,7 +6472,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A80">
         <v>8</v>
       </c>
@@ -6541,7 +6534,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A81">
         <v>9</v>
       </c>
@@ -6603,7 +6596,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A82">
         <v>9</v>
       </c>
@@ -6665,7 +6658,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A83">
         <v>9</v>
       </c>
@@ -6727,7 +6720,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A84">
         <v>9</v>
       </c>
@@ -6789,7 +6782,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A85">
         <v>9</v>
       </c>
@@ -6851,7 +6844,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A86">
         <v>9</v>
       </c>
@@ -6913,7 +6906,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A87">
         <v>9</v>
       </c>
@@ -6975,7 +6968,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A88">
         <v>9</v>
       </c>
@@ -7037,7 +7030,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A89">
         <v>9</v>
       </c>
@@ -7099,7 +7092,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A90">
         <v>9</v>
       </c>
@@ -7161,7 +7154,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A91">
         <v>9</v>
       </c>
@@ -7223,7 +7216,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A92">
         <v>9</v>
       </c>
@@ -7285,7 +7278,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A93">
         <v>9</v>
       </c>
@@ -7347,7 +7340,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A94">
         <v>9</v>
       </c>
@@ -7409,7 +7402,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A95">
         <v>9</v>
       </c>
@@ -7471,7 +7464,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A96">
         <v>9</v>
       </c>
@@ -7533,7 +7526,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A97">
         <v>9</v>
       </c>
@@ -7595,7 +7588,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A98">
         <v>9</v>
       </c>
@@ -7657,7 +7650,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A99">
         <v>9</v>
       </c>
@@ -7719,7 +7712,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A100">
         <v>9</v>
       </c>
@@ -7781,7 +7774,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A101">
         <v>9</v>
       </c>
@@ -7843,7 +7836,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A102">
         <v>9</v>
       </c>
@@ -7905,7 +7898,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A103">
         <v>9</v>
       </c>
@@ -7977,42 +7970,41 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3ED9FF6-8968-4FA6-BAEC-B95365AA2886}">
-  <dimension ref="A1:O55"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N55"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8.19921875" customWidth="1"/>
+    <col min="1" max="1" width="8.25" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.8984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="23.09765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.19921875" customWidth="1"/>
+    <col min="12" max="12" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>191</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>42</v>
       </c>
       <c r="F1" s="6" t="str">
         <f>LEFT(E1,LEN(E1)-5)&amp;VLOOKUP(LEFT(E1,LEN(E1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
-        <v>top_zand</v>
+        <v>top_zand_stdev</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>43</v>
@@ -8038,23 +8030,20 @@
       <c r="M1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="6" t="str">
+        <f>LEFT(M1,LEN(M1)-5)&amp;VLOOKUP(LEFT(M1,LEN(M1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
+        <v>d70_vc</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>47</v>
-      </c>
-      <c r="O1" s="6" t="str">
-        <f>LEFT(N1,LEN(N1)-5)&amp;VLOOKUP(LEFT(N1,LEN(N1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
-        <v>d70_vc</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>48</v>
       </c>
       <c r="D2">
         <v>0.5</v>
@@ -8083,17 +8072,14 @@
       <c r="L2">
         <v>0.39</v>
       </c>
-      <c r="M2">
-        <v>56</v>
-      </c>
-      <c r="N2" s="1">
+      <c r="M2" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O2">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N2">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8101,7 +8087,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3">
         <v>0.5</v>
@@ -8130,17 +8116,14 @@
       <c r="L3">
         <v>0.35</v>
       </c>
-      <c r="M3">
-        <v>52</v>
-      </c>
-      <c r="N3" s="1">
+      <c r="M3" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O3">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N3">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>1</v>
       </c>
@@ -8148,7 +8131,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -8171,14 +8154,14 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="N4" s="1">
+      <c r="M4" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O4">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N4">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>1</v>
       </c>
@@ -8206,12 +8189,12 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="N5" s="1"/>
-      <c r="O5">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M5" s="1"/>
+      <c r="N5">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>1</v>
       </c>
@@ -8239,12 +8222,12 @@
       <c r="K6">
         <v>0</v>
       </c>
-      <c r="N6" s="1"/>
-      <c r="O6">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M6" s="1"/>
+      <c r="N6">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>1</v>
       </c>
@@ -8272,12 +8255,12 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="N7" s="1"/>
-      <c r="O7">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M7" s="1"/>
+      <c r="N7">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>2</v>
       </c>
@@ -8285,7 +8268,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8">
         <v>0.5</v>
@@ -8314,17 +8297,14 @@
       <c r="L8">
         <v>0.39</v>
       </c>
-      <c r="M8">
-        <v>56</v>
-      </c>
-      <c r="N8" s="1">
+      <c r="M8" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O8">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N8">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>2</v>
       </c>
@@ -8332,7 +8312,7 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9">
         <v>0.5</v>
@@ -8361,17 +8341,14 @@
       <c r="L9">
         <v>0.35</v>
       </c>
-      <c r="M9">
-        <v>52</v>
-      </c>
-      <c r="N9" s="1">
+      <c r="M9" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O9">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N9">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>2</v>
       </c>
@@ -8379,7 +8356,7 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -8402,14 +8379,14 @@
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="N10" s="1">
+      <c r="M10" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O10">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N10">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>2</v>
       </c>
@@ -8437,12 +8414,12 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="N11" s="1"/>
-      <c r="O11">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M11" s="1"/>
+      <c r="N11">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>2</v>
       </c>
@@ -8470,12 +8447,12 @@
       <c r="K12">
         <v>0</v>
       </c>
-      <c r="N12" s="1"/>
-      <c r="O12">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M12" s="1"/>
+      <c r="N12">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>2</v>
       </c>
@@ -8503,12 +8480,12 @@
       <c r="K13">
         <v>0</v>
       </c>
-      <c r="N13" s="1"/>
-      <c r="O13">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M13" s="1"/>
+      <c r="N13">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>3</v>
       </c>
@@ -8516,7 +8493,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14">
         <v>0.5</v>
@@ -8545,17 +8522,14 @@
       <c r="L14">
         <v>0.39</v>
       </c>
-      <c r="M14">
-        <v>56</v>
-      </c>
-      <c r="N14" s="1">
+      <c r="M14" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O14">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N14">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>3</v>
       </c>
@@ -8563,7 +8537,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15">
         <v>0.5</v>
@@ -8592,17 +8566,14 @@
       <c r="L15">
         <v>0.35</v>
       </c>
-      <c r="M15">
-        <v>52</v>
-      </c>
-      <c r="N15" s="1">
+      <c r="M15" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O15">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N15">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>3</v>
       </c>
@@ -8610,7 +8581,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -8633,14 +8604,14 @@
       <c r="K16">
         <v>0</v>
       </c>
-      <c r="N16" s="1">
+      <c r="M16" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O16">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N16">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>3</v>
       </c>
@@ -8668,12 +8639,12 @@
       <c r="K17">
         <v>0</v>
       </c>
-      <c r="N17" s="1"/>
-      <c r="O17">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M17" s="1"/>
+      <c r="N17">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>3</v>
       </c>
@@ -8701,12 +8672,12 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="N18" s="1"/>
-      <c r="O18">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M18" s="1"/>
+      <c r="N18">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>3</v>
       </c>
@@ -8734,12 +8705,12 @@
       <c r="K19">
         <v>0</v>
       </c>
-      <c r="N19" s="1"/>
-      <c r="O19">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M19" s="1"/>
+      <c r="N19">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>4</v>
       </c>
@@ -8747,7 +8718,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D20">
         <v>0.5</v>
@@ -8776,17 +8747,14 @@
       <c r="L20">
         <v>0.39</v>
       </c>
-      <c r="M20">
-        <v>56</v>
-      </c>
-      <c r="N20" s="1">
+      <c r="M20" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O20">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N20">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>4</v>
       </c>
@@ -8794,7 +8762,7 @@
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D21">
         <v>0.5</v>
@@ -8823,17 +8791,14 @@
       <c r="L21">
         <v>0.35</v>
       </c>
-      <c r="M21">
-        <v>52</v>
-      </c>
-      <c r="N21" s="1">
+      <c r="M21" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O21">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N21">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>4</v>
       </c>
@@ -8841,7 +8806,7 @@
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -8864,14 +8829,14 @@
       <c r="K22">
         <v>0</v>
       </c>
-      <c r="N22" s="1">
+      <c r="M22" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O22">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N22">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>4</v>
       </c>
@@ -8899,12 +8864,12 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="N23" s="1"/>
-      <c r="O23">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M23" s="1"/>
+      <c r="N23">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>4</v>
       </c>
@@ -8932,12 +8897,12 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="N24" s="1"/>
-      <c r="O24">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M24" s="1"/>
+      <c r="N24">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>4</v>
       </c>
@@ -8965,12 +8930,12 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="N25" s="1"/>
-      <c r="O25">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M25" s="1"/>
+      <c r="N25">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>5</v>
       </c>
@@ -8978,7 +8943,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D26">
         <v>0.5</v>
@@ -9007,17 +8972,14 @@
       <c r="L26">
         <v>0.39</v>
       </c>
-      <c r="M26">
-        <v>56</v>
-      </c>
-      <c r="N26" s="1">
+      <c r="M26" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O26">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N26">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>5</v>
       </c>
@@ -9025,7 +8987,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D27">
         <v>0.5</v>
@@ -9054,17 +9016,14 @@
       <c r="L27">
         <v>0.35</v>
       </c>
-      <c r="M27">
-        <v>52</v>
-      </c>
-      <c r="N27" s="1">
+      <c r="M27" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O27">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N27">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>5</v>
       </c>
@@ -9072,7 +9031,7 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -9095,14 +9054,14 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="N28" s="1">
+      <c r="M28" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O28">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N28">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>5</v>
       </c>
@@ -9130,12 +9089,12 @@
       <c r="K29">
         <v>0</v>
       </c>
-      <c r="N29" s="1"/>
-      <c r="O29">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M29" s="1"/>
+      <c r="N29">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>5</v>
       </c>
@@ -9163,12 +9122,12 @@
       <c r="K30">
         <v>0</v>
       </c>
-      <c r="N30" s="1"/>
-      <c r="O30">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M30" s="1"/>
+      <c r="N30">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>5</v>
       </c>
@@ -9196,12 +9155,12 @@
       <c r="K31">
         <v>0</v>
       </c>
-      <c r="N31" s="1"/>
-      <c r="O31">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M31" s="1"/>
+      <c r="N31">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>6</v>
       </c>
@@ -9209,7 +9168,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D32">
         <v>0.5</v>
@@ -9238,17 +9197,14 @@
       <c r="L32">
         <v>0.39</v>
       </c>
-      <c r="M32">
-        <v>56</v>
-      </c>
-      <c r="N32" s="1">
+      <c r="M32" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O32">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N32">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>6</v>
       </c>
@@ -9256,7 +9212,7 @@
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D33">
         <v>0.5</v>
@@ -9285,17 +9241,14 @@
       <c r="L33">
         <v>0.35</v>
       </c>
-      <c r="M33">
-        <v>52</v>
-      </c>
-      <c r="N33" s="1">
+      <c r="M33" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O33">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N33">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>6</v>
       </c>
@@ -9303,7 +9256,7 @@
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -9326,14 +9279,14 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="N34" s="1">
+      <c r="M34" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O34">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N34">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>6</v>
       </c>
@@ -9361,12 +9314,12 @@
       <c r="K35">
         <v>0</v>
       </c>
-      <c r="N35" s="1"/>
-      <c r="O35">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M35" s="1"/>
+      <c r="N35">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>6</v>
       </c>
@@ -9394,12 +9347,12 @@
       <c r="K36">
         <v>0</v>
       </c>
-      <c r="N36" s="1"/>
-      <c r="O36">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M36" s="1"/>
+      <c r="N36">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>6</v>
       </c>
@@ -9427,12 +9380,12 @@
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="N37" s="1"/>
-      <c r="O37">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M37" s="1"/>
+      <c r="N37">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>7</v>
       </c>
@@ -9440,7 +9393,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D38">
         <v>0.5</v>
@@ -9469,17 +9422,14 @@
       <c r="L38">
         <v>0.39</v>
       </c>
-      <c r="M38">
-        <v>56</v>
-      </c>
-      <c r="N38" s="1">
+      <c r="M38" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O38">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N38">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>7</v>
       </c>
@@ -9487,7 +9437,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D39">
         <v>0.5</v>
@@ -9516,17 +9466,14 @@
       <c r="L39">
         <v>0.35</v>
       </c>
-      <c r="M39">
-        <v>52</v>
-      </c>
-      <c r="N39" s="1">
+      <c r="M39" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O39">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N39">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>7</v>
       </c>
@@ -9534,7 +9481,7 @@
         <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -9557,14 +9504,14 @@
       <c r="K40">
         <v>0</v>
       </c>
-      <c r="N40" s="1">
+      <c r="M40" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O40">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N40">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>7</v>
       </c>
@@ -9592,12 +9539,12 @@
       <c r="K41">
         <v>0</v>
       </c>
-      <c r="N41" s="1"/>
-      <c r="O41">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M41" s="1"/>
+      <c r="N41">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>7</v>
       </c>
@@ -9625,12 +9572,12 @@
       <c r="K42">
         <v>0</v>
       </c>
-      <c r="N42" s="1"/>
-      <c r="O42">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M42" s="1"/>
+      <c r="N42">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>7</v>
       </c>
@@ -9658,12 +9605,12 @@
       <c r="K43">
         <v>0</v>
       </c>
-      <c r="N43" s="1"/>
-      <c r="O43">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M43" s="1"/>
+      <c r="N43">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>8</v>
       </c>
@@ -9671,7 +9618,7 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D44">
         <v>0.5</v>
@@ -9700,17 +9647,14 @@
       <c r="L44">
         <v>0.39</v>
       </c>
-      <c r="M44">
-        <v>56</v>
-      </c>
-      <c r="N44" s="1">
+      <c r="M44" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O44">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N44">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>8</v>
       </c>
@@ -9718,7 +9662,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D45">
         <v>0.5</v>
@@ -9747,17 +9691,14 @@
       <c r="L45">
         <v>0.35</v>
       </c>
-      <c r="M45">
-        <v>52</v>
-      </c>
-      <c r="N45" s="1">
+      <c r="M45" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O45">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N45">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>8</v>
       </c>
@@ -9765,7 +9706,7 @@
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -9788,14 +9729,14 @@
       <c r="K46">
         <v>0</v>
       </c>
-      <c r="N46" s="1">
+      <c r="M46" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O46">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N46">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>8</v>
       </c>
@@ -9823,12 +9764,12 @@
       <c r="K47">
         <v>0</v>
       </c>
-      <c r="N47" s="1"/>
-      <c r="O47">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M47" s="1"/>
+      <c r="N47">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>8</v>
       </c>
@@ -9856,12 +9797,12 @@
       <c r="K48">
         <v>0</v>
       </c>
-      <c r="N48" s="1"/>
-      <c r="O48">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M48" s="1"/>
+      <c r="N48">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>8</v>
       </c>
@@ -9889,12 +9830,12 @@
       <c r="K49">
         <v>0</v>
       </c>
-      <c r="N49" s="1"/>
-      <c r="O49">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M49" s="1"/>
+      <c r="N49">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>9</v>
       </c>
@@ -9902,7 +9843,7 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D50">
         <v>0.5</v>
@@ -9931,17 +9872,14 @@
       <c r="L50">
         <v>0.39</v>
       </c>
-      <c r="M50">
-        <v>56</v>
-      </c>
-      <c r="N50" s="1">
+      <c r="M50" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O50">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N50">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>9</v>
       </c>
@@ -9949,7 +9887,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D51">
         <v>0.5</v>
@@ -9978,17 +9916,14 @@
       <c r="L51">
         <v>0.35</v>
       </c>
-      <c r="M51">
-        <v>52</v>
-      </c>
-      <c r="N51" s="1">
+      <c r="M51" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O51">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N51">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>9</v>
       </c>
@@ -9996,7 +9931,7 @@
         <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -10019,14 +9954,14 @@
       <c r="K52">
         <v>0</v>
       </c>
-      <c r="N52" s="1">
+      <c r="M52" s="1">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="O52">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N52">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>9</v>
       </c>
@@ -10054,12 +9989,12 @@
       <c r="K53">
         <v>0</v>
       </c>
-      <c r="N53" s="1"/>
-      <c r="O53">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M53" s="1"/>
+      <c r="N53">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>9</v>
       </c>
@@ -10087,12 +10022,12 @@
       <c r="K54">
         <v>0</v>
       </c>
-      <c r="N54" s="1"/>
-      <c r="O54">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M54" s="1"/>
+      <c r="N54">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>9</v>
       </c>
@@ -10120,13 +10055,13 @@
       <c r="K55">
         <v>0</v>
       </c>
-      <c r="N55" s="1"/>
-      <c r="O55">
+      <c r="M55" s="1"/>
+      <c r="N55">
         <v>0.12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1" xr:uid="{A3ED9FF6-8968-4FA6-BAEC-B95365AA2886}"/>
+  <autoFilter ref="A1:N1" xr:uid="{A3ED9FF6-8968-4FA6-BAEC-B95365AA2886}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
@@ -10138,192 +10073,192 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B7A8CE-63DA-4EEA-9A88-5E62FD2B5E40}">
   <dimension ref="A1:R69"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.8984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.25" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="17.25" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.19921875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="47.59765625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.19921875" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="47.625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.25" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>204</v>
-      </c>
       <c r="R1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" t="s">
         <v>55</v>
       </c>
-      <c r="L2" t="s">
-        <v>56</v>
-      </c>
       <c r="M2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
         <v>99</v>
       </c>
-      <c r="B3" t="s">
-        <v>100</v>
-      </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F4" t="s">
-        <v>57</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" t="s">
         <v>56</v>
-      </c>
-      <c r="O4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
@@ -10332,30 +10267,30 @@
         <v>60</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" t="s">
         <v>93</v>
       </c>
-      <c r="B6" t="s">
-        <v>94</v>
-      </c>
       <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
         <v>52</v>
       </c>
-      <c r="D6" t="s">
-        <v>53</v>
-      </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I6" s="1">
         <v>1.4999999999999999E-4</v>
@@ -10364,33 +10299,33 @@
         <v>5</v>
       </c>
       <c r="K6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
         <v>70</v>
       </c>
-      <c r="O6" t="s">
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" t="s">
         <v>56</v>
-      </c>
-      <c r="P6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
@@ -10399,27 +10334,27 @@
         <v>22</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" t="s">
         <v>84</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>85</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
         <v>86</v>
       </c>
-      <c r="D8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" t="s">
-        <v>87</v>
-      </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
@@ -10428,36 +10363,36 @@
         <v>4000</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
         <v>52</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>53</v>
-      </c>
-      <c r="E9" t="s">
-        <v>54</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
@@ -10466,102 +10401,102 @@
         <v>5000</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
         <v>52</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>53</v>
-      </c>
-      <c r="E10" t="s">
-        <v>54</v>
       </c>
       <c r="I10" s="2">
         <v>0</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L10" t="s">
         <v>55</v>
       </c>
-      <c r="L10" t="s">
-        <v>56</v>
-      </c>
       <c r="M10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
         <v>52</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>53</v>
-      </c>
-      <c r="E11" t="s">
-        <v>54</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" t="s">
         <v>55</v>
       </c>
-      <c r="L11" t="s">
-        <v>56</v>
-      </c>
       <c r="M11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
         <v>51</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>52</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>53</v>
-      </c>
-      <c r="E12" t="s">
-        <v>54</v>
       </c>
       <c r="I12" s="2">
         <v>5</v>
@@ -10570,39 +10505,39 @@
         <v>2000</v>
       </c>
       <c r="K12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" t="s">
         <v>55</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
+        <v>55</v>
+      </c>
+      <c r="N12" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" t="s">
+        <v>206</v>
+      </c>
+      <c r="C13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" t="s">
         <v>56</v>
-      </c>
-      <c r="M12" t="s">
-        <v>56</v>
-      </c>
-      <c r="N12" t="s">
-        <v>56</v>
-      </c>
-      <c r="O12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" t="s">
-        <v>208</v>
-      </c>
-      <c r="C13" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
       </c>
       <c r="G13" s="3">
         <v>1</v>
@@ -10613,30 +10548,27 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" t="s">
         <v>55</v>
       </c>
-      <c r="N13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="G14" s="3">
         <v>1</v>
@@ -10647,30 +10579,30 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O14" t="s">
         <v>55</v>
       </c>
-      <c r="O14" t="s">
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" t="s">
-        <v>87</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
       </c>
       <c r="G15" s="3">
         <v>1</v>
@@ -10681,108 +10613,111 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" t="s">
         <v>55</v>
       </c>
-      <c r="M15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" t="s">
         <v>53</v>
-      </c>
-      <c r="E16" t="s">
-        <v>54</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
         <v>19</v>
       </c>
       <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" t="s">
         <v>63</v>
       </c>
-      <c r="C17" t="s">
-        <v>64</v>
-      </c>
       <c r="D17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>53</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>54</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O17" t="s">
         <v>55</v>
       </c>
-      <c r="O17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" t="s">
         <v>53</v>
-      </c>
-      <c r="E18" t="s">
-        <v>54</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L18" t="s">
         <v>55</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18" t="s">
+        <v>55</v>
+      </c>
+      <c r="O18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A19" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" t="s">
         <v>56</v>
-      </c>
-      <c r="M18" t="s">
-        <v>56</v>
-      </c>
-      <c r="N18" t="s">
-        <v>56</v>
-      </c>
-      <c r="O18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>69</v>
       </c>
       <c r="I19" s="2">
         <v>-18</v>
@@ -10791,27 +10726,27 @@
         <v>15</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G20" s="1">
         <v>2.0799999999999999E-4</v>
@@ -10820,27 +10755,27 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G21">
         <v>0.25</v>
@@ -10848,24 +10783,24 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" t="s">
         <v>132</v>
       </c>
-      <c r="B22" t="s">
-        <v>133</v>
-      </c>
-      <c r="C22" t="s">
-        <v>134</v>
-      </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G22">
         <v>9.81</v>
@@ -10873,27 +10808,27 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G23" s="2">
         <v>26</v>
@@ -10902,27 +10837,27 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s">
         <v>81</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" t="s">
         <v>82</v>
       </c>
-      <c r="C24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" t="s">
-        <v>83</v>
-      </c>
       <c r="E24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G24">
         <v>9.81</v>
@@ -10931,44 +10866,44 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B25" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G25">
         <v>1.5</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G26" s="2">
         <v>0.5</v>
@@ -10979,67 +10914,67 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N26" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
+        <v>172</v>
+      </c>
+      <c r="B27" t="s">
+        <v>173</v>
+      </c>
+      <c r="C27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27">
+        <v>0.1</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A28" t="s">
         <v>174</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>175</v>
       </c>
-      <c r="C27" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" t="s">
-        <v>83</v>
-      </c>
-      <c r="G27">
-        <v>0.1</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>176</v>
-      </c>
-      <c r="B28" t="s">
-        <v>177</v>
-      </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G28">
         <v>0.01</v>
       </c>
       <c r="K28" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A29" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>111</v>
-      </c>
-      <c r="B29" t="s">
-        <v>112</v>
-      </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G29" s="2">
         <v>0.3</v>
@@ -11048,27 +10983,27 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O29" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30" t="s">
+        <v>126</v>
+      </c>
+      <c r="C30" t="s">
         <v>127</v>
       </c>
-      <c r="B30" t="s">
-        <v>128</v>
-      </c>
-      <c r="C30" t="s">
-        <v>129</v>
-      </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G30" s="2">
         <v>37</v>
@@ -11077,27 +11012,27 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
+        <v>133</v>
+      </c>
+      <c r="B31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C31" t="s">
         <v>135</v>
       </c>
-      <c r="B31" t="s">
-        <v>136</v>
-      </c>
-      <c r="C31" t="s">
-        <v>137</v>
-      </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G31" s="1">
         <v>1.33E-6</v>
@@ -11106,27 +11041,27 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" t="s">
         <v>75</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" t="s">
         <v>76</v>
       </c>
-      <c r="C32" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>77</v>
-      </c>
-      <c r="E32" t="s">
-        <v>78</v>
       </c>
       <c r="I32" s="2">
         <v>0.1</v>
@@ -11134,202 +11069,202 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" t="s">
         <v>79</v>
       </c>
-      <c r="B33" t="s">
-        <v>80</v>
-      </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D33" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" t="s">
         <v>77</v>
-      </c>
-      <c r="E33" t="s">
-        <v>78</v>
       </c>
       <c r="I33" s="2">
         <v>0.1</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B34" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
       <c r="O34" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B35" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
       <c r="O35" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B36" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
       <c r="M36" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C37" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
       <c r="N37" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B38" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="O38" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B39" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C39" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
       <c r="M39" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="O40" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B41" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C41" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
       <c r="N41" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
+        <v>89</v>
+      </c>
+      <c r="B42" t="s">
         <v>90</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>91</v>
       </c>
-      <c r="C42" t="s">
-        <v>92</v>
-      </c>
       <c r="D42" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I42" s="2">
         <v>1</v>
@@ -11339,359 +11274,443 @@
       </c>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B43" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D43" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
       <c r="L43" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A44" t="s">
+        <v>123</v>
+      </c>
+      <c r="B44" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>125</v>
-      </c>
-      <c r="B44" t="s">
-        <v>126</v>
-      </c>
       <c r="C44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D44" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="O44" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B45" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D45" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
       <c r="L45" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B46" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D46" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
       <c r="L46" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B47" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
       <c r="L47" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D48" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
       <c r="L48" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M48" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N48" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B49" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C49" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
       <c r="L49" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B50" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
       <c r="L50" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B51" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C51" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D51" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
       <c r="L51" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B52" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C52" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D52" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
       <c r="M52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O52" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B53" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C53" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D53" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="N53" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B54" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C54" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D54" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="O54" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B55" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C55" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
       <c r="M55" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A56" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
+      </c>
+      <c r="D56" t="s">
+        <v>52</v>
+      </c>
+      <c r="E56" t="s">
+        <v>53</v>
       </c>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A57" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
+      </c>
+      <c r="D57" t="s">
+        <v>52</v>
+      </c>
+      <c r="E57" t="s">
+        <v>53</v>
       </c>
       <c r="K57" s="2"/>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A58" s="4" t="s">
         <v>0</v>
       </c>
+      <c r="D58" t="s">
+        <v>52</v>
+      </c>
+      <c r="E58" t="s">
+        <v>53</v>
+      </c>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A59" s="4" t="s">
         <v>1</v>
       </c>
+      <c r="D59" t="s">
+        <v>52</v>
+      </c>
+      <c r="E59" t="s">
+        <v>53</v>
+      </c>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A60" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D60" t="s">
+        <v>52</v>
+      </c>
+      <c r="E60" t="s">
+        <v>53</v>
+      </c>
+      <c r="K60" s="2"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A61" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D61" t="s">
+        <v>52</v>
+      </c>
+      <c r="E61" t="s">
+        <v>53</v>
+      </c>
+      <c r="K61" s="2"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A62" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D62" t="s">
+        <v>52</v>
+      </c>
+      <c r="E62" t="s">
+        <v>53</v>
+      </c>
+      <c r="K62" s="2"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A63" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D63" t="s">
+        <v>52</v>
+      </c>
+      <c r="E63" t="s">
+        <v>53</v>
+      </c>
+      <c r="K63" s="2"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A64" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D64" t="s">
+        <v>52</v>
+      </c>
+      <c r="E64" t="s">
+        <v>53</v>
+      </c>
+      <c r="K64" s="2"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A65" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="K60" s="2"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A61" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="K61" s="2"/>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A62" s="4" t="s">
+      <c r="D65" t="s">
+        <v>52</v>
+      </c>
+      <c r="E65" t="s">
+        <v>53</v>
+      </c>
+      <c r="K65" s="2"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A66" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="K62" s="2"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A63" s="4" t="s">
+      <c r="D66" t="s">
+        <v>52</v>
+      </c>
+      <c r="E66" t="s">
+        <v>53</v>
+      </c>
+      <c r="K66" s="2"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A67" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="K63" s="2"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A64" s="4" t="s">
+      <c r="D67" t="s">
+        <v>52</v>
+      </c>
+      <c r="E67" t="s">
+        <v>53</v>
+      </c>
+      <c r="K67" s="2"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A68" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D68" t="s">
+        <v>52</v>
+      </c>
+      <c r="E68" t="s">
+        <v>53</v>
+      </c>
+      <c r="K68" s="2"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A69" t="s">
         <v>183</v>
       </c>
-      <c r="K64" s="2"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A65" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="K65" s="2"/>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A66" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="K66" s="2"/>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A67" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="K67" s="2"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A68" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="K68" s="2"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>185</v>
+      <c r="D69" t="s">
+        <v>52</v>
+      </c>
+      <c r="E69" t="s">
+        <v>53</v>
       </c>
       <c r="K69" s="2"/>
     </row>

--- a/workspaces/example_new_calculations/input/input.xlsx
+++ b/workspaces/example_new_calculations/input/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKL\Documents\Github\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739F3ADB-FA47-4B04-95F8-99A8E64F4571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0814C914-B6D6-4BA7-8C4A-A22C067F25B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
+    <workbookView xWindow="38280" yWindow="-165" windowWidth="25440" windowHeight="15270" activeTab="3" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
   </bookViews>
   <sheets>
     <sheet name="Vakken" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,6 @@
     <sheet name="Ondergrondscenarios" sheetId="3" r:id="rId3"/>
     <sheet name="Overzicht_variabelen" sheetId="2" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Ondergrondscenarios!$A$1:$N$1</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="220">
   <si>
     <t>M_van</t>
   </si>
@@ -107,15 +104,6 @@
     <t>polderpeil</t>
   </si>
   <si>
-    <t>modelfactor_u_mean</t>
-  </si>
-  <si>
-    <t>modelfactor_h_mean</t>
-  </si>
-  <si>
-    <t>modelfactor_p_mean</t>
-  </si>
-  <si>
     <t>&gt;10 m binnenteen</t>
   </si>
   <si>
@@ -194,54 +182,30 @@
     <t>TZ</t>
   </si>
   <si>
-    <t>Afstand van uittredepunt tot geometrische intredelijn</t>
-  </si>
-  <si>
     <t>m</t>
   </si>
   <si>
     <t>Input</t>
   </si>
   <si>
-    <t>none, deterministic</t>
-  </si>
-  <si>
-    <t>Uittredepunt</t>
-  </si>
-  <si>
     <t>input</t>
   </si>
   <si>
     <t>_stdev</t>
   </si>
   <si>
-    <t>Afstand van uittredepunt tot buitenteenlijn</t>
-  </si>
-  <si>
     <t>_vc</t>
   </si>
   <si>
-    <t>Afstand van uittredepunt tot binnenteenlijn</t>
-  </si>
-  <si>
-    <t>Afstand van uittredepunt tot Achterlandlengte</t>
-  </si>
-  <si>
     <t>Vakken</t>
   </si>
   <si>
-    <t>Bodemhoogte ter plaatse van uittredepunt</t>
-  </si>
-  <si>
     <t>m+NAP</t>
   </si>
   <si>
     <t>Representatieve bodemhoogte achterland binnen een vak</t>
   </si>
   <si>
-    <t>Polderpeil ter plaatse van uittredepunt</t>
-  </si>
-  <si>
     <t>top_zand</t>
   </si>
   <si>
@@ -251,9 +215,6 @@
     <t>normal</t>
   </si>
   <si>
-    <t>Ondergrondscenario</t>
-  </si>
-  <si>
     <t>gamma_sat_deklaag</t>
   </si>
   <si>
@@ -263,9 +224,6 @@
     <t>kN/m^3</t>
   </si>
   <si>
-    <t>lognormal, shift 10</t>
-  </si>
-  <si>
     <t>d_deklaag</t>
   </si>
   <si>
@@ -275,9 +233,6 @@
     <t>Calculated</t>
   </si>
   <si>
-    <t>normal, by functional design &gt;0,1 m</t>
-  </si>
-  <si>
     <t>d_deklaag_vak</t>
   </si>
   <si>
@@ -302,9 +257,6 @@
     <t>m^2/dag</t>
   </si>
   <si>
-    <t>lognormal</t>
-  </si>
-  <si>
     <t>D_wvp</t>
   </si>
   <si>
@@ -392,18 +344,12 @@
     <t>r_exit</t>
   </si>
   <si>
-    <t>Dempingsfactor bij uittredepunt</t>
-  </si>
-  <si>
     <t>output</t>
   </si>
   <si>
     <t>phi_exit</t>
   </si>
   <si>
-    <t>Theoretische stijghoogte bij uittredepunt</t>
-  </si>
-  <si>
     <t>h_exit</t>
   </si>
   <si>
@@ -614,9 +560,6 @@
     <t>ondergrondscenario_kans</t>
   </si>
   <si>
-    <t>variabele_name</t>
-  </si>
-  <si>
     <t>variable_description</t>
   </si>
   <si>
@@ -629,9 +572,6 @@
     <t>variable_distribution</t>
   </si>
   <si>
-    <t>variabele_spreidingstype</t>
-  </si>
-  <si>
     <t>variable_default_value_mean</t>
   </si>
   <si>
@@ -663,6 +603,102 @@
   </si>
   <si>
     <t xml:space="preserve">n </t>
+  </si>
+  <si>
+    <t>Uittredepunten</t>
+  </si>
+  <si>
+    <t>Dempingsfactor bij Uittredepunten</t>
+  </si>
+  <si>
+    <t>Ondergrondscenarios</t>
+  </si>
+  <si>
+    <t>Theoretische stijghoogte bij uittredepunten</t>
+  </si>
+  <si>
+    <t>Polderpeil ter plaatse van uittredepunten</t>
+  </si>
+  <si>
+    <t>Bodemhoogte ter plaatse van uittredepunten</t>
+  </si>
+  <si>
+    <t>Afstand van uittredepunten tot achterlandlengte</t>
+  </si>
+  <si>
+    <t>Afstand van uittredepunten tot binnenteenlijn</t>
+  </si>
+  <si>
+    <t>Afstand van uittredepunten tot buitenteenlijn</t>
+  </si>
+  <si>
+    <t>Afstand van uittredepunten tot geometrische intredelijn</t>
+  </si>
+  <si>
+    <t>RD x</t>
+  </si>
+  <si>
+    <t>RD y</t>
+  </si>
+  <si>
+    <t>vrij in te vullen</t>
+  </si>
+  <si>
+    <t>geheel getal startend bij 1</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>0 ≤ x ≤ 1</t>
+  </si>
+  <si>
+    <t>Kans van optreden van ondergrondscenario</t>
+  </si>
+  <si>
+    <t>Identificatienummer van het ondergrondscenario, wordt gebruikt in de tool</t>
+  </si>
+  <si>
+    <t>Identificatienummer van het uittredepunt, wordt gebruikt in de tool</t>
+  </si>
+  <si>
+    <t>Identificatienummer van het vak, wordt gebruikt in de tool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naam van het vak zoals deze door gebruiker wordt gedefinieerd </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naam van het ondergrondscenario zoals deze door gebruiker wordt gedefinieerd </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lengte van het vak </t>
+  </si>
+  <si>
+    <t>X-coordinaat van het uittrededpunt</t>
+  </si>
+  <si>
+    <t>Y-coordinaat van het uittrededpunt</t>
+  </si>
+  <si>
+    <t>Omschrijving van de uittredelocatie</t>
+  </si>
+  <si>
+    <t>Calculated variables</t>
+  </si>
+  <si>
+    <t>variable_name</t>
+  </si>
+  <si>
+    <t>variable_spreidingstype</t>
+  </si>
+  <si>
+    <t>deterministic</t>
+  </si>
+  <si>
+    <t>by functional design &gt;0,1 m</t>
+  </si>
+  <si>
+    <t>log_normal</t>
   </si>
 </sst>
 </file>
@@ -716,20 +752,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
@@ -781,8 +837,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D6DB1DEC-E085-4F6B-B7C4-D4E6DD7E1A8E}" name="Tabel9" displayName="Tabel9" ref="A2:T103" headerRowCount="0" totalsRowShown="0">
-  <tableColumns count="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D6DB1DEC-E085-4F6B-B7C4-D4E6DD7E1A8E}" name="Tabel9" displayName="Tabel9" ref="A2:N103" headerRowCount="0" totalsRowShown="0">
+  <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5EE94583-3EBC-4D61-9BDE-C9E94899637C}" name="Kolom1"/>
     <tableColumn id="2" xr3:uid="{8990A576-5075-4246-8F9A-BA6C41A7A01C}" name="Kolom2"/>
     <tableColumn id="3" xr3:uid="{49D363D0-5442-4E42-91BC-AD82E3246FFD}" name="Kolom3"/>
@@ -797,12 +853,6 @@
     <tableColumn id="12" xr3:uid="{63DC1136-49A2-44E7-9286-3F64EFA876CE}" name="Kolom12"/>
     <tableColumn id="13" xr3:uid="{D266588F-C618-4806-A218-A5D90FF4D5E3}" name="Kolom13"/>
     <tableColumn id="14" xr3:uid="{C17CFC23-4C11-4C47-AEE5-4FB4BCCD1A66}" name="Kolom14"/>
-    <tableColumn id="15" xr3:uid="{B8AA9FF1-422A-4A21-B749-78785E406323}" name="Kolom15"/>
-    <tableColumn id="16" xr3:uid="{86BC2586-E9DF-4126-97B8-988C714C46C6}" name="Kolom16"/>
-    <tableColumn id="17" xr3:uid="{191B7E22-498F-4FA7-BFC0-B95FA4A6E939}" name="Kolom17"/>
-    <tableColumn id="18" xr3:uid="{797FA1D5-B068-49BC-81F9-0DE453CCB74E}" name="Kolom18"/>
-    <tableColumn id="19" xr3:uid="{706AB974-E175-4BEB-93DA-6B13C7C37AE4}" name="Kolom19"/>
-    <tableColumn id="20" xr3:uid="{E1DA896C-C1E7-4050-A404-9A8160C991DF}" name="Kolom20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -823,7 +873,7 @@
     <tableColumn id="10" xr3:uid="{30E95029-7E84-4404-97EA-CC899B222DC3}" name="Kolom10"/>
     <tableColumn id="11" xr3:uid="{21D2E504-CBB5-45F7-9119-E1DA7B53C2D5}" name="Kolom11"/>
     <tableColumn id="12" xr3:uid="{FF7176FB-923E-4ECE-83AA-046E768AD06C}" name="Kolom12"/>
-    <tableColumn id="14" xr3:uid="{4E1A767E-8059-4EF5-B52B-A1637577AFDF}" name="Kolom14" headerRowDxfId="5" dataDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{4E1A767E-8059-4EF5-B52B-A1637577AFDF}" name="Kolom14" headerRowDxfId="8" dataDxfId="7"/>
     <tableColumn id="15" xr3:uid="{E12738E9-E3E4-4A5D-81C1-E333D11489B2}" name="Kolom15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -832,9 +882,9 @@
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{ECE0F829-0060-4D7E-94D4-430EA87FED82}" name="Tabel12" displayName="Tabel12" ref="A2:P69" headerRowCount="0" totalsRowShown="0">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P55">
-    <sortCondition ref="D2:D55" customList="Input,Input,can also be calculated,Constant,Calculated"/>
-    <sortCondition ref="A2:A55"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P69">
+    <sortCondition ref="D2:D69" customList="Input,Input,can also be calculated,Constant,Calculated"/>
+    <sortCondition ref="A2:A69"/>
   </sortState>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{EE720E76-FC11-4E08-B57C-F3D8111FE800}" name="Kolom1"/>
@@ -845,9 +895,9 @@
     <tableColumn id="6" xr3:uid="{FA05A46A-DA45-4C6A-9D17-689A03B15BA8}" name="Kolom6"/>
     <tableColumn id="7" xr3:uid="{25871E16-DA07-4B31-A7EF-FBA1FEE488DB}" name="Kolom7"/>
     <tableColumn id="8" xr3:uid="{A229D98E-F2F0-4491-8C3C-1FB943EA5058}" name="Kolom8"/>
-    <tableColumn id="9" xr3:uid="{1FBE756B-5426-4436-B3C8-55410DF75FDB}" name="Kolom9" headerRowDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{B851468F-D94B-4F13-9CF8-13DADE13A2A8}" name="Kolom10" headerRowDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{41B8BB8E-854F-4E90-B76F-4066FB0CA9A2}" name="Kolom11" headerRowDxfId="1" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{1FBE756B-5426-4436-B3C8-55410DF75FDB}" name="Kolom9" headerRowDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{B851468F-D94B-4F13-9CF8-13DADE13A2A8}" name="Kolom10" headerRowDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{41B8BB8E-854F-4E90-B76F-4066FB0CA9A2}" name="Kolom11" headerRowDxfId="4" dataDxfId="3"/>
     <tableColumn id="12" xr3:uid="{E7B2F49E-191F-4D24-8883-DCCF4F196399}" name="Kolom12"/>
     <tableColumn id="13" xr3:uid="{1DB6223F-5250-48AD-B68D-FD511FFC8150}" name="Kolom13"/>
     <tableColumn id="14" xr3:uid="{B2104B25-DEBD-4E44-A26A-46A71C2A832D}" name="Kolom14"/>
@@ -1176,26 +1226,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C253AA-AAA1-47E5-9332-CA169F978D7A}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.25" customWidth="1"/>
-    <col min="2" max="2" width="32.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.25" customWidth="1"/>
-    <col min="5" max="5" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.375" customWidth="1"/>
+    <col min="1" max="1" width="8.19921875" customWidth="1"/>
+    <col min="2" max="2" width="32.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.19921875" customWidth="1"/>
+    <col min="5" max="5" width="16.59765625" customWidth="1"/>
+    <col min="6" max="6" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.3984375" customWidth="1"/>
     <col min="10" max="10" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>0</v>
@@ -1204,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>2</v>
@@ -1215,19 +1265,19 @@
       <c r="H1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="6" t="str">
+      <c r="I1" s="4" t="str">
         <f>LEFT(H1,LEN(H1)-5)&amp;VLOOKUP(LEFT(H1,LEN(H1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>c_voorland_stdev</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="6" t="str">
+      <c r="K1" s="4" t="str">
         <f>LEFT(J1,LEN(J1)-5)&amp;VLOOKUP(LEFT(J1,LEN(J1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>c_achterland_vc</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1262,7 +1312,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1297,7 +1347,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1332,7 +1382,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1367,7 +1417,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1402,7 +1452,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1437,7 +1487,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1472,7 +1522,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1507,7 +1557,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1552,46 +1602,45 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB77777-746E-45C0-BE11-D138C11C003A}">
-  <dimension ref="A1:T103"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:N103"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.375" customWidth="1"/>
+    <col min="1" max="1" width="7.3984375" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.8984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.25" customWidth="1"/>
-    <col min="11" max="11" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.19921875" customWidth="1"/>
+    <col min="11" max="11" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.8984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>15</v>
@@ -1603,7 +1652,7 @@
         <v>17</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>18</v>
@@ -1614,29 +1663,8 @@
       <c r="N1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="P1" s="6" t="str">
-        <f>LEFT(O1,LEN(O1)-5)&amp;VLOOKUP(LEFT(O1,LEN(O1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
-        <v>modelfactor_u_stdev</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="R1" s="6" t="str">
-        <f>LEFT(Q1,LEN(Q1)-5)&amp;VLOOKUP(LEFT(Q1,LEN(Q1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
-        <v>modelfactor_h_stdev</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="T1" s="6" t="str">
-        <f>LEFT(S1,LEN(S1)-5)&amp;VLOOKUP(LEFT(S1,LEN(S1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
-        <v>modelfactor_p</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1650,7 +1678,7 @@
         <v>418878.19900000002</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>8.4789999999999992</v>
@@ -1668,7 +1696,7 @@
         <v>90.481999999999999</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L2">
         <v>13.295</v>
@@ -1679,26 +1707,8 @@
       <c r="N2">
         <v>7.75</v>
       </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <v>0.1</v>
-      </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <v>0.1</v>
-      </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
-      <c r="T2">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>3</v>
       </c>
@@ -1712,7 +1722,7 @@
         <v>418854.745</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>49.552</v>
@@ -1730,7 +1740,7 @@
         <v>47.110999999999997</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L3">
         <v>13.295</v>
@@ -1741,26 +1751,8 @@
       <c r="N3">
         <v>7.75</v>
       </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
-        <v>0.1</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>0.1</v>
-      </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="T3">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>4</v>
       </c>
@@ -1774,7 +1766,7 @@
         <v>418827.85800000001</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>147.995</v>
@@ -1792,7 +1784,7 @@
         <v>3.133</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L4">
         <v>13.295</v>
@@ -1803,26 +1795,8 @@
       <c r="N4">
         <v>7.75</v>
       </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>0.1</v>
-      </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>0.1</v>
-      </c>
-      <c r="S4">
-        <v>1</v>
-      </c>
-      <c r="T4">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1836,7 +1810,7 @@
         <v>418852.74300000002</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F5">
         <v>192.261</v>
@@ -1854,7 +1828,7 @@
         <v>3.5219999999999998</v>
       </c>
       <c r="K5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L5">
         <v>13.295</v>
@@ -1865,26 +1839,8 @@
       <c r="N5">
         <v>7.75</v>
       </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>0.1</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>0.1</v>
-      </c>
-      <c r="S5">
-        <v>1</v>
-      </c>
-      <c r="T5">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1898,7 +1854,7 @@
         <v>418871.62099999998</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>163.553</v>
@@ -1916,7 +1872,7 @@
         <v>46.121000000000002</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L6">
         <v>13.295</v>
@@ -1927,26 +1883,8 @@
       <c r="N6">
         <v>7.75</v>
       </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
-        <v>0.1</v>
-      </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>0.1</v>
-      </c>
-      <c r="S6">
-        <v>1</v>
-      </c>
-      <c r="T6">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1960,7 +1898,7 @@
         <v>418892.50099999999</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F7">
         <v>261.37900000000002</v>
@@ -1978,7 +1916,7 @@
         <v>4.4450000000000003</v>
       </c>
       <c r="K7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L7">
         <v>13.295</v>
@@ -1989,26 +1927,8 @@
       <c r="N7">
         <v>7.75</v>
       </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>0.1</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>0.1</v>
-      </c>
-      <c r="S7">
-        <v>1</v>
-      </c>
-      <c r="T7">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5</v>
       </c>
@@ -2022,7 +1942,7 @@
         <v>418922.82</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F8">
         <v>267.91199999999998</v>
@@ -2040,7 +1960,7 @@
         <v>35.957999999999998</v>
       </c>
       <c r="K8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L8">
         <v>13.295</v>
@@ -2051,26 +1971,8 @@
       <c r="N8">
         <v>7.75</v>
       </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
-        <v>0.1</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>0.1</v>
-      </c>
-      <c r="S8">
-        <v>1</v>
-      </c>
-      <c r="T8">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5</v>
       </c>
@@ -2084,7 +1986,7 @@
         <v>418899.93800000002</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F9">
         <v>277.45100000000002</v>
@@ -2102,7 +2004,7 @@
         <v>2.915</v>
       </c>
       <c r="K9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L9">
         <v>13.295</v>
@@ -2113,26 +2015,8 @@
       <c r="N9">
         <v>7.75</v>
       </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9">
-        <v>0.1</v>
-      </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>0.1</v>
-      </c>
-      <c r="S9">
-        <v>1</v>
-      </c>
-      <c r="T9">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>5</v>
       </c>
@@ -2146,7 +2030,7 @@
         <v>418917.386</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F10">
         <v>310.37799999999999</v>
@@ -2164,7 +2048,7 @@
         <v>3.0369999999999999</v>
       </c>
       <c r="K10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L10">
         <v>13.287000000000001</v>
@@ -2175,26 +2059,8 @@
       <c r="N10">
         <v>7.75</v>
       </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
-      <c r="P10">
-        <v>0.1</v>
-      </c>
-      <c r="Q10">
-        <v>1</v>
-      </c>
-      <c r="R10">
-        <v>0.1</v>
-      </c>
-      <c r="S10">
-        <v>1</v>
-      </c>
-      <c r="T10">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>5</v>
       </c>
@@ -2208,7 +2074,7 @@
         <v>418947.99099999998</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F11">
         <v>372.47800000000001</v>
@@ -2226,7 +2092,7 @@
         <v>2.4630000000000001</v>
       </c>
       <c r="K11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L11">
         <v>13.292999999999999</v>
@@ -2237,26 +2103,8 @@
       <c r="N11">
         <v>7.75</v>
       </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="P11">
-        <v>0.1</v>
-      </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
-      <c r="R11">
-        <v>0.1</v>
-      </c>
-      <c r="S11">
-        <v>1</v>
-      </c>
-      <c r="T11">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>5</v>
       </c>
@@ -2270,7 +2118,7 @@
         <v>418975.16399999999</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F12">
         <v>431.47</v>
@@ -2288,7 +2136,7 @@
         <v>3.2130000000000001</v>
       </c>
       <c r="K12" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L12">
         <v>13.292999999999999</v>
@@ -2299,26 +2147,8 @@
       <c r="N12">
         <v>7.75</v>
       </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-      <c r="P12">
-        <v>0.1</v>
-      </c>
-      <c r="Q12">
-        <v>1</v>
-      </c>
-      <c r="R12">
-        <v>0.1</v>
-      </c>
-      <c r="S12">
-        <v>1</v>
-      </c>
-      <c r="T12">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>5</v>
       </c>
@@ -2332,7 +2162,7 @@
         <v>419023.45</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F13">
         <v>453.46699999999998</v>
@@ -2350,7 +2180,7 @@
         <v>45.564</v>
       </c>
       <c r="K13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L13">
         <v>13.292999999999999</v>
@@ -2361,26 +2191,8 @@
       <c r="N13">
         <v>7.75</v>
       </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
-      <c r="P13">
-        <v>0.1</v>
-      </c>
-      <c r="Q13">
-        <v>1</v>
-      </c>
-      <c r="R13">
-        <v>0.1</v>
-      </c>
-      <c r="S13">
-        <v>1</v>
-      </c>
-      <c r="T13">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>5</v>
       </c>
@@ -2394,7 +2206,7 @@
         <v>418998.86900000001</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F14">
         <v>489.88200000000001</v>
@@ -2412,7 +2224,7 @@
         <v>1.6319999999999999</v>
       </c>
       <c r="K14" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L14">
         <v>13.292999999999999</v>
@@ -2423,26 +2235,8 @@
       <c r="N14">
         <v>7.75</v>
       </c>
-      <c r="O14">
-        <v>1</v>
-      </c>
-      <c r="P14">
-        <v>0.1</v>
-      </c>
-      <c r="Q14">
-        <v>1</v>
-      </c>
-      <c r="R14">
-        <v>0.1</v>
-      </c>
-      <c r="S14">
-        <v>1</v>
-      </c>
-      <c r="T14">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>5</v>
       </c>
@@ -2456,7 +2250,7 @@
         <v>419025.68400000001</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F15">
         <v>554.654</v>
@@ -2474,7 +2268,7 @@
         <v>2.2530000000000001</v>
       </c>
       <c r="K15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L15">
         <v>13.292999999999999</v>
@@ -2485,26 +2279,8 @@
       <c r="N15">
         <v>7.75</v>
       </c>
-      <c r="O15">
-        <v>1</v>
-      </c>
-      <c r="P15">
-        <v>0.1</v>
-      </c>
-      <c r="Q15">
-        <v>1</v>
-      </c>
-      <c r="R15">
-        <v>0.1</v>
-      </c>
-      <c r="S15">
-        <v>1</v>
-      </c>
-      <c r="T15">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>5</v>
       </c>
@@ -2518,7 +2294,7 @@
         <v>419053.89199999999</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F16">
         <v>566.74599999999998</v>
@@ -2536,7 +2312,7 @@
         <v>25.902000000000001</v>
       </c>
       <c r="K16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L16">
         <v>13.292999999999999</v>
@@ -2547,26 +2323,8 @@
       <c r="N16">
         <v>7.75</v>
       </c>
-      <c r="O16">
-        <v>1</v>
-      </c>
-      <c r="P16">
-        <v>0.1</v>
-      </c>
-      <c r="Q16">
-        <v>1</v>
-      </c>
-      <c r="R16">
-        <v>0.1</v>
-      </c>
-      <c r="S16">
-        <v>1</v>
-      </c>
-      <c r="T16">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>6</v>
       </c>
@@ -2580,7 +2338,7 @@
         <v>419047.56599999999</v>
       </c>
       <c r="E17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F17">
         <v>585.04399999999998</v>
@@ -2598,7 +2356,7 @@
         <v>6.2789999999999999</v>
       </c>
       <c r="K17" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L17">
         <v>13.292999999999999</v>
@@ -2609,26 +2367,8 @@
       <c r="N17">
         <v>7.75</v>
       </c>
-      <c r="O17">
-        <v>1</v>
-      </c>
-      <c r="P17">
-        <v>0.1</v>
-      </c>
-      <c r="Q17">
-        <v>1</v>
-      </c>
-      <c r="R17">
-        <v>0.1</v>
-      </c>
-      <c r="S17">
-        <v>1</v>
-      </c>
-      <c r="T17">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>6</v>
       </c>
@@ -2642,7 +2382,7 @@
         <v>419046.98</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F18">
         <v>592.95100000000002</v>
@@ -2660,7 +2400,7 @@
         <v>3.6560000000000001</v>
       </c>
       <c r="K18" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L18">
         <v>13.287000000000001</v>
@@ -2671,26 +2411,8 @@
       <c r="N18">
         <v>7.75</v>
       </c>
-      <c r="O18">
-        <v>1</v>
-      </c>
-      <c r="P18">
-        <v>0.1</v>
-      </c>
-      <c r="Q18">
-        <v>1</v>
-      </c>
-      <c r="R18">
-        <v>0.1</v>
-      </c>
-      <c r="S18">
-        <v>1</v>
-      </c>
-      <c r="T18">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>6</v>
       </c>
@@ -2704,7 +2426,7 @@
         <v>419049.81800000003</v>
       </c>
       <c r="E19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F19">
         <v>599.83299999999997</v>
@@ -2722,7 +2444,7 @@
         <v>4.9770000000000003</v>
       </c>
       <c r="K19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L19">
         <v>13.287000000000001</v>
@@ -2733,26 +2455,8 @@
       <c r="N19">
         <v>7.75</v>
       </c>
-      <c r="O19">
-        <v>1</v>
-      </c>
-      <c r="P19">
-        <v>0.1</v>
-      </c>
-      <c r="Q19">
-        <v>1</v>
-      </c>
-      <c r="R19">
-        <v>0.1</v>
-      </c>
-      <c r="S19">
-        <v>1</v>
-      </c>
-      <c r="T19">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>6</v>
       </c>
@@ -2766,7 +2470,7 @@
         <v>419060.68699999998</v>
       </c>
       <c r="E20" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F20">
         <v>630.61300000000006</v>
@@ -2784,7 +2488,7 @@
         <v>5.0990000000000002</v>
       </c>
       <c r="K20" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L20">
         <v>13.287000000000001</v>
@@ -2795,26 +2499,8 @@
       <c r="N20">
         <v>7.75</v>
       </c>
-      <c r="O20">
-        <v>1</v>
-      </c>
-      <c r="P20">
-        <v>0.1</v>
-      </c>
-      <c r="Q20">
-        <v>1</v>
-      </c>
-      <c r="R20">
-        <v>0.1</v>
-      </c>
-      <c r="S20">
-        <v>1</v>
-      </c>
-      <c r="T20">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>6</v>
       </c>
@@ -2828,7 +2514,7 @@
         <v>419069.84</v>
       </c>
       <c r="E21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F21">
         <v>646.86800000000005</v>
@@ -2846,7 +2532,7 @@
         <v>7.1630000000000003</v>
       </c>
       <c r="K21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L21">
         <v>13.287000000000001</v>
@@ -2857,26 +2543,8 @@
       <c r="N21">
         <v>7.75</v>
       </c>
-      <c r="O21">
-        <v>1</v>
-      </c>
-      <c r="P21">
-        <v>0.1</v>
-      </c>
-      <c r="Q21">
-        <v>1</v>
-      </c>
-      <c r="R21">
-        <v>0.1</v>
-      </c>
-      <c r="S21">
-        <v>1</v>
-      </c>
-      <c r="T21">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>6</v>
       </c>
@@ -2890,7 +2558,7 @@
         <v>419075.22</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F22">
         <v>650.18899999999996</v>
@@ -2908,7 +2576,7 @@
         <v>11.342000000000001</v>
       </c>
       <c r="K22" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L22">
         <v>13.287000000000001</v>
@@ -2919,26 +2587,8 @@
       <c r="N22">
         <v>7.75</v>
       </c>
-      <c r="O22">
-        <v>1</v>
-      </c>
-      <c r="P22">
-        <v>0.1</v>
-      </c>
-      <c r="Q22">
-        <v>1</v>
-      </c>
-      <c r="R22">
-        <v>0.1</v>
-      </c>
-      <c r="S22">
-        <v>1</v>
-      </c>
-      <c r="T22">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>6</v>
       </c>
@@ -2952,7 +2602,7 @@
         <v>419090.66600000003</v>
       </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F23">
         <v>649.197</v>
@@ -2970,7 +2620,7 @@
         <v>28.609000000000002</v>
       </c>
       <c r="K23" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L23">
         <v>13.287000000000001</v>
@@ -2981,26 +2631,8 @@
       <c r="N23">
         <v>7.75</v>
       </c>
-      <c r="O23">
-        <v>1</v>
-      </c>
-      <c r="P23">
-        <v>0.1</v>
-      </c>
-      <c r="Q23">
-        <v>1</v>
-      </c>
-      <c r="R23">
-        <v>0.1</v>
-      </c>
-      <c r="S23">
-        <v>1</v>
-      </c>
-      <c r="T23">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>6</v>
       </c>
@@ -3014,7 +2646,7 @@
         <v>419100.18800000002</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F24">
         <v>695.50300000000004</v>
@@ -3032,7 +2664,7 @@
         <v>16.428000000000001</v>
       </c>
       <c r="K24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L24">
         <v>13.29</v>
@@ -3043,26 +2675,8 @@
       <c r="N24">
         <v>7.75</v>
       </c>
-      <c r="O24">
-        <v>1</v>
-      </c>
-      <c r="P24">
-        <v>0.1</v>
-      </c>
-      <c r="Q24">
-        <v>1</v>
-      </c>
-      <c r="R24">
-        <v>0.1</v>
-      </c>
-      <c r="S24">
-        <v>1</v>
-      </c>
-      <c r="T24">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>6</v>
       </c>
@@ -3076,7 +2690,7 @@
         <v>419087.66700000002</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F25">
         <v>695.95699999999999</v>
@@ -3094,7 +2708,7 @@
         <v>2.2360000000000002</v>
       </c>
       <c r="K25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L25">
         <v>13.29</v>
@@ -3105,26 +2719,8 @@
       <c r="N25">
         <v>7.75</v>
       </c>
-      <c r="O25">
-        <v>1</v>
-      </c>
-      <c r="P25">
-        <v>0.1</v>
-      </c>
-      <c r="Q25">
-        <v>1</v>
-      </c>
-      <c r="R25">
-        <v>0.1</v>
-      </c>
-      <c r="S25">
-        <v>1</v>
-      </c>
-      <c r="T25">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>7</v>
       </c>
@@ -3138,7 +2734,7 @@
         <v>419101.538</v>
       </c>
       <c r="E26" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F26">
         <v>703.73099999999999</v>
@@ -3156,7 +2752,7 @@
         <v>10.31</v>
       </c>
       <c r="K26" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L26">
         <v>13.29</v>
@@ -3167,26 +2763,8 @@
       <c r="N26">
         <v>7.75</v>
       </c>
-      <c r="O26">
-        <v>1</v>
-      </c>
-      <c r="P26">
-        <v>0.1</v>
-      </c>
-      <c r="Q26">
-        <v>1</v>
-      </c>
-      <c r="R26">
-        <v>0.1</v>
-      </c>
-      <c r="S26">
-        <v>1</v>
-      </c>
-      <c r="T26">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>7</v>
       </c>
@@ -3200,7 +2778,7 @@
         <v>419104.837</v>
       </c>
       <c r="E27" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F27">
         <v>710.54200000000003</v>
@@ -3218,7 +2796,7 @@
         <v>10.231999999999999</v>
       </c>
       <c r="K27" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L27">
         <v>13.29</v>
@@ -3229,26 +2807,8 @@
       <c r="N27">
         <v>7.75</v>
       </c>
-      <c r="O27">
-        <v>1</v>
-      </c>
-      <c r="P27">
-        <v>0.1</v>
-      </c>
-      <c r="Q27">
-        <v>1</v>
-      </c>
-      <c r="R27">
-        <v>0.1</v>
-      </c>
-      <c r="S27">
-        <v>1</v>
-      </c>
-      <c r="T27">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>7</v>
       </c>
@@ -3262,7 +2822,7 @@
         <v>419121.408</v>
       </c>
       <c r="E28" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F28">
         <v>738.33199999999999</v>
@@ -3280,7 +2840,7 @@
         <v>10.26</v>
       </c>
       <c r="K28" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L28">
         <v>13.29</v>
@@ -3291,26 +2851,8 @@
       <c r="N28">
         <v>7.75</v>
       </c>
-      <c r="O28">
-        <v>1</v>
-      </c>
-      <c r="P28">
-        <v>0.1</v>
-      </c>
-      <c r="Q28">
-        <v>1</v>
-      </c>
-      <c r="R28">
-        <v>0.1</v>
-      </c>
-      <c r="S28">
-        <v>1</v>
-      </c>
-      <c r="T28">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>7</v>
       </c>
@@ -3324,7 +2866,7 @@
         <v>419119.15899999999</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F29">
         <v>747.67100000000005</v>
@@ -3342,7 +2884,7 @@
         <v>3.0219999999999998</v>
       </c>
       <c r="K29" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L29">
         <v>13.29</v>
@@ -3353,26 +2895,8 @@
       <c r="N29">
         <v>7.75</v>
       </c>
-      <c r="O29">
-        <v>1</v>
-      </c>
-      <c r="P29">
-        <v>0.1</v>
-      </c>
-      <c r="Q29">
-        <v>1</v>
-      </c>
-      <c r="R29">
-        <v>0.1</v>
-      </c>
-      <c r="S29">
-        <v>1</v>
-      </c>
-      <c r="T29">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>7</v>
       </c>
@@ -3386,7 +2910,7 @@
         <v>419096.88900000002</v>
       </c>
       <c r="E30" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F30">
         <v>707.31399999999996</v>
@@ -3404,7 +2928,7 @@
         <v>2.0760000000000001</v>
       </c>
       <c r="K30" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L30">
         <v>13.29</v>
@@ -3415,26 +2939,8 @@
       <c r="N30">
         <v>7.75</v>
       </c>
-      <c r="O30">
-        <v>1</v>
-      </c>
-      <c r="P30">
-        <v>0.1</v>
-      </c>
-      <c r="Q30">
-        <v>1</v>
-      </c>
-      <c r="R30">
-        <v>0.1</v>
-      </c>
-      <c r="S30">
-        <v>1</v>
-      </c>
-      <c r="T30">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>7</v>
       </c>
@@ -3448,7 +2954,7 @@
         <v>419109.03600000002</v>
       </c>
       <c r="E31" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F31">
         <v>728.125</v>
@@ -3466,7 +2972,7 @@
         <v>2.0449999999999999</v>
       </c>
       <c r="K31" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L31">
         <v>13.29</v>
@@ -3477,26 +2983,8 @@
       <c r="N31">
         <v>7.75</v>
       </c>
-      <c r="O31">
-        <v>1</v>
-      </c>
-      <c r="P31">
-        <v>0.1</v>
-      </c>
-      <c r="Q31">
-        <v>1</v>
-      </c>
-      <c r="R31">
-        <v>0.1</v>
-      </c>
-      <c r="S31">
-        <v>1</v>
-      </c>
-      <c r="T31">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>7</v>
       </c>
@@ -3510,7 +2998,7 @@
         <v>419132.505</v>
       </c>
       <c r="E32" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F32">
         <v>754.85</v>
@@ -3528,7 +3016,7 @@
         <v>13.978</v>
       </c>
       <c r="K32" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L32">
         <v>13.29</v>
@@ -3539,26 +3027,8 @@
       <c r="N32">
         <v>7.75</v>
       </c>
-      <c r="O32">
-        <v>1</v>
-      </c>
-      <c r="P32">
-        <v>0.1</v>
-      </c>
-      <c r="Q32">
-        <v>1</v>
-      </c>
-      <c r="R32">
-        <v>0.1</v>
-      </c>
-      <c r="S32">
-        <v>1</v>
-      </c>
-      <c r="T32">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>7</v>
       </c>
@@ -3572,7 +3042,7 @@
         <v>419151.09899999999</v>
       </c>
       <c r="E33" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F33">
         <v>789.178</v>
@@ -3590,7 +3060,7 @@
         <v>13.022</v>
       </c>
       <c r="K33" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L33">
         <v>13.281000000000001</v>
@@ -3601,26 +3071,8 @@
       <c r="N33">
         <v>7.75</v>
       </c>
-      <c r="O33">
-        <v>1</v>
-      </c>
-      <c r="P33">
-        <v>0.1</v>
-      </c>
-      <c r="Q33">
-        <v>1</v>
-      </c>
-      <c r="R33">
-        <v>0.1</v>
-      </c>
-      <c r="S33">
-        <v>1</v>
-      </c>
-      <c r="T33">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>7</v>
       </c>
@@ -3634,7 +3086,7 @@
         <v>419159.00699999998</v>
       </c>
       <c r="E34" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F34">
         <v>800.52499999999998</v>
@@ -3652,7 +3104,7 @@
         <v>13.021000000000001</v>
       </c>
       <c r="K34" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L34">
         <v>13.281000000000001</v>
@@ -3663,26 +3115,8 @@
       <c r="N34">
         <v>7.75</v>
       </c>
-      <c r="O34">
-        <v>1</v>
-      </c>
-      <c r="P34">
-        <v>0.1</v>
-      </c>
-      <c r="Q34">
-        <v>1</v>
-      </c>
-      <c r="R34">
-        <v>0.1</v>
-      </c>
-      <c r="S34">
-        <v>1</v>
-      </c>
-      <c r="T34">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>7</v>
       </c>
@@ -3696,7 +3130,7 @@
         <v>419145.946</v>
       </c>
       <c r="E35" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F35">
         <v>780.13199999999995</v>
@@ -3714,7 +3148,7 @@
         <v>13.185</v>
       </c>
       <c r="K35" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L35">
         <v>13.281000000000001</v>
@@ -3725,26 +3159,8 @@
       <c r="N35">
         <v>7.75</v>
       </c>
-      <c r="O35">
-        <v>1</v>
-      </c>
-      <c r="P35">
-        <v>0.1</v>
-      </c>
-      <c r="Q35">
-        <v>1</v>
-      </c>
-      <c r="R35">
-        <v>0.1</v>
-      </c>
-      <c r="S35">
-        <v>1</v>
-      </c>
-      <c r="T35">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>7</v>
       </c>
@@ -3758,7 +3174,7 @@
         <v>419171.94900000002</v>
       </c>
       <c r="E36" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F36">
         <v>823.99099999999999</v>
@@ -3776,7 +3192,7 @@
         <v>13.202999999999999</v>
       </c>
       <c r="K36" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L36">
         <v>13.281000000000001</v>
@@ -3787,26 +3203,8 @@
       <c r="N36">
         <v>7.75</v>
       </c>
-      <c r="O36">
-        <v>1</v>
-      </c>
-      <c r="P36">
-        <v>0.1</v>
-      </c>
-      <c r="Q36">
-        <v>1</v>
-      </c>
-      <c r="R36">
-        <v>0.1</v>
-      </c>
-      <c r="S36">
-        <v>1</v>
-      </c>
-      <c r="T36">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>7</v>
       </c>
@@ -3820,7 +3218,7 @@
         <v>419186.44799999997</v>
       </c>
       <c r="E37" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F37">
         <v>847.505</v>
@@ -3838,7 +3236,7 @@
         <v>13.199</v>
       </c>
       <c r="K37" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L37">
         <v>13.281000000000001</v>
@@ -3849,26 +3247,8 @@
       <c r="N37">
         <v>7.75</v>
       </c>
-      <c r="O37">
-        <v>1</v>
-      </c>
-      <c r="P37">
-        <v>0.1</v>
-      </c>
-      <c r="Q37">
-        <v>1</v>
-      </c>
-      <c r="R37">
-        <v>0.1</v>
-      </c>
-      <c r="S37">
-        <v>1</v>
-      </c>
-      <c r="T37">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>7</v>
       </c>
@@ -3882,7 +3262,7 @@
         <v>419199.03</v>
       </c>
       <c r="E38" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F38">
         <v>868.30799999999999</v>
@@ -3900,7 +3280,7 @@
         <v>13.427</v>
       </c>
       <c r="K38" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L38">
         <v>13.281000000000001</v>
@@ -3911,26 +3291,8 @@
       <c r="N38">
         <v>7.75</v>
       </c>
-      <c r="O38">
-        <v>1</v>
-      </c>
-      <c r="P38">
-        <v>0.1</v>
-      </c>
-      <c r="Q38">
-        <v>1</v>
-      </c>
-      <c r="R38">
-        <v>0.1</v>
-      </c>
-      <c r="S38">
-        <v>1</v>
-      </c>
-      <c r="T38">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>7</v>
       </c>
@@ -3944,7 +3306,7 @@
         <v>419211.13299999997</v>
       </c>
       <c r="E39" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F39">
         <v>887.98299999999995</v>
@@ -3962,7 +3324,7 @@
         <v>13.805999999999999</v>
       </c>
       <c r="K39" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L39">
         <v>13.28</v>
@@ -3973,26 +3335,8 @@
       <c r="N39">
         <v>7.75</v>
       </c>
-      <c r="O39">
-        <v>1</v>
-      </c>
-      <c r="P39">
-        <v>0.1</v>
-      </c>
-      <c r="Q39">
-        <v>1</v>
-      </c>
-      <c r="R39">
-        <v>0.1</v>
-      </c>
-      <c r="S39">
-        <v>1</v>
-      </c>
-      <c r="T39">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>7</v>
       </c>
@@ -4006,7 +3350,7 @@
         <v>419222.51699999999</v>
       </c>
       <c r="E40" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F40">
         <v>907.00599999999997</v>
@@ -4024,7 +3368,7 @@
         <v>13.393000000000001</v>
       </c>
       <c r="K40" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L40">
         <v>13.28</v>
@@ -4035,26 +3379,8 @@
       <c r="N40">
         <v>7.75</v>
       </c>
-      <c r="O40">
-        <v>1</v>
-      </c>
-      <c r="P40">
-        <v>0.1</v>
-      </c>
-      <c r="Q40">
-        <v>1</v>
-      </c>
-      <c r="R40">
-        <v>0.1</v>
-      </c>
-      <c r="S40">
-        <v>1</v>
-      </c>
-      <c r="T40">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>8</v>
       </c>
@@ -4068,7 +3394,7 @@
         <v>419287.82400000002</v>
       </c>
       <c r="E41" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F41">
         <v>997.81200000000001</v>
@@ -4086,7 +3412,7 @@
         <v>25.576000000000001</v>
       </c>
       <c r="K41" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L41">
         <v>13.284000000000001</v>
@@ -4097,26 +3423,8 @@
       <c r="N41">
         <v>7.75</v>
       </c>
-      <c r="O41">
-        <v>1</v>
-      </c>
-      <c r="P41">
-        <v>0.1</v>
-      </c>
-      <c r="Q41">
-        <v>1</v>
-      </c>
-      <c r="R41">
-        <v>0.1</v>
-      </c>
-      <c r="S41">
-        <v>1</v>
-      </c>
-      <c r="T41">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>8</v>
       </c>
@@ -4130,7 +3438,7 @@
         <v>419301.304</v>
       </c>
       <c r="E42" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F42">
         <v>1015.9160000000001</v>
@@ -4148,7 +3456,7 @@
         <v>27.145</v>
       </c>
       <c r="K42" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L42">
         <v>13.284000000000001</v>
@@ -4159,26 +3467,8 @@
       <c r="N42">
         <v>7.75</v>
       </c>
-      <c r="O42">
-        <v>1</v>
-      </c>
-      <c r="P42">
-        <v>0.1</v>
-      </c>
-      <c r="Q42">
-        <v>1</v>
-      </c>
-      <c r="R42">
-        <v>0.1</v>
-      </c>
-      <c r="S42">
-        <v>1</v>
-      </c>
-      <c r="T42">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>8</v>
       </c>
@@ -4192,7 +3482,7 @@
         <v>419313.1</v>
       </c>
       <c r="E43" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F43">
         <v>1034.155</v>
@@ -4210,7 +3500,7 @@
         <v>27.32</v>
       </c>
       <c r="K43" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L43">
         <v>13.284000000000001</v>
@@ -4221,26 +3511,8 @@
       <c r="N43">
         <v>7.75</v>
       </c>
-      <c r="O43">
-        <v>1</v>
-      </c>
-      <c r="P43">
-        <v>0.1</v>
-      </c>
-      <c r="Q43">
-        <v>1</v>
-      </c>
-      <c r="R43">
-        <v>0.1</v>
-      </c>
-      <c r="S43">
-        <v>1</v>
-      </c>
-      <c r="T43">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
@@ -4254,7 +3526,7 @@
         <v>419322.83600000001</v>
       </c>
       <c r="E44" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F44">
         <v>1048.1289999999999</v>
@@ -4272,7 +3544,7 @@
         <v>27.140999999999998</v>
       </c>
       <c r="K44" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L44">
         <v>13.284000000000001</v>
@@ -4283,26 +3555,8 @@
       <c r="N44">
         <v>7.75</v>
       </c>
-      <c r="O44">
-        <v>1</v>
-      </c>
-      <c r="P44">
-        <v>0.1</v>
-      </c>
-      <c r="Q44">
-        <v>1</v>
-      </c>
-      <c r="R44">
-        <v>0.1</v>
-      </c>
-      <c r="S44">
-        <v>1</v>
-      </c>
-      <c r="T44">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
@@ -4316,7 +3570,7 @@
         <v>419331.07400000002</v>
       </c>
       <c r="E45" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F45">
         <v>1060.712</v>
@@ -4334,7 +3588,7 @@
         <v>27.53</v>
       </c>
       <c r="K45" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L45">
         <v>13.284000000000001</v>
@@ -4345,26 +3599,8 @@
       <c r="N45">
         <v>7.75</v>
       </c>
-      <c r="O45">
-        <v>1</v>
-      </c>
-      <c r="P45">
-        <v>0.1</v>
-      </c>
-      <c r="Q45">
-        <v>1</v>
-      </c>
-      <c r="R45">
-        <v>0.1</v>
-      </c>
-      <c r="S45">
-        <v>1</v>
-      </c>
-      <c r="T45">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>8</v>
       </c>
@@ -4378,7 +3614,7 @@
         <v>419338.00199999998</v>
       </c>
       <c r="E46" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F46">
         <v>1070.6469999999999</v>
@@ -4396,7 +3632,7 @@
         <v>27.189</v>
       </c>
       <c r="K46" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L46">
         <v>13.287000000000001</v>
@@ -4407,26 +3643,8 @@
       <c r="N46">
         <v>7.75</v>
       </c>
-      <c r="O46">
-        <v>1</v>
-      </c>
-      <c r="P46">
-        <v>0.1</v>
-      </c>
-      <c r="Q46">
-        <v>1</v>
-      </c>
-      <c r="R46">
-        <v>0.1</v>
-      </c>
-      <c r="S46">
-        <v>1</v>
-      </c>
-      <c r="T46">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>8</v>
       </c>
@@ -4440,7 +3658,7 @@
         <v>419239.05300000001</v>
       </c>
       <c r="E47" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F47">
         <v>936.30600000000004</v>
@@ -4458,7 +3676,7 @@
         <v>9.4960000000000004</v>
       </c>
       <c r="K47" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L47">
         <v>13.28</v>
@@ -4469,26 +3687,8 @@
       <c r="N47">
         <v>7.75</v>
       </c>
-      <c r="O47">
-        <v>1</v>
-      </c>
-      <c r="P47">
-        <v>0.1</v>
-      </c>
-      <c r="Q47">
-        <v>1</v>
-      </c>
-      <c r="R47">
-        <v>0.1</v>
-      </c>
-      <c r="S47">
-        <v>1</v>
-      </c>
-      <c r="T47">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>8</v>
       </c>
@@ -4502,7 +3702,7 @@
         <v>419252.11499999999</v>
       </c>
       <c r="E48" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F48">
         <v>957.68</v>
@@ -4520,7 +3720,7 @@
         <v>8.9510000000000005</v>
       </c>
       <c r="K48" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L48">
         <v>13.284000000000001</v>
@@ -4531,26 +3731,8 @@
       <c r="N48">
         <v>7.75</v>
       </c>
-      <c r="O48">
-        <v>1</v>
-      </c>
-      <c r="P48">
-        <v>0.1</v>
-      </c>
-      <c r="Q48">
-        <v>1</v>
-      </c>
-      <c r="R48">
-        <v>0.1</v>
-      </c>
-      <c r="S48">
-        <v>1</v>
-      </c>
-      <c r="T48">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>8</v>
       </c>
@@ -4564,7 +3746,7 @@
         <v>419266.85399999999</v>
       </c>
       <c r="E49" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F49">
         <v>980.90899999999999</v>
@@ -4582,7 +3764,7 @@
         <v>9.6110000000000007</v>
       </c>
       <c r="K49" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L49">
         <v>13.284000000000001</v>
@@ -4593,26 +3775,8 @@
       <c r="N49">
         <v>7.75</v>
       </c>
-      <c r="O49">
-        <v>1</v>
-      </c>
-      <c r="P49">
-        <v>0.1</v>
-      </c>
-      <c r="Q49">
-        <v>1</v>
-      </c>
-      <c r="R49">
-        <v>0.1</v>
-      </c>
-      <c r="S49">
-        <v>1</v>
-      </c>
-      <c r="T49">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>8</v>
       </c>
@@ -4626,7 +3790,7 @@
         <v>419286.549</v>
       </c>
       <c r="E50" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F50">
         <v>1006.271</v>
@@ -4644,7 +3808,7 @@
         <v>15.634</v>
       </c>
       <c r="K50" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L50">
         <v>13.284000000000001</v>
@@ -4655,26 +3819,8 @@
       <c r="N50">
         <v>7.75</v>
       </c>
-      <c r="O50">
-        <v>1</v>
-      </c>
-      <c r="P50">
-        <v>0.1</v>
-      </c>
-      <c r="Q50">
-        <v>1</v>
-      </c>
-      <c r="R50">
-        <v>0.1</v>
-      </c>
-      <c r="S50">
-        <v>1</v>
-      </c>
-      <c r="T50">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>8</v>
       </c>
@@ -4688,7 +3834,7 @@
         <v>419303.49699999997</v>
       </c>
       <c r="E51" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F51">
         <v>1033.482</v>
@@ -4706,7 +3852,7 @@
         <v>14.721</v>
       </c>
       <c r="K51" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L51">
         <v>13.284000000000001</v>
@@ -4717,26 +3863,8 @@
       <c r="N51">
         <v>7.75</v>
       </c>
-      <c r="O51">
-        <v>1</v>
-      </c>
-      <c r="P51">
-        <v>0.1</v>
-      </c>
-      <c r="Q51">
-        <v>1</v>
-      </c>
-      <c r="R51">
-        <v>0.1</v>
-      </c>
-      <c r="S51">
-        <v>1</v>
-      </c>
-      <c r="T51">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>8</v>
       </c>
@@ -4750,7 +3878,7 @@
         <v>419321.36599999998</v>
       </c>
       <c r="E52" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F52">
         <v>1060.5540000000001</v>
@@ -4768,7 +3896,7 @@
         <v>14.151999999999999</v>
       </c>
       <c r="K52" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L52">
         <v>13.284000000000001</v>
@@ -4779,26 +3907,8 @@
       <c r="N52">
         <v>7.75</v>
       </c>
-      <c r="O52">
-        <v>1</v>
-      </c>
-      <c r="P52">
-        <v>0.1</v>
-      </c>
-      <c r="Q52">
-        <v>1</v>
-      </c>
-      <c r="R52">
-        <v>0.1</v>
-      </c>
-      <c r="S52">
-        <v>1</v>
-      </c>
-      <c r="T52">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>8</v>
       </c>
@@ -4812,7 +3922,7 @@
         <v>419341.74699999997</v>
       </c>
       <c r="E53" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F53">
         <v>1076.2159999999999</v>
@@ -4830,7 +3940,7 @@
         <v>26.984999999999999</v>
       </c>
       <c r="K53" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L53">
         <v>13.287000000000001</v>
@@ -4841,26 +3951,8 @@
       <c r="N53">
         <v>7.75</v>
       </c>
-      <c r="O53">
-        <v>1</v>
-      </c>
-      <c r="P53">
-        <v>0.1</v>
-      </c>
-      <c r="Q53">
-        <v>1</v>
-      </c>
-      <c r="R53">
-        <v>0.1</v>
-      </c>
-      <c r="S53">
-        <v>1</v>
-      </c>
-      <c r="T53">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
@@ -4874,7 +3966,7 @@
         <v>419322.09499999997</v>
       </c>
       <c r="E54" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F54">
         <v>1034.4190000000001</v>
@@ -4892,7 +3984,7 @@
         <v>39.465000000000003</v>
       </c>
       <c r="K54" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L54">
         <v>13.284000000000001</v>
@@ -4903,26 +3995,8 @@
       <c r="N54">
         <v>7.75</v>
       </c>
-      <c r="O54">
-        <v>1</v>
-      </c>
-      <c r="P54">
-        <v>0.1</v>
-      </c>
-      <c r="Q54">
-        <v>1</v>
-      </c>
-      <c r="R54">
-        <v>0.1</v>
-      </c>
-      <c r="S54">
-        <v>1</v>
-      </c>
-      <c r="T54">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>8</v>
       </c>
@@ -4936,7 +4010,7 @@
         <v>419339.94900000002</v>
       </c>
       <c r="E55" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F55">
         <v>1061.3240000000001</v>
@@ -4954,7 +4028,7 @@
         <v>39.244999999999997</v>
       </c>
       <c r="K55" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L55">
         <v>13.284000000000001</v>
@@ -4965,26 +4039,8 @@
       <c r="N55">
         <v>7.75</v>
       </c>
-      <c r="O55">
-        <v>1</v>
-      </c>
-      <c r="P55">
-        <v>0.1</v>
-      </c>
-      <c r="Q55">
-        <v>1</v>
-      </c>
-      <c r="R55">
-        <v>0.1</v>
-      </c>
-      <c r="S55">
-        <v>1</v>
-      </c>
-      <c r="T55">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>8</v>
       </c>
@@ -4998,7 +4054,7 @@
         <v>419311.31</v>
       </c>
       <c r="E56" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F56">
         <v>1015.1609999999999</v>
@@ -5016,7 +4072,7 @@
         <v>41.247</v>
       </c>
       <c r="K56" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L56">
         <v>13.284000000000001</v>
@@ -5027,26 +4083,8 @@
       <c r="N56">
         <v>7.75</v>
       </c>
-      <c r="O56">
-        <v>1</v>
-      </c>
-      <c r="P56">
-        <v>0.1</v>
-      </c>
-      <c r="Q56">
-        <v>1</v>
-      </c>
-      <c r="R56">
-        <v>0.1</v>
-      </c>
-      <c r="S56">
-        <v>1</v>
-      </c>
-      <c r="T56">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>8</v>
       </c>
@@ -5060,7 +4098,7 @@
         <v>419346.54</v>
       </c>
       <c r="E57" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F57">
         <v>1082.752</v>
@@ -5078,7 +4116,7 @@
         <v>27.300999999999998</v>
       </c>
       <c r="K57" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L57">
         <v>13.287000000000001</v>
@@ -5089,26 +4127,8 @@
       <c r="N57">
         <v>7.75</v>
       </c>
-      <c r="O57">
-        <v>1</v>
-      </c>
-      <c r="P57">
-        <v>0.1</v>
-      </c>
-      <c r="Q57">
-        <v>1</v>
-      </c>
-      <c r="R57">
-        <v>0.1</v>
-      </c>
-      <c r="S57">
-        <v>1</v>
-      </c>
-      <c r="T57">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>8</v>
       </c>
@@ -5122,7 +4142,7 @@
         <v>419359.96100000001</v>
       </c>
       <c r="E58" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F58">
         <v>1102.925</v>
@@ -5140,7 +4160,7 @@
         <v>27.064</v>
       </c>
       <c r="K58" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L58">
         <v>13.287000000000001</v>
@@ -5151,26 +4171,8 @@
       <c r="N58">
         <v>7.75</v>
       </c>
-      <c r="O58">
-        <v>1</v>
-      </c>
-      <c r="P58">
-        <v>0.1</v>
-      </c>
-      <c r="Q58">
-        <v>1</v>
-      </c>
-      <c r="R58">
-        <v>0.1</v>
-      </c>
-      <c r="S58">
-        <v>1</v>
-      </c>
-      <c r="T58">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>8</v>
       </c>
@@ -5184,7 +4186,7 @@
         <v>419373.50099999999</v>
       </c>
       <c r="E59" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F59">
         <v>1121.778</v>
@@ -5202,7 +4204,7 @@
         <v>27.420999999999999</v>
       </c>
       <c r="K59" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L59">
         <v>13.287000000000001</v>
@@ -5213,26 +4215,8 @@
       <c r="N59">
         <v>7.75</v>
       </c>
-      <c r="O59">
-        <v>1</v>
-      </c>
-      <c r="P59">
-        <v>0.1</v>
-      </c>
-      <c r="Q59">
-        <v>1</v>
-      </c>
-      <c r="R59">
-        <v>0.1</v>
-      </c>
-      <c r="S59">
-        <v>1</v>
-      </c>
-      <c r="T59">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>8</v>
       </c>
@@ -5246,7 +4230,7 @@
         <v>419387.641</v>
       </c>
       <c r="E60" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F60">
         <v>1142.2719999999999</v>
@@ -5264,7 +4248,7 @@
         <v>27.614999999999998</v>
       </c>
       <c r="K60" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L60">
         <v>13.287000000000001</v>
@@ -5275,26 +4259,8 @@
       <c r="N60">
         <v>7.75</v>
       </c>
-      <c r="O60">
-        <v>1</v>
-      </c>
-      <c r="P60">
-        <v>0.1</v>
-      </c>
-      <c r="Q60">
-        <v>1</v>
-      </c>
-      <c r="R60">
-        <v>0.1</v>
-      </c>
-      <c r="S60">
-        <v>1</v>
-      </c>
-      <c r="T60">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>8</v>
       </c>
@@ -5308,7 +4274,7 @@
         <v>419352.29200000002</v>
       </c>
       <c r="E61" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F61">
         <v>1102.644</v>
@@ -5326,7 +4292,7 @@
         <v>16.472999999999999</v>
       </c>
       <c r="K61" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L61">
         <v>13.287000000000001</v>
@@ -5337,26 +4303,8 @@
       <c r="N61">
         <v>7.75</v>
       </c>
-      <c r="O61">
-        <v>1</v>
-      </c>
-      <c r="P61">
-        <v>0.1</v>
-      </c>
-      <c r="Q61">
-        <v>1</v>
-      </c>
-      <c r="R61">
-        <v>0.1</v>
-      </c>
-      <c r="S61">
-        <v>1</v>
-      </c>
-      <c r="T61">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>8</v>
       </c>
@@ -5370,7 +4318,7 @@
         <v>419381.53</v>
       </c>
       <c r="E62" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F62">
         <v>1143.4760000000001</v>
@@ -5388,7 +4336,7 @@
         <v>17.288</v>
       </c>
       <c r="K62" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L62">
         <v>13.287000000000001</v>
@@ -5399,26 +4347,8 @@
       <c r="N62">
         <v>7.75</v>
       </c>
-      <c r="O62">
-        <v>1</v>
-      </c>
-      <c r="P62">
-        <v>0.1</v>
-      </c>
-      <c r="Q62">
-        <v>1</v>
-      </c>
-      <c r="R62">
-        <v>0.1</v>
-      </c>
-      <c r="S62">
-        <v>1</v>
-      </c>
-      <c r="T62">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>8</v>
       </c>
@@ -5432,7 +4362,7 @@
         <v>419368.70799999998</v>
       </c>
       <c r="E63" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F63">
         <v>1103.2940000000001</v>
@@ -5450,7 +4380,7 @@
         <v>39.094000000000001</v>
       </c>
       <c r="K63" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L63">
         <v>13.287000000000001</v>
@@ -5461,26 +4391,8 @@
       <c r="N63">
         <v>7.75</v>
       </c>
-      <c r="O63">
-        <v>1</v>
-      </c>
-      <c r="P63">
-        <v>0.1</v>
-      </c>
-      <c r="Q63">
-        <v>1</v>
-      </c>
-      <c r="R63">
-        <v>0.1</v>
-      </c>
-      <c r="S63">
-        <v>1</v>
-      </c>
-      <c r="T63">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>8</v>
       </c>
@@ -5494,7 +4406,7 @@
         <v>419395.071</v>
       </c>
       <c r="E64" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F64">
         <v>1141.7909999999999</v>
@@ -5512,7 +4424,7 @@
         <v>39.088000000000001</v>
       </c>
       <c r="K64" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L64">
         <v>13.287000000000001</v>
@@ -5523,26 +4435,8 @@
       <c r="N64">
         <v>7.75</v>
       </c>
-      <c r="O64">
-        <v>1</v>
-      </c>
-      <c r="P64">
-        <v>0.1</v>
-      </c>
-      <c r="Q64">
-        <v>1</v>
-      </c>
-      <c r="R64">
-        <v>0.1</v>
-      </c>
-      <c r="S64">
-        <v>1</v>
-      </c>
-      <c r="T64">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>8</v>
       </c>
@@ -5556,7 +4450,7 @@
         <v>419404.41700000002</v>
       </c>
       <c r="E65" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F65">
         <v>1165.519</v>
@@ -5574,7 +4468,7 @@
         <v>27.256</v>
       </c>
       <c r="K65" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L65">
         <v>13.29</v>
@@ -5585,26 +4479,8 @@
       <c r="N65">
         <v>7.75</v>
       </c>
-      <c r="O65">
-        <v>1</v>
-      </c>
-      <c r="P65">
-        <v>0.1</v>
-      </c>
-      <c r="Q65">
-        <v>1</v>
-      </c>
-      <c r="R65">
-        <v>0.1</v>
-      </c>
-      <c r="S65">
-        <v>1</v>
-      </c>
-      <c r="T65">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>8</v>
       </c>
@@ -5618,7 +4494,7 @@
         <v>419422.75099999999</v>
       </c>
       <c r="E66" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F66">
         <v>1190.154</v>
@@ -5636,7 +4512,7 @@
         <v>27.446000000000002</v>
       </c>
       <c r="K66" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L66">
         <v>13.29</v>
@@ -5647,26 +4523,8 @@
       <c r="N66">
         <v>7.75</v>
       </c>
-      <c r="O66">
-        <v>1</v>
-      </c>
-      <c r="P66">
-        <v>0.1</v>
-      </c>
-      <c r="Q66">
-        <v>1</v>
-      </c>
-      <c r="R66">
-        <v>0.1</v>
-      </c>
-      <c r="S66">
-        <v>1</v>
-      </c>
-      <c r="T66">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>8</v>
       </c>
@@ -5680,7 +4538,7 @@
         <v>419416.4</v>
       </c>
       <c r="E67" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F67">
         <v>1191.6679999999999</v>
@@ -5698,7 +4556,7 @@
         <v>16.11</v>
       </c>
       <c r="K67" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L67">
         <v>13.29</v>
@@ -5709,26 +4567,8 @@
       <c r="N67">
         <v>7.75</v>
       </c>
-      <c r="O67">
-        <v>1</v>
-      </c>
-      <c r="P67">
-        <v>0.1</v>
-      </c>
-      <c r="Q67">
-        <v>1</v>
-      </c>
-      <c r="R67">
-        <v>0.1</v>
-      </c>
-      <c r="S67">
-        <v>1</v>
-      </c>
-      <c r="T67">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>8</v>
       </c>
@@ -5742,7 +4582,7 @@
         <v>419439.76699999999</v>
       </c>
       <c r="E68" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F68">
         <v>1214.1369999999999</v>
@@ -5760,7 +4600,7 @@
         <v>27.241</v>
       </c>
       <c r="K68" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L68">
         <v>13.29</v>
@@ -5771,26 +4611,8 @@
       <c r="N68">
         <v>7.75</v>
       </c>
-      <c r="O68">
-        <v>1</v>
-      </c>
-      <c r="P68">
-        <v>0.1</v>
-      </c>
-      <c r="Q68">
-        <v>1</v>
-      </c>
-      <c r="R68">
-        <v>0.1</v>
-      </c>
-      <c r="S68">
-        <v>1</v>
-      </c>
-      <c r="T68">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>8</v>
       </c>
@@ -5804,7 +4626,7 @@
         <v>419456.14600000001</v>
       </c>
       <c r="E69" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F69">
         <v>1236.9159999999999</v>
@@ -5822,7 +4644,7 @@
         <v>27.57</v>
       </c>
       <c r="K69" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L69">
         <v>13.29</v>
@@ -5833,26 +4655,8 @@
       <c r="N69">
         <v>7.75</v>
       </c>
-      <c r="O69">
-        <v>1</v>
-      </c>
-      <c r="P69">
-        <v>0.1</v>
-      </c>
-      <c r="Q69">
-        <v>1</v>
-      </c>
-      <c r="R69">
-        <v>0.1</v>
-      </c>
-      <c r="S69">
-        <v>1</v>
-      </c>
-      <c r="T69">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>8</v>
       </c>
@@ -5866,7 +4670,7 @@
         <v>419472.06099999999</v>
       </c>
       <c r="E70" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F70">
         <v>1256.5050000000001</v>
@@ -5884,7 +4688,7 @@
         <v>28.573</v>
       </c>
       <c r="K70" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L70">
         <v>13.29</v>
@@ -5895,26 +4699,8 @@
       <c r="N70">
         <v>7.75</v>
       </c>
-      <c r="O70">
-        <v>1</v>
-      </c>
-      <c r="P70">
-        <v>0.1</v>
-      </c>
-      <c r="Q70">
-        <v>1</v>
-      </c>
-      <c r="R70">
-        <v>0.1</v>
-      </c>
-      <c r="S70">
-        <v>1</v>
-      </c>
-      <c r="T70">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>8</v>
       </c>
@@ -5928,7 +4714,7 @@
         <v>419487.03899999999</v>
       </c>
       <c r="E71" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F71">
         <v>1275.7829999999999</v>
@@ -5946,7 +4732,7 @@
         <v>24.151</v>
       </c>
       <c r="K71" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L71">
         <v>13.29</v>
@@ -5957,26 +4743,8 @@
       <c r="N71">
         <v>7.75</v>
       </c>
-      <c r="O71">
-        <v>1</v>
-      </c>
-      <c r="P71">
-        <v>0.1</v>
-      </c>
-      <c r="Q71">
-        <v>1</v>
-      </c>
-      <c r="R71">
-        <v>0.1</v>
-      </c>
-      <c r="S71">
-        <v>1</v>
-      </c>
-      <c r="T71">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>8</v>
       </c>
@@ -5990,7 +4758,7 @@
         <v>419497.712</v>
       </c>
       <c r="E72" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F72">
         <v>1282.0719999999999</v>
@@ -6008,7 +4776,7 @@
         <v>26.064</v>
       </c>
       <c r="K72" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L72">
         <v>13.29</v>
@@ -6019,26 +4787,8 @@
       <c r="N72">
         <v>7.75</v>
       </c>
-      <c r="O72">
-        <v>1</v>
-      </c>
-      <c r="P72">
-        <v>0.1</v>
-      </c>
-      <c r="Q72">
-        <v>1</v>
-      </c>
-      <c r="R72">
-        <v>0.1</v>
-      </c>
-      <c r="S72">
-        <v>1</v>
-      </c>
-      <c r="T72">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>8</v>
       </c>
@@ -6052,7 +4802,7 @@
         <v>419503.516</v>
       </c>
       <c r="E73" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F73">
         <v>1278.3689999999999</v>
@@ -6070,7 +4820,7 @@
         <v>41.290999999999997</v>
       </c>
       <c r="K73" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L73">
         <v>13.29</v>
@@ -6081,26 +4831,8 @@
       <c r="N73">
         <v>7.75</v>
       </c>
-      <c r="O73">
-        <v>1</v>
-      </c>
-      <c r="P73">
-        <v>0.1</v>
-      </c>
-      <c r="Q73">
-        <v>1</v>
-      </c>
-      <c r="R73">
-        <v>0.1</v>
-      </c>
-      <c r="S73">
-        <v>1</v>
-      </c>
-      <c r="T73">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>8</v>
       </c>
@@ -6114,7 +4846,7 @@
         <v>419465.50799999997</v>
       </c>
       <c r="E74" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F74">
         <v>1257.171</v>
@@ -6132,7 +4864,7 @@
         <v>16.7</v>
       </c>
       <c r="K74" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L74">
         <v>13.29</v>
@@ -6143,26 +4875,8 @@
       <c r="N74">
         <v>7.75</v>
       </c>
-      <c r="O74">
-        <v>1</v>
-      </c>
-      <c r="P74">
-        <v>0.1</v>
-      </c>
-      <c r="Q74">
-        <v>1</v>
-      </c>
-      <c r="R74">
-        <v>0.1</v>
-      </c>
-      <c r="S74">
-        <v>1</v>
-      </c>
-      <c r="T74">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>8</v>
       </c>
@@ -6176,7 +4890,7 @@
         <v>419467.56699999998</v>
       </c>
       <c r="E75" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F75">
         <v>1235.684</v>
@@ -6194,7 +4908,7 @@
         <v>48.253999999999998</v>
       </c>
       <c r="K75" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L75">
         <v>13.29</v>
@@ -6205,26 +4919,8 @@
       <c r="N75">
         <v>7.75</v>
       </c>
-      <c r="O75">
-        <v>1</v>
-      </c>
-      <c r="P75">
-        <v>0.1</v>
-      </c>
-      <c r="Q75">
-        <v>1</v>
-      </c>
-      <c r="R75">
-        <v>0.1</v>
-      </c>
-      <c r="S75">
-        <v>1</v>
-      </c>
-      <c r="T75">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>8</v>
       </c>
@@ -6238,7 +4934,7 @@
         <v>419413.65600000002</v>
       </c>
       <c r="E76" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F76">
         <v>1165.53</v>
@@ -6256,7 +4952,7 @@
         <v>41.021999999999998</v>
       </c>
       <c r="K76" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L76">
         <v>13.29</v>
@@ -6267,26 +4963,8 @@
       <c r="N76">
         <v>7.75</v>
       </c>
-      <c r="O76">
-        <v>1</v>
-      </c>
-      <c r="P76">
-        <v>0.1</v>
-      </c>
-      <c r="Q76">
-        <v>1</v>
-      </c>
-      <c r="R76">
-        <v>0.1</v>
-      </c>
-      <c r="S76">
-        <v>1</v>
-      </c>
-      <c r="T76">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>8</v>
       </c>
@@ -6300,7 +4978,7 @@
         <v>419432.37900000002</v>
       </c>
       <c r="E77" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F77">
         <v>1189.2349999999999</v>
@@ -6318,7 +4996,7 @@
         <v>43.037999999999997</v>
       </c>
       <c r="K77" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L77">
         <v>13.29</v>
@@ -6329,26 +5007,8 @@
       <c r="N77">
         <v>7.75</v>
       </c>
-      <c r="O77">
-        <v>1</v>
-      </c>
-      <c r="P77">
-        <v>0.1</v>
-      </c>
-      <c r="Q77">
-        <v>1</v>
-      </c>
-      <c r="R77">
-        <v>0.1</v>
-      </c>
-      <c r="S77">
-        <v>1</v>
-      </c>
-      <c r="T77">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>8</v>
       </c>
@@ -6362,7 +5022,7 @@
         <v>419519.26699999999</v>
       </c>
       <c r="E78" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F78">
         <v>1263.3040000000001</v>
@@ -6380,7 +5040,7 @@
         <v>87.822000000000003</v>
       </c>
       <c r="K78" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L78">
         <v>13.29</v>
@@ -6391,26 +5051,8 @@
       <c r="N78">
         <v>7.75</v>
       </c>
-      <c r="O78">
-        <v>1</v>
-      </c>
-      <c r="P78">
-        <v>0.1</v>
-      </c>
-      <c r="Q78">
-        <v>1</v>
-      </c>
-      <c r="R78">
-        <v>0.1</v>
-      </c>
-      <c r="S78">
-        <v>1</v>
-      </c>
-      <c r="T78">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>8</v>
       </c>
@@ -6424,7 +5066,7 @@
         <v>419537.11200000002</v>
       </c>
       <c r="E79" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F79">
         <v>1287.1410000000001</v>
@@ -6442,7 +5084,7 @@
         <v>81.563999999999993</v>
       </c>
       <c r="K79" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L79">
         <v>13.29</v>
@@ -6453,26 +5095,8 @@
       <c r="N79">
         <v>7.75</v>
       </c>
-      <c r="O79">
-        <v>1</v>
-      </c>
-      <c r="P79">
-        <v>0.1</v>
-      </c>
-      <c r="Q79">
-        <v>1</v>
-      </c>
-      <c r="R79">
-        <v>0.1</v>
-      </c>
-      <c r="S79">
-        <v>1</v>
-      </c>
-      <c r="T79">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>8</v>
       </c>
@@ -6486,7 +5110,7 @@
         <v>419526.58100000001</v>
       </c>
       <c r="E80" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F80">
         <v>1301.2470000000001</v>
@@ -6504,7 +5128,7 @@
         <v>41.65</v>
       </c>
       <c r="K80" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L80">
         <v>13.29</v>
@@ -6515,26 +5139,8 @@
       <c r="N80">
         <v>7.75</v>
       </c>
-      <c r="O80">
-        <v>1</v>
-      </c>
-      <c r="P80">
-        <v>0.1</v>
-      </c>
-      <c r="Q80">
-        <v>1</v>
-      </c>
-      <c r="R80">
-        <v>0.1</v>
-      </c>
-      <c r="S80">
-        <v>1</v>
-      </c>
-      <c r="T80">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>9</v>
       </c>
@@ -6548,7 +5154,7 @@
         <v>419522.19199999998</v>
       </c>
       <c r="E81" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F81">
         <v>1318.586</v>
@@ -6566,7 +5172,7 @@
         <v>12.044</v>
       </c>
       <c r="K81" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L81">
         <v>13.29</v>
@@ -6577,26 +5183,8 @@
       <c r="N81">
         <v>7.75</v>
       </c>
-      <c r="O81">
-        <v>1</v>
-      </c>
-      <c r="P81">
-        <v>0.1</v>
-      </c>
-      <c r="Q81">
-        <v>1</v>
-      </c>
-      <c r="R81">
-        <v>0.1</v>
-      </c>
-      <c r="S81">
-        <v>1</v>
-      </c>
-      <c r="T81">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>9</v>
       </c>
@@ -6610,7 +5198,7 @@
         <v>419529.21399999998</v>
       </c>
       <c r="E82" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F82">
         <v>1336.444</v>
@@ -6628,7 +5216,7 @@
         <v>8.7789999999999999</v>
       </c>
       <c r="K82" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L82">
         <v>13.29</v>
@@ -6639,26 +5227,8 @@
       <c r="N82">
         <v>7.75</v>
       </c>
-      <c r="O82">
-        <v>1</v>
-      </c>
-      <c r="P82">
-        <v>0.1</v>
-      </c>
-      <c r="Q82">
-        <v>1</v>
-      </c>
-      <c r="R82">
-        <v>0.1</v>
-      </c>
-      <c r="S82">
-        <v>1</v>
-      </c>
-      <c r="T82">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>9</v>
       </c>
@@ -6672,7 +5242,7 @@
         <v>419553.50699999998</v>
       </c>
       <c r="E83" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F83">
         <v>1366.923</v>
@@ -6690,7 +5260,7 @@
         <v>9.6579999999999995</v>
       </c>
       <c r="K83" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L83">
         <v>13.29</v>
@@ -6701,26 +5271,8 @@
       <c r="N83">
         <v>7.75</v>
       </c>
-      <c r="O83">
-        <v>1</v>
-      </c>
-      <c r="P83">
-        <v>0.1</v>
-      </c>
-      <c r="Q83">
-        <v>1</v>
-      </c>
-      <c r="R83">
-        <v>0.1</v>
-      </c>
-      <c r="S83">
-        <v>1</v>
-      </c>
-      <c r="T83">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>9</v>
       </c>
@@ -6734,7 +5286,7 @@
         <v>419573.54100000003</v>
       </c>
       <c r="E84" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F84">
         <v>1391.097</v>
@@ -6752,7 +5304,7 @@
         <v>9.3379999999999992</v>
       </c>
       <c r="K84" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L84">
         <v>13.29</v>
@@ -6763,26 +5315,8 @@
       <c r="N84">
         <v>7.75</v>
       </c>
-      <c r="O84">
-        <v>1</v>
-      </c>
-      <c r="P84">
-        <v>0.1</v>
-      </c>
-      <c r="Q84">
-        <v>1</v>
-      </c>
-      <c r="R84">
-        <v>0.1</v>
-      </c>
-      <c r="S84">
-        <v>1</v>
-      </c>
-      <c r="T84">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>9</v>
       </c>
@@ -6796,7 +5330,7 @@
         <v>419593.38799999998</v>
       </c>
       <c r="E85" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F85">
         <v>1414.4690000000001</v>
@@ -6814,7 +5348,7 @@
         <v>8.4359999999999999</v>
       </c>
       <c r="K85" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L85">
         <v>13.29</v>
@@ -6825,26 +5359,8 @@
       <c r="N85">
         <v>7.75</v>
       </c>
-      <c r="O85">
-        <v>1</v>
-      </c>
-      <c r="P85">
-        <v>0.1</v>
-      </c>
-      <c r="Q85">
-        <v>1</v>
-      </c>
-      <c r="R85">
-        <v>0.1</v>
-      </c>
-      <c r="S85">
-        <v>1</v>
-      </c>
-      <c r="T85">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>9</v>
       </c>
@@ -6858,7 +5374,7 @@
         <v>419617.353</v>
       </c>
       <c r="E86" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F86">
         <v>1442.1369999999999</v>
@@ -6876,7 +5392,7 @@
         <v>8.3759999999999994</v>
       </c>
       <c r="K86" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L86">
         <v>13.29</v>
@@ -6887,26 +5403,8 @@
       <c r="N86">
         <v>7.75</v>
       </c>
-      <c r="O86">
-        <v>1</v>
-      </c>
-      <c r="P86">
-        <v>0.1</v>
-      </c>
-      <c r="Q86">
-        <v>1</v>
-      </c>
-      <c r="R86">
-        <v>0.1</v>
-      </c>
-      <c r="S86">
-        <v>1</v>
-      </c>
-      <c r="T86">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>9</v>
       </c>
@@ -6920,7 +5418,7 @@
         <v>419604.24699999997</v>
       </c>
       <c r="E87" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F87">
         <v>1412.019</v>
@@ -6938,7 +5436,7 @@
         <v>34.829000000000001</v>
       </c>
       <c r="K87" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L87">
         <v>13.29</v>
@@ -6949,26 +5447,8 @@
       <c r="N87">
         <v>7.75</v>
       </c>
-      <c r="O87">
-        <v>1</v>
-      </c>
-      <c r="P87">
-        <v>0.1</v>
-      </c>
-      <c r="Q87">
-        <v>1</v>
-      </c>
-      <c r="R87">
-        <v>0.1</v>
-      </c>
-      <c r="S87">
-        <v>1</v>
-      </c>
-      <c r="T87">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>9</v>
       </c>
@@ -6982,7 +5462,7 @@
         <v>419584.21299999999</v>
       </c>
       <c r="E88" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F88">
         <v>1385.58</v>
@@ -7000,7 +5480,7 @@
         <v>38.756</v>
       </c>
       <c r="K88" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L88">
         <v>13.29</v>
@@ -7011,26 +5491,8 @@
       <c r="N88">
         <v>7.75</v>
       </c>
-      <c r="O88">
-        <v>1</v>
-      </c>
-      <c r="P88">
-        <v>0.1</v>
-      </c>
-      <c r="Q88">
-        <v>1</v>
-      </c>
-      <c r="R88">
-        <v>0.1</v>
-      </c>
-      <c r="S88">
-        <v>1</v>
-      </c>
-      <c r="T88">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>9</v>
       </c>
@@ -7044,7 +5506,7 @@
         <v>419562.12</v>
       </c>
       <c r="E89" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F89">
         <v>1359.9880000000001</v>
@@ -7062,7 +5524,7 @@
         <v>37.752000000000002</v>
       </c>
       <c r="K89" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L89">
         <v>13.29</v>
@@ -7073,26 +5535,8 @@
       <c r="N89">
         <v>7.75</v>
       </c>
-      <c r="O89">
-        <v>1</v>
-      </c>
-      <c r="P89">
-        <v>0.1</v>
-      </c>
-      <c r="Q89">
-        <v>1</v>
-      </c>
-      <c r="R89">
-        <v>0.1</v>
-      </c>
-      <c r="S89">
-        <v>1</v>
-      </c>
-      <c r="T89">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>9</v>
       </c>
@@ -7106,7 +5550,7 @@
         <v>419539.09</v>
       </c>
       <c r="E90" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F90">
         <v>1331.779</v>
@@ -7124,7 +5568,7 @@
         <v>27.361999999999998</v>
       </c>
       <c r="K90" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L90">
         <v>13.29</v>
@@ -7135,26 +5579,8 @@
       <c r="N90">
         <v>7.75</v>
       </c>
-      <c r="O90">
-        <v>1</v>
-      </c>
-      <c r="P90">
-        <v>0.1</v>
-      </c>
-      <c r="Q90">
-        <v>1</v>
-      </c>
-      <c r="R90">
-        <v>0.1</v>
-      </c>
-      <c r="S90">
-        <v>1</v>
-      </c>
-      <c r="T90">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>9</v>
       </c>
@@ -7168,7 +5594,7 @@
         <v>419626.10100000002</v>
       </c>
       <c r="E91" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F91">
         <v>1433.96</v>
@@ -7186,7 +5612,7 @@
         <v>40.136000000000003</v>
       </c>
       <c r="K91" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L91">
         <v>13.29</v>
@@ -7197,26 +5623,8 @@
       <c r="N91">
         <v>7.75</v>
       </c>
-      <c r="O91">
-        <v>1</v>
-      </c>
-      <c r="P91">
-        <v>0.1</v>
-      </c>
-      <c r="Q91">
-        <v>1</v>
-      </c>
-      <c r="R91">
-        <v>0.1</v>
-      </c>
-      <c r="S91">
-        <v>1</v>
-      </c>
-      <c r="T91">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>9</v>
       </c>
@@ -7230,7 +5638,7 @@
         <v>419634.609</v>
       </c>
       <c r="E92" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F92">
         <v>1462.4069999999999</v>
@@ -7248,7 +5656,7 @@
         <v>7.7350000000000003</v>
       </c>
       <c r="K92" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L92">
         <v>13.29</v>
@@ -7259,26 +5667,8 @@
       <c r="N92">
         <v>7.75</v>
       </c>
-      <c r="O92">
-        <v>1</v>
-      </c>
-      <c r="P92">
-        <v>0.1</v>
-      </c>
-      <c r="Q92">
-        <v>1</v>
-      </c>
-      <c r="R92">
-        <v>0.1</v>
-      </c>
-      <c r="S92">
-        <v>1</v>
-      </c>
-      <c r="T92">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>9</v>
       </c>
@@ -7292,7 +5682,7 @@
         <v>419652.34299999999</v>
       </c>
       <c r="E93" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F93">
         <v>1482.5709999999999</v>
@@ -7310,7 +5700,7 @@
         <v>8.2720000000000002</v>
       </c>
       <c r="K93" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L93">
         <v>13.29</v>
@@ -7321,26 +5711,8 @@
       <c r="N93">
         <v>7.75</v>
       </c>
-      <c r="O93">
-        <v>1</v>
-      </c>
-      <c r="P93">
-        <v>0.1</v>
-      </c>
-      <c r="Q93">
-        <v>1</v>
-      </c>
-      <c r="R93">
-        <v>0.1</v>
-      </c>
-      <c r="S93">
-        <v>1</v>
-      </c>
-      <c r="T93">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>9</v>
       </c>
@@ -7354,7 +5726,7 @@
         <v>419666.84299999999</v>
       </c>
       <c r="E94" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F94">
         <v>1498.367</v>
@@ -7372,7 +5744,7 @@
         <v>8.3780000000000001</v>
       </c>
       <c r="K94" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L94">
         <v>13.29</v>
@@ -7383,26 +5755,8 @@
       <c r="N94">
         <v>7.75</v>
       </c>
-      <c r="O94">
-        <v>1</v>
-      </c>
-      <c r="P94">
-        <v>0.1</v>
-      </c>
-      <c r="Q94">
-        <v>1</v>
-      </c>
-      <c r="R94">
-        <v>0.1</v>
-      </c>
-      <c r="S94">
-        <v>1</v>
-      </c>
-      <c r="T94">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>9</v>
       </c>
@@ -7416,7 +5770,7 @@
         <v>419680.50300000003</v>
       </c>
       <c r="E95" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F95">
         <v>1513.9159999999999</v>
@@ -7434,7 +5788,7 @@
         <v>8.0960000000000001</v>
       </c>
       <c r="K95" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L95">
         <v>13.29</v>
@@ -7445,26 +5799,8 @@
       <c r="N95">
         <v>7.75</v>
       </c>
-      <c r="O95">
-        <v>1</v>
-      </c>
-      <c r="P95">
-        <v>0.1</v>
-      </c>
-      <c r="Q95">
-        <v>1</v>
-      </c>
-      <c r="R95">
-        <v>0.1</v>
-      </c>
-      <c r="S95">
-        <v>1</v>
-      </c>
-      <c r="T95">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>9</v>
       </c>
@@ -7478,7 +5814,7 @@
         <v>419681.58199999999</v>
       </c>
       <c r="E96" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F96">
         <v>1495.748</v>
@@ -7496,7 +5832,7 @@
         <v>47.176000000000002</v>
       </c>
       <c r="K96" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L96">
         <v>13.29</v>
@@ -7507,26 +5843,8 @@
       <c r="N96">
         <v>7.75</v>
       </c>
-      <c r="O96">
-        <v>1</v>
-      </c>
-      <c r="P96">
-        <v>0.1</v>
-      </c>
-      <c r="Q96">
-        <v>1</v>
-      </c>
-      <c r="R96">
-        <v>0.1</v>
-      </c>
-      <c r="S96">
-        <v>1</v>
-      </c>
-      <c r="T96">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>9</v>
       </c>
@@ -7540,7 +5858,7 @@
         <v>419689.25099999999</v>
       </c>
       <c r="E97" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F97">
         <v>1492.5930000000001</v>
@@ -7558,7 +5876,7 @@
         <v>70.381</v>
       </c>
       <c r="K97" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L97">
         <v>13.29</v>
@@ -7569,26 +5887,8 @@
       <c r="N97">
         <v>7.75</v>
       </c>
-      <c r="O97">
-        <v>1</v>
-      </c>
-      <c r="P97">
-        <v>0.1</v>
-      </c>
-      <c r="Q97">
-        <v>1</v>
-      </c>
-      <c r="R97">
-        <v>0.1</v>
-      </c>
-      <c r="S97">
-        <v>1</v>
-      </c>
-      <c r="T97">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>9</v>
       </c>
@@ -7602,7 +5902,7 @@
         <v>419634.489</v>
       </c>
       <c r="E98" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F98">
         <v>1429.615</v>
@@ -7620,7 +5920,7 @@
         <v>64.856999999999999</v>
       </c>
       <c r="K98" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L98">
         <v>13.29</v>
@@ -7631,26 +5931,8 @@
       <c r="N98">
         <v>7.75</v>
       </c>
-      <c r="O98">
-        <v>1</v>
-      </c>
-      <c r="P98">
-        <v>0.1</v>
-      </c>
-      <c r="Q98">
-        <v>1</v>
-      </c>
-      <c r="R98">
-        <v>0.1</v>
-      </c>
-      <c r="S98">
-        <v>1</v>
-      </c>
-      <c r="T98">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>9</v>
       </c>
@@ -7664,7 +5946,7 @@
         <v>419689.73</v>
       </c>
       <c r="E99" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F99">
         <v>1524.9290000000001</v>
@@ -7682,7 +5964,7 @@
         <v>8.9260000000000002</v>
       </c>
       <c r="K99" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L99">
         <v>13.29</v>
@@ -7693,26 +5975,8 @@
       <c r="N99">
         <v>7.75</v>
       </c>
-      <c r="O99">
-        <v>1</v>
-      </c>
-      <c r="P99">
-        <v>0.1</v>
-      </c>
-      <c r="Q99">
-        <v>1</v>
-      </c>
-      <c r="R99">
-        <v>0.1</v>
-      </c>
-      <c r="S99">
-        <v>1</v>
-      </c>
-      <c r="T99">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>9</v>
       </c>
@@ -7726,7 +5990,7 @@
         <v>419641.679</v>
       </c>
       <c r="E100" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F100">
         <v>1462.16</v>
@@ -7744,7 +6008,7 @@
         <v>23.966999999999999</v>
       </c>
       <c r="K100" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L100">
         <v>13.29</v>
@@ -7755,26 +6019,8 @@
       <c r="N100">
         <v>7.75</v>
       </c>
-      <c r="O100">
-        <v>1</v>
-      </c>
-      <c r="P100">
-        <v>0.1</v>
-      </c>
-      <c r="Q100">
-        <v>1</v>
-      </c>
-      <c r="R100">
-        <v>0.1</v>
-      </c>
-      <c r="S100">
-        <v>1</v>
-      </c>
-      <c r="T100">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>9</v>
       </c>
@@ -7788,7 +6034,7 @@
         <v>419687.45299999998</v>
       </c>
       <c r="E101" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F101">
         <v>1512.579</v>
@@ -7806,7 +6052,7 @@
         <v>25.442</v>
       </c>
       <c r="K101" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L101">
         <v>13.29</v>
@@ -7817,26 +6063,8 @@
       <c r="N101">
         <v>7.75</v>
       </c>
-      <c r="O101">
-        <v>1</v>
-      </c>
-      <c r="P101">
-        <v>0.1</v>
-      </c>
-      <c r="Q101">
-        <v>1</v>
-      </c>
-      <c r="R101">
-        <v>0.1</v>
-      </c>
-      <c r="S101">
-        <v>1</v>
-      </c>
-      <c r="T101">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>9</v>
       </c>
@@ -7850,7 +6078,7 @@
         <v>419658.81400000001</v>
       </c>
       <c r="E102" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F102">
         <v>1481.1030000000001</v>
@@ -7868,7 +6096,7 @@
         <v>25.503</v>
       </c>
       <c r="K102" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L102">
         <v>13.29</v>
@@ -7879,26 +6107,8 @@
       <c r="N102">
         <v>7.75</v>
       </c>
-      <c r="O102">
-        <v>1</v>
-      </c>
-      <c r="P102">
-        <v>0.1</v>
-      </c>
-      <c r="Q102">
-        <v>1</v>
-      </c>
-      <c r="R102">
-        <v>0.1</v>
-      </c>
-      <c r="S102">
-        <v>1</v>
-      </c>
-      <c r="T102">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.15">
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>9</v>
       </c>
@@ -7912,7 +6122,7 @@
         <v>419699.67599999998</v>
       </c>
       <c r="E103" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F103">
         <v>1527.6120000000001</v>
@@ -7930,7 +6140,7 @@
         <v>26.507999999999999</v>
       </c>
       <c r="K103" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L103">
         <v>13.29</v>
@@ -7940,24 +6150,6 @@
       </c>
       <c r="N103">
         <v>7.75</v>
-      </c>
-      <c r="O103">
-        <v>1</v>
-      </c>
-      <c r="P103">
-        <v>0.1</v>
-      </c>
-      <c r="Q103">
-        <v>1</v>
-      </c>
-      <c r="R103">
-        <v>0.1</v>
-      </c>
-      <c r="S103">
-        <v>1</v>
-      </c>
-      <c r="T103">
-        <v>0.12</v>
       </c>
     </row>
   </sheetData>
@@ -7971,71 +6163,71 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3ED9FF6-8968-4FA6-BAEC-B95365AA2886}">
   <dimension ref="A1:N55"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="8.19921875" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.69921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="23.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.59765625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.25" customWidth="1"/>
+    <col min="12" max="12" width="11.3984375" customWidth="1"/>
+    <col min="13" max="13" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="6" t="str">
+        <v>39</v>
+      </c>
+      <c r="F1" s="4" t="str">
         <f>LEFT(E1,LEN(E1)-5)&amp;VLOOKUP(LEFT(E1,LEN(E1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>top_zand_stdev</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H1" s="6" t="str">
+        <v>40</v>
+      </c>
+      <c r="H1" s="4" t="str">
         <f>LEFT(G1,LEN(G1)-5)&amp;VLOOKUP(LEFT(G1,LEN(G1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>gamma_sat_deklaag_stdev</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J1" s="6" t="str">
+        <v>41</v>
+      </c>
+      <c r="J1" s="4" t="str">
         <f>LEFT(I1,LEN(I1)-5)&amp;VLOOKUP(LEFT(I1,LEN(I1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>D_wvp_stdev</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L1" s="6" t="str">
+        <v>42</v>
+      </c>
+      <c r="L1" s="4" t="str">
         <f>LEFT(K1,LEN(K1)-5)&amp;VLOOKUP(LEFT(K1,LEN(K1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>kD_wvp_vc</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="N1" s="6" t="str">
+        <v>43</v>
+      </c>
+      <c r="N1" s="4" t="str">
         <f>LEFT(M1,LEN(M1)-5)&amp;VLOOKUP(LEFT(M1,LEN(M1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>d70_vc</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -8043,7 +6235,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D2">
         <v>0.5</v>
@@ -8079,7 +6271,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8087,7 +6279,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D3">
         <v>0.5</v>
@@ -8123,7 +6315,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -8131,7 +6323,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -8161,7 +6353,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -8194,7 +6386,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
@@ -8227,7 +6419,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
@@ -8260,7 +6452,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2</v>
       </c>
@@ -8268,7 +6460,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D8">
         <v>0.5</v>
@@ -8304,7 +6496,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2</v>
       </c>
@@ -8312,7 +6504,7 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D9">
         <v>0.5</v>
@@ -8348,7 +6540,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2</v>
       </c>
@@ -8356,7 +6548,7 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -8386,7 +6578,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2</v>
       </c>
@@ -8419,7 +6611,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
@@ -8452,7 +6644,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
@@ -8485,7 +6677,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>3</v>
       </c>
@@ -8493,7 +6685,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D14">
         <v>0.5</v>
@@ -8529,7 +6721,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>3</v>
       </c>
@@ -8537,7 +6729,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D15">
         <v>0.5</v>
@@ -8573,7 +6765,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>3</v>
       </c>
@@ -8581,7 +6773,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -8611,7 +6803,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>3</v>
       </c>
@@ -8644,7 +6836,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>3</v>
       </c>
@@ -8677,7 +6869,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
@@ -8710,7 +6902,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>4</v>
       </c>
@@ -8718,7 +6910,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D20">
         <v>0.5</v>
@@ -8754,7 +6946,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>4</v>
       </c>
@@ -8762,7 +6954,7 @@
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D21">
         <v>0.5</v>
@@ -8798,7 +6990,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>4</v>
       </c>
@@ -8806,7 +6998,7 @@
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -8836,7 +7028,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>4</v>
       </c>
@@ -8869,7 +7061,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>4</v>
       </c>
@@ -8902,7 +7094,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>4</v>
       </c>
@@ -8935,7 +7127,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>5</v>
       </c>
@@ -8943,7 +7135,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D26">
         <v>0.5</v>
@@ -8979,7 +7171,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>5</v>
       </c>
@@ -8987,7 +7179,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D27">
         <v>0.5</v>
@@ -9023,7 +7215,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>5</v>
       </c>
@@ -9031,7 +7223,7 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -9061,7 +7253,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>5</v>
       </c>
@@ -9094,7 +7286,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>5</v>
       </c>
@@ -9127,7 +7319,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>5</v>
       </c>
@@ -9160,7 +7352,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>6</v>
       </c>
@@ -9168,7 +7360,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D32">
         <v>0.5</v>
@@ -9204,7 +7396,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>6</v>
       </c>
@@ -9212,7 +7404,7 @@
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D33">
         <v>0.5</v>
@@ -9248,7 +7440,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>6</v>
       </c>
@@ -9256,7 +7448,7 @@
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -9286,7 +7478,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>6</v>
       </c>
@@ -9319,7 +7511,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>6</v>
       </c>
@@ -9352,7 +7544,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
@@ -9385,7 +7577,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>7</v>
       </c>
@@ -9393,7 +7585,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D38">
         <v>0.5</v>
@@ -9429,7 +7621,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>7</v>
       </c>
@@ -9437,7 +7629,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D39">
         <v>0.5</v>
@@ -9473,7 +7665,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>7</v>
       </c>
@@ -9481,7 +7673,7 @@
         <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -9511,7 +7703,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
@@ -9544,7 +7736,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
@@ -9577,7 +7769,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
@@ -9610,7 +7802,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
@@ -9618,7 +7810,7 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D44">
         <v>0.5</v>
@@ -9654,7 +7846,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
@@ -9662,7 +7854,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D45">
         <v>0.5</v>
@@ -9698,7 +7890,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>8</v>
       </c>
@@ -9706,7 +7898,7 @@
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -9736,7 +7928,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>8</v>
       </c>
@@ -9769,7 +7961,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>8</v>
       </c>
@@ -9802,7 +7994,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>8</v>
       </c>
@@ -9835,7 +8027,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>9</v>
       </c>
@@ -9843,7 +8035,7 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D50">
         <v>0.5</v>
@@ -9879,7 +8071,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>9</v>
       </c>
@@ -9887,7 +8079,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D51">
         <v>0.5</v>
@@ -9923,7 +8115,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>9</v>
       </c>
@@ -9931,7 +8123,7 @@
         <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -9961,7 +8153,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>9</v>
       </c>
@@ -9994,7 +8186,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>9</v>
       </c>
@@ -10027,7 +8219,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
@@ -10061,11 +8253,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1" xr:uid="{A3ED9FF6-8968-4FA6-BAEC-B95365AA2886}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -10073,1656 +8263,1839 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B7A8CE-63DA-4EEA-9A88-5E62FD2B5E40}">
   <dimension ref="A1:R69"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="17.19921875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.19921875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="47.625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.25" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="47.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="L1" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2" t="s">
         <v>201</v>
       </c>
-      <c r="M1" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="R1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" t="s">
-        <v>63</v>
-      </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>217</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="L2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N2" t="s">
-        <v>55</v>
-      </c>
-      <c r="O2" t="s">
-        <v>55</v>
-      </c>
-      <c r="R2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>208</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F3" t="s">
-        <v>58</v>
+        <v>217</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" t="s">
-        <v>97</v>
+        <v>0</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
+        <v>217</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" t="s">
-        <v>51</v>
+        <v>1</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
-        <v>60</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="O5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
+        <v>217</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" t="s">
-        <v>51</v>
+        <v>210</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.4999999999999999E-4</v>
-      </c>
-      <c r="J6" s="1">
-        <v>5</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="O6" t="s">
-        <v>55</v>
-      </c>
-      <c r="P6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
+        <v>217</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>201</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>22</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
+        <v>217</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>211</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
-        <v>4000</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L8" t="s">
-        <v>55</v>
-      </c>
-      <c r="M8" t="s">
-        <v>55</v>
-      </c>
-      <c r="N8" t="s">
-        <v>55</v>
-      </c>
-      <c r="O8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
+        <v>217</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>169</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>212</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
-        <v>5000</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" t="s">
-        <v>55</v>
-      </c>
-      <c r="M9" t="s">
-        <v>55</v>
-      </c>
-      <c r="N9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
+        <v>217</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>164</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>213</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>200</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="L10" t="s">
-        <v>55</v>
-      </c>
-      <c r="M10" t="s">
-        <v>55</v>
-      </c>
-      <c r="N10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" t="s">
-        <v>51</v>
+        <v>165</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="L11" t="s">
-        <v>55</v>
-      </c>
-      <c r="M11" t="s">
-        <v>55</v>
-      </c>
-      <c r="N11" t="s">
-        <v>55</v>
-      </c>
-      <c r="O11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>51</v>
+        <v>166</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" s="2">
-        <v>5</v>
-      </c>
-      <c r="J12" s="2">
-        <v>2000</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="L12" t="s">
-        <v>55</v>
-      </c>
-      <c r="M12" t="s">
-        <v>55</v>
-      </c>
-      <c r="N12" t="s">
-        <v>55</v>
-      </c>
-      <c r="O12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.15">
+        <v>217</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>201</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="3">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>0.1</v>
+        <v>217</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s">
-        <v>105</v>
+        <v>209</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>200</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <v>0.12</v>
+        <v>217</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="O14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>100</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>204</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>203</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>86</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1</v>
-      </c>
-      <c r="H15">
-        <v>0.1</v>
+        <v>217</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
-      <c r="K15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>53</v>
+        <v>217</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A17" s="7" t="s">
-        <v>19</v>
+        <v>188</v>
+      </c>
+      <c r="L16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N16" t="s">
+        <v>49</v>
+      </c>
+      <c r="O16" t="s">
+        <v>49</v>
+      </c>
+      <c r="P16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>83</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>53</v>
+        <v>48</v>
+      </c>
+      <c r="E17" t="s">
+        <v>219</v>
+      </c>
+      <c r="F17" t="s">
+        <v>51</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="O17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
+        <v>52</v>
+      </c>
+      <c r="L17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>53</v>
+        <v>219</v>
+      </c>
+      <c r="F18" t="s">
+        <v>50</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="L18" t="s">
+        <v>49</v>
+      </c>
+      <c r="O18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" t="s">
+        <v>219</v>
+      </c>
+      <c r="F19" t="s">
+        <v>50</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="J19" s="2">
+        <v>60</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="O19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" t="s">
+        <v>219</v>
+      </c>
+      <c r="F20" t="s">
+        <v>51</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="J20" s="1">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="O20" t="s">
+        <v>49</v>
+      </c>
+      <c r="P20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" t="s">
+        <v>219</v>
+      </c>
+      <c r="F21" t="s">
+        <v>50</v>
+      </c>
+      <c r="I21" s="2">
+        <v>10</v>
+      </c>
+      <c r="J21" s="2">
+        <v>22</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" t="s">
+        <v>219</v>
+      </c>
+      <c r="F22" t="s">
+        <v>51</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="J22" s="2">
+        <v>4000</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="L22" t="s">
+        <v>49</v>
+      </c>
+      <c r="M22" t="s">
+        <v>49</v>
+      </c>
+      <c r="N22" t="s">
+        <v>49</v>
+      </c>
+      <c r="O22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" t="s">
+        <v>194</v>
+      </c>
+      <c r="C23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" t="s">
+        <v>217</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
+        <v>5000</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L23" t="s">
+        <v>49</v>
+      </c>
+      <c r="M23" t="s">
+        <v>49</v>
+      </c>
+      <c r="N23" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" t="s">
+        <v>195</v>
+      </c>
+      <c r="C24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" t="s">
+        <v>217</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="L24" t="s">
+        <v>49</v>
+      </c>
+      <c r="M24" t="s">
+        <v>49</v>
+      </c>
+      <c r="N24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" t="s">
+        <v>217</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="L25" t="s">
+        <v>49</v>
+      </c>
+      <c r="M25" t="s">
+        <v>49</v>
+      </c>
+      <c r="N25" t="s">
+        <v>49</v>
+      </c>
+      <c r="O25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>197</v>
+      </c>
+      <c r="C26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" t="s">
+        <v>217</v>
+      </c>
+      <c r="I26" s="2">
+        <v>5</v>
+      </c>
+      <c r="J26" s="2">
+        <v>2000</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="L26" t="s">
+        <v>49</v>
+      </c>
+      <c r="M26" t="s">
+        <v>49</v>
+      </c>
+      <c r="N26" t="s">
+        <v>49</v>
+      </c>
+      <c r="O26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" t="s">
         <v>54</v>
       </c>
-      <c r="L18" t="s">
-        <v>55</v>
-      </c>
-      <c r="M18" t="s">
-        <v>55</v>
-      </c>
-      <c r="N18" t="s">
-        <v>55</v>
-      </c>
-      <c r="O18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A19" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C27" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" t="s">
+        <v>217</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" t="s">
-        <v>56</v>
-      </c>
-      <c r="I19" s="2">
-        <v>-18</v>
-      </c>
-      <c r="J19" s="2">
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>193</v>
+      </c>
+      <c r="C28" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" t="s">
+        <v>217</v>
+      </c>
+      <c r="I28" s="2">
+        <v>-4</v>
+      </c>
+      <c r="J28" s="2">
         <v>15</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="O19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A20" t="s">
-        <v>128</v>
-      </c>
-      <c r="B20" t="s">
-        <v>129</v>
-      </c>
-      <c r="C20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="K28" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="O28" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" t="s">
+        <v>192</v>
+      </c>
+      <c r="C29" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="1">
-        <v>2.0799999999999999E-4</v>
-      </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="O20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A21" t="s">
-        <v>113</v>
-      </c>
-      <c r="B21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21">
-        <v>0.25</v>
-      </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A22" t="s">
-        <v>130</v>
-      </c>
-      <c r="B22" t="s">
-        <v>131</v>
-      </c>
-      <c r="C22" t="s">
-        <v>132</v>
-      </c>
-      <c r="D22" t="s">
-        <v>82</v>
-      </c>
-      <c r="E22" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22">
-        <v>9.81</v>
-      </c>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="O22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A23" t="s">
-        <v>136</v>
-      </c>
-      <c r="B23" t="s">
-        <v>137</v>
-      </c>
-      <c r="C23" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" s="2">
-        <v>26</v>
-      </c>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="O23" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A24" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24">
-        <v>9.81</v>
-      </c>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A25" t="s">
-        <v>176</v>
-      </c>
-      <c r="B25" t="s">
-        <v>177</v>
-      </c>
-      <c r="C25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25">
-        <v>1.5</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B26" t="s">
-        <v>107</v>
-      </c>
-      <c r="C26" t="s">
-        <v>102</v>
-      </c>
-      <c r="D26" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26" t="s">
-        <v>86</v>
-      </c>
-      <c r="F26" t="s">
-        <v>56</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="H26" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="N26" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A27" t="s">
-        <v>172</v>
-      </c>
-      <c r="B27" t="s">
-        <v>173</v>
-      </c>
-      <c r="C27" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27">
-        <v>0.1</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A28" t="s">
-        <v>174</v>
-      </c>
-      <c r="B28" t="s">
-        <v>175</v>
-      </c>
-      <c r="C28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28">
-        <v>0.01</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A29" t="s">
-        <v>109</v>
-      </c>
-      <c r="B29" t="s">
-        <v>110</v>
-      </c>
-      <c r="C29" t="s">
-        <v>102</v>
-      </c>
       <c r="D29" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>53</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="H29" s="2"/>
+        <v>217</v>
+      </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>108</v>
+        <v>188</v>
+      </c>
+      <c r="L29" t="s">
+        <v>49</v>
+      </c>
+      <c r="M29" t="s">
+        <v>49</v>
+      </c>
+      <c r="N29" t="s">
+        <v>49</v>
       </c>
       <c r="O29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A30" t="s">
-        <v>125</v>
-      </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="D30" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
-      </c>
-      <c r="G30" s="2">
-        <v>37</v>
-      </c>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="F30" t="s">
+        <v>50</v>
+      </c>
+      <c r="I30" s="2">
+        <v>-18</v>
+      </c>
+      <c r="J30" s="2">
+        <v>15</v>
+      </c>
       <c r="K30" s="2" t="s">
-        <v>108</v>
+        <v>190</v>
       </c>
       <c r="O30" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="B31" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="E31" t="s">
-        <v>53</v>
+        <v>217</v>
       </c>
       <c r="G31" s="1">
-        <v>1.33E-6</v>
+        <v>2.0799999999999999E-4</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="O31" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="D32" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E32" t="s">
-        <v>77</v>
-      </c>
-      <c r="I32" s="2">
-        <v>0.1</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="G32">
+        <v>0.25</v>
+      </c>
+      <c r="I32" s="2"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K32" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E33" t="s">
-        <v>77</v>
-      </c>
-      <c r="I33" s="2">
-        <v>0.1</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="G33">
+        <v>9.81</v>
+      </c>
+      <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
+        <v>93</v>
+      </c>
+      <c r="O33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="B34" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="C34" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="E34" t="s">
+        <v>217</v>
+      </c>
+      <c r="G34" s="2">
+        <v>26</v>
+      </c>
+      <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
+      <c r="K34" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="O34" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="C35" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D35" t="s">
-        <v>76</v>
+        <v>68</v>
+      </c>
+      <c r="E35" t="s">
+        <v>217</v>
+      </c>
+      <c r="G35">
+        <v>9.81</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="O35" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K35" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="B36" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D36" t="s">
-        <v>76</v>
-      </c>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="M36" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
+        <v>68</v>
+      </c>
+      <c r="E36" t="s">
+        <v>217</v>
+      </c>
+      <c r="G36">
+        <v>1.5</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>168</v>
+        <v>91</v>
       </c>
       <c r="B37" t="s">
-        <v>169</v>
+        <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>76</v>
+        <v>68</v>
+      </c>
+      <c r="E37" t="s">
+        <v>219</v>
+      </c>
+      <c r="F37" t="s">
+        <v>50</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0.1</v>
       </c>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
+      <c r="K37" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="N37" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="B38" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="D38" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" t="s">
+        <v>219</v>
+      </c>
+      <c r="F38" t="s">
+        <v>50</v>
+      </c>
+      <c r="G38">
+        <v>0.1</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>157</v>
+      </c>
+      <c r="B39" t="s">
+        <v>158</v>
+      </c>
+      <c r="C39" t="s">
         <v>76</v>
       </c>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="O38" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A39" t="s">
-        <v>166</v>
-      </c>
-      <c r="B39" t="s">
-        <v>167</v>
-      </c>
-      <c r="C39" t="s">
-        <v>102</v>
-      </c>
       <c r="D39" t="s">
-        <v>76</v>
-      </c>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="M39" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
+        <v>68</v>
+      </c>
+      <c r="E39" t="s">
+        <v>219</v>
+      </c>
+      <c r="F39" t="s">
+        <v>50</v>
+      </c>
+      <c r="G39">
+        <v>0.01</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="C40" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="D40" t="s">
-        <v>76</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="E40" t="s">
+        <v>217</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
+      <c r="K40" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="O40" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>142</v>
+        <v>108</v>
       </c>
       <c r="B41" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D41" t="s">
-        <v>76</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="E41" t="s">
+        <v>217</v>
+      </c>
+      <c r="G41" s="2">
+        <v>37</v>
+      </c>
+      <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="N41" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K41" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="O41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="B42" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="C42" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="D42" t="s">
-        <v>76</v>
-      </c>
-      <c r="I42" s="2">
+        <v>68</v>
+      </c>
+      <c r="E42" t="s">
+        <v>217</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1.33E-6</v>
+      </c>
+      <c r="H42" s="1"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="O42" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>88</v>
+      </c>
+      <c r="B43" t="s">
+        <v>187</v>
+      </c>
+      <c r="C43" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" t="s">
+        <v>68</v>
+      </c>
+      <c r="E43" t="s">
+        <v>219</v>
+      </c>
+      <c r="F43" t="s">
+        <v>50</v>
+      </c>
+      <c r="G43" s="3">
         <v>1</v>
       </c>
-      <c r="J42" s="2">
-        <v>110</v>
-      </c>
-      <c r="K42" s="2"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A43" t="s">
-        <v>156</v>
-      </c>
-      <c r="B43" t="s">
-        <v>157</v>
-      </c>
-      <c r="C43" t="s">
-        <v>51</v>
-      </c>
-      <c r="D43" t="s">
-        <v>76</v>
+      <c r="H43">
+        <v>0.1</v>
       </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K43" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="N43" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C44" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="D44" t="s">
-        <v>76</v>
+        <v>68</v>
+      </c>
+      <c r="E44" t="s">
+        <v>219</v>
+      </c>
+      <c r="F44" t="s">
+        <v>50</v>
+      </c>
+      <c r="G44" s="3">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>0.12</v>
       </c>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
+      <c r="K44" s="2" t="s">
+        <v>188</v>
+      </c>
       <c r="O44" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>154</v>
+        <v>85</v>
       </c>
       <c r="B45" t="s">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="C45" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="D45" t="s">
-        <v>76</v>
+        <v>68</v>
+      </c>
+      <c r="E45" t="s">
+        <v>219</v>
+      </c>
+      <c r="F45" t="s">
+        <v>50</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>0.1</v>
       </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K45" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="M45" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>160</v>
+        <v>61</v>
       </c>
       <c r="B46" t="s">
-        <v>161</v>
+        <v>62</v>
       </c>
       <c r="C46" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D46" t="s">
-        <v>76</v>
-      </c>
-      <c r="I46" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0.1</v>
+      </c>
       <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K46" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="P46" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="B47" t="s">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="C47" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D47" t="s">
-        <v>76</v>
-      </c>
-      <c r="I47" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="I47" s="2">
+        <v>0.1</v>
+      </c>
       <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K47" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="P47" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B48" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C48" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" t="s">
         <v>63</v>
-      </c>
-      <c r="D48" t="s">
-        <v>76</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" t="s">
-        <v>117</v>
-      </c>
-      <c r="M48" t="s">
-        <v>55</v>
-      </c>
-      <c r="N48" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K48" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="O48" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B49" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="D49" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K49" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="O49" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="B50" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="C50" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D50" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K50" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="M50" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="B51" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C51" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="D51" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="L51" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K51" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="N51" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B52" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D52" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="M52" t="s">
-        <v>55</v>
-      </c>
-      <c r="N52" t="s">
-        <v>55</v>
+      <c r="K52" s="2" t="s">
+        <v>214</v>
       </c>
       <c r="O52" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B53" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C53" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D53" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="N53" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K53" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="M53" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>150</v>
+        <v>103</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="C54" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="D54" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
+      <c r="K54" s="2" t="s">
+        <v>214</v>
+      </c>
       <c r="O54" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="B55" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="C55" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D55" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-      <c r="M55" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A56" s="4" t="s">
-        <v>178</v>
+      <c r="K55" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="N55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>74</v>
+      </c>
+      <c r="B56" t="s">
+        <v>75</v>
+      </c>
+      <c r="C56" t="s">
+        <v>76</v>
       </c>
       <c r="D56" t="s">
-        <v>52</v>
-      </c>
-      <c r="E56" t="s">
+        <v>63</v>
+      </c>
+      <c r="I56" s="2">
+        <v>1</v>
+      </c>
+      <c r="J56" s="2">
+        <v>110</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>139</v>
+      </c>
+      <c r="B57" t="s">
+        <v>140</v>
+      </c>
+      <c r="C57" t="s">
+        <v>47</v>
+      </c>
+      <c r="D57" t="s">
+        <v>63</v>
+      </c>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="L57" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>106</v>
+      </c>
+      <c r="B58" t="s">
+        <v>107</v>
+      </c>
+      <c r="C58" t="s">
+        <v>47</v>
+      </c>
+      <c r="D58" t="s">
+        <v>63</v>
+      </c>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="O58" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>137</v>
+      </c>
+      <c r="B59" t="s">
+        <v>138</v>
+      </c>
+      <c r="C59" t="s">
+        <v>47</v>
+      </c>
+      <c r="D59" t="s">
+        <v>63</v>
+      </c>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="L59" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>143</v>
+      </c>
+      <c r="B60" t="s">
+        <v>144</v>
+      </c>
+      <c r="C60" t="s">
+        <v>47</v>
+      </c>
+      <c r="D60" t="s">
+        <v>63</v>
+      </c>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="L60" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>141</v>
+      </c>
+      <c r="B61" t="s">
+        <v>142</v>
+      </c>
+      <c r="C61" t="s">
+        <v>47</v>
+      </c>
+      <c r="D61" t="s">
+        <v>63</v>
+      </c>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="L61" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>102</v>
+      </c>
+      <c r="B62" t="s">
+        <v>191</v>
+      </c>
+      <c r="C62" t="s">
         <v>53</v>
       </c>
-      <c r="K56" s="2"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A57" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="D57" t="s">
-        <v>52</v>
-      </c>
-      <c r="E57" t="s">
-        <v>53</v>
-      </c>
-      <c r="K57" s="2"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A58" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D58" t="s">
-        <v>52</v>
-      </c>
-      <c r="E58" t="s">
-        <v>53</v>
-      </c>
-      <c r="K58" s="2"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A59" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D59" t="s">
-        <v>52</v>
-      </c>
-      <c r="E59" t="s">
-        <v>53</v>
-      </c>
-      <c r="K59" s="2"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A60" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D60" t="s">
-        <v>52</v>
-      </c>
-      <c r="E60" t="s">
-        <v>53</v>
-      </c>
-      <c r="K60" s="2"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A61" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D61" t="s">
-        <v>52</v>
-      </c>
-      <c r="E61" t="s">
-        <v>53</v>
-      </c>
-      <c r="K61" s="2"/>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A62" s="4" t="s">
-        <v>185</v>
-      </c>
       <c r="D62" t="s">
-        <v>52</v>
-      </c>
-      <c r="E62" t="s">
-        <v>53</v>
-      </c>
-      <c r="K62" s="2"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A63" s="4" t="s">
-        <v>186</v>
+        <v>63</v>
+      </c>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="L62" t="s">
+        <v>101</v>
+      </c>
+      <c r="M62" t="s">
+        <v>49</v>
+      </c>
+      <c r="N62" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>100</v>
+      </c>
+      <c r="B63" t="s">
+        <v>189</v>
+      </c>
+      <c r="C63" t="s">
+        <v>87</v>
       </c>
       <c r="D63" t="s">
-        <v>52</v>
-      </c>
-      <c r="E63" t="s">
-        <v>53</v>
-      </c>
-      <c r="K63" s="2"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A64" s="4" t="s">
-        <v>181</v>
+        <v>63</v>
+      </c>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="L63" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>147</v>
+      </c>
+      <c r="B64" t="s">
+        <v>148</v>
+      </c>
+      <c r="C64" t="s">
+        <v>47</v>
       </c>
       <c r="D64" t="s">
-        <v>52</v>
-      </c>
-      <c r="E64" t="s">
-        <v>53</v>
-      </c>
-      <c r="K64" s="2"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A65" s="4" t="s">
-        <v>182</v>
+        <v>63</v>
+      </c>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="L64" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>145</v>
+      </c>
+      <c r="B65" t="s">
+        <v>146</v>
+      </c>
+      <c r="C65" t="s">
+        <v>47</v>
       </c>
       <c r="D65" t="s">
-        <v>52</v>
-      </c>
-      <c r="E65" t="s">
-        <v>53</v>
-      </c>
-      <c r="K65" s="2"/>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A66" s="4" t="s">
-        <v>187</v>
+        <v>63</v>
+      </c>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="L65" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>135</v>
+      </c>
+      <c r="B66" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66" t="s">
+        <v>87</v>
       </c>
       <c r="D66" t="s">
-        <v>52</v>
-      </c>
-      <c r="E66" t="s">
-        <v>53</v>
-      </c>
-      <c r="K66" s="2"/>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A67" s="4" t="s">
-        <v>188</v>
+        <v>63</v>
+      </c>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="M66" t="s">
+        <v>49</v>
+      </c>
+      <c r="N66" t="s">
+        <v>49</v>
+      </c>
+      <c r="O66" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" t="s">
+        <v>132</v>
+      </c>
+      <c r="C67" t="s">
+        <v>87</v>
       </c>
       <c r="D67" t="s">
-        <v>52</v>
-      </c>
-      <c r="E67" t="s">
-        <v>53</v>
-      </c>
-      <c r="K67" s="2"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A68" s="4" t="s">
-        <v>189</v>
+        <v>63</v>
+      </c>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="N67" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" t="s">
+        <v>134</v>
+      </c>
+      <c r="C68" t="s">
+        <v>87</v>
       </c>
       <c r="D68" t="s">
-        <v>52</v>
-      </c>
-      <c r="E68" t="s">
-        <v>53</v>
-      </c>
-      <c r="K68" s="2"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.15">
+        <v>63</v>
+      </c>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="O68" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>183</v>
+        <v>129</v>
+      </c>
+      <c r="B69" t="s">
+        <v>130</v>
+      </c>
+      <c r="C69" t="s">
+        <v>87</v>
       </c>
       <c r="D69" t="s">
-        <v>52</v>
-      </c>
-      <c r="E69" t="s">
-        <v>53</v>
-      </c>
-      <c r="K69" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="M69" t="s">
+        <v>101</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F55" xr:uid="{0C4D3287-2227-4749-A999-A3EC2866277F}">
-      <formula1>$R$1:$R$2</formula1>
+  <conditionalFormatting sqref="H1:H1048576 F1:F1048576">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$E1="deterministic"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F69" xr:uid="{0C4D3287-2227-4749-A999-A3EC2866277F}">
+      <formula1>"_stdev,_vc"</formula1>
     </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D2:D69" xr:uid="{AA09C33A-A013-4395-933B-875C1EC68FEA}">
+      <formula1>"Input,Constant,Calculated"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="E2:E45" xr:uid="{A46D7AB9-7C96-4620-B61F-7A7D97EDACC4}">
+      <formula1>"deterministic,normal,log_normal"</formula1>
+    </dataValidation>
+    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="E46:E69" xr:uid="{910AEE68-F2A4-46F1-9254-4E7A6B8B9583}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/workspaces/example_new_calculations/input/input.xlsx
+++ b/workspaces/example_new_calculations/input/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKL\Documents\Github\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0814C914-B6D6-4BA7-8C4A-A22C067F25B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9B8DC0-234B-48BC-A785-19CED76329CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-165" windowWidth="25440" windowHeight="15270" activeTab="3" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Uittredepunten" sheetId="4" r:id="rId2"/>
     <sheet name="Ondergrondscenarios" sheetId="3" r:id="rId3"/>
     <sheet name="Overzicht_variabelen" sheetId="2" r:id="rId4"/>
+    <sheet name="Settings" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="234">
   <si>
     <t>M_van</t>
   </si>
@@ -185,9 +186,6 @@
     <t>m</t>
   </si>
   <si>
-    <t>Input</t>
-  </si>
-  <si>
     <t>input</t>
   </si>
   <si>
@@ -230,9 +228,6 @@
     <t>Dikte van de cohesieve deklaag</t>
   </si>
   <si>
-    <t>Calculated</t>
-  </si>
-  <si>
     <t>d_deklaag_vak</t>
   </si>
   <si>
@@ -245,9 +240,6 @@
     <t>Volumegewicht van water</t>
   </si>
   <si>
-    <t>Constant</t>
-  </si>
-  <si>
     <t>kD_wvp</t>
   </si>
   <si>
@@ -699,13 +691,64 @@
   </si>
   <si>
     <t>log_normal</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>save_realizations</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>maximum_iterations</t>
+  </si>
+  <si>
+    <t>int / float</t>
+  </si>
+  <si>
+    <t>variation_coefficient</t>
+  </si>
+  <si>
+    <t>start_value</t>
+  </si>
+  <si>
+    <t>relaxation_factor</t>
+  </si>
+  <si>
+    <t>str</t>
+  </si>
+  <si>
+    <t>form</t>
+  </si>
+  <si>
+    <t>reliability_method</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>metadata</t>
+  </si>
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>constant</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="9"/>
       <color theme="1"/>
@@ -713,11 +756,26 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Verdana"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -749,22 +807,257 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{11010186-4FF4-48E2-AD4E-93BC10A29908}"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="42">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -873,7 +1166,7 @@
     <tableColumn id="10" xr3:uid="{30E95029-7E84-4404-97EA-CC899B222DC3}" name="Kolom10"/>
     <tableColumn id="11" xr3:uid="{21D2E504-CBB5-45F7-9119-E1DA7B53C2D5}" name="Kolom11"/>
     <tableColumn id="12" xr3:uid="{FF7176FB-923E-4ECE-83AA-046E768AD06C}" name="Kolom12"/>
-    <tableColumn id="14" xr3:uid="{4E1A767E-8059-4EF5-B52B-A1637577AFDF}" name="Kolom14" headerRowDxfId="8" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{4E1A767E-8059-4EF5-B52B-A1637577AFDF}" name="Kolom14" headerRowDxfId="41" dataDxfId="40"/>
     <tableColumn id="15" xr3:uid="{E12738E9-E3E4-4A5D-81C1-E333D11489B2}" name="Kolom15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -895,9 +1188,9 @@
     <tableColumn id="6" xr3:uid="{FA05A46A-DA45-4C6A-9D17-689A03B15BA8}" name="Kolom6"/>
     <tableColumn id="7" xr3:uid="{25871E16-DA07-4B31-A7EF-FBA1FEE488DB}" name="Kolom7"/>
     <tableColumn id="8" xr3:uid="{A229D98E-F2F0-4491-8C3C-1FB943EA5058}" name="Kolom8"/>
-    <tableColumn id="9" xr3:uid="{1FBE756B-5426-4436-B3C8-55410DF75FDB}" name="Kolom9" headerRowDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{B851468F-D94B-4F13-9CF8-13DADE13A2A8}" name="Kolom10" headerRowDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{41B8BB8E-854F-4E90-B76F-4066FB0CA9A2}" name="Kolom11" headerRowDxfId="4" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{1FBE756B-5426-4436-B3C8-55410DF75FDB}" name="Kolom9" headerRowDxfId="39"/>
+    <tableColumn id="10" xr3:uid="{B851468F-D94B-4F13-9CF8-13DADE13A2A8}" name="Kolom10" headerRowDxfId="38"/>
+    <tableColumn id="11" xr3:uid="{41B8BB8E-854F-4E90-B76F-4066FB0CA9A2}" name="Kolom11" headerRowDxfId="37" dataDxfId="36"/>
     <tableColumn id="12" xr3:uid="{E7B2F49E-191F-4D24-8883-DCCF4F196399}" name="Kolom12"/>
     <tableColumn id="13" xr3:uid="{1DB6223F-5250-48AD-B68D-FD511FFC8150}" name="Kolom13"/>
     <tableColumn id="14" xr3:uid="{B2104B25-DEBD-4E44-A26A-46A71C2A832D}" name="Kolom14"/>
@@ -1242,10 +1535,10 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>0</v>
@@ -1254,7 +1547,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>2</v>
@@ -1622,25 +1915,25 @@
   <sheetData>
     <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>164</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>15</v>
@@ -1652,7 +1945,7 @@
         <v>17</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>18</v>
@@ -6180,16 +6473,16 @@
   <sheetData>
     <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>39</v>
@@ -8262,7 +8555,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B7A8CE-63DA-4EEA-9A88-5E62FD2B5E40}">
-  <dimension ref="A1:R69"/>
+  <dimension ref="A1:P69"/>
   <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
@@ -8283,69 +8576,66 @@
   <sheetData>
     <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="F1" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -8353,19 +8643,16 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -8377,13 +8664,10 @@
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -8395,13 +8679,10 @@
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -8409,19 +8690,16 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -8429,19 +8707,16 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B7" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C7" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -8449,19 +8724,16 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B8" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -8469,19 +8741,16 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -8489,19 +8758,16 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -8509,17 +8775,14 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -8527,17 +8790,14 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -8545,19 +8805,16 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C13" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -8565,19 +8822,16 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C14" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -8585,22 +8839,26 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E15" t="s">
-        <v>217</v>
-      </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1</v>
+      </c>
       <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
@@ -8608,115 +8866,115 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E16" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P16" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E17" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E18" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
         <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E19" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I19" s="2">
         <v>1.5</v>
@@ -8725,30 +8983,30 @@
         <v>60</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="O19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
         <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E20" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I20" s="1">
         <v>1.4999999999999999E-4</v>
@@ -8757,33 +9015,33 @@
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="O20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P20" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
         <v>58</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>59</v>
       </c>
-      <c r="C21" t="s">
-        <v>60</v>
-      </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E21" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I21" s="2">
         <v>10</v>
@@ -8792,27 +9050,27 @@
         <v>22</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E22" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I22" s="2">
         <v>1.5</v>
@@ -8821,19 +9079,19 @@
         <v>4000</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
@@ -8841,16 +9099,16 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C23" t="s">
         <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E23" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I23" s="2">
         <v>0</v>
@@ -8859,16 +9117,16 @@
         <v>5000</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
@@ -8876,32 +9134,32 @@
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C24" t="s">
         <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E24" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I24" s="2">
         <v>0</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="L24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
@@ -8909,35 +9167,35 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C25" t="s">
         <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E25" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I25" s="2">
         <v>0</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="L25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
@@ -8945,16 +9203,16 @@
         <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C26" t="s">
         <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E26" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I26" s="2">
         <v>5</v>
@@ -8963,19 +9221,19 @@
         <v>2000</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="L26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
@@ -8983,21 +9241,21 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E27" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
@@ -9005,16 +9263,16 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E28" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I28" s="2">
         <v>-4</v>
@@ -9023,10 +9281,10 @@
         <v>15</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
@@ -9034,53 +9292,53 @@
         <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E29" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="L29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" t="s">
         <v>55</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E30" t="s">
         <v>56</v>
       </c>
-      <c r="C30" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" t="s">
-        <v>57</v>
-      </c>
       <c r="F30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I30" s="2">
         <v>-18</v>
@@ -9089,27 +9347,27 @@
         <v>15</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="O30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s">
         <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="E31" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G31" s="1">
         <v>2.0799999999999999E-4</v>
@@ -9118,27 +9376,27 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D32" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="E32" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G32">
         <v>0.25</v>
@@ -9146,24 +9404,24 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="E33" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G33">
         <v>9.81</v>
@@ -9171,27 +9429,27 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D34" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="E34" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G34" s="2">
         <v>26</v>
@@ -9200,27 +9458,27 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D35" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="E35" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G35">
         <v>9.81</v>
@@ -9228,50 +9486,50 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B36" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C36" t="s">
         <v>47</v>
       </c>
       <c r="D36" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="E36" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G36">
         <v>1.5</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D37" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="E37" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G37" s="2">
         <v>0.5</v>
@@ -9282,79 +9540,79 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B38" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C38" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D38" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="E38" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G38">
         <v>0.1</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B39" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C39" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D39" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="E39" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G39">
         <v>0.01</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D40" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="E40" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G40" s="2">
         <v>0.3</v>
@@ -9363,27 +9621,27 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B41" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C41" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D41" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="E41" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G41" s="2">
         <v>37</v>
@@ -9392,27 +9650,27 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C42" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D42" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="E42" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G42" s="1">
         <v>1.33E-6</v>
@@ -9421,30 +9679,30 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B43" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C43" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D43" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="E43" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G43" s="3">
         <v>1</v>
@@ -9455,30 +9713,30 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="N43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B44" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D44" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="E44" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G44" s="3">
         <v>1</v>
@@ -9489,30 +9747,30 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B45" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C45" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D45" t="s">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="E45" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G45" s="3">
         <v>1</v>
@@ -9523,574 +9781,580 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="M45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" t="s">
         <v>61</v>
-      </c>
-      <c r="B46" t="s">
-        <v>62</v>
       </c>
       <c r="C46" t="s">
         <v>47</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
-      </c>
-      <c r="I46" s="2">
-        <v>0.1</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P46" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C47" t="s">
         <v>47</v>
       </c>
       <c r="D47" t="s">
-        <v>63</v>
-      </c>
-      <c r="I47" s="2">
-        <v>0.1</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P47" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B48" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C48" t="s">
         <v>47</v>
       </c>
       <c r="D48" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O48" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B49" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C49" t="s">
         <v>47</v>
       </c>
       <c r="D49" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O49" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B50" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C50" t="s">
         <v>47</v>
       </c>
       <c r="D50" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M50" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B51" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C51" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N51" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B52" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C52" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D52" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O52" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C53" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D53" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M53" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D54" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O54" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C55" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D55" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N55" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
-      </c>
-      <c r="I56" s="2">
-        <v>1</v>
-      </c>
-      <c r="J56" s="2">
-        <v>110</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B57" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C57" t="s">
         <v>47</v>
       </c>
       <c r="D57" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L57" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B58" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C58" t="s">
         <v>47</v>
       </c>
       <c r="D58" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O58" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C59" t="s">
         <v>47</v>
       </c>
       <c r="D59" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L59" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B60" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C60" t="s">
         <v>47</v>
       </c>
       <c r="D60" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L60" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B61" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C61" t="s">
         <v>47</v>
       </c>
       <c r="D61" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L61" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>99</v>
+      </c>
+      <c r="B62" t="s">
+        <v>188</v>
+      </c>
+      <c r="C62" t="s">
+        <v>52</v>
+      </c>
+      <c r="D62" t="s">
         <v>102</v>
-      </c>
-      <c r="B62" t="s">
-        <v>191</v>
-      </c>
-      <c r="C62" t="s">
-        <v>53</v>
-      </c>
-      <c r="D62" t="s">
-        <v>63</v>
       </c>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L62" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M62" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N62" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B63" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C63" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D63" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L63" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B64" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C64" t="s">
         <v>47</v>
       </c>
       <c r="D64" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L64" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B65" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C65" t="s">
         <v>47</v>
       </c>
       <c r="D65" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="L65" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B66" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C66" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D66" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M66" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N66" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O66" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B67" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C67" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D67" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N67" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B68" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C68" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D68" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O68" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B69" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C69" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D69" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M69" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H1:H1048576 F1:F1048576">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$E1="deterministic"</formula>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="expression" dxfId="15" priority="2">
+      <formula>OR($D1="metadata", $D1="calculated")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <conditionalFormatting sqref="F1:F69">
+    <cfRule type="expression" dxfId="14" priority="4">
+      <formula>OR($E1="deterministic", ISBLANK($E1))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:H69">
+    <cfRule type="expression" dxfId="13" priority="3">
+      <formula>$D2&lt;&gt;"constant"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:J69">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>AND($D2&lt;&gt;"variable",$D2&lt;&gt;"constant")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F69" xr:uid="{0C4D3287-2227-4749-A999-A3EC2866277F}">
       <formula1>"_stdev,_vc"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D2:D69" xr:uid="{AA09C33A-A013-4395-933B-875C1EC68FEA}">
-      <formula1>"Input,Constant,Calculated"</formula1>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{7DBF22A6-4D9E-4F91-90D4-678B52A281D8}">
+      <formula1>"metadata,variable,constant,calculated"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="E2:E45" xr:uid="{A46D7AB9-7C96-4620-B61F-7A7D97EDACC4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E69" xr:uid="{275783A2-AEC2-4F92-8AAF-45A3C5FDAAC7}">
       <formula1>"deterministic,normal,log_normal"</formula1>
     </dataValidation>
-    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="E46:E69" xr:uid="{910AEE68-F2A4-46F1-9254-4E7A6B8B9583}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10098,4 +10362,109 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7FD5E8-359B-4F56-B38E-FCA72B85D698}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.796875" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4" s="7">
+        <v>0</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B6" s="7">
+        <v>100</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B7" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6" xr:uid="{94AA1909-8159-4ABD-8194-E5CC31B00066}">
+      <formula1>AND(ISNUMBER(B6),B6=INT(B6))</formula1>
+    </dataValidation>
+    <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" sqref="B3:B5" xr:uid="{0F940659-071E-4396-94AE-334C05124B18}">
+      <formula1>ISNUMBER(B3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{73A82C8D-457E-4F26-8920-E365EC9333FD}">
+      <formula1>"form,numerical_integration,crude_monte_carlo,importance_sampling,directional_sampling,subset_simulation,numerical_bisection,latin_hypercube,cobyla_reliability,form_then_directional_sampling,directional_sampling_then_form"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{05F071D7-CE12-4A8B-B2AB-37DFC65D1C77}">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/workspaces/example_new_calculations/input/input.xlsx
+++ b/workspaces/example_new_calculations/input/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKL\Documents\Github\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9B8DC0-234B-48BC-A785-19CED76329CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A649AE8-E2B8-467A-841A-3324CE662DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-165" windowWidth="25440" windowHeight="15270" activeTab="3" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Vakken" sheetId="1" r:id="rId1"/>
     <sheet name="Uittredepunten" sheetId="4" r:id="rId2"/>
     <sheet name="Ondergrondscenarios" sheetId="3" r:id="rId3"/>
-    <sheet name="Overzicht_variabelen" sheetId="2" r:id="rId4"/>
+    <sheet name="Overzicht_parameters" sheetId="2" r:id="rId4"/>
     <sheet name="Settings" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -552,33 +552,6 @@
     <t>ondergrondscenario_kans</t>
   </si>
   <si>
-    <t>variable_description</t>
-  </si>
-  <si>
-    <t>variable_unit</t>
-  </si>
-  <si>
-    <t>variable_type</t>
-  </si>
-  <si>
-    <t>variable_distribution</t>
-  </si>
-  <si>
-    <t>variable_default_value_mean</t>
-  </si>
-  <si>
-    <t>variable_default_value_stdev</t>
-  </si>
-  <si>
-    <t>variable_mean_lower_bound</t>
-  </si>
-  <si>
-    <t>variable_mean_upper_bound</t>
-  </si>
-  <si>
-    <t>variable_member_of</t>
-  </si>
-  <si>
     <t>potentiaalberekening</t>
   </si>
   <si>
@@ -678,12 +651,6 @@
     <t>Calculated variables</t>
   </si>
   <si>
-    <t>variable_name</t>
-  </si>
-  <si>
-    <t>variable_spreidingstype</t>
-  </si>
-  <si>
     <t>deterministic</t>
   </si>
   <si>
@@ -742,6 +709,39 @@
   </si>
   <si>
     <t>constant</t>
+  </si>
+  <si>
+    <t>parameter_description</t>
+  </si>
+  <si>
+    <t>parameter_unit</t>
+  </si>
+  <si>
+    <t>parameter_type</t>
+  </si>
+  <si>
+    <t>parameter_distribution</t>
+  </si>
+  <si>
+    <t>parameter_spreidingstype</t>
+  </si>
+  <si>
+    <t>parameter_default_value_mean</t>
+  </si>
+  <si>
+    <t>parameter_default_value_stdev</t>
+  </si>
+  <si>
+    <t>parameter_mean_lower_bound</t>
+  </si>
+  <si>
+    <t>parameter_mean_upper_bound</t>
+  </si>
+  <si>
+    <t>parameter_member_of</t>
+  </si>
+  <si>
+    <t>parameter_name</t>
   </si>
 </sst>
 </file>
@@ -826,231 +826,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{11010186-4FF4-48E2-AD4E-93BC10A29908}"/>
   </cellStyles>
-  <dxfs count="42">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill>
@@ -1132,8 +908,8 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D6DB1DEC-E085-4F6B-B7C4-D4E6DD7E1A8E}" name="Tabel9" displayName="Tabel9" ref="A2:N103" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{5EE94583-3EBC-4D61-9BDE-C9E94899637C}" name="Kolom1"/>
     <tableColumn id="2" xr3:uid="{8990A576-5075-4246-8F9A-BA6C41A7A01C}" name="Kolom2"/>
+    <tableColumn id="15" xr3:uid="{5ACFB144-9626-4B12-88BF-8A0D8D4CFFEC}" name="Column1"/>
     <tableColumn id="3" xr3:uid="{49D363D0-5442-4E42-91BC-AD82E3246FFD}" name="Kolom3"/>
     <tableColumn id="4" xr3:uid="{2B5B55CC-C9C3-42B2-9AFA-CB70AF604173}" name="Kolom4"/>
     <tableColumn id="5" xr3:uid="{AA47A627-CE95-4D80-9EBB-2C3556F0D6AE}" name="Kolom5"/>
@@ -1154,8 +930,8 @@
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9844274D-7B34-420F-9662-89C5C9A298BD}" name="Tabel10" displayName="Tabel10" ref="A2:N55" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{849DD8E4-53A6-4E3D-B1F9-91F33ED43571}" name="Kolom1"/>
     <tableColumn id="2" xr3:uid="{E80206AD-C5FD-4475-B5E4-08A08DA66E4A}" name="Kolom2"/>
+    <tableColumn id="13" xr3:uid="{39F38892-EB92-4E2D-A4CE-461B1DC8B27E}" name="Column1"/>
     <tableColumn id="3" xr3:uid="{1769008F-0E39-48C3-B6C5-959D62F52592}" name="Kolom3"/>
     <tableColumn id="4" xr3:uid="{DFE5E45D-588E-4E07-BEFE-30F8B98F73E8}" name="Kolom4"/>
     <tableColumn id="5" xr3:uid="{D8D86CD9-C3BF-42A4-A962-B1DB26AE3B59}" name="Kolom5"/>
@@ -1166,7 +942,7 @@
     <tableColumn id="10" xr3:uid="{30E95029-7E84-4404-97EA-CC899B222DC3}" name="Kolom10"/>
     <tableColumn id="11" xr3:uid="{21D2E504-CBB5-45F7-9119-E1DA7B53C2D5}" name="Kolom11"/>
     <tableColumn id="12" xr3:uid="{FF7176FB-923E-4ECE-83AA-046E768AD06C}" name="Kolom12"/>
-    <tableColumn id="14" xr3:uid="{4E1A767E-8059-4EF5-B52B-A1637577AFDF}" name="Kolom14" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="14" xr3:uid="{4E1A767E-8059-4EF5-B52B-A1637577AFDF}" name="Kolom14" headerRowDxfId="9" dataDxfId="8"/>
     <tableColumn id="15" xr3:uid="{E12738E9-E3E4-4A5D-81C1-E333D11489B2}" name="Kolom15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1188,9 +964,9 @@
     <tableColumn id="6" xr3:uid="{FA05A46A-DA45-4C6A-9D17-689A03B15BA8}" name="Kolom6"/>
     <tableColumn id="7" xr3:uid="{25871E16-DA07-4B31-A7EF-FBA1FEE488DB}" name="Kolom7"/>
     <tableColumn id="8" xr3:uid="{A229D98E-F2F0-4491-8C3C-1FB943EA5058}" name="Kolom8"/>
-    <tableColumn id="9" xr3:uid="{1FBE756B-5426-4436-B3C8-55410DF75FDB}" name="Kolom9" headerRowDxfId="39"/>
-    <tableColumn id="10" xr3:uid="{B851468F-D94B-4F13-9CF8-13DADE13A2A8}" name="Kolom10" headerRowDxfId="38"/>
-    <tableColumn id="11" xr3:uid="{41B8BB8E-854F-4E90-B76F-4066FB0CA9A2}" name="Kolom11" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{1FBE756B-5426-4436-B3C8-55410DF75FDB}" name="Kolom9" headerRowDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{B851468F-D94B-4F13-9CF8-13DADE13A2A8}" name="Kolom10" headerRowDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{41B8BB8E-854F-4E90-B76F-4066FB0CA9A2}" name="Kolom11" headerRowDxfId="5" dataDxfId="4"/>
     <tableColumn id="12" xr3:uid="{E7B2F49E-191F-4D24-8883-DCCF4F196399}" name="Kolom12"/>
     <tableColumn id="13" xr3:uid="{1DB6223F-5250-48AD-B68D-FD511FFC8150}" name="Kolom13"/>
     <tableColumn id="14" xr3:uid="{B2104B25-DEBD-4E44-A26A-46A71C2A832D}" name="Kolom14"/>
@@ -1559,14 +1335,14 @@
         <v>4</v>
       </c>
       <c r="I1" s="4" t="str">
-        <f>LEFT(H1,LEN(H1)-5)&amp;VLOOKUP(LEFT(H1,LEN(H1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
+        <f>LEFT(H1,LEN(H1)-5)&amp;VLOOKUP(LEFT(H1,LEN(H1)-5),Overzicht_parameters!$A$2:$F$69,6,(FALSE))</f>
         <v>c_voorland_stdev</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="K1" s="4" t="str">
-        <f>LEFT(J1,LEN(J1)-5)&amp;VLOOKUP(LEFT(J1,LEN(J1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
+        <f>LEFT(J1,LEN(J1)-5)&amp;VLOOKUP(LEFT(J1,LEN(J1)-5),Overzicht_parameters!$A$2:$F$69,6,(FALSE))</f>
         <v>c_achterland_vc</v>
       </c>
     </row>
@@ -1898,8 +1674,8 @@
   <dimension ref="A1:N103"/>
   <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.3984375" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3984375" customWidth="1"/>
     <col min="3" max="4" width="19.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.8984375" bestFit="1" customWidth="1"/>
@@ -1915,10 +1691,10 @@
   <sheetData>
     <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>164</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>165</v>
@@ -2003,10 +1779,10 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
         <v>3</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
       </c>
       <c r="C3">
         <v>188488.46799999999</v>
@@ -2047,10 +1823,10 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
         <v>4</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
       </c>
       <c r="C4">
         <v>188448.99600000001</v>
@@ -2135,10 +1911,10 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
         <v>4</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
       </c>
       <c r="C6">
         <v>188460.43700000001</v>
@@ -2179,10 +1955,10 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
         <v>5</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
       </c>
       <c r="C7">
         <v>188355.46400000001</v>
@@ -2223,10 +1999,10 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
         <v>5</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
       </c>
       <c r="C8">
         <v>188366.61900000001</v>
@@ -2267,10 +2043,10 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
         <v>5</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
       </c>
       <c r="C9">
         <v>188341.16200000001</v>
@@ -2311,10 +2087,10 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
         <v>5</v>
-      </c>
-      <c r="B10">
-        <v>9</v>
       </c>
       <c r="C10">
         <v>188313.13099999999</v>
@@ -2355,10 +2131,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
         <v>5</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
       </c>
       <c r="C11">
         <v>188258.785</v>
@@ -2399,10 +2175,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
         <v>5</v>
-      </c>
-      <c r="B12">
-        <v>11</v>
       </c>
       <c r="C12">
         <v>188206.155</v>
@@ -2443,10 +2219,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
         <v>5</v>
-      </c>
-      <c r="B13">
-        <v>12</v>
       </c>
       <c r="C13">
         <v>188203.97399999999</v>
@@ -2487,10 +2263,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
         <v>5</v>
-      </c>
-      <c r="B14">
-        <v>13</v>
       </c>
       <c r="C14">
         <v>188152.57800000001</v>
@@ -2531,10 +2307,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
         <v>5</v>
-      </c>
-      <c r="B15">
-        <v>14</v>
       </c>
       <c r="C15">
         <v>188093.584</v>
@@ -2575,10 +2351,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
         <v>5</v>
-      </c>
-      <c r="B16">
-        <v>15</v>
       </c>
       <c r="C16">
         <v>188092.655</v>
@@ -2619,10 +2395,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
         <v>6</v>
-      </c>
-      <c r="B17">
-        <v>16</v>
       </c>
       <c r="C17">
         <v>188069.57399999999</v>
@@ -2663,10 +2439,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
         <v>6</v>
-      </c>
-      <c r="B18">
-        <v>17</v>
       </c>
       <c r="C18">
         <v>188060.905</v>
@@ -2707,10 +2483,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
         <v>6</v>
-      </c>
-      <c r="B19">
-        <v>18</v>
       </c>
       <c r="C19">
         <v>188054.845</v>
@@ -2751,10 +2527,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
         <v>6</v>
-      </c>
-      <c r="B20">
-        <v>19</v>
       </c>
       <c r="C20">
         <v>188026.242</v>
@@ -2795,10 +2571,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
         <v>6</v>
-      </c>
-      <c r="B21">
-        <v>20</v>
       </c>
       <c r="C21">
         <v>188013.084</v>
@@ -2839,10 +2615,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
         <v>6</v>
-      </c>
-      <c r="B22">
-        <v>21</v>
       </c>
       <c r="C22">
         <v>188011.78200000001</v>
@@ -2883,10 +2659,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
         <v>6</v>
-      </c>
-      <c r="B23">
-        <v>22</v>
       </c>
       <c r="C23">
         <v>188019.50599999999</v>
@@ -2927,10 +2703,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
         <v>6</v>
-      </c>
-      <c r="B24">
-        <v>23</v>
       </c>
       <c r="C24">
         <v>187979.166</v>
@@ -2971,10 +2747,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
         <v>6</v>
-      </c>
-      <c r="B25">
-        <v>24</v>
       </c>
       <c r="C25">
         <v>187970.318</v>
@@ -3015,10 +2791,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
         <v>7</v>
-      </c>
-      <c r="B26">
-        <v>25</v>
       </c>
       <c r="C26">
         <v>187970.318</v>
@@ -3059,10 +2835,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
         <v>7</v>
-      </c>
-      <c r="B27">
-        <v>26</v>
       </c>
       <c r="C27">
         <v>187965.96900000001</v>
@@ -3103,10 +2879,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
         <v>7</v>
-      </c>
-      <c r="B28">
-        <v>27</v>
       </c>
       <c r="C28">
         <v>187943.85</v>
@@ -3147,10 +2923,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
         <v>7</v>
-      </c>
-      <c r="B29">
-        <v>28</v>
       </c>
       <c r="C29">
         <v>187930.42800000001</v>
@@ -3191,10 +2967,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
         <v>7</v>
-      </c>
-      <c r="B30">
-        <v>29</v>
       </c>
       <c r="C30">
         <v>187962.89499999999</v>
@@ -3235,10 +3011,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
         <v>7</v>
-      </c>
-      <c r="B31">
-        <v>30</v>
       </c>
       <c r="C31">
         <v>187947.299</v>
@@ -3279,10 +3055,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
         <v>7</v>
-      </c>
-      <c r="B32">
-        <v>31</v>
       </c>
       <c r="C32">
         <v>187929.45300000001</v>
@@ -3323,10 +3099,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
         <v>7</v>
-      </c>
-      <c r="B33">
-        <v>32</v>
       </c>
       <c r="C33">
         <v>187903.32800000001</v>
@@ -3367,10 +3143,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
         <v>7</v>
-      </c>
-      <c r="B34">
-        <v>33</v>
       </c>
       <c r="C34">
         <v>187892.783</v>
@@ -3411,10 +3187,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
         <v>7</v>
-      </c>
-      <c r="B35">
-        <v>34</v>
       </c>
       <c r="C35">
         <v>187910.39799999999</v>
@@ -3455,10 +3231,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
         <v>7</v>
-      </c>
-      <c r="B36">
-        <v>35</v>
       </c>
       <c r="C36">
         <v>187875.76699999999</v>
@@ -3499,10 +3275,10 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
         <v>7</v>
-      </c>
-      <c r="B37">
-        <v>36</v>
       </c>
       <c r="C37">
         <v>187856.35500000001</v>
@@ -3543,10 +3319,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
         <v>7</v>
-      </c>
-      <c r="B38">
-        <v>37</v>
       </c>
       <c r="C38">
         <v>187839.81899999999</v>
@@ -3587,10 +3363,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
         <v>7</v>
-      </c>
-      <c r="B39">
-        <v>38</v>
       </c>
       <c r="C39">
         <v>187824.12100000001</v>
@@ -3631,10 +3407,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
         <v>7</v>
-      </c>
-      <c r="B40">
-        <v>39</v>
       </c>
       <c r="C40">
         <v>187808.06400000001</v>
@@ -3675,10 +3451,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
         <v>8</v>
-      </c>
-      <c r="B41">
-        <v>40</v>
       </c>
       <c r="C41">
         <v>187750.77100000001</v>
@@ -3719,10 +3495,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
         <v>8</v>
-      </c>
-      <c r="B42">
-        <v>41</v>
       </c>
       <c r="C42">
         <v>187736.166</v>
@@ -3763,10 +3539,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
         <v>8</v>
-      </c>
-      <c r="B43">
-        <v>42</v>
       </c>
       <c r="C43">
         <v>187723.80900000001</v>
@@ -3807,10 +3583,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
         <v>8</v>
-      </c>
-      <c r="B44">
-        <v>43</v>
       </c>
       <c r="C44">
         <v>187713.13699999999</v>
@@ -3851,10 +3627,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
         <v>8</v>
-      </c>
-      <c r="B45">
-        <v>44</v>
       </c>
       <c r="C45">
         <v>187704.89799999999</v>
@@ -3895,10 +3671,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
         <v>8</v>
-      </c>
-      <c r="B46">
-        <v>45</v>
       </c>
       <c r="C46">
         <v>187697.035</v>
@@ -3939,10 +3715,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
         <v>8</v>
-      </c>
-      <c r="B47">
-        <v>46</v>
       </c>
       <c r="C47">
         <v>187786.01500000001</v>
@@ -3983,10 +3759,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
         <v>8</v>
-      </c>
-      <c r="B48">
-        <v>47</v>
       </c>
       <c r="C48">
         <v>187769.59899999999</v>
@@ -4027,10 +3803,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
         <v>8</v>
-      </c>
-      <c r="B49">
-        <v>48</v>
       </c>
       <c r="C49">
         <v>187751.864</v>
@@ -4071,10 +3847,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
         <v>8</v>
-      </c>
-      <c r="B50">
-        <v>49</v>
       </c>
       <c r="C50">
         <v>187736.109</v>
@@ -4115,10 +3891,10 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
         <v>8</v>
-      </c>
-      <c r="B51">
-        <v>50</v>
       </c>
       <c r="C51">
         <v>187715.633</v>
@@ -4159,10 +3935,10 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
         <v>8</v>
-      </c>
-      <c r="B52">
-        <v>51</v>
       </c>
       <c r="C52">
         <v>187695.693</v>
@@ -4203,10 +3979,10 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
         <v>8</v>
-      </c>
-      <c r="B53">
-        <v>52</v>
       </c>
       <c r="C53">
         <v>187693.02799999999</v>
@@ -4247,10 +4023,10 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
         <v>8</v>
-      </c>
-      <c r="B54">
-        <v>53</v>
       </c>
       <c r="C54">
         <v>187731.97200000001</v>
@@ -4291,10 +4067,10 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
         <v>8</v>
-      </c>
-      <c r="B55">
-        <v>54</v>
       </c>
       <c r="C55">
         <v>187712.56</v>
@@ -4335,10 +4111,10 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
         <v>8</v>
-      </c>
-      <c r="B56">
-        <v>55</v>
       </c>
       <c r="C56">
         <v>187746.11199999999</v>
@@ -4379,10 +4155,10 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
         <v>8</v>
-      </c>
-      <c r="B57">
-        <v>56</v>
       </c>
       <c r="C57">
         <v>187688.71400000001</v>
@@ -4423,10 +4199,10 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
         <v>8</v>
-      </c>
-      <c r="B58">
-        <v>57</v>
       </c>
       <c r="C58">
         <v>187675.054</v>
@@ -4467,10 +4243,10 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
         <v>8</v>
-      </c>
-      <c r="B59">
-        <v>58</v>
       </c>
       <c r="C59">
         <v>187662.11199999999</v>
@@ -4511,10 +4287,10 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
         <v>8</v>
-      </c>
-      <c r="B60">
-        <v>59</v>
       </c>
       <c r="C60">
         <v>187649.171</v>
@@ -4555,10 +4331,10 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
         <v>8</v>
-      </c>
-      <c r="B61">
-        <v>60</v>
       </c>
       <c r="C61">
         <v>187667.74400000001</v>
@@ -4599,10 +4375,10 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
         <v>8</v>
-      </c>
-      <c r="B62">
-        <v>61</v>
       </c>
       <c r="C62">
         <v>187640.78200000001</v>
@@ -4643,10 +4419,10 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
         <v>8</v>
-      </c>
-      <c r="B63">
-        <v>62</v>
       </c>
       <c r="C63">
         <v>187683.32199999999</v>
@@ -4687,10 +4463,10 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
         <v>8</v>
-      </c>
-      <c r="B64">
-        <v>63</v>
       </c>
       <c r="C64">
         <v>187657.91800000001</v>
@@ -4731,10 +4507,10 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
         <v>8</v>
-      </c>
-      <c r="B65">
-        <v>64</v>
       </c>
       <c r="C65">
         <v>187633.71299999999</v>
@@ -4775,10 +4551,10 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
         <v>8</v>
-      </c>
-      <c r="B66">
-        <v>65</v>
       </c>
       <c r="C66">
         <v>187617.89499999999</v>
@@ -4819,10 +4595,10 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
         <v>8</v>
-      </c>
-      <c r="B67">
-        <v>66</v>
       </c>
       <c r="C67">
         <v>187608.429</v>
@@ -4863,10 +4639,10 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
         <v>8</v>
-      </c>
-      <c r="B68">
-        <v>67</v>
       </c>
       <c r="C68">
         <v>187603.39600000001</v>
@@ -4907,10 +4683,10 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69">
         <v>8</v>
-      </c>
-      <c r="B69">
-        <v>68</v>
       </c>
       <c r="C69">
         <v>187590.125</v>
@@ -4951,10 +4727,10 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
         <v>8</v>
-      </c>
-      <c r="B70">
-        <v>69</v>
       </c>
       <c r="C70">
         <v>187578.704</v>
@@ -4995,10 +4771,10 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
         <v>8</v>
-      </c>
-      <c r="B71">
-        <v>70</v>
       </c>
       <c r="C71">
         <v>187568.59299999999</v>
@@ -5039,10 +4815,10 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
         <v>8</v>
-      </c>
-      <c r="B72">
-        <v>71</v>
       </c>
       <c r="C72">
         <v>187572.899</v>
@@ -5083,10 +4859,10 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73">
         <v>8</v>
-      </c>
-      <c r="B73">
-        <v>72</v>
       </c>
       <c r="C73">
         <v>187587.69099999999</v>
@@ -5127,10 +4903,10 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74">
         <v>8</v>
-      </c>
-      <c r="B74">
-        <v>73</v>
       </c>
       <c r="C74">
         <v>187568.78</v>
@@ -5171,10 +4947,10 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75">
         <v>8</v>
-      </c>
-      <c r="B75">
-        <v>74</v>
       </c>
       <c r="C75">
         <v>187607.53700000001</v>
@@ -5215,10 +4991,10 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76">
         <v>8</v>
-      </c>
-      <c r="B76">
-        <v>75</v>
       </c>
       <c r="C76">
         <v>187643.91899999999</v>
@@ -5259,10 +5035,10 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77">
         <v>8</v>
-      </c>
-      <c r="B77">
-        <v>76</v>
       </c>
       <c r="C77">
         <v>187630.16899999999</v>
@@ -5303,10 +5079,10 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78">
         <v>8</v>
-      </c>
-      <c r="B78">
-        <v>77</v>
       </c>
       <c r="C78">
         <v>187631.924</v>
@@ -5347,10 +5123,10 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79">
         <v>8</v>
-      </c>
-      <c r="B79">
-        <v>78</v>
       </c>
       <c r="C79">
         <v>187620.51500000001</v>
@@ -5391,10 +5167,10 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80">
         <v>8</v>
-      </c>
-      <c r="B80">
-        <v>79</v>
       </c>
       <c r="C80">
         <v>187581.89799999999</v>
@@ -5435,10 +5211,10 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81">
         <v>9</v>
-      </c>
-      <c r="B81">
-        <v>80</v>
       </c>
       <c r="C81">
         <v>187548.54699999999</v>
@@ -5479,10 +5255,10 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
         <v>9</v>
-      </c>
-      <c r="B82">
-        <v>81</v>
       </c>
       <c r="C82">
         <v>187525.728</v>
@@ -5523,10 +5299,10 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83">
         <v>9</v>
-      </c>
-      <c r="B83">
-        <v>82</v>
       </c>
       <c r="C83">
         <v>187506.432</v>
@@ -5567,10 +5343,10 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
         <v>9</v>
-      </c>
-      <c r="B84">
-        <v>83</v>
       </c>
       <c r="C84">
         <v>187495.01</v>
@@ -5611,10 +5387,10 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85">
         <v>9</v>
-      </c>
-      <c r="B85">
-        <v>84</v>
       </c>
       <c r="C85">
         <v>187483.02799999999</v>
@@ -5655,10 +5431,10 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
         <v>9</v>
-      </c>
-      <c r="B86">
-        <v>85</v>
       </c>
       <c r="C86">
         <v>187469.734</v>
@@ -5699,10 +5475,10 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87">
         <v>9</v>
-      </c>
-      <c r="B87">
-        <v>86</v>
       </c>
       <c r="C87">
         <v>187507.18100000001</v>
@@ -5743,10 +5519,10 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
         <v>9</v>
-      </c>
-      <c r="B88">
-        <v>87</v>
       </c>
       <c r="C88">
         <v>187522.72099999999</v>
@@ -5787,10 +5563,10 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
         <v>9</v>
-      </c>
-      <c r="B89">
-        <v>88</v>
       </c>
       <c r="C89">
         <v>187533.76800000001</v>
@@ -5831,10 +5607,10 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
         <v>9</v>
-      </c>
-      <c r="B90">
-        <v>89</v>
       </c>
       <c r="C90">
         <v>187546.87400000001</v>
@@ -5875,10 +5651,10 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
         <v>9</v>
-      </c>
-      <c r="B91">
-        <v>90</v>
       </c>
       <c r="C91">
         <v>187501.182</v>
@@ -5919,10 +5695,10 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
         <v>9</v>
-      </c>
-      <c r="B92">
-        <v>91</v>
       </c>
       <c r="C92">
         <v>187459.96</v>
@@ -5963,10 +5739,10 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
         <v>9</v>
-      </c>
-      <c r="B93">
-        <v>92</v>
       </c>
       <c r="C93">
         <v>187451.33300000001</v>
@@ -6007,10 +5783,10 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
         <v>9</v>
-      </c>
-      <c r="B94">
-        <v>93</v>
       </c>
       <c r="C94">
         <v>187443.90299999999</v>
@@ -6051,10 +5827,10 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
         <v>9</v>
-      </c>
-      <c r="B95">
-        <v>94</v>
       </c>
       <c r="C95">
         <v>187436.47399999999</v>
@@ -6095,10 +5871,10 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
         <v>9</v>
-      </c>
-      <c r="B96">
-        <v>95</v>
       </c>
       <c r="C96">
         <v>187479.97200000001</v>
@@ -6139,10 +5915,10 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97">
         <v>9</v>
-      </c>
-      <c r="B97">
-        <v>96</v>
       </c>
       <c r="C97">
         <v>187502.14</v>
@@ -6183,10 +5959,10 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98">
         <v>9</v>
-      </c>
-      <c r="B98">
-        <v>97</v>
       </c>
       <c r="C98">
         <v>187524.788</v>
@@ -6227,10 +6003,10 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99">
         <v>9</v>
-      </c>
-      <c r="B99">
-        <v>98</v>
       </c>
       <c r="C99">
         <v>187432.52</v>
@@ -6271,10 +6047,10 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100">
+        <v>100</v>
+      </c>
+      <c r="B100">
         <v>9</v>
-      </c>
-      <c r="B100">
-        <v>100</v>
       </c>
       <c r="C100">
         <v>187474.58</v>
@@ -6315,10 +6091,10 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101">
+        <v>101</v>
+      </c>
+      <c r="B101">
         <v>9</v>
-      </c>
-      <c r="B101">
-        <v>101</v>
       </c>
       <c r="C101">
         <v>187452.41099999999</v>
@@ -6359,10 +6135,10 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102">
+        <v>102</v>
+      </c>
+      <c r="B102">
         <v>9</v>
-      </c>
-      <c r="B102">
-        <v>102</v>
       </c>
       <c r="C102">
         <v>187467.39</v>
@@ -6403,10 +6179,10 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103">
+        <v>103</v>
+      </c>
+      <c r="B103">
         <v>9</v>
-      </c>
-      <c r="B103">
-        <v>103</v>
       </c>
       <c r="C103">
         <v>187447.019</v>
@@ -6458,8 +6234,8 @@
   <dimension ref="A1:N55"/>
   <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.19921875" customWidth="1"/>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.19921875" customWidth="1"/>
     <col min="3" max="3" width="21.69921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="13.8984375" bestFit="1" customWidth="1"/>
@@ -6473,10 +6249,10 @@
   <sheetData>
     <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>167</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>168</v>
@@ -6488,35 +6264,35 @@
         <v>39</v>
       </c>
       <c r="F1" s="4" t="str">
-        <f>LEFT(E1,LEN(E1)-5)&amp;VLOOKUP(LEFT(E1,LEN(E1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
+        <f>LEFT(E1,LEN(E1)-5)&amp;VLOOKUP(LEFT(E1,LEN(E1)-5),Overzicht_parameters!$A$2:$F$69,6,(FALSE))</f>
         <v>top_zand_stdev</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>40</v>
       </c>
       <c r="H1" s="4" t="str">
-        <f>LEFT(G1,LEN(G1)-5)&amp;VLOOKUP(LEFT(G1,LEN(G1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
+        <f>LEFT(G1,LEN(G1)-5)&amp;VLOOKUP(LEFT(G1,LEN(G1)-5),Overzicht_parameters!$A$2:$F$69,6,(FALSE))</f>
         <v>gamma_sat_deklaag_stdev</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>41</v>
       </c>
       <c r="J1" s="4" t="str">
-        <f>LEFT(I1,LEN(I1)-5)&amp;VLOOKUP(LEFT(I1,LEN(I1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
+        <f>LEFT(I1,LEN(I1)-5)&amp;VLOOKUP(LEFT(I1,LEN(I1)-5),Overzicht_parameters!$A$2:$F$69,6,(FALSE))</f>
         <v>D_wvp_stdev</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>42</v>
       </c>
       <c r="L1" s="4" t="str">
-        <f>LEFT(K1,LEN(K1)-5)&amp;VLOOKUP(LEFT(K1,LEN(K1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
+        <f>LEFT(K1,LEN(K1)-5)&amp;VLOOKUP(LEFT(K1,LEN(K1)-5),Overzicht_parameters!$A$2:$F$69,6,(FALSE))</f>
         <v>kD_wvp_vc</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>43</v>
       </c>
       <c r="N1" s="4" t="str">
-        <f>LEFT(M1,LEN(M1)-5)&amp;VLOOKUP(LEFT(M1,LEN(M1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
+        <f>LEFT(M1,LEN(M1)-5)&amp;VLOOKUP(LEFT(M1,LEN(M1)-5),Overzicht_parameters!$A$2:$F$69,6,(FALSE))</f>
         <v>d70_vc</v>
       </c>
     </row>
@@ -6566,10 +6342,10 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
         <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>45</v>
@@ -6610,10 +6386,10 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
         <v>1</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -6648,10 +6424,10 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
         <v>1</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -6681,10 +6457,10 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
         <v>1</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -6714,10 +6490,10 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
         <v>1</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -6747,10 +6523,10 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
         <v>2</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
       </c>
       <c r="C8" t="s">
         <v>44</v>
@@ -6791,7 +6567,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -6835,10 +6611,10 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
         <v>2</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -6873,10 +6649,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
         <v>2</v>
-      </c>
-      <c r="B11">
-        <v>4</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6906,10 +6682,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
         <v>2</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6939,10 +6715,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
         <v>2</v>
-      </c>
-      <c r="B13">
-        <v>6</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -6972,10 +6748,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
         <v>3</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
       </c>
       <c r="C14" t="s">
         <v>44</v>
@@ -7016,10 +6792,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
         <v>3</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
       </c>
       <c r="C15" t="s">
         <v>45</v>
@@ -7060,7 +6836,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -7098,10 +6874,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
         <v>3</v>
-      </c>
-      <c r="B17">
-        <v>4</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7131,10 +6907,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
         <v>3</v>
-      </c>
-      <c r="B18">
-        <v>5</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -7164,10 +6940,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
         <v>3</v>
-      </c>
-      <c r="B19">
-        <v>6</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -7197,10 +6973,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
         <v>4</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
       </c>
       <c r="C20" t="s">
         <v>44</v>
@@ -7241,10 +7017,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
         <v>4</v>
-      </c>
-      <c r="B21">
-        <v>2</v>
       </c>
       <c r="C21" t="s">
         <v>45</v>
@@ -7285,10 +7061,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
         <v>4</v>
-      </c>
-      <c r="B22">
-        <v>3</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -7323,7 +7099,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B23">
         <v>4</v>
@@ -7356,10 +7132,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
         <v>4</v>
-      </c>
-      <c r="B24">
-        <v>5</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -7389,10 +7165,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
         <v>4</v>
-      </c>
-      <c r="B25">
-        <v>6</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -7422,10 +7198,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
         <v>5</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
       </c>
       <c r="C26" t="s">
         <v>44</v>
@@ -7466,10 +7242,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
         <v>5</v>
-      </c>
-      <c r="B27">
-        <v>2</v>
       </c>
       <c r="C27" t="s">
         <v>45</v>
@@ -7510,10 +7286,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
         <v>5</v>
-      </c>
-      <c r="B28">
-        <v>3</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -7548,10 +7324,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
         <v>5</v>
-      </c>
-      <c r="B29">
-        <v>4</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -7581,7 +7357,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>5</v>
@@ -7614,10 +7390,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
         <v>5</v>
-      </c>
-      <c r="B31">
-        <v>6</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -7647,10 +7423,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
         <v>6</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
       </c>
       <c r="C32" t="s">
         <v>44</v>
@@ -7691,10 +7467,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
         <v>6</v>
-      </c>
-      <c r="B33">
-        <v>2</v>
       </c>
       <c r="C33" t="s">
         <v>45</v>
@@ -7735,10 +7511,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
         <v>6</v>
-      </c>
-      <c r="B34">
-        <v>3</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -7773,10 +7549,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
         <v>6</v>
-      </c>
-      <c r="B35">
-        <v>4</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -7806,10 +7582,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
         <v>6</v>
-      </c>
-      <c r="B36">
-        <v>5</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -7839,7 +7615,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B37">
         <v>6</v>
@@ -7872,10 +7648,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
         <v>7</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
       </c>
       <c r="C38" t="s">
         <v>44</v>
@@ -7916,10 +7692,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
         <v>7</v>
-      </c>
-      <c r="B39">
-        <v>2</v>
       </c>
       <c r="C39" t="s">
         <v>45</v>
@@ -7960,10 +7736,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
         <v>7</v>
-      </c>
-      <c r="B40">
-        <v>3</v>
       </c>
       <c r="C40" t="s">
         <v>46</v>
@@ -7998,10 +7774,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
         <v>7</v>
-      </c>
-      <c r="B41">
-        <v>4</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -8031,10 +7807,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
         <v>7</v>
-      </c>
-      <c r="B42">
-        <v>5</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -8064,10 +7840,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
         <v>7</v>
-      </c>
-      <c r="B43">
-        <v>6</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -8097,10 +7873,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
         <v>8</v>
-      </c>
-      <c r="B44">
-        <v>1</v>
       </c>
       <c r="C44" t="s">
         <v>44</v>
@@ -8141,10 +7917,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
         <v>8</v>
-      </c>
-      <c r="B45">
-        <v>2</v>
       </c>
       <c r="C45" t="s">
         <v>45</v>
@@ -8185,10 +7961,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
         <v>8</v>
-      </c>
-      <c r="B46">
-        <v>3</v>
       </c>
       <c r="C46" t="s">
         <v>46</v>
@@ -8223,10 +7999,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
         <v>8</v>
-      </c>
-      <c r="B47">
-        <v>4</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -8256,10 +8032,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
         <v>8</v>
-      </c>
-      <c r="B48">
-        <v>5</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -8289,10 +8065,10 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
         <v>8</v>
-      </c>
-      <c r="B49">
-        <v>6</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -8322,10 +8098,10 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
         <v>9</v>
-      </c>
-      <c r="B50">
-        <v>1</v>
       </c>
       <c r="C50" t="s">
         <v>44</v>
@@ -8366,10 +8142,10 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
         <v>9</v>
-      </c>
-      <c r="B51">
-        <v>2</v>
       </c>
       <c r="C51" t="s">
         <v>45</v>
@@ -8410,10 +8186,10 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
         <v>9</v>
-      </c>
-      <c r="B52">
-        <v>3</v>
       </c>
       <c r="C52" t="s">
         <v>46</v>
@@ -8448,10 +8224,10 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
         <v>9</v>
-      </c>
-      <c r="B53">
-        <v>4</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -8481,10 +8257,10 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
         <v>9</v>
-      </c>
-      <c r="B54">
-        <v>5</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -8514,10 +8290,10 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
         <v>9</v>
-      </c>
-      <c r="B55">
-        <v>6</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -8576,52 +8352,52 @@
   <sheetData>
     <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
@@ -8629,13 +8405,13 @@
         <v>158</v>
       </c>
       <c r="B2" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -8646,13 +8422,13 @@
         <v>159</v>
       </c>
       <c r="B3" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C3" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D3" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -8664,10 +8440,10 @@
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D4" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -8679,10 +8455,10 @@
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D5" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -8693,13 +8469,13 @@
         <v>160</v>
       </c>
       <c r="B6" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D6" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -8710,13 +8486,13 @@
         <v>164</v>
       </c>
       <c r="B7" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C7" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D7" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -8727,13 +8503,13 @@
         <v>165</v>
       </c>
       <c r="B8" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="D8" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -8744,13 +8520,13 @@
         <v>166</v>
       </c>
       <c r="B9" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="C9" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D9" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -8761,13 +8537,13 @@
         <v>161</v>
       </c>
       <c r="B10" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C10" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D10" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -8779,10 +8555,10 @@
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D11" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -8794,10 +8570,10 @@
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D12" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -8808,13 +8584,13 @@
         <v>167</v>
       </c>
       <c r="B13" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C13" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D13" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -8825,13 +8601,13 @@
         <v>168</v>
       </c>
       <c r="B14" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C14" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D14" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -8842,16 +8618,16 @@
         <v>169</v>
       </c>
       <c r="B15" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D15" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E15" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
@@ -8872,15 +8648,15 @@
         <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E16" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s">
         <v>48</v>
@@ -8909,10 +8685,10 @@
         <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E17" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F17" t="s">
         <v>50</v>
@@ -8937,10 +8713,10 @@
         <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E18" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F18" t="s">
         <v>49</v>
@@ -8948,7 +8724,7 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="L18" t="s">
         <v>48</v>
@@ -8968,10 +8744,10 @@
         <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E19" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F19" t="s">
         <v>49</v>
@@ -8983,7 +8759,7 @@
         <v>60</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="O19" t="s">
         <v>48</v>
@@ -9000,10 +8776,10 @@
         <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E20" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F20" t="s">
         <v>50</v>
@@ -9015,7 +8791,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="O20" t="s">
         <v>48</v>
@@ -9035,10 +8811,10 @@
         <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E21" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F21" t="s">
         <v>49</v>
@@ -9050,7 +8826,7 @@
         <v>22</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
@@ -9064,10 +8840,10 @@
         <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E22" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F22" t="s">
         <v>50</v>
@@ -9079,7 +8855,7 @@
         <v>4000</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="L22" t="s">
         <v>48</v>
@@ -9099,16 +8875,16 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C23" t="s">
         <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E23" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="I23" s="2">
         <v>0</v>
@@ -9134,23 +8910,23 @@
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C24" t="s">
         <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E24" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="I24" s="2">
         <v>0</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="L24" t="s">
         <v>48</v>
@@ -9167,23 +8943,23 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C25" t="s">
         <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E25" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="I25" s="2">
         <v>0</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="L25" t="s">
         <v>48</v>
@@ -9203,16 +8979,16 @@
         <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C26" t="s">
         <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E26" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="I26" s="2">
         <v>5</v>
@@ -9221,7 +8997,7 @@
         <v>2000</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="L26" t="s">
         <v>48</v>
@@ -9247,10 +9023,10 @@
         <v>52</v>
       </c>
       <c r="D27" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E27" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
@@ -9263,16 +9039,16 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C28" t="s">
         <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E28" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="I28" s="2">
         <v>-4</v>
@@ -9281,7 +9057,7 @@
         <v>15</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="O28" t="s">
         <v>48</v>
@@ -9292,21 +9068,21 @@
         <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C29" t="s">
         <v>52</v>
       </c>
       <c r="D29" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E29" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="L29" t="s">
         <v>48</v>
@@ -9332,7 +9108,7 @@
         <v>52</v>
       </c>
       <c r="D30" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E30" t="s">
         <v>56</v>
@@ -9347,7 +9123,7 @@
         <v>15</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="O30" t="s">
         <v>48</v>
@@ -9364,10 +9140,10 @@
         <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E31" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G31" s="1">
         <v>2.0799999999999999E-4</v>
@@ -9393,10 +9169,10 @@
         <v>84</v>
       </c>
       <c r="D32" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E32" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G32">
         <v>0.25</v>
@@ -9418,10 +9194,10 @@
         <v>112</v>
       </c>
       <c r="D33" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E33" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G33">
         <v>9.81</v>
@@ -9446,10 +9222,10 @@
         <v>59</v>
       </c>
       <c r="D34" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E34" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G34" s="2">
         <v>26</v>
@@ -9475,10 +9251,10 @@
         <v>59</v>
       </c>
       <c r="D35" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E35" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G35">
         <v>9.81</v>
@@ -9500,10 +9276,10 @@
         <v>47</v>
       </c>
       <c r="D36" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E36" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G36">
         <v>1.5</v>
@@ -9523,10 +9299,10 @@
         <v>84</v>
       </c>
       <c r="D37" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E37" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F37" t="s">
         <v>49</v>
@@ -9557,10 +9333,10 @@
         <v>73</v>
       </c>
       <c r="D38" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E38" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F38" t="s">
         <v>49</v>
@@ -9583,10 +9359,10 @@
         <v>73</v>
       </c>
       <c r="D39" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E39" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F39" t="s">
         <v>49</v>
@@ -9609,10 +9385,10 @@
         <v>84</v>
       </c>
       <c r="D40" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E40" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G40" s="2">
         <v>0.3</v>
@@ -9638,10 +9414,10 @@
         <v>107</v>
       </c>
       <c r="D41" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E41" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G41" s="2">
         <v>37</v>
@@ -9667,10 +9443,10 @@
         <v>115</v>
       </c>
       <c r="D42" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E42" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G42" s="1">
         <v>1.33E-6</v>
@@ -9690,16 +9466,16 @@
         <v>85</v>
       </c>
       <c r="B43" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C43" t="s">
         <v>84</v>
       </c>
       <c r="D43" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E43" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F43" t="s">
         <v>49</v>
@@ -9713,7 +9489,7 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="N43" t="s">
         <v>48</v>
@@ -9730,10 +9506,10 @@
         <v>84</v>
       </c>
       <c r="D44" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E44" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F44" t="s">
         <v>49</v>
@@ -9747,7 +9523,7 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="O44" t="s">
         <v>48</v>
@@ -9764,10 +9540,10 @@
         <v>84</v>
       </c>
       <c r="D45" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E45" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F45" t="s">
         <v>49</v>
@@ -9781,7 +9557,7 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="M45" t="s">
         <v>48</v>
@@ -9803,10 +9579,10 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="P46" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
@@ -9825,10 +9601,10 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="P47" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
@@ -9847,7 +9623,7 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="O48" t="s">
         <v>102</v>
@@ -9869,7 +9645,7 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="O49" t="s">
         <v>102</v>
@@ -9891,7 +9667,7 @@
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="M50" t="s">
         <v>102</v>
@@ -9913,7 +9689,7 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="N51" t="s">
         <v>98</v>
@@ -9935,7 +9711,7 @@
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="O52" t="s">
         <v>98</v>
@@ -9957,7 +9733,7 @@
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="M53" t="s">
         <v>98</v>
@@ -9979,7 +9755,7 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="O54" t="s">
         <v>102</v>
@@ -10001,7 +9777,7 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="N55" t="s">
         <v>102</v>
@@ -10023,7 +9799,7 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.2">
@@ -10042,7 +9818,7 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="L57" t="s">
         <v>102</v>
@@ -10064,7 +9840,7 @@
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="O58" t="s">
         <v>102</v>
@@ -10086,7 +9862,7 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="L59" t="s">
         <v>102</v>
@@ -10108,7 +9884,7 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="L60" t="s">
         <v>102</v>
@@ -10130,7 +9906,7 @@
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="L61" t="s">
         <v>102</v>
@@ -10141,7 +9917,7 @@
         <v>99</v>
       </c>
       <c r="B62" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C62" t="s">
         <v>52</v>
@@ -10152,7 +9928,7 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="L62" t="s">
         <v>98</v>
@@ -10169,7 +9945,7 @@
         <v>97</v>
       </c>
       <c r="B63" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C63" t="s">
         <v>84</v>
@@ -10180,7 +9956,7 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="L63" t="s">
         <v>98</v>
@@ -10202,7 +9978,7 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="L64" t="s">
         <v>102</v>
@@ -10224,7 +10000,7 @@
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="L65" t="s">
         <v>102</v>
@@ -10246,7 +10022,7 @@
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="M66" t="s">
         <v>48</v>
@@ -10274,7 +10050,7 @@
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="N67" t="s">
         <v>98</v>
@@ -10296,7 +10072,7 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="O68" t="s">
         <v>98</v>
@@ -10318,7 +10094,7 @@
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="M69" t="s">
         <v>98</v>
@@ -10326,22 +10102,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="expression" dxfId="15" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>OR($D1="metadata", $D1="calculated")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F69">
-    <cfRule type="expression" dxfId="14" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>OR($E1="deterministic", ISBLANK($E1))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:H69">
-    <cfRule type="expression" dxfId="13" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>$D2&lt;&gt;"constant"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:J69">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND($D2&lt;&gt;"variable",$D2&lt;&gt;"constant")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10367,87 +10143,87 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7FD5E8-359B-4F56-B38E-FCA72B85D698}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.796875" style="7"/>
+    <col min="2" max="16384" width="8.69921875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B3" s="7">
         <v>0.75</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="B4" s="7">
         <v>0</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="B5" s="7">
         <v>0.01</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="B6" s="7">
         <v>100</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="B7" s="7" t="b">
         <v>1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/example_new_calculations/input/input.xlsx
+++ b/workspaces/example_new_calculations/input/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKL\Documents\Github\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A649AE8-E2B8-467A-841A-3324CE662DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6A4E11-75C2-4C05-96AC-7A229ADBDE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-165" windowWidth="25440" windowHeight="15270" activeTab="3" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="233">
   <si>
     <t>M_van</t>
   </si>
@@ -676,9 +676,6 @@
   </si>
   <si>
     <t>variation_coefficient</t>
-  </si>
-  <si>
-    <t>start_value</t>
   </si>
   <si>
     <t>relaxation_factor</t>
@@ -8352,37 +8349,37 @@
   <sheetData>
     <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>232</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>170</v>
@@ -8411,7 +8408,7 @@
         <v>189</v>
       </c>
       <c r="D2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -8428,7 +8425,7 @@
         <v>188</v>
       </c>
       <c r="D3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -8443,7 +8440,7 @@
         <v>190</v>
       </c>
       <c r="D4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -8458,7 +8455,7 @@
         <v>190</v>
       </c>
       <c r="D5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -8475,7 +8472,7 @@
         <v>190</v>
       </c>
       <c r="D6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -8492,7 +8489,7 @@
         <v>189</v>
       </c>
       <c r="D7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -8509,7 +8506,7 @@
         <v>186</v>
       </c>
       <c r="D8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -8526,7 +8523,7 @@
         <v>187</v>
       </c>
       <c r="D9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -8543,7 +8540,7 @@
         <v>188</v>
       </c>
       <c r="D10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -8558,7 +8555,7 @@
         <v>190</v>
       </c>
       <c r="D11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -8573,7 +8570,7 @@
         <v>190</v>
       </c>
       <c r="D12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -8590,7 +8587,7 @@
         <v>189</v>
       </c>
       <c r="D13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -8607,7 +8604,7 @@
         <v>188</v>
       </c>
       <c r="D14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -8624,7 +8621,7 @@
         <v>191</v>
       </c>
       <c r="D15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E15" t="s">
         <v>203</v>
@@ -8648,7 +8645,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E16" t="s">
         <v>203</v>
@@ -8685,7 +8682,7 @@
         <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E17" t="s">
         <v>205</v>
@@ -8713,7 +8710,7 @@
         <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E18" t="s">
         <v>205</v>
@@ -8744,7 +8741,7 @@
         <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E19" t="s">
         <v>205</v>
@@ -8776,7 +8773,7 @@
         <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E20" t="s">
         <v>205</v>
@@ -8811,7 +8808,7 @@
         <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E21" t="s">
         <v>205</v>
@@ -8840,7 +8837,7 @@
         <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E22" t="s">
         <v>205</v>
@@ -8881,7 +8878,7 @@
         <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E23" t="s">
         <v>203</v>
@@ -8916,7 +8913,7 @@
         <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E24" t="s">
         <v>203</v>
@@ -8949,7 +8946,7 @@
         <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E25" t="s">
         <v>203</v>
@@ -8985,7 +8982,7 @@
         <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E26" t="s">
         <v>203</v>
@@ -9023,7 +9020,7 @@
         <v>52</v>
       </c>
       <c r="D27" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E27" t="s">
         <v>203</v>
@@ -9045,7 +9042,7 @@
         <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E28" t="s">
         <v>203</v>
@@ -9074,7 +9071,7 @@
         <v>52</v>
       </c>
       <c r="D29" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E29" t="s">
         <v>203</v>
@@ -9108,7 +9105,7 @@
         <v>52</v>
       </c>
       <c r="D30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E30" t="s">
         <v>56</v>
@@ -9140,7 +9137,7 @@
         <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E31" t="s">
         <v>203</v>
@@ -9169,7 +9166,7 @@
         <v>84</v>
       </c>
       <c r="D32" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E32" t="s">
         <v>203</v>
@@ -9194,7 +9191,7 @@
         <v>112</v>
       </c>
       <c r="D33" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E33" t="s">
         <v>203</v>
@@ -9222,7 +9219,7 @@
         <v>59</v>
       </c>
       <c r="D34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E34" t="s">
         <v>203</v>
@@ -9251,7 +9248,7 @@
         <v>59</v>
       </c>
       <c r="D35" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E35" t="s">
         <v>203</v>
@@ -9276,7 +9273,7 @@
         <v>47</v>
       </c>
       <c r="D36" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E36" t="s">
         <v>203</v>
@@ -9299,7 +9296,7 @@
         <v>84</v>
       </c>
       <c r="D37" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E37" t="s">
         <v>205</v>
@@ -9333,7 +9330,7 @@
         <v>73</v>
       </c>
       <c r="D38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E38" t="s">
         <v>205</v>
@@ -9359,7 +9356,7 @@
         <v>73</v>
       </c>
       <c r="D39" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E39" t="s">
         <v>205</v>
@@ -9385,7 +9382,7 @@
         <v>84</v>
       </c>
       <c r="D40" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E40" t="s">
         <v>203</v>
@@ -9414,7 +9411,7 @@
         <v>107</v>
       </c>
       <c r="D41" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E41" t="s">
         <v>203</v>
@@ -9443,7 +9440,7 @@
         <v>115</v>
       </c>
       <c r="D42" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E42" t="s">
         <v>203</v>
@@ -9472,7 +9469,7 @@
         <v>84</v>
       </c>
       <c r="D43" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E43" t="s">
         <v>205</v>
@@ -9506,7 +9503,7 @@
         <v>84</v>
       </c>
       <c r="D44" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E44" t="s">
         <v>205</v>
@@ -9540,7 +9537,7 @@
         <v>84</v>
       </c>
       <c r="D45" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E45" t="s">
         <v>205</v>
@@ -10142,7 +10139,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7FD5E8-359B-4F56-B38E-FCA72B85D698}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.09765625" style="7" bestFit="1" customWidth="1"/>
@@ -10151,29 +10148,29 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B3" s="7">
         <v>0.75</v>
@@ -10184,10 +10181,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B4" s="7">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>210</v>
@@ -10195,50 +10192,39 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B5" s="7">
-        <v>0.01</v>
+        <v>100</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B6" s="7">
-        <v>100</v>
+        <v>207</v>
+      </c>
+      <c r="B6" s="7" t="b">
+        <v>1</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="B7" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="C7" s="7" t="s">
         <v>206</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6" xr:uid="{94AA1909-8159-4ABD-8194-E5CC31B00066}">
-      <formula1>AND(ISNUMBER(B6),B6=INT(B6))</formula1>
-    </dataValidation>
-    <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" sqref="B3:B5" xr:uid="{0F940659-071E-4396-94AE-334C05124B18}">
-      <formula1>ISNUMBER(B3)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{94AA1909-8159-4ABD-8194-E5CC31B00066}">
+      <formula1>AND(ISNUMBER(B5),B5=INT(B5))</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{73A82C8D-457E-4F26-8920-E365EC9333FD}">
       <formula1>"form,numerical_integration,crude_monte_carlo,importance_sampling,directional_sampling,subset_simulation,numerical_bisection,latin_hypercube,cobyla_reliability,form_then_directional_sampling,directional_sampling_then_form"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{05F071D7-CE12-4A8B-B2AB-37DFC65D1C77}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6" xr:uid="{05F071D7-CE12-4A8B-B2AB-37DFC65D1C77}">
       <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" sqref="B3:B4" xr:uid="{0F940659-071E-4396-94AE-334C05124B18}">
+      <formula1>ISNUMBER(B3)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/workspaces/example_new_calculations/input/input.xlsx
+++ b/workspaces/example_new_calculations/input/input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKL\Documents\Github\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oscop\Documents\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9AABB1-8C0C-43A9-B9D2-267F6B69BDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3D101B-95A1-4771-B5C6-C7949644EB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-180" windowWidth="29040" windowHeight="17520" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
   </bookViews>
   <sheets>
     <sheet name="Vakken" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="226">
   <si>
     <t>M_van</t>
   </si>
@@ -194,9 +194,6 @@
     <t>TZ</t>
   </si>
   <si>
-    <t>Afstand van uittredepunt tot geometrische intredelijn</t>
-  </si>
-  <si>
     <t>m</t>
   </si>
   <si>
@@ -206,42 +203,24 @@
     <t>none, deterministic</t>
   </si>
   <si>
-    <t>Uittredepunt</t>
-  </si>
-  <si>
     <t>input</t>
   </si>
   <si>
     <t>_stdev</t>
   </si>
   <si>
-    <t>Afstand van uittredepunt tot buitenteenlijn</t>
-  </si>
-  <si>
     <t>_vc</t>
   </si>
   <si>
-    <t>Afstand van uittredepunt tot binnenteenlijn</t>
-  </si>
-  <si>
-    <t>Afstand van uittredepunt tot Achterlandlengte</t>
-  </si>
-  <si>
     <t>Vakken</t>
   </si>
   <si>
-    <t>Bodemhoogte ter plaatse van uittredepunt</t>
-  </si>
-  <si>
     <t>m+NAP</t>
   </si>
   <si>
     <t>Representatieve bodemhoogte achterland binnen een vak</t>
   </si>
   <si>
-    <t>Polderpeil ter plaatse van uittredepunt</t>
-  </si>
-  <si>
     <t>top_zand</t>
   </si>
   <si>
@@ -251,9 +230,6 @@
     <t>normal</t>
   </si>
   <si>
-    <t>Ondergrondscenario</t>
-  </si>
-  <si>
     <t>gamma_sat_deklaag</t>
   </si>
   <si>
@@ -395,18 +371,12 @@
     <t>r_exit</t>
   </si>
   <si>
-    <t>Dempingsfactor bij uittredepunt</t>
-  </si>
-  <si>
     <t>output</t>
   </si>
   <si>
     <t>phi_exit</t>
   </si>
   <si>
-    <t>Theoretische stijghoogte bij uittredepunt</t>
-  </si>
-  <si>
     <t>h_exit</t>
   </si>
   <si>
@@ -666,6 +636,87 @@
   </si>
   <si>
     <t xml:space="preserve">n </t>
+  </si>
+  <si>
+    <t>Uittredepunten</t>
+  </si>
+  <si>
+    <t>Dempingsfactor bij Uittredepunten</t>
+  </si>
+  <si>
+    <t>Ondergrondscenarios</t>
+  </si>
+  <si>
+    <t>Theoretische stijghoogte bij uittredepunten</t>
+  </si>
+  <si>
+    <t>Polderpeil ter plaatse van uittredepunten</t>
+  </si>
+  <si>
+    <t>Bodemhoogte ter plaatse van uittredepunten</t>
+  </si>
+  <si>
+    <t>Afstand van uittredepunten tot achterlandlengte</t>
+  </si>
+  <si>
+    <t>Afstand van uittredepunten tot binnenteenlijn</t>
+  </si>
+  <si>
+    <t>Afstand van uittredepunten tot buitenteenlijn</t>
+  </si>
+  <si>
+    <t>Afstand van uittredepunten tot geometrische intredelijn</t>
+  </si>
+  <si>
+    <t>RD x</t>
+  </si>
+  <si>
+    <t>RD y</t>
+  </si>
+  <si>
+    <t>vrij in te vullen</t>
+  </si>
+  <si>
+    <t>geheel getal startend bij 1</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>0 ≤ x ≤ 1</t>
+  </si>
+  <si>
+    <t>Kans van optreden van ondergrondscenario</t>
+  </si>
+  <si>
+    <t>Identificatienummer van het ondergrondscenario, wordt gebruikt in de tool</t>
+  </si>
+  <si>
+    <t>Identificatienummer van het uittredepunt, wordt gebruikt in de tool</t>
+  </si>
+  <si>
+    <t>Identificatienummer van het vak, wordt gebruikt in de tool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naam van het vak zoals deze door gebruiker wordt gedefinieerd </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naam van het ondergrondscenario zoals deze door gebruiker wordt gedefinieerd </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lengte van het vak </t>
+  </si>
+  <si>
+    <t>X-coordinaat van het uittrededpunt</t>
+  </si>
+  <si>
+    <t>Y-coordinaat van het uittrededpunt</t>
+  </si>
+  <si>
+    <t>Omschrijving van de uittredelocatie</t>
+  </si>
+  <si>
+    <t>Calculated variables</t>
   </si>
 </sst>
 </file>
@@ -687,7 +738,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -697,6 +748,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -713,18 +770,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <numFmt numFmtId="15" formatCode="0.00E+00"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
@@ -736,9 +808,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="15" formatCode="0.00E+00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="15" formatCode="0.00E+00"/>
@@ -818,8 +887,8 @@
     <tableColumn id="10" xr3:uid="{30E95029-7E84-4404-97EA-CC899B222DC3}" name="Kolom10"/>
     <tableColumn id="11" xr3:uid="{21D2E504-CBB5-45F7-9119-E1DA7B53C2D5}" name="Kolom11"/>
     <tableColumn id="12" xr3:uid="{FF7176FB-923E-4ECE-83AA-046E768AD06C}" name="Kolom12"/>
-    <tableColumn id="13" xr3:uid="{F65A6039-B474-4D50-AEEB-0C9E748E2BE5}" name="Kolom13"/>
-    <tableColumn id="14" xr3:uid="{4E1A767E-8059-4EF5-B52B-A1637577AFDF}" name="Kolom14" headerRowDxfId="5" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{F65A6039-B474-4D50-AEEB-0C9E748E2BE5}" name="Kolom13" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{4E1A767E-8059-4EF5-B52B-A1637577AFDF}" name="Kolom14" headerRowDxfId="6" dataDxfId="0"/>
     <tableColumn id="15" xr3:uid="{E12738E9-E3E4-4A5D-81C1-E333D11489B2}" name="Kolom15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -827,10 +896,10 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{ECE0F829-0060-4D7E-94D4-430EA87FED82}" name="Tabel12" displayName="Tabel12" ref="A2:P55" headerRowCount="0" totalsRowShown="0">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P55">
-    <sortCondition ref="D2:D55" customList="Input,Input,can also be calculated,Constant,Calculated"/>
-    <sortCondition ref="A2:A55"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{ECE0F829-0060-4D7E-94D4-430EA87FED82}" name="Tabel12" displayName="Tabel12" ref="A2:P69" headerRowCount="0" totalsRowShown="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P69">
+    <sortCondition ref="D2:D69" customList="Input,Input,can also be calculated,Constant,Calculated"/>
+    <sortCondition ref="A2:A69"/>
   </sortState>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{EE720E76-FC11-4E08-B57C-F3D8111FE800}" name="Kolom1"/>
@@ -841,9 +910,9 @@
     <tableColumn id="6" xr3:uid="{FA05A46A-DA45-4C6A-9D17-689A03B15BA8}" name="Kolom6"/>
     <tableColumn id="7" xr3:uid="{25871E16-DA07-4B31-A7EF-FBA1FEE488DB}" name="Kolom7"/>
     <tableColumn id="8" xr3:uid="{A229D98E-F2F0-4491-8C3C-1FB943EA5058}" name="Kolom8"/>
-    <tableColumn id="9" xr3:uid="{1FBE756B-5426-4436-B3C8-55410DF75FDB}" name="Kolom9" headerRowDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{B851468F-D94B-4F13-9CF8-13DADE13A2A8}" name="Kolom10" headerRowDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{41B8BB8E-854F-4E90-B76F-4066FB0CA9A2}" name="Kolom11" headerRowDxfId="1" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{1FBE756B-5426-4436-B3C8-55410DF75FDB}" name="Kolom9" headerRowDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{B851468F-D94B-4F13-9CF8-13DADE13A2A8}" name="Kolom10" headerRowDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{41B8BB8E-854F-4E90-B76F-4066FB0CA9A2}" name="Kolom11" headerRowDxfId="3" dataDxfId="2"/>
     <tableColumn id="12" xr3:uid="{E7B2F49E-191F-4D24-8883-DCCF4F196399}" name="Kolom12"/>
     <tableColumn id="13" xr3:uid="{1DB6223F-5250-48AD-B68D-FD511FFC8150}" name="Kolom13"/>
     <tableColumn id="14" xr3:uid="{B2104B25-DEBD-4E44-A26A-46A71C2A832D}" name="Kolom14"/>
@@ -855,7 +924,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1172,26 +1241,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C253AA-AAA1-47E5-9332-CA169F978D7A}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.25" customWidth="1"/>
-    <col min="2" max="2" width="32.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.25" customWidth="1"/>
-    <col min="5" max="5" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.19921875" customWidth="1"/>
+    <col min="2" max="2" width="32.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.19921875" customWidth="1"/>
+    <col min="5" max="5" width="16.59765625" customWidth="1"/>
+    <col min="6" max="6" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.09765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.375" customWidth="1"/>
+    <col min="9" max="9" width="17.3984375" customWidth="1"/>
     <col min="10" max="10" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>0</v>
@@ -1200,7 +1269,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>2</v>
@@ -1212,18 +1281,18 @@
         <v>4</v>
       </c>
       <c r="I1" s="4" t="str">
-        <f>LEFT(H1,LEN(H1)-5)&amp;VLOOKUP(LEFT(H1,LEN(H1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+        <f>LEFT(H1,LEN(H1)-5)&amp;VLOOKUP(LEFT(H1,LEN(H1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>c_voorland_stdev</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="K1" s="4" t="str">
-        <f>LEFT(J1,LEN(J1)-5)&amp;VLOOKUP(LEFT(J1,LEN(J1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+        <f>LEFT(J1,LEN(J1)-5)&amp;VLOOKUP(LEFT(J1,LEN(J1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>c_achterland_vc</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1258,7 +1327,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1293,7 +1362,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1328,7 +1397,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1363,7 +1432,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1398,7 +1467,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1433,7 +1502,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1468,7 +1537,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1503,7 +1572,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1549,45 +1618,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB77777-746E-45C0-BE11-D138C11C003A}">
   <dimension ref="A1:T103"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.375" customWidth="1"/>
+    <col min="1" max="1" width="7.3984375" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.8984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.25" customWidth="1"/>
-    <col min="11" max="11" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.19921875" customWidth="1"/>
+    <col min="11" max="11" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.8984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="17.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>15</v>
@@ -1599,7 +1668,7 @@
         <v>17</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>18</v>
@@ -1614,25 +1683,25 @@
         <v>21</v>
       </c>
       <c r="P1" s="4" t="str">
-        <f>LEFT(O1,LEN(O1)-5)&amp;VLOOKUP(LEFT(O1,LEN(O1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+        <f>LEFT(O1,LEN(O1)-5)&amp;VLOOKUP(LEFT(O1,LEN(O1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>modelfactor_u_stdev</v>
       </c>
       <c r="Q1" s="4" t="s">
         <v>22</v>
       </c>
       <c r="R1" s="4" t="str">
-        <f>LEFT(Q1,LEN(Q1)-5)&amp;VLOOKUP(LEFT(Q1,LEN(Q1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+        <f>LEFT(Q1,LEN(Q1)-5)&amp;VLOOKUP(LEFT(Q1,LEN(Q1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>modelfactor_h_stdev</v>
       </c>
       <c r="S1" s="4" t="s">
         <v>23</v>
       </c>
       <c r="T1" s="4" t="str">
-        <f>LEFT(S1,LEN(S1)-5)&amp;VLOOKUP(LEFT(S1,LEN(S1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+        <f>LEFT(S1,LEN(S1)-5)&amp;VLOOKUP(LEFT(S1,LEN(S1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>modelfactor_p_stdev</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1694,7 +1763,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>3</v>
       </c>
@@ -1756,7 +1825,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>4</v>
       </c>
@@ -1818,7 +1887,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1880,7 +1949,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1942,7 +2011,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2004,7 +2073,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5</v>
       </c>
@@ -2066,7 +2135,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5</v>
       </c>
@@ -2128,7 +2197,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>5</v>
       </c>
@@ -2190,7 +2259,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>5</v>
       </c>
@@ -2252,7 +2321,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>5</v>
       </c>
@@ -2314,7 +2383,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>5</v>
       </c>
@@ -2376,7 +2445,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>5</v>
       </c>
@@ -2438,7 +2507,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>5</v>
       </c>
@@ -2500,7 +2569,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>5</v>
       </c>
@@ -2562,7 +2631,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>6</v>
       </c>
@@ -2624,7 +2693,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>6</v>
       </c>
@@ -2686,7 +2755,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>6</v>
       </c>
@@ -2748,7 +2817,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>6</v>
       </c>
@@ -2810,7 +2879,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>6</v>
       </c>
@@ -2872,7 +2941,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>6</v>
       </c>
@@ -2934,7 +3003,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>6</v>
       </c>
@@ -2996,7 +3065,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>6</v>
       </c>
@@ -3058,7 +3127,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>6</v>
       </c>
@@ -3120,7 +3189,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>7</v>
       </c>
@@ -3182,7 +3251,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>7</v>
       </c>
@@ -3244,7 +3313,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>7</v>
       </c>
@@ -3306,7 +3375,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>7</v>
       </c>
@@ -3368,7 +3437,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>7</v>
       </c>
@@ -3430,7 +3499,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>7</v>
       </c>
@@ -3492,7 +3561,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>7</v>
       </c>
@@ -3554,7 +3623,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>7</v>
       </c>
@@ -3616,7 +3685,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>7</v>
       </c>
@@ -3678,7 +3747,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>7</v>
       </c>
@@ -3740,7 +3809,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>7</v>
       </c>
@@ -3802,7 +3871,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>7</v>
       </c>
@@ -3864,7 +3933,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>7</v>
       </c>
@@ -3926,7 +3995,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>7</v>
       </c>
@@ -3988,7 +4057,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>7</v>
       </c>
@@ -4050,7 +4119,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>8</v>
       </c>
@@ -4112,7 +4181,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>8</v>
       </c>
@@ -4174,7 +4243,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>8</v>
       </c>
@@ -4236,7 +4305,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
@@ -4298,7 +4367,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
@@ -4360,7 +4429,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>8</v>
       </c>
@@ -4422,7 +4491,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>8</v>
       </c>
@@ -4484,7 +4553,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>8</v>
       </c>
@@ -4546,7 +4615,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>8</v>
       </c>
@@ -4608,7 +4677,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>8</v>
       </c>
@@ -4670,7 +4739,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>8</v>
       </c>
@@ -4732,7 +4801,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>8</v>
       </c>
@@ -4794,7 +4863,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>8</v>
       </c>
@@ -4856,7 +4925,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>8</v>
       </c>
@@ -4918,7 +4987,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>8</v>
       </c>
@@ -4980,7 +5049,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>8</v>
       </c>
@@ -5042,7 +5111,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>8</v>
       </c>
@@ -5104,7 +5173,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>8</v>
       </c>
@@ -5166,7 +5235,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>8</v>
       </c>
@@ -5228,7 +5297,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>8</v>
       </c>
@@ -5290,7 +5359,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>8</v>
       </c>
@@ -5352,7 +5421,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>8</v>
       </c>
@@ -5414,7 +5483,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>8</v>
       </c>
@@ -5476,7 +5545,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>8</v>
       </c>
@@ -5538,7 +5607,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>8</v>
       </c>
@@ -5600,7 +5669,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>8</v>
       </c>
@@ -5662,7 +5731,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>8</v>
       </c>
@@ -5724,7 +5793,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>8</v>
       </c>
@@ -5786,7 +5855,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>8</v>
       </c>
@@ -5848,7 +5917,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>8</v>
       </c>
@@ -5910,7 +5979,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>8</v>
       </c>
@@ -5972,7 +6041,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>8</v>
       </c>
@@ -6034,7 +6103,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>8</v>
       </c>
@@ -6096,7 +6165,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>8</v>
       </c>
@@ -6158,7 +6227,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>8</v>
       </c>
@@ -6220,7 +6289,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>8</v>
       </c>
@@ -6282,7 +6351,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>8</v>
       </c>
@@ -6344,7 +6413,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>8</v>
       </c>
@@ -6406,7 +6475,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>8</v>
       </c>
@@ -6468,7 +6537,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>8</v>
       </c>
@@ -6530,7 +6599,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>9</v>
       </c>
@@ -6592,7 +6661,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>9</v>
       </c>
@@ -6654,7 +6723,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>9</v>
       </c>
@@ -6716,7 +6785,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>9</v>
       </c>
@@ -6778,7 +6847,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>9</v>
       </c>
@@ -6840,7 +6909,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>9</v>
       </c>
@@ -6902,7 +6971,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>9</v>
       </c>
@@ -6964,7 +7033,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>9</v>
       </c>
@@ -7026,7 +7095,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>9</v>
       </c>
@@ -7088,7 +7157,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>9</v>
       </c>
@@ -7150,7 +7219,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>9</v>
       </c>
@@ -7212,7 +7281,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>9</v>
       </c>
@@ -7274,7 +7343,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>9</v>
       </c>
@@ -7336,7 +7405,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>9</v>
       </c>
@@ -7398,7 +7467,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>9</v>
       </c>
@@ -7460,7 +7529,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>9</v>
       </c>
@@ -7522,7 +7591,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>9</v>
       </c>
@@ -7584,7 +7653,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>9</v>
       </c>
@@ -7646,7 +7715,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>9</v>
       </c>
@@ -7708,7 +7777,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>9</v>
       </c>
@@ -7770,7 +7839,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>9</v>
       </c>
@@ -7832,7 +7901,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>9</v>
       </c>
@@ -7894,7 +7963,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>9</v>
       </c>
@@ -7967,75 +8036,75 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3ED9FF6-8968-4FA6-BAEC-B95365AA2886}">
   <dimension ref="A1:O55"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="8.19921875" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.69921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="23.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.59765625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.25" customWidth="1"/>
+    <col min="12" max="12" width="11.3984375" customWidth="1"/>
+    <col min="13" max="13" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>190</v>
-      </c>
       <c r="D1" s="4" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>42</v>
       </c>
       <c r="F1" s="4" t="str">
-        <f>LEFT(E1,LEN(E1)-5)&amp;VLOOKUP(LEFT(E1,LEN(E1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
-        <v>top_zand</v>
+        <f>LEFT(E1,LEN(E1)-5)&amp;VLOOKUP(LEFT(E1,LEN(E1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
+        <v>top_zand_stdev</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>43</v>
       </c>
       <c r="H1" s="4" t="str">
-        <f>LEFT(G1,LEN(G1)-5)&amp;VLOOKUP(LEFT(G1,LEN(G1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+        <f>LEFT(G1,LEN(G1)-5)&amp;VLOOKUP(LEFT(G1,LEN(G1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>gamma_sat_deklaag_stdev</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>44</v>
       </c>
       <c r="J1" s="4" t="str">
-        <f>LEFT(I1,LEN(I1)-5)&amp;VLOOKUP(LEFT(I1,LEN(I1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+        <f>LEFT(I1,LEN(I1)-5)&amp;VLOOKUP(LEFT(I1,LEN(I1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>D_wvp_stdev</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L1" s="4" t="str">
-        <f>LEFT(K1,LEN(K1)-5)&amp;VLOOKUP(LEFT(K1,LEN(K1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+        <f>LEFT(K1,LEN(K1)-5)&amp;VLOOKUP(LEFT(K1,LEN(K1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>kD_wvp_vc</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="7" t="s">
         <v>46</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>47</v>
       </c>
       <c r="O1" s="4" t="str">
-        <f>LEFT(N1,LEN(N1)-5)&amp;VLOOKUP(LEFT(N1,LEN(N1)-5),Overzicht_variabelen!$A$2:$F$55,6,(FALSE))</f>
+        <f>LEFT(N1,LEN(N1)-5)&amp;VLOOKUP(LEFT(N1,LEN(N1)-5),Overzicht_variabelen!$A$2:$F$69,6,(FALSE))</f>
         <v>d70_vc</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -8072,7 +8141,7 @@
       <c r="L2">
         <v>0.39</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="6">
         <v>56</v>
       </c>
       <c r="N2" s="1">
@@ -8082,7 +8151,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8119,7 +8188,7 @@
       <c r="L3">
         <v>0.35</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="6">
         <v>52</v>
       </c>
       <c r="N3" s="1">
@@ -8129,7 +8198,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -8167,7 +8236,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -8200,7 +8269,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
@@ -8233,7 +8302,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
@@ -8266,7 +8335,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2</v>
       </c>
@@ -8303,7 +8372,7 @@
       <c r="L8">
         <v>0.39</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="6">
         <v>56</v>
       </c>
       <c r="N8" s="1">
@@ -8313,7 +8382,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2</v>
       </c>
@@ -8350,7 +8419,7 @@
       <c r="L9">
         <v>0.35</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="6">
         <v>52</v>
       </c>
       <c r="N9" s="1">
@@ -8360,7 +8429,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2</v>
       </c>
@@ -8398,7 +8467,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2</v>
       </c>
@@ -8431,7 +8500,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
@@ -8464,7 +8533,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
@@ -8497,7 +8566,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>3</v>
       </c>
@@ -8534,7 +8603,7 @@
       <c r="L14">
         <v>0.39</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="6">
         <v>56</v>
       </c>
       <c r="N14" s="1">
@@ -8544,7 +8613,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>3</v>
       </c>
@@ -8581,7 +8650,7 @@
       <c r="L15">
         <v>0.35</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="6">
         <v>52</v>
       </c>
       <c r="N15" s="1">
@@ -8591,7 +8660,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>3</v>
       </c>
@@ -8629,7 +8698,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>3</v>
       </c>
@@ -8662,7 +8731,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>3</v>
       </c>
@@ -8695,7 +8764,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3</v>
       </c>
@@ -8728,7 +8797,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>4</v>
       </c>
@@ -8765,7 +8834,7 @@
       <c r="L20">
         <v>0.39</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="6">
         <v>56</v>
       </c>
       <c r="N20" s="1">
@@ -8775,7 +8844,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>4</v>
       </c>
@@ -8812,7 +8881,7 @@
       <c r="L21">
         <v>0.35</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="6">
         <v>52</v>
       </c>
       <c r="N21" s="1">
@@ -8822,7 +8891,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>4</v>
       </c>
@@ -8860,7 +8929,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>4</v>
       </c>
@@ -8893,7 +8962,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>4</v>
       </c>
@@ -8926,7 +8995,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>4</v>
       </c>
@@ -8959,7 +9028,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>5</v>
       </c>
@@ -8996,7 +9065,7 @@
       <c r="L26">
         <v>0.39</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="6">
         <v>56</v>
       </c>
       <c r="N26" s="1">
@@ -9006,7 +9075,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>5</v>
       </c>
@@ -9043,7 +9112,7 @@
       <c r="L27">
         <v>0.35</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="6">
         <v>52</v>
       </c>
       <c r="N27" s="1">
@@ -9053,7 +9122,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>5</v>
       </c>
@@ -9091,7 +9160,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>5</v>
       </c>
@@ -9124,7 +9193,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>5</v>
       </c>
@@ -9157,7 +9226,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>5</v>
       </c>
@@ -9190,7 +9259,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>6</v>
       </c>
@@ -9227,7 +9296,7 @@
       <c r="L32">
         <v>0.39</v>
       </c>
-      <c r="M32">
+      <c r="M32" s="6">
         <v>56</v>
       </c>
       <c r="N32" s="1">
@@ -9237,7 +9306,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>6</v>
       </c>
@@ -9274,7 +9343,7 @@
       <c r="L33">
         <v>0.35</v>
       </c>
-      <c r="M33">
+      <c r="M33" s="6">
         <v>52</v>
       </c>
       <c r="N33" s="1">
@@ -9284,7 +9353,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>6</v>
       </c>
@@ -9322,7 +9391,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>6</v>
       </c>
@@ -9355,7 +9424,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>6</v>
       </c>
@@ -9388,7 +9457,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
@@ -9421,7 +9490,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>7</v>
       </c>
@@ -9458,7 +9527,7 @@
       <c r="L38">
         <v>0.39</v>
       </c>
-      <c r="M38">
+      <c r="M38" s="6">
         <v>56</v>
       </c>
       <c r="N38" s="1">
@@ -9468,7 +9537,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>7</v>
       </c>
@@ -9505,7 +9574,7 @@
       <c r="L39">
         <v>0.35</v>
       </c>
-      <c r="M39">
+      <c r="M39" s="6">
         <v>52</v>
       </c>
       <c r="N39" s="1">
@@ -9515,7 +9584,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>7</v>
       </c>
@@ -9553,7 +9622,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
@@ -9586,7 +9655,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
@@ -9619,7 +9688,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
@@ -9652,7 +9721,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>8</v>
       </c>
@@ -9689,7 +9758,7 @@
       <c r="L44">
         <v>0.39</v>
       </c>
-      <c r="M44">
+      <c r="M44" s="6">
         <v>56</v>
       </c>
       <c r="N44" s="1">
@@ -9699,7 +9768,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>8</v>
       </c>
@@ -9736,7 +9805,7 @@
       <c r="L45">
         <v>0.35</v>
       </c>
-      <c r="M45">
+      <c r="M45" s="6">
         <v>52</v>
       </c>
       <c r="N45" s="1">
@@ -9746,7 +9815,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>8</v>
       </c>
@@ -9784,7 +9853,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>8</v>
       </c>
@@ -9817,7 +9886,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>8</v>
       </c>
@@ -9850,7 +9919,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>8</v>
       </c>
@@ -9883,7 +9952,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>9</v>
       </c>
@@ -9920,7 +9989,7 @@
       <c r="L50">
         <v>0.39</v>
       </c>
-      <c r="M50">
+      <c r="M50" s="6">
         <v>56</v>
       </c>
       <c r="N50" s="1">
@@ -9930,7 +9999,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>9</v>
       </c>
@@ -9967,7 +10036,7 @@
       <c r="L51">
         <v>0.35</v>
       </c>
-      <c r="M51">
+      <c r="M51" s="6">
         <v>52</v>
       </c>
       <c r="N51" s="1">
@@ -9977,7 +10046,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>9</v>
       </c>
@@ -10015,7 +10084,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>9</v>
       </c>
@@ -10048,7 +10117,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>9</v>
       </c>
@@ -10081,7 +10150,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>9</v>
       </c>
@@ -10124,1132 +10193,998 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B7A8CE-63DA-4EEA-9A88-5E62FD2B5E40}">
-  <dimension ref="A1:R55"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:R69"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="17.19921875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.19921875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="47.625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.25" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="47.59765625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.19921875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>204</v>
-      </c>
       <c r="R1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>218</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" t="s">
-        <v>114</v>
+        <v>212</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="K2" s="2"/>
+      <c r="R2" t="s">
         <v>56</v>
       </c>
-      <c r="M2" t="s">
-        <v>56</v>
-      </c>
-      <c r="N2" t="s">
-        <v>56</v>
-      </c>
-      <c r="O2" t="s">
-        <v>56</v>
-      </c>
-      <c r="R2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>219</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" t="s">
-        <v>59</v>
+        <v>211</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F4" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6" t="s">
+        <v>213</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" t="s">
-        <v>56</v>
-      </c>
-      <c r="O4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="J5" s="2">
-        <v>60</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="O5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>172</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.4999999999999999E-4</v>
-      </c>
-      <c r="J6" s="1">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="O6" t="s">
-        <v>56</v>
-      </c>
-      <c r="P6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
+        <v>221</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>217</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I7" s="2">
-        <v>10</v>
-      </c>
-      <c r="J7" s="2">
-        <v>22</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
+        <v>212</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>222</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="J8" s="2">
-        <v>4000</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L8" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" t="s">
-        <v>56</v>
-      </c>
-      <c r="N8" t="s">
-        <v>56</v>
-      </c>
-      <c r="O8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
+        <v>209</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>178</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>223</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
-        <v>5000</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M9" t="s">
-        <v>56</v>
-      </c>
-      <c r="N9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
+        <v>210</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>173</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>224</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L10" t="s">
-        <v>56</v>
-      </c>
-      <c r="M10" t="s">
-        <v>56</v>
-      </c>
-      <c r="N10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N11" t="s">
-        <v>56</v>
-      </c>
-      <c r="O11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" t="s">
-        <v>54</v>
-      </c>
-      <c r="I12" s="2">
-        <v>5</v>
-      </c>
-      <c r="J12" s="2">
-        <v>2000</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L12" t="s">
-        <v>56</v>
-      </c>
-      <c r="M12" t="s">
-        <v>56</v>
-      </c>
-      <c r="N12" t="s">
-        <v>56</v>
-      </c>
-      <c r="O12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.15">
+        <v>175</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="B13" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="3">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>0.1</v>
+        <v>212</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>180</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>220</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <v>0.12</v>
+        <v>211</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="O14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>215</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" t="s">
-        <v>87</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1</v>
-      </c>
-      <c r="H15">
-        <v>0.1</v>
+        <v>214</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
-      <c r="K15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
+        <v>199</v>
+      </c>
+      <c r="L16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16" t="s">
+        <v>54</v>
+      </c>
+      <c r="O16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" t="s">
+        <v>56</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="L17" t="s">
         <v>54</v>
       </c>
-      <c r="I17" s="2">
-        <v>-4</v>
-      </c>
-      <c r="J17" s="2">
-        <v>15</v>
-      </c>
-      <c r="K17" s="2" t="s">
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" t="s">
         <v>55</v>
-      </c>
-      <c r="O17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" t="s">
-        <v>54</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="L18" t="s">
+        <v>54</v>
+      </c>
+      <c r="O18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" t="s">
         <v>55</v>
       </c>
-      <c r="L18" t="s">
+      <c r="I19" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="J19" s="2">
+        <v>60</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" t="s">
         <v>56</v>
       </c>
-      <c r="M18" t="s">
+      <c r="I20" s="1">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="J20" s="1">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="O20" t="s">
+        <v>54</v>
+      </c>
+      <c r="P20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" t="s">
+        <v>55</v>
+      </c>
+      <c r="I21" s="2">
+        <v>10</v>
+      </c>
+      <c r="J21" s="2">
+        <v>22</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" t="s">
         <v>56</v>
       </c>
-      <c r="N18" t="s">
-        <v>56</v>
-      </c>
-      <c r="O18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A19" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="I22" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="J22" s="2">
+        <v>4000</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="L22" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" t="s">
+        <v>54</v>
+      </c>
+      <c r="N22" t="s">
+        <v>54</v>
+      </c>
+      <c r="O22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" t="s">
+        <v>205</v>
+      </c>
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" t="s">
         <v>53</v>
       </c>
-      <c r="E19" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" s="2">
-        <v>-18</v>
-      </c>
-      <c r="J19" s="2">
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
+        <v>5000</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L23" t="s">
+        <v>54</v>
+      </c>
+      <c r="M23" t="s">
+        <v>54</v>
+      </c>
+      <c r="N23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" t="s">
+        <v>206</v>
+      </c>
+      <c r="C24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="L24" t="s">
+        <v>54</v>
+      </c>
+      <c r="M24" t="s">
+        <v>54</v>
+      </c>
+      <c r="N24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" t="s">
+        <v>207</v>
+      </c>
+      <c r="C25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" t="s">
+        <v>53</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="L25" t="s">
+        <v>54</v>
+      </c>
+      <c r="M25" t="s">
+        <v>54</v>
+      </c>
+      <c r="N25" t="s">
+        <v>54</v>
+      </c>
+      <c r="O25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>15</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="O19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A20" t="s">
-        <v>130</v>
-      </c>
-      <c r="B20" t="s">
-        <v>131</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B26" t="s">
+        <v>208</v>
+      </c>
+      <c r="C26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" t="s">
         <v>52</v>
       </c>
-      <c r="D20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="E26" t="s">
+        <v>53</v>
+      </c>
+      <c r="I26" s="2">
+        <v>5</v>
+      </c>
+      <c r="J26" s="2">
+        <v>2000</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="L26" t="s">
         <v>54</v>
       </c>
-      <c r="G20" s="1">
-        <v>2.0799999999999999E-4</v>
-      </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="O20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" t="s">
-        <v>116</v>
-      </c>
-      <c r="C21" t="s">
-        <v>104</v>
-      </c>
-      <c r="D21" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="M26" t="s">
         <v>54</v>
       </c>
-      <c r="G21">
-        <v>0.25</v>
-      </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A22" t="s">
-        <v>132</v>
-      </c>
-      <c r="B22" t="s">
-        <v>133</v>
-      </c>
-      <c r="C22" t="s">
-        <v>134</v>
-      </c>
-      <c r="D22" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="N26" t="s">
         <v>54</v>
       </c>
-      <c r="G22">
-        <v>9.81</v>
-      </c>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="O22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A23" t="s">
-        <v>138</v>
-      </c>
-      <c r="B23" t="s">
-        <v>139</v>
-      </c>
-      <c r="C23" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="O26" t="s">
         <v>54</v>
       </c>
-      <c r="G23" s="2">
-        <v>26</v>
-      </c>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="O23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A24" t="s">
-        <v>81</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" t="s">
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C27" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" t="s">
+        <v>55</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>0.1</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="N27" t="s">
         <v>54</v>
       </c>
-      <c r="G24">
-        <v>9.81</v>
-      </c>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A25" t="s">
-        <v>178</v>
-      </c>
-      <c r="B25" t="s">
-        <v>179</v>
-      </c>
-      <c r="C25" t="s">
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" t="s">
         <v>52</v>
       </c>
-      <c r="D25" t="s">
-        <v>83</v>
-      </c>
-      <c r="G25">
-        <v>1.5</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A26" t="s">
-        <v>108</v>
-      </c>
-      <c r="B26" t="s">
-        <v>109</v>
-      </c>
-      <c r="C26" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" t="s">
-        <v>83</v>
-      </c>
-      <c r="E26" t="s">
-        <v>87</v>
-      </c>
-      <c r="F26" t="s">
-        <v>57</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="H26" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="N26" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A27" t="s">
-        <v>174</v>
-      </c>
-      <c r="B27" t="s">
-        <v>175</v>
-      </c>
-      <c r="C27" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" t="s">
-        <v>83</v>
-      </c>
-      <c r="G27">
-        <v>0.1</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A28" t="s">
-        <v>176</v>
-      </c>
-      <c r="B28" t="s">
-        <v>177</v>
-      </c>
-      <c r="C28" t="s">
-        <v>92</v>
-      </c>
-      <c r="D28" t="s">
-        <v>83</v>
-      </c>
-      <c r="G28">
-        <v>0.01</v>
-      </c>
+      <c r="E28" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G28" s="3">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>0.12</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
+        <v>199</v>
+      </c>
+      <c r="O28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E29" t="s">
-        <v>54</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="H29" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="F29" t="s">
+        <v>55</v>
+      </c>
+      <c r="G29" s="3">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>0.1</v>
+      </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="O29" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
+        <v>199</v>
+      </c>
+      <c r="M29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>129</v>
+        <v>58</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E30" t="s">
-        <v>54</v>
-      </c>
-      <c r="G30" s="2">
-        <v>37</v>
-      </c>
-      <c r="H30" s="2"/>
+        <v>53</v>
+      </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="O30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="C31" t="s">
-        <v>137</v>
+        <v>58</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E31" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31" s="2">
+        <v>-4</v>
+      </c>
+      <c r="J31" s="2">
+        <v>15</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="O31" t="s">
         <v>54</v>
       </c>
-      <c r="G31" s="1">
-        <v>1.33E-6</v>
-      </c>
-      <c r="H31" s="1"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="O31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" t="s">
+        <v>203</v>
+      </c>
+      <c r="C32" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" t="s">
+        <v>53</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="L32" t="s">
+        <v>54</v>
+      </c>
+      <c r="M32" t="s">
+        <v>54</v>
+      </c>
+      <c r="N32" t="s">
+        <v>54</v>
+      </c>
+      <c r="O32" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I33" s="2">
+        <v>-18</v>
+      </c>
+      <c r="J33" s="2">
+        <v>15</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>120</v>
+      </c>
+      <c r="B34" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" t="s">
         <v>75</v>
       </c>
-      <c r="B32" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32" t="s">
-        <v>78</v>
-      </c>
-      <c r="I32" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A33" t="s">
-        <v>79</v>
-      </c>
-      <c r="B33" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" t="s">
-        <v>77</v>
-      </c>
-      <c r="E33" t="s">
-        <v>78</v>
-      </c>
-      <c r="I33" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A34" t="s">
-        <v>146</v>
-      </c>
-      <c r="B34" t="s">
-        <v>147</v>
-      </c>
-      <c r="C34" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" t="s">
-        <v>77</v>
-      </c>
+      <c r="E34" t="s">
+        <v>53</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2.0799999999999999E-4</v>
+      </c>
+      <c r="H34" s="1"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
+      <c r="K34" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="O34" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>77</v>
+        <v>75</v>
+      </c>
+      <c r="E35" t="s">
+        <v>53</v>
+      </c>
+      <c r="G35">
+        <v>0.25</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="O35" t="s">
+      <c r="K35" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A36" t="s">
-        <v>140</v>
-      </c>
-      <c r="B36" t="s">
-        <v>141</v>
-      </c>
-      <c r="C36" t="s">
-        <v>52</v>
-      </c>
       <c r="D36" t="s">
-        <v>77</v>
+        <v>75</v>
+      </c>
+      <c r="E36" t="s">
+        <v>53</v>
+      </c>
+      <c r="G36">
+        <v>9.81</v>
       </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="M36" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K36" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="O36" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="B37" t="s">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="D37" t="s">
-        <v>77</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="E37" t="s">
+        <v>53</v>
+      </c>
+      <c r="G37" s="2">
+        <v>26</v>
+      </c>
+      <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="N37" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K37" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="O37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>172</v>
+        <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>173</v>
+        <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="D38" t="s">
-        <v>77</v>
+        <v>75</v>
+      </c>
+      <c r="E38" t="s">
+        <v>53</v>
+      </c>
+      <c r="G38">
+        <v>9.81</v>
       </c>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="O38" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K38" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>168</v>
       </c>
@@ -11257,360 +11192,734 @@
         <v>169</v>
       </c>
       <c r="C39" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="D39" t="s">
-        <v>77</v>
-      </c>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="M39" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
+        <v>75</v>
+      </c>
+      <c r="G39">
+        <v>1.5</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="D40" t="s">
-        <v>77</v>
+        <v>75</v>
+      </c>
+      <c r="E40" t="s">
+        <v>79</v>
+      </c>
+      <c r="F40" t="s">
+        <v>55</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H40" s="2">
+        <v>0.1</v>
       </c>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="O40" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K40" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="N40" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="B41" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="C41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" t="s">
+        <v>75</v>
+      </c>
+      <c r="G41">
+        <v>0.1</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>166</v>
+      </c>
+      <c r="B42" t="s">
+        <v>167</v>
+      </c>
+      <c r="C42" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42" t="s">
+        <v>75</v>
+      </c>
+      <c r="G42">
+        <v>0.01</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43" t="s">
         <v>104</v>
       </c>
-      <c r="D41" t="s">
-        <v>77</v>
-      </c>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="N41" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A42" t="s">
-        <v>90</v>
-      </c>
-      <c r="B42" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" t="s">
-        <v>92</v>
-      </c>
-      <c r="D42" t="s">
-        <v>77</v>
-      </c>
-      <c r="I42" s="2">
-        <v>1</v>
-      </c>
-      <c r="J42" s="2">
-        <v>110</v>
-      </c>
-      <c r="K42" s="2"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A43" t="s">
-        <v>158</v>
-      </c>
-      <c r="B43" t="s">
-        <v>159</v>
-      </c>
       <c r="C43" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="D43" t="s">
-        <v>77</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="E43" t="s">
+        <v>53</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K43" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="O43" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B44" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C44" t="s">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="D44" t="s">
-        <v>77</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="E44" t="s">
+        <v>53</v>
+      </c>
+      <c r="G44" s="2">
+        <v>37</v>
+      </c>
+      <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
+      <c r="K44" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="O44" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="B45" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="C45" t="s">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="D45" t="s">
-        <v>77</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="E45" t="s">
+        <v>53</v>
+      </c>
+      <c r="G45" s="1">
+        <v>1.33E-6</v>
+      </c>
+      <c r="H45" s="1"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K45" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="O45" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>67</v>
       </c>
       <c r="B46" t="s">
-        <v>163</v>
+        <v>68</v>
       </c>
       <c r="C46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D46" t="s">
-        <v>77</v>
-      </c>
-      <c r="I46" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="E46" t="s">
+        <v>70</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0.1</v>
+      </c>
       <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A47" t="s">
-        <v>160</v>
-      </c>
-      <c r="B47" t="s">
-        <v>161</v>
-      </c>
-      <c r="C47" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" t="s">
-        <v>77</v>
-      </c>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K46" s="8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I47" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="C48" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D48" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" t="s">
-        <v>119</v>
-      </c>
-      <c r="M48" t="s">
-        <v>56</v>
-      </c>
-      <c r="N48" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K48" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="O48" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="B49" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="C49" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="D49" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K49" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="O49" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="B50" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="C50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D50" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K50" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="M50" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B51" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C51" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="D51" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="L51" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K51" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="N51" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B52" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C52" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D52" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="M52" t="s">
-        <v>56</v>
-      </c>
-      <c r="N52" t="s">
-        <v>56</v>
+      <c r="K52" s="8" t="s">
+        <v>225</v>
       </c>
       <c r="O52" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B53" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C53" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D53" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="N53" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="K53" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="M53" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="B54" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="C54" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="D54" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
+      <c r="K54" s="8" t="s">
+        <v>225</v>
+      </c>
       <c r="O54" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B55" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="C55" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D55" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-      <c r="M55" t="s">
-        <v>119</v>
+      <c r="K55" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="N55" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>82</v>
+      </c>
+      <c r="B56" t="s">
+        <v>83</v>
+      </c>
+      <c r="C56" t="s">
+        <v>84</v>
+      </c>
+      <c r="D56" t="s">
+        <v>69</v>
+      </c>
+      <c r="I56" s="2">
+        <v>1</v>
+      </c>
+      <c r="J56" s="2">
+        <v>110</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>148</v>
+      </c>
+      <c r="B57" t="s">
+        <v>149</v>
+      </c>
+      <c r="C57" t="s">
+        <v>51</v>
+      </c>
+      <c r="D57" t="s">
+        <v>69</v>
+      </c>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="L57" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" t="s">
+        <v>51</v>
+      </c>
+      <c r="D58" t="s">
+        <v>69</v>
+      </c>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="O58" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>146</v>
+      </c>
+      <c r="B59" t="s">
+        <v>147</v>
+      </c>
+      <c r="C59" t="s">
+        <v>51</v>
+      </c>
+      <c r="D59" t="s">
+        <v>69</v>
+      </c>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="L59" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>152</v>
+      </c>
+      <c r="B60" t="s">
+        <v>153</v>
+      </c>
+      <c r="C60" t="s">
+        <v>51</v>
+      </c>
+      <c r="D60" t="s">
+        <v>69</v>
+      </c>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="L60" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>150</v>
+      </c>
+      <c r="B61" t="s">
+        <v>151</v>
+      </c>
+      <c r="C61" t="s">
+        <v>51</v>
+      </c>
+      <c r="D61" t="s">
+        <v>69</v>
+      </c>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="L61" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>111</v>
+      </c>
+      <c r="B62" t="s">
+        <v>202</v>
+      </c>
+      <c r="C62" t="s">
+        <v>58</v>
+      </c>
+      <c r="D62" t="s">
+        <v>69</v>
+      </c>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="L62" t="s">
+        <v>110</v>
+      </c>
+      <c r="M62" t="s">
+        <v>54</v>
+      </c>
+      <c r="N62" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>109</v>
+      </c>
+      <c r="B63" t="s">
+        <v>200</v>
+      </c>
+      <c r="C63" t="s">
+        <v>96</v>
+      </c>
+      <c r="D63" t="s">
+        <v>69</v>
+      </c>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="L63" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>156</v>
+      </c>
+      <c r="B64" t="s">
+        <v>157</v>
+      </c>
+      <c r="C64" t="s">
+        <v>51</v>
+      </c>
+      <c r="D64" t="s">
+        <v>69</v>
+      </c>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="L64" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>154</v>
+      </c>
+      <c r="B65" t="s">
+        <v>155</v>
+      </c>
+      <c r="C65" t="s">
+        <v>51</v>
+      </c>
+      <c r="D65" t="s">
+        <v>69</v>
+      </c>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="L65" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>144</v>
+      </c>
+      <c r="B66" t="s">
+        <v>145</v>
+      </c>
+      <c r="C66" t="s">
+        <v>96</v>
+      </c>
+      <c r="D66" t="s">
+        <v>69</v>
+      </c>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="M66" t="s">
+        <v>54</v>
+      </c>
+      <c r="N66" t="s">
+        <v>54</v>
+      </c>
+      <c r="O66" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67" t="s">
+        <v>141</v>
+      </c>
+      <c r="C67" t="s">
+        <v>96</v>
+      </c>
+      <c r="D67" t="s">
+        <v>69</v>
+      </c>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="N67" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>142</v>
+      </c>
+      <c r="B68" t="s">
+        <v>143</v>
+      </c>
+      <c r="C68" t="s">
+        <v>96</v>
+      </c>
+      <c r="D68" t="s">
+        <v>69</v>
+      </c>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="O68" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>138</v>
+      </c>
+      <c r="B69" t="s">
+        <v>139</v>
+      </c>
+      <c r="C69" t="s">
+        <v>96</v>
+      </c>
+      <c r="D69" t="s">
+        <v>69</v>
+      </c>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="M69" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2 F3:F55" xr:uid="{0C4D3287-2227-4749-A999-A3EC2866277F}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F69" xr:uid="{0C4D3287-2227-4749-A999-A3EC2866277F}">
       <formula1>$R$1:$R$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/workspaces/example_new_calculations/input/input.xlsx
+++ b/workspaces/example_new_calculations/input/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKL\Documents\Github\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A2AD12-6EE9-4727-B2CE-A765F9A6E149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A173DDC1-18B9-4F5D-A0D1-FA1259D2FAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-165" windowWidth="25440" windowHeight="15270" activeTab="3" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
   </bookViews>
   <sheets>
     <sheet name="Vakken" sheetId="1" r:id="rId1"/>
@@ -726,9 +726,6 @@
     <t>parameter_default_value_mean</t>
   </si>
   <si>
-    <t>parameter_default_value_stdev</t>
-  </si>
-  <si>
     <t>parameter_mean_lower_bound</t>
   </si>
   <si>
@@ -739,6 +736,9 @@
   </si>
   <si>
     <t>parameter_name</t>
+  </si>
+  <si>
+    <t>parameter_default_value_spreiding</t>
   </si>
 </sst>
 </file>
@@ -1292,21 +1292,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C253AA-AAA1-47E5-9332-CA169F978D7A}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8.19921875" customWidth="1"/>
-    <col min="2" max="2" width="32.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.19921875" customWidth="1"/>
-    <col min="5" max="5" width="16.59765625" customWidth="1"/>
-    <col min="6" max="6" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.25" customWidth="1"/>
+    <col min="2" max="2" width="32.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.25" customWidth="1"/>
+    <col min="5" max="5" width="16.625" customWidth="1"/>
+    <col min="6" max="6" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.3984375" customWidth="1"/>
+    <col min="9" max="9" width="17.375" customWidth="1"/>
     <col min="10" max="10" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.59765625" customWidth="1"/>
+    <col min="11" max="11" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>158</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>c_achterland_vc</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1669,24 +1669,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB77777-746E-45C0-BE11-D138C11C003A}">
   <dimension ref="A1:N103"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.3984375" customWidth="1"/>
-    <col min="3" max="4" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.375" customWidth="1"/>
+    <col min="3" max="4" width="19.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.8984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.8984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.19921875" customWidth="1"/>
-    <col min="11" max="11" width="19.19921875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.09765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.25" customWidth="1"/>
+    <col min="11" max="11" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>164</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3578,7 +3578,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3886,7 +3886,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3930,7 +3930,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4106,7 +4106,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4414,7 +4414,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4546,7 +4546,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4590,7 +4590,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4766,7 +4766,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4942,7 +4942,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4986,7 +4986,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5030,7 +5030,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5162,7 +5162,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5206,7 +5206,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5382,7 +5382,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5426,7 +5426,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5514,7 +5514,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5646,7 +5646,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5690,7 +5690,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5778,7 +5778,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5822,7 +5822,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5866,7 +5866,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5998,7 +5998,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A99">
         <v>98</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A100">
         <v>100</v>
       </c>
@@ -6086,7 +6086,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A101">
         <v>101</v>
       </c>
@@ -6130,7 +6130,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A102">
         <v>102</v>
       </c>
@@ -6174,7 +6174,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A103">
         <v>103</v>
       </c>
@@ -6229,22 +6229,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3ED9FF6-8968-4FA6-BAEC-B95365AA2886}">
   <dimension ref="A1:N55"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.19921875" customWidth="1"/>
-    <col min="3" max="3" width="21.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="21.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.8984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="23.09765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.3984375" customWidth="1"/>
-    <col min="13" max="13" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.19921875" customWidth="1"/>
+    <col min="12" max="12" width="11.375" customWidth="1"/>
+    <col min="13" max="13" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>167</v>
       </c>
@@ -6293,7 +6293,7 @@
         <v>d70_vc</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6337,7 +6337,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6381,7 +6381,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6419,7 +6419,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6452,7 +6452,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6485,7 +6485,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6518,7 +6518,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -6562,7 +6562,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6606,7 +6606,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -6644,7 +6644,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6787,7 +6787,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6831,7 +6831,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6869,7 +6869,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6935,7 +6935,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6968,7 +6968,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>19</v>
       </c>
@@ -7012,7 +7012,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -7056,7 +7056,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>21</v>
       </c>
@@ -7094,7 +7094,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>22</v>
       </c>
@@ -7127,7 +7127,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>23</v>
       </c>
@@ -7160,7 +7160,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -7193,7 +7193,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>25</v>
       </c>
@@ -7237,7 +7237,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>26</v>
       </c>
@@ -7281,7 +7281,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>27</v>
       </c>
@@ -7319,7 +7319,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>28</v>
       </c>
@@ -7352,7 +7352,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>29</v>
       </c>
@@ -7385,7 +7385,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>30</v>
       </c>
@@ -7418,7 +7418,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>31</v>
       </c>
@@ -7462,7 +7462,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>32</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>33</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>34</v>
       </c>
@@ -7577,7 +7577,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>35</v>
       </c>
@@ -7610,7 +7610,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>36</v>
       </c>
@@ -7643,7 +7643,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>37</v>
       </c>
@@ -7687,7 +7687,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>38</v>
       </c>
@@ -7731,7 +7731,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>39</v>
       </c>
@@ -7769,7 +7769,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>40</v>
       </c>
@@ -7802,7 +7802,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>41</v>
       </c>
@@ -7835,7 +7835,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>42</v>
       </c>
@@ -7868,7 +7868,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>43</v>
       </c>
@@ -7912,7 +7912,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>44</v>
       </c>
@@ -7956,7 +7956,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>45</v>
       </c>
@@ -7994,7 +7994,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>46</v>
       </c>
@@ -8027,7 +8027,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>47</v>
       </c>
@@ -8060,7 +8060,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>48</v>
       </c>
@@ -8093,7 +8093,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>49</v>
       </c>
@@ -8137,7 +8137,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>50</v>
       </c>
@@ -8181,7 +8181,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>51</v>
       </c>
@@ -8219,7 +8219,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>52</v>
       </c>
@@ -8252,7 +8252,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>53</v>
       </c>
@@ -8285,7 +8285,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>54</v>
       </c>
@@ -8329,27 +8329,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B7A8CE-63DA-4EEA-9A88-5E62FD2B5E40}">
   <dimension ref="A1:P69"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.8984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.25" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="17.25" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.19921875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="47.59765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="47.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>222</v>
@@ -8370,16 +8370,16 @@
         <v>227</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>230</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>231</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>170</v>
@@ -8397,7 +8397,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>158</v>
       </c>
@@ -8414,7 +8414,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>159</v>
       </c>
@@ -8431,7 +8431,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -8446,7 +8446,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -8461,7 +8461,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>160</v>
       </c>
@@ -8478,7 +8478,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>164</v>
       </c>
@@ -8495,7 +8495,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>165</v>
       </c>
@@ -8512,7 +8512,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>166</v>
       </c>
@@ -8529,7 +8529,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>161</v>
       </c>
@@ -8546,7 +8546,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>162</v>
       </c>
@@ -8561,7 +8561,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>163</v>
       </c>
@@ -8576,7 +8576,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>167</v>
       </c>
@@ -8593,7 +8593,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>168</v>
       </c>
@@ -8610,7 +8610,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>169</v>
       </c>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -8671,7 +8671,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>80</v>
       </c>
@@ -8699,7 +8699,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>77</v>
       </c>
@@ -8730,7 +8730,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>69</v>
       </c>
@@ -8762,7 +8762,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>74</v>
       </c>
@@ -8797,7 +8797,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -8826,7 +8826,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>66</v>
       </c>
@@ -8867,7 +8867,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -8902,7 +8902,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -8971,7 +8971,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>2</v>
       </c>
@@ -9031,7 +9031,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>19</v>
       </c>
@@ -9060,7 +9060,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>20</v>
       </c>
@@ -9094,7 +9094,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -9126,7 +9126,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>108</v>
       </c>
@@ -9155,7 +9155,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>95</v>
       </c>
@@ -9180,7 +9180,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>110</v>
       </c>
@@ -9208,7 +9208,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>116</v>
       </c>
@@ -9237,7 +9237,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>64</v>
       </c>
@@ -9262,7 +9262,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>156</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -9319,7 +9319,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>152</v>
       </c>
@@ -9345,7 +9345,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>154</v>
       </c>
@@ -9371,7 +9371,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
         <v>91</v>
       </c>
@@ -9400,7 +9400,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
         <v>105</v>
       </c>
@@ -9429,7 +9429,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
         <v>113</v>
       </c>
@@ -9458,7 +9458,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
         <v>85</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
         <v>86</v>
       </c>
@@ -9526,7 +9526,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
         <v>82</v>
       </c>
@@ -9560,7 +9560,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
         <v>60</v>
       </c>
@@ -9582,7 +9582,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
         <v>62</v>
       </c>
@@ -9604,7 +9604,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
         <v>124</v>
       </c>
@@ -9626,7 +9626,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
         <v>120</v>
       </c>
@@ -9648,7 +9648,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
         <v>118</v>
       </c>
@@ -9670,7 +9670,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
         <v>148</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
         <v>150</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
         <v>146</v>
       </c>
@@ -9736,7 +9736,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
         <v>100</v>
       </c>
@@ -9758,7 +9758,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
         <v>122</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A56" t="s">
         <v>71</v>
       </c>
@@ -9799,7 +9799,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A57" t="s">
         <v>136</v>
       </c>
@@ -9821,7 +9821,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
         <v>103</v>
       </c>
@@ -9843,7 +9843,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
         <v>134</v>
       </c>
@@ -9865,7 +9865,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A60" t="s">
         <v>140</v>
       </c>
@@ -9887,7 +9887,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A61" t="s">
         <v>138</v>
       </c>
@@ -9909,7 +9909,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A62" t="s">
         <v>99</v>
       </c>
@@ -9937,7 +9937,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A63" t="s">
         <v>97</v>
       </c>
@@ -9959,7 +9959,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A64" t="s">
         <v>144</v>
       </c>
@@ -9981,7 +9981,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A65" t="s">
         <v>142</v>
       </c>
@@ -10003,7 +10003,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A66" t="s">
         <v>132</v>
       </c>
@@ -10031,7 +10031,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A67" t="s">
         <v>128</v>
       </c>
@@ -10053,7 +10053,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A68" t="s">
         <v>130</v>
       </c>
@@ -10075,7 +10075,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A69" t="s">
         <v>126</v>
       </c>
@@ -10140,13 +10140,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7FD5E8-359B-4F56-B38E-FCA72B85D698}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.69921875" style="7"/>
+    <col min="1" max="1" width="23.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.75" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>218</v>
       </c>
@@ -10157,7 +10157,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>215</v>
       </c>
@@ -10168,7 +10168,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>212</v>
       </c>
@@ -10179,7 +10179,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>211</v>
       </c>
@@ -10190,7 +10190,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>209</v>
       </c>
@@ -10201,7 +10201,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>207</v>
       </c>

--- a/workspaces/example_new_calculations/input/input.xlsx
+++ b/workspaces/example_new_calculations/input/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKL\Documents\Github\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A173DDC1-18B9-4F5D-A0D1-FA1259D2FAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E56C82A-63BE-46A7-885B-71C4D30E5B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
   </bookViews>

--- a/workspaces/example_new_calculations/input/input.xlsx
+++ b/workspaces/example_new_calculations/input/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKL\Documents\Github\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E56C82A-63BE-46A7-885B-71C4D30E5B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B1A6DC-E1F9-4F82-BBF7-9503A7B8D29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
   </bookViews>
   <sheets>
     <sheet name="Vakken" sheetId="1" r:id="rId1"/>
@@ -108,57 +108,12 @@
     <t>&gt;10 m binnenteen</t>
   </si>
   <si>
-    <t>MA_1_41_4_dk_00004</t>
-  </si>
-  <si>
     <t>&lt;10 m binnenteen</t>
   </si>
   <si>
-    <t>MA_1_41_4_dk_00005</t>
-  </si>
-  <si>
-    <t>MA_1_41_4_dk_00006</t>
-  </si>
-  <si>
-    <t>MA_1_41_4_dk_00007</t>
-  </si>
-  <si>
-    <t>MA_1_41_4_dk_00008</t>
-  </si>
-  <si>
-    <t>MA_1_41_4_dk_00009</t>
-  </si>
-  <si>
-    <t>MA_1_41_4_dk_00010</t>
-  </si>
-  <si>
     <t>Watergang</t>
   </si>
   <si>
-    <t>MA_1_41_4_dk_00011</t>
-  </si>
-  <si>
-    <t>MA_1_41_4_dk_00012</t>
-  </si>
-  <si>
-    <t>MA_1_41_4_dk_00013</t>
-  </si>
-  <si>
-    <t>MA_1_41_4_dk_00014</t>
-  </si>
-  <si>
-    <t>MA_1_41_4_dk_00015</t>
-  </si>
-  <si>
-    <t>MA_1_41_4_dk_00016</t>
-  </si>
-  <si>
-    <t>MA_1_41_4_dk_00017</t>
-  </si>
-  <si>
-    <t>MA_1_41_4_dk_00018</t>
-  </si>
-  <si>
     <t>top_zand_mean</t>
   </si>
   <si>
@@ -387,9 +342,6 @@
     <t>Kinematische viscositeit – Sellmeijer</t>
   </si>
   <si>
-    <t>m²/s</t>
-  </si>
-  <si>
     <t>gamma_korrel</t>
   </si>
   <si>
@@ -739,13 +691,61 @@
   </si>
   <si>
     <t>parameter_default_value_spreiding</t>
+  </si>
+  <si>
+    <t>m^2/s</t>
+  </si>
+  <si>
+    <t>MA_1_41-4_dk_00004</t>
+  </si>
+  <si>
+    <t>MA_1_41-4_dk_00005</t>
+  </si>
+  <si>
+    <t>MA_1_41-4_dk_00006</t>
+  </si>
+  <si>
+    <t>MA_1_41-4_dk_00007</t>
+  </si>
+  <si>
+    <t>MA_1_41-4_dk_00008</t>
+  </si>
+  <si>
+    <t>MA_1_41-4_dk_00009</t>
+  </si>
+  <si>
+    <t>MA_1_41-4_dk_00010</t>
+  </si>
+  <si>
+    <t>MA_1_41-4_dk_00011</t>
+  </si>
+  <si>
+    <t>MA_1_41-4_dk_00012</t>
+  </si>
+  <si>
+    <t>MA_1_41-4_dk_00013</t>
+  </si>
+  <si>
+    <t>MA_1_41-4_dk_00014</t>
+  </si>
+  <si>
+    <t>MA_1_41-4_dk_00015</t>
+  </si>
+  <si>
+    <t>MA_1_41-4_dk_00016</t>
+  </si>
+  <si>
+    <t>MA_1_41-4_dk_00017</t>
+  </si>
+  <si>
+    <t>MA_1_41-4_dk_00018</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="9"/>
       <color theme="1"/>
@@ -773,6 +773,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Verdana"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1292,26 +1297,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C253AA-AAA1-47E5-9332-CA169F978D7A}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.25" customWidth="1"/>
-    <col min="2" max="2" width="32.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.25" customWidth="1"/>
-    <col min="5" max="5" width="16.625" customWidth="1"/>
-    <col min="6" max="6" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.19921875" customWidth="1"/>
+    <col min="2" max="2" width="32.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.19921875" customWidth="1"/>
+    <col min="5" max="5" width="16.59765625" customWidth="1"/>
+    <col min="6" max="6" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.09765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.375" customWidth="1"/>
+    <col min="9" max="9" width="17.3984375" customWidth="1"/>
     <col min="10" max="10" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.625" customWidth="1"/>
+    <col min="11" max="11" width="16.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>0</v>
@@ -1320,7 +1325,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>2</v>
@@ -1343,7 +1348,7 @@
         <v>c_achterland_vc</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1378,7 +1383,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1413,7 +1418,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1448,7 +1453,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1483,7 +1488,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1518,7 +1523,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1553,7 +1558,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1588,7 +1593,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1623,7 +1628,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1669,44 +1674,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB77777-746E-45C0-BE11-D138C11C003A}">
   <dimension ref="A1:N103"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.375" customWidth="1"/>
-    <col min="3" max="4" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3984375" customWidth="1"/>
+    <col min="3" max="4" width="19.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.8984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.25" customWidth="1"/>
-    <col min="11" max="11" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.19921875" customWidth="1"/>
+    <col min="11" max="11" width="23.8984375" customWidth="1"/>
+    <col min="12" max="12" width="17.09765625" customWidth="1"/>
+    <col min="13" max="13" width="11.8984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>15</v>
@@ -1718,7 +1723,7 @@
         <v>17</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>18</v>
@@ -1730,7 +1735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1762,7 +1767,7 @@
         <v>90.481999999999999</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>218</v>
       </c>
       <c r="L2">
         <v>13.295</v>
@@ -1774,7 +1779,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1806,7 +1811,7 @@
         <v>47.110999999999997</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>218</v>
       </c>
       <c r="L3">
         <v>13.295</v>
@@ -1818,7 +1823,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1832,7 +1837,7 @@
         <v>418827.85800000001</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4">
         <v>147.995</v>
@@ -1850,7 +1855,7 @@
         <v>3.133</v>
       </c>
       <c r="K4" t="s">
-        <v>22</v>
+        <v>218</v>
       </c>
       <c r="L4">
         <v>13.295</v>
@@ -1862,7 +1867,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1876,7 +1881,7 @@
         <v>418852.74300000002</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>192.261</v>
@@ -1894,7 +1899,7 @@
         <v>3.5219999999999998</v>
       </c>
       <c r="K5" t="s">
-        <v>24</v>
+        <v>219</v>
       </c>
       <c r="L5">
         <v>13.295</v>
@@ -1906,7 +1911,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1938,7 +1943,7 @@
         <v>46.121000000000002</v>
       </c>
       <c r="K6" t="s">
-        <v>22</v>
+        <v>218</v>
       </c>
       <c r="L6">
         <v>13.295</v>
@@ -1950,7 +1955,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1964,7 +1969,7 @@
         <v>418892.50099999999</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7">
         <v>261.37900000000002</v>
@@ -1982,7 +1987,7 @@
         <v>4.4450000000000003</v>
       </c>
       <c r="K7" t="s">
-        <v>24</v>
+        <v>219</v>
       </c>
       <c r="L7">
         <v>13.295</v>
@@ -1994,7 +1999,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2026,7 +2031,7 @@
         <v>35.957999999999998</v>
       </c>
       <c r="K8" t="s">
-        <v>24</v>
+        <v>219</v>
       </c>
       <c r="L8">
         <v>13.295</v>
@@ -2038,7 +2043,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2052,7 +2057,7 @@
         <v>418899.93800000002</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F9">
         <v>277.45100000000002</v>
@@ -2070,7 +2075,7 @@
         <v>2.915</v>
       </c>
       <c r="K9" t="s">
-        <v>24</v>
+        <v>219</v>
       </c>
       <c r="L9">
         <v>13.295</v>
@@ -2082,7 +2087,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2096,7 +2101,7 @@
         <v>418917.386</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F10">
         <v>310.37799999999999</v>
@@ -2114,7 +2119,7 @@
         <v>3.0369999999999999</v>
       </c>
       <c r="K10" t="s">
-        <v>25</v>
+        <v>220</v>
       </c>
       <c r="L10">
         <v>13.287000000000001</v>
@@ -2126,7 +2131,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2140,7 +2145,7 @@
         <v>418947.99099999998</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F11">
         <v>372.47800000000001</v>
@@ -2158,7 +2163,7 @@
         <v>2.4630000000000001</v>
       </c>
       <c r="K11" t="s">
-        <v>26</v>
+        <v>221</v>
       </c>
       <c r="L11">
         <v>13.292999999999999</v>
@@ -2170,7 +2175,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2184,7 +2189,7 @@
         <v>418975.16399999999</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F12">
         <v>431.47</v>
@@ -2202,7 +2207,7 @@
         <v>3.2130000000000001</v>
       </c>
       <c r="K12" t="s">
-        <v>26</v>
+        <v>221</v>
       </c>
       <c r="L12">
         <v>13.292999999999999</v>
@@ -2214,7 +2219,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2246,7 +2251,7 @@
         <v>45.564</v>
       </c>
       <c r="K13" t="s">
-        <v>26</v>
+        <v>221</v>
       </c>
       <c r="L13">
         <v>13.292999999999999</v>
@@ -2258,7 +2263,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2272,7 +2277,7 @@
         <v>418998.86900000001</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F14">
         <v>489.88200000000001</v>
@@ -2290,7 +2295,7 @@
         <v>1.6319999999999999</v>
       </c>
       <c r="K14" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="L14">
         <v>13.292999999999999</v>
@@ -2302,7 +2307,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2316,7 +2321,7 @@
         <v>419025.68400000001</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F15">
         <v>554.654</v>
@@ -2334,7 +2339,7 @@
         <v>2.2530000000000001</v>
       </c>
       <c r="K15" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="L15">
         <v>13.292999999999999</v>
@@ -2346,7 +2351,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2378,7 +2383,7 @@
         <v>25.902000000000001</v>
       </c>
       <c r="K16" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="L16">
         <v>13.292999999999999</v>
@@ -2390,7 +2395,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2404,7 +2409,7 @@
         <v>419047.56599999999</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F17">
         <v>585.04399999999998</v>
@@ -2422,7 +2427,7 @@
         <v>6.2789999999999999</v>
       </c>
       <c r="K17" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="L17">
         <v>13.292999999999999</v>
@@ -2434,7 +2439,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2448,7 +2453,7 @@
         <v>419046.98</v>
       </c>
       <c r="E18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F18">
         <v>592.95100000000002</v>
@@ -2466,7 +2471,7 @@
         <v>3.6560000000000001</v>
       </c>
       <c r="K18" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="L18">
         <v>13.287000000000001</v>
@@ -2478,7 +2483,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2492,7 +2497,7 @@
         <v>419049.81800000003</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F19">
         <v>599.83299999999997</v>
@@ -2510,7 +2515,7 @@
         <v>4.9770000000000003</v>
       </c>
       <c r="K19" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="L19">
         <v>13.287000000000001</v>
@@ -2522,7 +2527,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2536,7 +2541,7 @@
         <v>419060.68699999998</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F20">
         <v>630.61300000000006</v>
@@ -2554,7 +2559,7 @@
         <v>5.0990000000000002</v>
       </c>
       <c r="K20" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="L20">
         <v>13.287000000000001</v>
@@ -2566,7 +2571,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2580,7 +2585,7 @@
         <v>419069.84</v>
       </c>
       <c r="E21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F21">
         <v>646.86800000000005</v>
@@ -2598,7 +2603,7 @@
         <v>7.1630000000000003</v>
       </c>
       <c r="K21" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="L21">
         <v>13.287000000000001</v>
@@ -2610,7 +2615,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2642,7 +2647,7 @@
         <v>11.342000000000001</v>
       </c>
       <c r="K22" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="L22">
         <v>13.287000000000001</v>
@@ -2654,7 +2659,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2686,7 +2691,7 @@
         <v>28.609000000000002</v>
       </c>
       <c r="K23" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="L23">
         <v>13.287000000000001</v>
@@ -2698,7 +2703,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2730,7 +2735,7 @@
         <v>16.428000000000001</v>
       </c>
       <c r="K24" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="L24">
         <v>13.29</v>
@@ -2742,7 +2747,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2756,7 +2761,7 @@
         <v>419087.66700000002</v>
       </c>
       <c r="E25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F25">
         <v>695.95699999999999</v>
@@ -2774,7 +2779,7 @@
         <v>2.2360000000000002</v>
       </c>
       <c r="K25" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="L25">
         <v>13.29</v>
@@ -2786,7 +2791,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2800,7 +2805,7 @@
         <v>419101.538</v>
       </c>
       <c r="E26" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F26">
         <v>703.73099999999999</v>
@@ -2818,7 +2823,7 @@
         <v>10.31</v>
       </c>
       <c r="K26" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="L26">
         <v>13.29</v>
@@ -2830,7 +2835,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2844,7 +2849,7 @@
         <v>419104.837</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F27">
         <v>710.54200000000003</v>
@@ -2862,7 +2867,7 @@
         <v>10.231999999999999</v>
       </c>
       <c r="K27" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="L27">
         <v>13.29</v>
@@ -2874,7 +2879,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2888,7 +2893,7 @@
         <v>419121.408</v>
       </c>
       <c r="E28" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F28">
         <v>738.33199999999999</v>
@@ -2906,7 +2911,7 @@
         <v>10.26</v>
       </c>
       <c r="K28" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="L28">
         <v>13.29</v>
@@ -2918,7 +2923,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2932,7 +2937,7 @@
         <v>419119.15899999999</v>
       </c>
       <c r="E29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F29">
         <v>747.67100000000005</v>
@@ -2950,7 +2955,7 @@
         <v>3.0219999999999998</v>
       </c>
       <c r="K29" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="L29">
         <v>13.29</v>
@@ -2962,7 +2967,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2976,7 +2981,7 @@
         <v>419096.88900000002</v>
       </c>
       <c r="E30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F30">
         <v>707.31399999999996</v>
@@ -2994,7 +2999,7 @@
         <v>2.0760000000000001</v>
       </c>
       <c r="K30" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="L30">
         <v>13.29</v>
@@ -3006,7 +3011,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3020,7 +3025,7 @@
         <v>419109.03600000002</v>
       </c>
       <c r="E31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F31">
         <v>728.125</v>
@@ -3038,7 +3043,7 @@
         <v>2.0449999999999999</v>
       </c>
       <c r="K31" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="L31">
         <v>13.29</v>
@@ -3050,7 +3055,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3064,7 +3069,7 @@
         <v>419132.505</v>
       </c>
       <c r="E32" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F32">
         <v>754.85</v>
@@ -3082,7 +3087,7 @@
         <v>13.978</v>
       </c>
       <c r="K32" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="L32">
         <v>13.29</v>
@@ -3094,7 +3099,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3108,7 +3113,7 @@
         <v>419151.09899999999</v>
       </c>
       <c r="E33" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F33">
         <v>789.178</v>
@@ -3126,7 +3131,7 @@
         <v>13.022</v>
       </c>
       <c r="K33" t="s">
-        <v>31</v>
+        <v>225</v>
       </c>
       <c r="L33">
         <v>13.281000000000001</v>
@@ -3138,7 +3143,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3152,7 +3157,7 @@
         <v>419159.00699999998</v>
       </c>
       <c r="E34" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F34">
         <v>800.52499999999998</v>
@@ -3170,7 +3175,7 @@
         <v>13.021000000000001</v>
       </c>
       <c r="K34" t="s">
-        <v>31</v>
+        <v>225</v>
       </c>
       <c r="L34">
         <v>13.281000000000001</v>
@@ -3182,7 +3187,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3196,7 +3201,7 @@
         <v>419145.946</v>
       </c>
       <c r="E35" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F35">
         <v>780.13199999999995</v>
@@ -3214,7 +3219,7 @@
         <v>13.185</v>
       </c>
       <c r="K35" t="s">
-        <v>31</v>
+        <v>225</v>
       </c>
       <c r="L35">
         <v>13.281000000000001</v>
@@ -3226,7 +3231,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3240,7 +3245,7 @@
         <v>419171.94900000002</v>
       </c>
       <c r="E36" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F36">
         <v>823.99099999999999</v>
@@ -3258,7 +3263,7 @@
         <v>13.202999999999999</v>
       </c>
       <c r="K36" t="s">
-        <v>31</v>
+        <v>225</v>
       </c>
       <c r="L36">
         <v>13.281000000000001</v>
@@ -3270,7 +3275,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3284,7 +3289,7 @@
         <v>419186.44799999997</v>
       </c>
       <c r="E37" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F37">
         <v>847.505</v>
@@ -3302,7 +3307,7 @@
         <v>13.199</v>
       </c>
       <c r="K37" t="s">
-        <v>31</v>
+        <v>225</v>
       </c>
       <c r="L37">
         <v>13.281000000000001</v>
@@ -3314,7 +3319,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3328,7 +3333,7 @@
         <v>419199.03</v>
       </c>
       <c r="E38" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F38">
         <v>868.30799999999999</v>
@@ -3346,7 +3351,7 @@
         <v>13.427</v>
       </c>
       <c r="K38" t="s">
-        <v>31</v>
+        <v>225</v>
       </c>
       <c r="L38">
         <v>13.281000000000001</v>
@@ -3358,7 +3363,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3372,7 +3377,7 @@
         <v>419211.13299999997</v>
       </c>
       <c r="E39" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F39">
         <v>887.98299999999995</v>
@@ -3390,7 +3395,7 @@
         <v>13.805999999999999</v>
       </c>
       <c r="K39" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="L39">
         <v>13.28</v>
@@ -3402,7 +3407,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3416,7 +3421,7 @@
         <v>419222.51699999999</v>
       </c>
       <c r="E40" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F40">
         <v>907.00599999999997</v>
@@ -3434,7 +3439,7 @@
         <v>13.393000000000001</v>
       </c>
       <c r="K40" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="L40">
         <v>13.28</v>
@@ -3446,7 +3451,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3460,7 +3465,7 @@
         <v>419287.82400000002</v>
       </c>
       <c r="E41" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F41">
         <v>997.81200000000001</v>
@@ -3478,7 +3483,7 @@
         <v>25.576000000000001</v>
       </c>
       <c r="K41" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="L41">
         <v>13.284000000000001</v>
@@ -3490,7 +3495,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3504,7 +3509,7 @@
         <v>419301.304</v>
       </c>
       <c r="E42" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F42">
         <v>1015.9160000000001</v>
@@ -3522,7 +3527,7 @@
         <v>27.145</v>
       </c>
       <c r="K42" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="L42">
         <v>13.284000000000001</v>
@@ -3534,7 +3539,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3548,7 +3553,7 @@
         <v>419313.1</v>
       </c>
       <c r="E43" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F43">
         <v>1034.155</v>
@@ -3566,7 +3571,7 @@
         <v>27.32</v>
       </c>
       <c r="K43" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="L43">
         <v>13.284000000000001</v>
@@ -3578,7 +3583,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3592,7 +3597,7 @@
         <v>419322.83600000001</v>
       </c>
       <c r="E44" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F44">
         <v>1048.1289999999999</v>
@@ -3610,7 +3615,7 @@
         <v>27.140999999999998</v>
       </c>
       <c r="K44" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="L44">
         <v>13.284000000000001</v>
@@ -3622,7 +3627,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3636,7 +3641,7 @@
         <v>419331.07400000002</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F45">
         <v>1060.712</v>
@@ -3654,7 +3659,7 @@
         <v>27.53</v>
       </c>
       <c r="K45" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="L45">
         <v>13.284000000000001</v>
@@ -3666,7 +3671,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3680,7 +3685,7 @@
         <v>419338.00199999998</v>
       </c>
       <c r="E46" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F46">
         <v>1070.6469999999999</v>
@@ -3698,7 +3703,7 @@
         <v>27.189</v>
       </c>
       <c r="K46" t="s">
-        <v>34</v>
+        <v>228</v>
       </c>
       <c r="L46">
         <v>13.287000000000001</v>
@@ -3710,7 +3715,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3724,7 +3729,7 @@
         <v>419239.05300000001</v>
       </c>
       <c r="E47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F47">
         <v>936.30600000000004</v>
@@ -3742,7 +3747,7 @@
         <v>9.4960000000000004</v>
       </c>
       <c r="K47" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="L47">
         <v>13.28</v>
@@ -3754,7 +3759,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3768,7 +3773,7 @@
         <v>419252.11499999999</v>
       </c>
       <c r="E48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F48">
         <v>957.68</v>
@@ -3786,7 +3791,7 @@
         <v>8.9510000000000005</v>
       </c>
       <c r="K48" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="L48">
         <v>13.284000000000001</v>
@@ -3798,7 +3803,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3812,7 +3817,7 @@
         <v>419266.85399999999</v>
       </c>
       <c r="E49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F49">
         <v>980.90899999999999</v>
@@ -3830,7 +3835,7 @@
         <v>9.6110000000000007</v>
       </c>
       <c r="K49" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="L49">
         <v>13.284000000000001</v>
@@ -3842,7 +3847,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3874,7 +3879,7 @@
         <v>15.634</v>
       </c>
       <c r="K50" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="L50">
         <v>13.284000000000001</v>
@@ -3886,7 +3891,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3918,7 +3923,7 @@
         <v>14.721</v>
       </c>
       <c r="K51" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="L51">
         <v>13.284000000000001</v>
@@ -3930,7 +3935,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3962,7 +3967,7 @@
         <v>14.151999999999999</v>
       </c>
       <c r="K52" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="L52">
         <v>13.284000000000001</v>
@@ -3974,7 +3979,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3988,7 +3993,7 @@
         <v>419341.74699999997</v>
       </c>
       <c r="E53" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F53">
         <v>1076.2159999999999</v>
@@ -4006,7 +4011,7 @@
         <v>26.984999999999999</v>
       </c>
       <c r="K53" t="s">
-        <v>34</v>
+        <v>228</v>
       </c>
       <c r="L53">
         <v>13.287000000000001</v>
@@ -4018,7 +4023,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4050,7 +4055,7 @@
         <v>39.465000000000003</v>
       </c>
       <c r="K54" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="L54">
         <v>13.284000000000001</v>
@@ -4062,7 +4067,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4094,7 +4099,7 @@
         <v>39.244999999999997</v>
       </c>
       <c r="K55" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="L55">
         <v>13.284000000000001</v>
@@ -4106,7 +4111,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4138,7 +4143,7 @@
         <v>41.247</v>
       </c>
       <c r="K56" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="L56">
         <v>13.284000000000001</v>
@@ -4150,7 +4155,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4164,7 +4169,7 @@
         <v>419346.54</v>
       </c>
       <c r="E57" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F57">
         <v>1082.752</v>
@@ -4182,7 +4187,7 @@
         <v>27.300999999999998</v>
       </c>
       <c r="K57" t="s">
-        <v>34</v>
+        <v>228</v>
       </c>
       <c r="L57">
         <v>13.287000000000001</v>
@@ -4194,7 +4199,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4208,7 +4213,7 @@
         <v>419359.96100000001</v>
       </c>
       <c r="E58" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F58">
         <v>1102.925</v>
@@ -4226,7 +4231,7 @@
         <v>27.064</v>
       </c>
       <c r="K58" t="s">
-        <v>34</v>
+        <v>228</v>
       </c>
       <c r="L58">
         <v>13.287000000000001</v>
@@ -4238,7 +4243,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4252,7 +4257,7 @@
         <v>419373.50099999999</v>
       </c>
       <c r="E59" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F59">
         <v>1121.778</v>
@@ -4270,7 +4275,7 @@
         <v>27.420999999999999</v>
       </c>
       <c r="K59" t="s">
-        <v>34</v>
+        <v>228</v>
       </c>
       <c r="L59">
         <v>13.287000000000001</v>
@@ -4282,7 +4287,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4296,7 +4301,7 @@
         <v>419387.641</v>
       </c>
       <c r="E60" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F60">
         <v>1142.2719999999999</v>
@@ -4314,7 +4319,7 @@
         <v>27.614999999999998</v>
       </c>
       <c r="K60" t="s">
-        <v>34</v>
+        <v>228</v>
       </c>
       <c r="L60">
         <v>13.287000000000001</v>
@@ -4326,7 +4331,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4358,7 +4363,7 @@
         <v>16.472999999999999</v>
       </c>
       <c r="K61" t="s">
-        <v>34</v>
+        <v>228</v>
       </c>
       <c r="L61">
         <v>13.287000000000001</v>
@@ -4370,7 +4375,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4402,7 +4407,7 @@
         <v>17.288</v>
       </c>
       <c r="K62" t="s">
-        <v>34</v>
+        <v>228</v>
       </c>
       <c r="L62">
         <v>13.287000000000001</v>
@@ -4414,7 +4419,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4446,7 +4451,7 @@
         <v>39.094000000000001</v>
       </c>
       <c r="K63" t="s">
-        <v>34</v>
+        <v>228</v>
       </c>
       <c r="L63">
         <v>13.287000000000001</v>
@@ -4458,7 +4463,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4490,7 +4495,7 @@
         <v>39.088000000000001</v>
       </c>
       <c r="K64" t="s">
-        <v>34</v>
+        <v>228</v>
       </c>
       <c r="L64">
         <v>13.287000000000001</v>
@@ -4502,7 +4507,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4516,7 +4521,7 @@
         <v>419404.41700000002</v>
       </c>
       <c r="E65" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F65">
         <v>1165.519</v>
@@ -4534,7 +4539,7 @@
         <v>27.256</v>
       </c>
       <c r="K65" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="L65">
         <v>13.29</v>
@@ -4546,7 +4551,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4560,7 +4565,7 @@
         <v>419422.75099999999</v>
       </c>
       <c r="E66" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F66">
         <v>1190.154</v>
@@ -4578,7 +4583,7 @@
         <v>27.446000000000002</v>
       </c>
       <c r="K66" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="L66">
         <v>13.29</v>
@@ -4590,7 +4595,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4622,7 +4627,7 @@
         <v>16.11</v>
       </c>
       <c r="K67" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="L67">
         <v>13.29</v>
@@ -4634,7 +4639,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4648,7 +4653,7 @@
         <v>419439.76699999999</v>
       </c>
       <c r="E68" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F68">
         <v>1214.1369999999999</v>
@@ -4666,7 +4671,7 @@
         <v>27.241</v>
       </c>
       <c r="K68" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="L68">
         <v>13.29</v>
@@ -4678,7 +4683,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4692,7 +4697,7 @@
         <v>419456.14600000001</v>
       </c>
       <c r="E69" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F69">
         <v>1236.9159999999999</v>
@@ -4710,7 +4715,7 @@
         <v>27.57</v>
       </c>
       <c r="K69" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="L69">
         <v>13.29</v>
@@ -4722,7 +4727,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4736,7 +4741,7 @@
         <v>419472.06099999999</v>
       </c>
       <c r="E70" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F70">
         <v>1256.5050000000001</v>
@@ -4754,7 +4759,7 @@
         <v>28.573</v>
       </c>
       <c r="K70" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="L70">
         <v>13.29</v>
@@ -4766,7 +4771,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4780,7 +4785,7 @@
         <v>419487.03899999999</v>
       </c>
       <c r="E71" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F71">
         <v>1275.7829999999999</v>
@@ -4798,7 +4803,7 @@
         <v>24.151</v>
       </c>
       <c r="K71" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="L71">
         <v>13.29</v>
@@ -4810,7 +4815,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4824,7 +4829,7 @@
         <v>419497.712</v>
       </c>
       <c r="E72" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F72">
         <v>1282.0719999999999</v>
@@ -4842,7 +4847,7 @@
         <v>26.064</v>
       </c>
       <c r="K72" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="L72">
         <v>13.29</v>
@@ -4854,7 +4859,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4868,7 +4873,7 @@
         <v>419503.516</v>
       </c>
       <c r="E73" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F73">
         <v>1278.3689999999999</v>
@@ -4886,7 +4891,7 @@
         <v>41.290999999999997</v>
       </c>
       <c r="K73" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="L73">
         <v>13.29</v>
@@ -4898,7 +4903,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4930,7 +4935,7 @@
         <v>16.7</v>
       </c>
       <c r="K74" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="L74">
         <v>13.29</v>
@@ -4942,7 +4947,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4974,7 +4979,7 @@
         <v>48.253999999999998</v>
       </c>
       <c r="K75" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="L75">
         <v>13.29</v>
@@ -4986,7 +4991,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5018,7 +5023,7 @@
         <v>41.021999999999998</v>
       </c>
       <c r="K76" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="L76">
         <v>13.29</v>
@@ -5030,7 +5035,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5062,7 +5067,7 @@
         <v>43.037999999999997</v>
       </c>
       <c r="K77" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="L77">
         <v>13.29</v>
@@ -5074,7 +5079,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5088,7 +5093,7 @@
         <v>419519.26699999999</v>
       </c>
       <c r="E78" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F78">
         <v>1263.3040000000001</v>
@@ -5106,7 +5111,7 @@
         <v>87.822000000000003</v>
       </c>
       <c r="K78" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="L78">
         <v>13.29</v>
@@ -5118,7 +5123,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5132,7 +5137,7 @@
         <v>419537.11200000002</v>
       </c>
       <c r="E79" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F79">
         <v>1287.1410000000001</v>
@@ -5150,7 +5155,7 @@
         <v>81.563999999999993</v>
       </c>
       <c r="K79" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="L79">
         <v>13.29</v>
@@ -5162,7 +5167,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5176,7 +5181,7 @@
         <v>419526.58100000001</v>
       </c>
       <c r="E80" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F80">
         <v>1301.2470000000001</v>
@@ -5194,7 +5199,7 @@
         <v>41.65</v>
       </c>
       <c r="K80" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="L80">
         <v>13.29</v>
@@ -5206,7 +5211,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5220,7 +5225,7 @@
         <v>419522.19199999998</v>
       </c>
       <c r="E81" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F81">
         <v>1318.586</v>
@@ -5238,7 +5243,7 @@
         <v>12.044</v>
       </c>
       <c r="K81" t="s">
-        <v>36</v>
+        <v>230</v>
       </c>
       <c r="L81">
         <v>13.29</v>
@@ -5250,7 +5255,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5264,7 +5269,7 @@
         <v>419529.21399999998</v>
       </c>
       <c r="E82" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F82">
         <v>1336.444</v>
@@ -5282,7 +5287,7 @@
         <v>8.7789999999999999</v>
       </c>
       <c r="K82" t="s">
-        <v>36</v>
+        <v>230</v>
       </c>
       <c r="L82">
         <v>13.29</v>
@@ -5294,7 +5299,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5308,7 +5313,7 @@
         <v>419553.50699999998</v>
       </c>
       <c r="E83" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F83">
         <v>1366.923</v>
@@ -5326,7 +5331,7 @@
         <v>9.6579999999999995</v>
       </c>
       <c r="K83" t="s">
-        <v>37</v>
+        <v>231</v>
       </c>
       <c r="L83">
         <v>13.29</v>
@@ -5338,7 +5343,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5352,7 +5357,7 @@
         <v>419573.54100000003</v>
       </c>
       <c r="E84" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F84">
         <v>1391.097</v>
@@ -5370,7 +5375,7 @@
         <v>9.3379999999999992</v>
       </c>
       <c r="K84" t="s">
-        <v>37</v>
+        <v>231</v>
       </c>
       <c r="L84">
         <v>13.29</v>
@@ -5382,7 +5387,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5396,7 +5401,7 @@
         <v>419593.38799999998</v>
       </c>
       <c r="E85" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F85">
         <v>1414.4690000000001</v>
@@ -5414,7 +5419,7 @@
         <v>8.4359999999999999</v>
       </c>
       <c r="K85" t="s">
-        <v>37</v>
+        <v>231</v>
       </c>
       <c r="L85">
         <v>13.29</v>
@@ -5426,7 +5431,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5440,7 +5445,7 @@
         <v>419617.353</v>
       </c>
       <c r="E86" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F86">
         <v>1442.1369999999999</v>
@@ -5458,7 +5463,7 @@
         <v>8.3759999999999994</v>
       </c>
       <c r="K86" t="s">
-        <v>37</v>
+        <v>231</v>
       </c>
       <c r="L86">
         <v>13.29</v>
@@ -5470,7 +5475,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5502,7 +5507,7 @@
         <v>34.829000000000001</v>
       </c>
       <c r="K87" t="s">
-        <v>37</v>
+        <v>231</v>
       </c>
       <c r="L87">
         <v>13.29</v>
@@ -5514,7 +5519,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5546,7 +5551,7 @@
         <v>38.756</v>
       </c>
       <c r="K88" t="s">
-        <v>37</v>
+        <v>231</v>
       </c>
       <c r="L88">
         <v>13.29</v>
@@ -5558,7 +5563,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5590,7 +5595,7 @@
         <v>37.752000000000002</v>
       </c>
       <c r="K89" t="s">
-        <v>37</v>
+        <v>231</v>
       </c>
       <c r="L89">
         <v>13.29</v>
@@ -5602,7 +5607,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5634,7 +5639,7 @@
         <v>27.361999999999998</v>
       </c>
       <c r="K90" t="s">
-        <v>36</v>
+        <v>230</v>
       </c>
       <c r="L90">
         <v>13.29</v>
@@ -5646,7 +5651,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5678,7 +5683,7 @@
         <v>40.136000000000003</v>
       </c>
       <c r="K91" t="s">
-        <v>37</v>
+        <v>231</v>
       </c>
       <c r="L91">
         <v>13.29</v>
@@ -5690,7 +5695,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5704,7 +5709,7 @@
         <v>419634.609</v>
       </c>
       <c r="E92" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F92">
         <v>1462.4069999999999</v>
@@ -5722,7 +5727,7 @@
         <v>7.7350000000000003</v>
       </c>
       <c r="K92" t="s">
-        <v>37</v>
+        <v>231</v>
       </c>
       <c r="L92">
         <v>13.29</v>
@@ -5734,7 +5739,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5748,7 +5753,7 @@
         <v>419652.34299999999</v>
       </c>
       <c r="E93" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F93">
         <v>1482.5709999999999</v>
@@ -5766,7 +5771,7 @@
         <v>8.2720000000000002</v>
       </c>
       <c r="K93" t="s">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="L93">
         <v>13.29</v>
@@ -5778,7 +5783,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5792,7 +5797,7 @@
         <v>419666.84299999999</v>
       </c>
       <c r="E94" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F94">
         <v>1498.367</v>
@@ -5810,7 +5815,7 @@
         <v>8.3780000000000001</v>
       </c>
       <c r="K94" t="s">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="L94">
         <v>13.29</v>
@@ -5822,7 +5827,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5836,7 +5841,7 @@
         <v>419680.50300000003</v>
       </c>
       <c r="E95" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F95">
         <v>1513.9159999999999</v>
@@ -5854,7 +5859,7 @@
         <v>8.0960000000000001</v>
       </c>
       <c r="K95" t="s">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="L95">
         <v>13.29</v>
@@ -5866,7 +5871,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5898,7 +5903,7 @@
         <v>47.176000000000002</v>
       </c>
       <c r="K96" t="s">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="L96">
         <v>13.29</v>
@@ -5910,7 +5915,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5942,7 +5947,7 @@
         <v>70.381</v>
       </c>
       <c r="K97" t="s">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="L97">
         <v>13.29</v>
@@ -5954,7 +5959,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5986,7 +5991,7 @@
         <v>64.856999999999999</v>
       </c>
       <c r="K98" t="s">
-        <v>37</v>
+        <v>231</v>
       </c>
       <c r="L98">
         <v>13.29</v>
@@ -5998,7 +6003,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -6012,7 +6017,7 @@
         <v>419689.73</v>
       </c>
       <c r="E99" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F99">
         <v>1524.9290000000001</v>
@@ -6030,7 +6035,7 @@
         <v>8.9260000000000002</v>
       </c>
       <c r="K99" t="s">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="L99">
         <v>13.29</v>
@@ -6042,7 +6047,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>100</v>
       </c>
@@ -6074,7 +6079,7 @@
         <v>23.966999999999999</v>
       </c>
       <c r="K100" t="s">
-        <v>37</v>
+        <v>231</v>
       </c>
       <c r="L100">
         <v>13.29</v>
@@ -6086,7 +6091,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>101</v>
       </c>
@@ -6118,7 +6123,7 @@
         <v>25.442</v>
       </c>
       <c r="K101" t="s">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="L101">
         <v>13.29</v>
@@ -6130,7 +6135,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>102</v>
       </c>
@@ -6162,7 +6167,7 @@
         <v>25.503</v>
       </c>
       <c r="K102" t="s">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="L102">
         <v>13.29</v>
@@ -6174,7 +6179,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>103</v>
       </c>
@@ -6206,7 +6211,7 @@
         <v>26.507999999999999</v>
       </c>
       <c r="K103" t="s">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="L103">
         <v>13.29</v>
@@ -6219,6 +6224,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -6229,71 +6235,71 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3ED9FF6-8968-4FA6-BAEC-B95365AA2886}">
   <dimension ref="A1:N55"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.25" customWidth="1"/>
-    <col min="3" max="3" width="21.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.19921875" customWidth="1"/>
+    <col min="3" max="3" width="21.69921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="23.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.59765625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.375" customWidth="1"/>
-    <col min="13" max="13" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.25" customWidth="1"/>
+    <col min="12" max="12" width="11.3984375" customWidth="1"/>
+    <col min="13" max="13" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F1" s="4" t="str">
         <f>LEFT(E1,LEN(E1)-5)&amp;VLOOKUP(LEFT(E1,LEN(E1)-5),Overzicht_parameters!$A$2:$F$69,6,(FALSE))</f>
         <v>top_zand_stdev</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H1" s="4" t="str">
         <f>LEFT(G1,LEN(G1)-5)&amp;VLOOKUP(LEFT(G1,LEN(G1)-5),Overzicht_parameters!$A$2:$F$69,6,(FALSE))</f>
         <v>gamma_sat_deklaag_stdev</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="J1" s="4" t="str">
         <f>LEFT(I1,LEN(I1)-5)&amp;VLOOKUP(LEFT(I1,LEN(I1)-5),Overzicht_parameters!$A$2:$F$69,6,(FALSE))</f>
         <v>D_wvp_stdev</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="L1" s="4" t="str">
         <f>LEFT(K1,LEN(K1)-5)&amp;VLOOKUP(LEFT(K1,LEN(K1)-5),Overzicht_parameters!$A$2:$F$69,6,(FALSE))</f>
         <v>kD_wvp_vc</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="N1" s="4" t="str">
         <f>LEFT(M1,LEN(M1)-5)&amp;VLOOKUP(LEFT(M1,LEN(M1)-5),Overzicht_parameters!$A$2:$F$69,6,(FALSE))</f>
         <v>d70_vc</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6301,7 +6307,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>0.5</v>
@@ -6337,7 +6343,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6345,7 +6351,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>0.5</v>
@@ -6381,7 +6387,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6389,7 +6395,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -6419,7 +6425,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6452,7 +6458,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6485,7 +6491,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6518,7 +6524,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -6526,7 +6532,7 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D8">
         <v>0.5</v>
@@ -6562,7 +6568,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6570,7 +6576,7 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D9">
         <v>0.5</v>
@@ -6606,7 +6612,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -6614,7 +6620,7 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -6644,7 +6650,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6677,7 +6683,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6710,7 +6716,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6743,7 +6749,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6751,7 +6757,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D14">
         <v>0.5</v>
@@ -6787,7 +6793,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6795,7 +6801,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D15">
         <v>0.5</v>
@@ -6831,7 +6837,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6839,7 +6845,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -6869,7 +6875,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6902,7 +6908,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6935,7 +6941,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6968,7 +6974,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6976,7 +6982,7 @@
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D20">
         <v>0.5</v>
@@ -7012,7 +7018,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -7020,7 +7026,7 @@
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D21">
         <v>0.5</v>
@@ -7056,7 +7062,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -7064,7 +7070,7 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -7094,7 +7100,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -7127,7 +7133,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -7160,7 +7166,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -7193,7 +7199,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -7201,7 +7207,7 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D26">
         <v>0.5</v>
@@ -7237,7 +7243,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -7245,7 +7251,7 @@
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D27">
         <v>0.5</v>
@@ -7281,7 +7287,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -7289,7 +7295,7 @@
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -7319,7 +7325,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -7352,7 +7358,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -7385,7 +7391,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -7418,7 +7424,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -7426,7 +7432,7 @@
         <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D32">
         <v>0.5</v>
@@ -7462,7 +7468,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -7470,7 +7476,7 @@
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D33">
         <v>0.5</v>
@@ -7506,7 +7512,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -7514,7 +7520,7 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -7544,7 +7550,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -7577,7 +7583,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -7610,7 +7616,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -7643,7 +7649,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -7651,7 +7657,7 @@
         <v>7</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D38">
         <v>0.5</v>
@@ -7687,7 +7693,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -7695,7 +7701,7 @@
         <v>7</v>
       </c>
       <c r="C39" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D39">
         <v>0.5</v>
@@ -7731,7 +7737,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -7739,7 +7745,7 @@
         <v>7</v>
       </c>
       <c r="C40" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -7769,7 +7775,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -7802,7 +7808,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -7835,7 +7841,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -7868,7 +7874,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -7876,7 +7882,7 @@
         <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D44">
         <v>0.5</v>
@@ -7912,7 +7918,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -7920,7 +7926,7 @@
         <v>8</v>
       </c>
       <c r="C45" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D45">
         <v>0.5</v>
@@ -7956,7 +7962,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -7964,7 +7970,7 @@
         <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -7994,7 +8000,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -8027,7 +8033,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -8060,7 +8066,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -8093,7 +8099,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -8101,7 +8107,7 @@
         <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D50">
         <v>0.5</v>
@@ -8137,7 +8143,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -8145,7 +8151,7 @@
         <v>9</v>
       </c>
       <c r="C51" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D51">
         <v>0.5</v>
@@ -8181,7 +8187,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -8189,7 +8195,7 @@
         <v>9</v>
       </c>
       <c r="C52" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -8219,7 +8225,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -8252,7 +8258,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -8285,7 +8291,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -8329,302 +8335,302 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B7A8CE-63DA-4EEA-9A88-5E62FD2B5E40}">
   <dimension ref="A1:P69"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="17.19921875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.19921875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="47.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="47.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="N1" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" t="s">
         <v>173</v>
       </c>
-      <c r="O1" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C2" t="s">
-        <v>189</v>
-      </c>
       <c r="D2" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D3" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D4" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D5" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="B6" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D6" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="B7" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="C7" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="D7" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="C8" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="D8" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="B9" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="C9" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D10" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D11" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D12" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="D13" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="B14" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C14" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D14" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="B15" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="C15" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="D15" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E15" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
@@ -8634,120 +8640,120 @@
       </c>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E16" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="L16" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="M16" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N16" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="O16" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="P16" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.15">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E17" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="L17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E18" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="L18" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="O18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E19" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I19" s="2">
         <v>1.5</v>
@@ -8756,30 +8762,30 @@
         <v>60</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="O19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E20" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F20" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I20" s="1">
         <v>1.4999999999999999E-4</v>
@@ -8788,33 +8794,33 @@
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="O20" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="P20" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.15">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E21" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F21" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I21" s="2">
         <v>10</v>
@@ -8823,27 +8829,27 @@
         <v>22</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.15">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E22" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F22" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I22" s="2">
         <v>1.5</v>
@@ -8852,36 +8858,36 @@
         <v>4000</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="L22" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="M22" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N22" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="O22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E23" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="I23" s="2">
         <v>0</v>
@@ -8890,102 +8896,102 @@
         <v>5000</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="L23" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="M23" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E24" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="I24" s="2">
         <v>0</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="L24" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="M24" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E25" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="I25" s="2">
         <v>0</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="L25" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="M25" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N25" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="O25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E26" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="I26" s="2">
         <v>5</v>
@@ -8994,58 +9000,58 @@
         <v>2000</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="M26" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N26" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="O26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D27" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E27" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.15">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E28" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="I28" s="2">
         <v>-4</v>
@@ -9054,64 +9060,64 @@
         <v>15</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="O28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E29" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="L29" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="M29" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N29" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="O29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F30" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I30" s="2">
         <v>-18</v>
@@ -9120,27 +9126,27 @@
         <v>15</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="O30" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="B31" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D31" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E31" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="G31" s="1">
         <v>2.0799999999999999E-4</v>
@@ -9149,27 +9155,27 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="O31" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E32" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="G32">
         <v>0.25</v>
@@ -9177,24 +9183,24 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.15">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E33" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="G33">
         <v>9.81</v>
@@ -9202,27 +9208,27 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="O33" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E34" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="G34" s="2">
         <v>26</v>
@@ -9231,27 +9237,27 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="O34" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E35" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="G35">
         <v>9.81</v>
@@ -9259,50 +9265,50 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.15">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="B36" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D36" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E36" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="G36">
         <v>1.5</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.15">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D37" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E37" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F37" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G37" s="2">
         <v>0.5</v>
@@ -9313,79 +9319,79 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="N37" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D38" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E38" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F38" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G38">
         <v>0.1</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.15">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="B39" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C39" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D39" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E39" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F39" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G39">
         <v>0.01</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.15">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D40" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E40" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="G40" s="2">
         <v>0.3</v>
@@ -9394,27 +9400,27 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="O40" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>90</v>
       </c>
-      <c r="O40" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A41" t="s">
-        <v>105</v>
-      </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C41" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="D41" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E41" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="G41" s="2">
         <v>37</v>
@@ -9423,27 +9429,27 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="O41" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="B42" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
-        <v>115</v>
+        <v>217</v>
       </c>
       <c r="D42" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E42" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="G42" s="1">
         <v>1.33E-6</v>
@@ -9452,30 +9458,30 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="O42" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="C43" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D43" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E43" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F43" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G43" s="3">
         <v>1</v>
@@ -9486,30 +9492,30 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="N43" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D44" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E44" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F44" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G44" s="3">
         <v>1</v>
@@ -9520,30 +9526,30 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="O44" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="B45" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D45" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E45" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F45" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G45" s="3">
         <v>1</v>
@@ -9554,547 +9560,547 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="M45" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C46" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D46" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="P46" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.15">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C47" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="P47" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.15">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="B48" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="C48" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D48" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="O48" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="B49" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="C49" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D49" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="O49" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A50" t="s">
-        <v>118</v>
-      </c>
       <c r="B50" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="C50" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D50" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="M50" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="B51" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C51" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D51" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="N51" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="B52" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C52" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D52" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="O52" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="C53" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D53" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="M53" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C54" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D54" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="O54" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B55" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="C55" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D55" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="N55" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.15">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C56" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D56" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.15">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="B57" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C57" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D57" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="L57" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.15">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="B58" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="C58" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D58" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="O58" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.15">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="B59" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="C59" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D59" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="L59" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.15">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="B60" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="C60" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D60" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="L60" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.15">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="B61" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="C61" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D61" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="L61" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.15">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B62" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="C62" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D62" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="L62" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="M62" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N62" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="B63" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="C63" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D63" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="L63" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B64" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="C64" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D64" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="L64" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.15">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B65" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="C65" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D65" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="L65" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.15">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="B66" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="C66" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D66" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="M66" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N66" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="O66" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="B67" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="C67" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D67" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="N67" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="B68" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="C68" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D68" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="O68" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="B69" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C69" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D69" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="M69" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -10140,76 +10146,76 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7FD5E8-359B-4F56-B38E-FCA72B85D698}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.75" style="7"/>
+    <col min="1" max="1" width="23.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.69921875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="B3" s="7">
         <v>0.75</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="B4" s="7">
         <v>0.01</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="B5" s="7">
         <v>100</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="B6" s="7" t="b">
         <v>1</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/example_new_calculations/input/input.xlsx
+++ b/workspaces/example_new_calculations/input/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKL\Documents\Github\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B1A6DC-E1F9-4F82-BBF7-9503A7B8D29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098B7AA6-A806-47C5-9754-45A47EB3D239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
   </bookViews>
   <sheets>
     <sheet name="Vakken" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="233">
   <si>
     <t>M_van</t>
   </si>
@@ -276,12 +276,6 @@
     <t>Reductieconstante van het verval over de deklaag</t>
   </si>
   <si>
-    <t>Buitenwaterstand</t>
-  </si>
-  <si>
-    <t>extreme value of CDF</t>
-  </si>
-  <si>
     <t>eta</t>
   </si>
   <si>
@@ -739,6 +733,12 @@
   </si>
   <si>
     <t>MA_1_41-4_dk_00018</t>
+  </si>
+  <si>
+    <t>o.b.v. overschrijdingsfrequentielijn berekend met Pydra in Python</t>
+  </si>
+  <si>
+    <t>Buitenwaterstand, o.b.v. overschrijdingsfrequentielijn berekend met Pydra in Python</t>
   </si>
 </sst>
 </file>
@@ -908,8 +908,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D6DB1DEC-E085-4F6B-B7C4-D4E6DD7E1A8E}" name="Tabel9" displayName="Tabel9" ref="A2:N103" headerRowCount="0" totalsRowShown="0">
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D6DB1DEC-E085-4F6B-B7C4-D4E6DD7E1A8E}" name="Tabel9" displayName="Tabel9" ref="A2:M103" headerRowCount="0" totalsRowShown="0">
+  <tableColumns count="13">
     <tableColumn id="2" xr3:uid="{8990A576-5075-4246-8F9A-BA6C41A7A01C}" name="Kolom2"/>
     <tableColumn id="15" xr3:uid="{5ACFB144-9626-4B12-88BF-8A0D8D4CFFEC}" name="Column1"/>
     <tableColumn id="3" xr3:uid="{49D363D0-5442-4E42-91BC-AD82E3246FFD}" name="Kolom3"/>
@@ -921,7 +921,6 @@
     <tableColumn id="9" xr3:uid="{C7E61DAC-831F-4734-9A0F-D17FA66D5C5C}" name="Kolom9"/>
     <tableColumn id="10" xr3:uid="{DC962EDF-740C-439F-836D-211E1F74A71C}" name="Kolom10"/>
     <tableColumn id="11" xr3:uid="{2DF82AEB-01BF-44F4-BB8B-81DDACEA5D0F}" name="Kolom11"/>
-    <tableColumn id="12" xr3:uid="{63DC1136-49A2-44E7-9286-3F64EFA876CE}" name="Kolom12"/>
     <tableColumn id="13" xr3:uid="{D266588F-C618-4806-A218-A5D90FF4D5E3}" name="Kolom13"/>
     <tableColumn id="14" xr3:uid="{C17CFC23-4C11-4C47-AEE5-4FB4BCCD1A66}" name="Kolom14"/>
   </tableColumns>
@@ -1313,10 +1312,10 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>0</v>
@@ -1325,7 +1324,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>2</v>
@@ -1673,7 +1672,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB77777-746E-45C0-BE11-D138C11C003A}">
-  <dimension ref="A1:N103"/>
+  <dimension ref="A1:M103"/>
   <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -1686,32 +1685,31 @@
     <col min="9" max="9" width="7.8984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.19921875" customWidth="1"/>
     <col min="11" max="11" width="23.8984375" customWidth="1"/>
-    <col min="12" max="12" width="17.09765625" customWidth="1"/>
-    <col min="13" max="13" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.8984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>150</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>15</v>
@@ -1723,19 +1721,16 @@
         <v>17</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N1" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1767,19 +1762,16 @@
         <v>90.481999999999999</v>
       </c>
       <c r="K2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L2">
-        <v>13.295</v>
+        <v>10.2043</v>
       </c>
       <c r="M2">
-        <v>10.2043</v>
-      </c>
-      <c r="N2">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1811,19 +1803,16 @@
         <v>47.110999999999997</v>
       </c>
       <c r="K3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L3">
-        <v>13.295</v>
+        <v>11.3071</v>
       </c>
       <c r="M3">
-        <v>11.3071</v>
-      </c>
-      <c r="N3">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1855,19 +1844,16 @@
         <v>3.133</v>
       </c>
       <c r="K4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L4">
-        <v>13.295</v>
+        <v>14.162699999999999</v>
       </c>
       <c r="M4">
-        <v>14.162699999999999</v>
-      </c>
-      <c r="N4">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1899,19 +1885,16 @@
         <v>3.5219999999999998</v>
       </c>
       <c r="K5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L5">
-        <v>13.295</v>
+        <v>14.102399999999999</v>
       </c>
       <c r="M5">
-        <v>14.102399999999999</v>
-      </c>
-      <c r="N5">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1943,19 +1926,16 @@
         <v>46.121000000000002</v>
       </c>
       <c r="K6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L6">
-        <v>13.295</v>
+        <v>12.430300000000001</v>
       </c>
       <c r="M6">
-        <v>12.430300000000001</v>
-      </c>
-      <c r="N6">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1987,19 +1967,16 @@
         <v>4.4450000000000003</v>
       </c>
       <c r="K7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L7">
-        <v>13.295</v>
+        <v>13.128</v>
       </c>
       <c r="M7">
-        <v>13.128</v>
-      </c>
-      <c r="N7">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2031,19 +2008,16 @@
         <v>35.957999999999998</v>
       </c>
       <c r="K8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L8">
-        <v>13.295</v>
+        <v>12.598000000000001</v>
       </c>
       <c r="M8">
-        <v>12.598000000000001</v>
-      </c>
-      <c r="N8">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2075,19 +2049,16 @@
         <v>2.915</v>
       </c>
       <c r="K9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="L9">
-        <v>13.295</v>
+        <v>12.921900000000001</v>
       </c>
       <c r="M9">
-        <v>12.921900000000001</v>
-      </c>
-      <c r="N9">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2119,19 +2090,16 @@
         <v>3.0369999999999999</v>
       </c>
       <c r="K10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L10">
-        <v>13.287000000000001</v>
+        <v>12.8507</v>
       </c>
       <c r="M10">
-        <v>12.8507</v>
-      </c>
-      <c r="N10">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2163,19 +2131,16 @@
         <v>2.4630000000000001</v>
       </c>
       <c r="K11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L11">
-        <v>13.292999999999999</v>
+        <v>12.9312</v>
       </c>
       <c r="M11">
-        <v>12.9312</v>
-      </c>
-      <c r="N11">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2207,19 +2172,16 @@
         <v>3.2130000000000001</v>
       </c>
       <c r="K12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L12">
-        <v>13.292999999999999</v>
+        <v>13.003399999999999</v>
       </c>
       <c r="M12">
-        <v>13.003399999999999</v>
-      </c>
-      <c r="N12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2251,19 +2213,16 @@
         <v>45.564</v>
       </c>
       <c r="K13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L13">
-        <v>13.292999999999999</v>
+        <v>10.3439</v>
       </c>
       <c r="M13">
-        <v>10.3439</v>
-      </c>
-      <c r="N13">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2295,19 +2254,16 @@
         <v>1.6319999999999999</v>
       </c>
       <c r="K14" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="L14">
-        <v>13.292999999999999</v>
+        <v>12.850300000000001</v>
       </c>
       <c r="M14">
-        <v>12.850300000000001</v>
-      </c>
-      <c r="N14">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2339,19 +2295,16 @@
         <v>2.2530000000000001</v>
       </c>
       <c r="K15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="L15">
-        <v>13.292999999999999</v>
+        <v>12.824999999999999</v>
       </c>
       <c r="M15">
-        <v>12.824999999999999</v>
-      </c>
-      <c r="N15">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2383,19 +2336,16 @@
         <v>25.902000000000001</v>
       </c>
       <c r="K16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="L16">
-        <v>13.292999999999999</v>
+        <v>9.9861000000000004</v>
       </c>
       <c r="M16">
-        <v>9.9861000000000004</v>
-      </c>
-      <c r="N16">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2427,19 +2377,16 @@
         <v>6.2789999999999999</v>
       </c>
       <c r="K17" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="L17">
-        <v>13.292999999999999</v>
+        <v>10.509600000000001</v>
       </c>
       <c r="M17">
-        <v>10.509600000000001</v>
-      </c>
-      <c r="N17">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2471,19 +2418,16 @@
         <v>3.6560000000000001</v>
       </c>
       <c r="K18" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L18">
-        <v>13.287000000000001</v>
+        <v>10.592499999999999</v>
       </c>
       <c r="M18">
-        <v>10.592499999999999</v>
-      </c>
-      <c r="N18">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2515,19 +2459,16 @@
         <v>4.9770000000000003</v>
       </c>
       <c r="K19" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L19">
-        <v>13.287000000000001</v>
+        <v>10.4916</v>
       </c>
       <c r="M19">
-        <v>10.4916</v>
-      </c>
-      <c r="N19">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2559,19 +2500,16 @@
         <v>5.0990000000000002</v>
       </c>
       <c r="K20" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L20">
-        <v>13.287000000000001</v>
+        <v>10.553800000000001</v>
       </c>
       <c r="M20">
-        <v>10.553800000000001</v>
-      </c>
-      <c r="N20">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2603,19 +2541,16 @@
         <v>7.1630000000000003</v>
       </c>
       <c r="K21" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L21">
-        <v>13.287000000000001</v>
+        <v>10.2805</v>
       </c>
       <c r="M21">
-        <v>10.2805</v>
-      </c>
-      <c r="N21">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2647,19 +2582,16 @@
         <v>11.342000000000001</v>
       </c>
       <c r="K22" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L22">
-        <v>13.287000000000001</v>
+        <v>10.1736</v>
       </c>
       <c r="M22">
-        <v>10.1736</v>
-      </c>
-      <c r="N22">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2691,19 +2623,16 @@
         <v>28.609000000000002</v>
       </c>
       <c r="K23" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L23">
-        <v>13.287000000000001</v>
+        <v>10.081200000000001</v>
       </c>
       <c r="M23">
-        <v>10.081200000000001</v>
-      </c>
-      <c r="N23">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2735,19 +2664,16 @@
         <v>16.428000000000001</v>
       </c>
       <c r="K24" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L24">
-        <v>13.29</v>
+        <v>9.9170999999999996</v>
       </c>
       <c r="M24">
-        <v>9.9170999999999996</v>
-      </c>
-      <c r="N24">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2779,19 +2705,16 @@
         <v>2.2360000000000002</v>
       </c>
       <c r="K25" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L25">
-        <v>13.29</v>
+        <v>10.31</v>
       </c>
       <c r="M25">
-        <v>10.31</v>
-      </c>
-      <c r="N25">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2823,19 +2746,16 @@
         <v>10.31</v>
       </c>
       <c r="K26" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L26">
-        <v>13.29</v>
+        <v>9.5640999999999998</v>
       </c>
       <c r="M26">
-        <v>9.5640999999999998</v>
-      </c>
-      <c r="N26">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2867,19 +2787,16 @@
         <v>10.231999999999999</v>
       </c>
       <c r="K27" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L27">
-        <v>13.29</v>
+        <v>9.5790000000000006</v>
       </c>
       <c r="M27">
-        <v>9.5790000000000006</v>
-      </c>
-      <c r="N27">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2911,19 +2828,16 @@
         <v>10.26</v>
       </c>
       <c r="K28" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L28">
-        <v>13.29</v>
+        <v>9.4616000000000007</v>
       </c>
       <c r="M28">
-        <v>9.4616000000000007</v>
-      </c>
-      <c r="N28">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2955,19 +2869,16 @@
         <v>3.0219999999999998</v>
       </c>
       <c r="K29" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L29">
-        <v>13.29</v>
+        <v>11.1126</v>
       </c>
       <c r="M29">
-        <v>11.1126</v>
-      </c>
-      <c r="N29">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2999,19 +2910,16 @@
         <v>2.0760000000000001</v>
       </c>
       <c r="K30" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L30">
-        <v>13.29</v>
+        <v>10.895899999999999</v>
       </c>
       <c r="M30">
-        <v>10.895899999999999</v>
-      </c>
-      <c r="N30">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3043,19 +2951,16 @@
         <v>2.0449999999999999</v>
       </c>
       <c r="K31" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L31">
-        <v>13.29</v>
+        <v>10.970700000000001</v>
       </c>
       <c r="M31">
-        <v>10.970700000000001</v>
-      </c>
-      <c r="N31">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3087,19 +2992,16 @@
         <v>13.978</v>
       </c>
       <c r="K32" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L32">
-        <v>13.29</v>
+        <v>9.3927999999999994</v>
       </c>
       <c r="M32">
-        <v>9.3927999999999994</v>
-      </c>
-      <c r="N32">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3131,19 +3033,16 @@
         <v>13.022</v>
       </c>
       <c r="K33" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L33">
-        <v>13.281000000000001</v>
+        <v>9.4320000000000004</v>
       </c>
       <c r="M33">
-        <v>9.4320000000000004</v>
-      </c>
-      <c r="N33">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3175,19 +3074,16 @@
         <v>13.021000000000001</v>
       </c>
       <c r="K34" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L34">
-        <v>13.281000000000001</v>
+        <v>9.3580000000000005</v>
       </c>
       <c r="M34">
-        <v>9.3580000000000005</v>
-      </c>
-      <c r="N34">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3219,19 +3115,16 @@
         <v>13.185</v>
       </c>
       <c r="K35" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L35">
-        <v>13.281000000000001</v>
+        <v>10.359500000000001</v>
       </c>
       <c r="M35">
-        <v>10.359500000000001</v>
-      </c>
-      <c r="N35">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3263,19 +3156,16 @@
         <v>13.202999999999999</v>
       </c>
       <c r="K36" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L36">
-        <v>13.281000000000001</v>
+        <v>9.4057999999999993</v>
       </c>
       <c r="M36">
-        <v>9.4057999999999993</v>
-      </c>
-      <c r="N36">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3307,19 +3197,16 @@
         <v>13.199</v>
       </c>
       <c r="K37" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L37">
-        <v>13.281000000000001</v>
+        <v>9.3960000000000008</v>
       </c>
       <c r="M37">
-        <v>9.3960000000000008</v>
-      </c>
-      <c r="N37">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3351,19 +3238,16 @@
         <v>13.427</v>
       </c>
       <c r="K38" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L38">
-        <v>13.281000000000001</v>
+        <v>9.2929999999999993</v>
       </c>
       <c r="M38">
-        <v>9.2929999999999993</v>
-      </c>
-      <c r="N38">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3395,19 +3279,16 @@
         <v>13.805999999999999</v>
       </c>
       <c r="K39" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L39">
-        <v>13.28</v>
+        <v>9.2729999999999997</v>
       </c>
       <c r="M39">
-        <v>9.2729999999999997</v>
-      </c>
-      <c r="N39">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3439,19 +3320,16 @@
         <v>13.393000000000001</v>
       </c>
       <c r="K40" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L40">
-        <v>13.28</v>
+        <v>9.2373999999999992</v>
       </c>
       <c r="M40">
-        <v>9.2373999999999992</v>
-      </c>
-      <c r="N40">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3483,19 +3361,16 @@
         <v>25.576000000000001</v>
       </c>
       <c r="K41" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L41">
-        <v>13.284000000000001</v>
+        <v>9.0991</v>
       </c>
       <c r="M41">
-        <v>9.0991</v>
-      </c>
-      <c r="N41">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3527,19 +3402,16 @@
         <v>27.145</v>
       </c>
       <c r="K42" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L42">
-        <v>13.284000000000001</v>
+        <v>9.1163000000000007</v>
       </c>
       <c r="M42">
-        <v>9.1163000000000007</v>
-      </c>
-      <c r="N42">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3571,19 +3443,16 @@
         <v>27.32</v>
       </c>
       <c r="K43" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L43">
-        <v>13.284000000000001</v>
+        <v>9.0764999999999993</v>
       </c>
       <c r="M43">
-        <v>9.0764999999999993</v>
-      </c>
-      <c r="N43">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3615,19 +3484,16 @@
         <v>27.140999999999998</v>
       </c>
       <c r="K44" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L44">
-        <v>13.284000000000001</v>
+        <v>9.0787999999999993</v>
       </c>
       <c r="M44">
-        <v>9.0787999999999993</v>
-      </c>
-      <c r="N44">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3659,19 +3525,16 @@
         <v>27.53</v>
       </c>
       <c r="K45" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L45">
-        <v>13.284000000000001</v>
+        <v>9.0907</v>
       </c>
       <c r="M45">
-        <v>9.0907</v>
-      </c>
-      <c r="N45">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3703,19 +3566,16 @@
         <v>27.189</v>
       </c>
       <c r="K46" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L46">
-        <v>13.287000000000001</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="M46">
-        <v>9.0299999999999994</v>
-      </c>
-      <c r="N46">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3747,19 +3607,16 @@
         <v>9.4960000000000004</v>
       </c>
       <c r="K47" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L47">
-        <v>13.28</v>
+        <v>10.5002</v>
       </c>
       <c r="M47">
-        <v>10.5002</v>
-      </c>
-      <c r="N47">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3791,19 +3648,16 @@
         <v>8.9510000000000005</v>
       </c>
       <c r="K48" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L48">
-        <v>13.284000000000001</v>
+        <v>10.527699999999999</v>
       </c>
       <c r="M48">
-        <v>10.527699999999999</v>
-      </c>
-      <c r="N48">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3835,19 +3689,16 @@
         <v>9.6110000000000007</v>
       </c>
       <c r="K49" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L49">
-        <v>13.284000000000001</v>
+        <v>10.632</v>
       </c>
       <c r="M49">
-        <v>10.632</v>
-      </c>
-      <c r="N49">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3879,19 +3730,16 @@
         <v>15.634</v>
       </c>
       <c r="K50" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L50">
-        <v>13.284000000000001</v>
+        <v>10.427</v>
       </c>
       <c r="M50">
-        <v>10.427</v>
-      </c>
-      <c r="N50">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3923,19 +3771,16 @@
         <v>14.721</v>
       </c>
       <c r="K51" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L51">
-        <v>13.284000000000001</v>
+        <v>10.532999999999999</v>
       </c>
       <c r="M51">
-        <v>10.532999999999999</v>
-      </c>
-      <c r="N51">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3967,19 +3812,16 @@
         <v>14.151999999999999</v>
       </c>
       <c r="K52" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L52">
-        <v>13.284000000000001</v>
+        <v>10.5641</v>
       </c>
       <c r="M52">
-        <v>10.5641</v>
-      </c>
-      <c r="N52">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4011,19 +3853,16 @@
         <v>26.984999999999999</v>
       </c>
       <c r="K53" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L53">
-        <v>13.287000000000001</v>
+        <v>9.8963999999999999</v>
       </c>
       <c r="M53">
-        <v>9.8963999999999999</v>
-      </c>
-      <c r="N53">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4055,19 +3894,16 @@
         <v>39.465000000000003</v>
       </c>
       <c r="K54" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L54">
-        <v>13.284000000000001</v>
+        <v>9.5132999999999992</v>
       </c>
       <c r="M54">
-        <v>9.5132999999999992</v>
-      </c>
-      <c r="N54">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4099,19 +3935,16 @@
         <v>39.244999999999997</v>
       </c>
       <c r="K55" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L55">
-        <v>13.284000000000001</v>
+        <v>9.5338999999999992</v>
       </c>
       <c r="M55">
-        <v>9.5338999999999992</v>
-      </c>
-      <c r="N55">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4143,19 +3976,16 @@
         <v>41.247</v>
       </c>
       <c r="K56" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L56">
-        <v>13.284000000000001</v>
+        <v>9.5863999999999994</v>
       </c>
       <c r="M56">
-        <v>9.5863999999999994</v>
-      </c>
-      <c r="N56">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4187,19 +4017,16 @@
         <v>27.300999999999998</v>
       </c>
       <c r="K57" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L57">
-        <v>13.287000000000001</v>
+        <v>9.109</v>
       </c>
       <c r="M57">
-        <v>9.109</v>
-      </c>
-      <c r="N57">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4231,19 +4058,16 @@
         <v>27.064</v>
       </c>
       <c r="K58" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L58">
-        <v>13.287000000000001</v>
+        <v>9.0741999999999994</v>
       </c>
       <c r="M58">
-        <v>9.0741999999999994</v>
-      </c>
-      <c r="N58">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4275,19 +4099,16 @@
         <v>27.420999999999999</v>
       </c>
       <c r="K59" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L59">
-        <v>13.287000000000001</v>
+        <v>9.1675000000000004</v>
       </c>
       <c r="M59">
-        <v>9.1675000000000004</v>
-      </c>
-      <c r="N59">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4319,19 +4140,16 @@
         <v>27.614999999999998</v>
       </c>
       <c r="K60" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L60">
-        <v>13.287000000000001</v>
+        <v>9.1737000000000002</v>
       </c>
       <c r="M60">
-        <v>9.1737000000000002</v>
-      </c>
-      <c r="N60">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4363,19 +4181,16 @@
         <v>16.472999999999999</v>
       </c>
       <c r="K61" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L61">
-        <v>13.287000000000001</v>
+        <v>10.505100000000001</v>
       </c>
       <c r="M61">
-        <v>10.505100000000001</v>
-      </c>
-      <c r="N61">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4407,19 +4222,16 @@
         <v>17.288</v>
       </c>
       <c r="K62" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L62">
-        <v>13.287000000000001</v>
+        <v>10.4526</v>
       </c>
       <c r="M62">
-        <v>10.4526</v>
-      </c>
-      <c r="N62">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4451,19 +4263,16 @@
         <v>39.094000000000001</v>
       </c>
       <c r="K63" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L63">
-        <v>13.287000000000001</v>
+        <v>9.7959999999999994</v>
       </c>
       <c r="M63">
-        <v>9.7959999999999994</v>
-      </c>
-      <c r="N63">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4495,19 +4304,16 @@
         <v>39.088000000000001</v>
       </c>
       <c r="K64" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L64">
-        <v>13.287000000000001</v>
+        <v>9.6658000000000008</v>
       </c>
       <c r="M64">
-        <v>9.6658000000000008</v>
-      </c>
-      <c r="N64">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4539,19 +4345,16 @@
         <v>27.256</v>
       </c>
       <c r="K65" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L65">
-        <v>13.29</v>
+        <v>9.1157000000000004</v>
       </c>
       <c r="M65">
-        <v>9.1157000000000004</v>
-      </c>
-      <c r="N65">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4583,19 +4386,16 @@
         <v>27.446000000000002</v>
       </c>
       <c r="K66" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L66">
-        <v>13.29</v>
+        <v>9.1294000000000004</v>
       </c>
       <c r="M66">
-        <v>9.1294000000000004</v>
-      </c>
-      <c r="N66">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4627,19 +4427,16 @@
         <v>16.11</v>
       </c>
       <c r="K67" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L67">
-        <v>13.29</v>
+        <v>10.5085</v>
       </c>
       <c r="M67">
-        <v>10.5085</v>
-      </c>
-      <c r="N67">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4671,19 +4468,16 @@
         <v>27.241</v>
       </c>
       <c r="K68" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L68">
-        <v>13.29</v>
+        <v>9.1258999999999997</v>
       </c>
       <c r="M68">
-        <v>9.1258999999999997</v>
-      </c>
-      <c r="N68">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4715,19 +4509,16 @@
         <v>27.57</v>
       </c>
       <c r="K69" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L69">
-        <v>13.29</v>
+        <v>9.1498000000000008</v>
       </c>
       <c r="M69">
-        <v>9.1498000000000008</v>
-      </c>
-      <c r="N69">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4759,19 +4550,16 @@
         <v>28.573</v>
       </c>
       <c r="K70" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L70">
-        <v>13.29</v>
+        <v>9.2566000000000006</v>
       </c>
       <c r="M70">
-        <v>9.2566000000000006</v>
-      </c>
-      <c r="N70">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4803,19 +4591,16 @@
         <v>24.151</v>
       </c>
       <c r="K71" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L71">
-        <v>13.29</v>
+        <v>9.2270000000000003</v>
       </c>
       <c r="M71">
-        <v>9.2270000000000003</v>
-      </c>
-      <c r="N71">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4847,19 +4632,16 @@
         <v>26.064</v>
       </c>
       <c r="K72" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L72">
-        <v>13.29</v>
+        <v>9.0945999999999998</v>
       </c>
       <c r="M72">
-        <v>9.0945999999999998</v>
-      </c>
-      <c r="N72">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4891,19 +4673,16 @@
         <v>41.290999999999997</v>
       </c>
       <c r="K73" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L73">
-        <v>13.29</v>
+        <v>9.1628000000000007</v>
       </c>
       <c r="M73">
-        <v>9.1628000000000007</v>
-      </c>
-      <c r="N73">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4935,19 +4714,16 @@
         <v>16.7</v>
       </c>
       <c r="K74" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L74">
-        <v>13.29</v>
+        <v>10.579599999999999</v>
       </c>
       <c r="M74">
-        <v>10.579599999999999</v>
-      </c>
-      <c r="N74">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4979,19 +4755,16 @@
         <v>48.253999999999998</v>
       </c>
       <c r="K75" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L75">
-        <v>13.29</v>
+        <v>9.9273000000000007</v>
       </c>
       <c r="M75">
-        <v>9.9273000000000007</v>
-      </c>
-      <c r="N75">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5023,19 +4796,16 @@
         <v>41.021999999999998</v>
       </c>
       <c r="K76" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L76">
-        <v>13.29</v>
+        <v>9.1294002532958896</v>
       </c>
       <c r="M76">
-        <v>9.1294002532958896</v>
-      </c>
-      <c r="N76">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5067,19 +4837,16 @@
         <v>43.037999999999997</v>
       </c>
       <c r="K77" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L77">
-        <v>13.29</v>
+        <v>9.1294002532958896</v>
       </c>
       <c r="M77">
-        <v>9.1294002532958896</v>
-      </c>
-      <c r="N77">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5111,19 +4878,16 @@
         <v>87.822000000000003</v>
       </c>
       <c r="K78" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L78">
-        <v>13.29</v>
+        <v>9.0883000000000003</v>
       </c>
       <c r="M78">
-        <v>9.0883000000000003</v>
-      </c>
-      <c r="N78">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5155,19 +4919,16 @@
         <v>81.563999999999993</v>
       </c>
       <c r="K79" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L79">
-        <v>13.29</v>
+        <v>9.3460999999999999</v>
       </c>
       <c r="M79">
-        <v>9.3460999999999999</v>
-      </c>
-      <c r="N79">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5199,19 +4960,16 @@
         <v>41.65</v>
       </c>
       <c r="K80" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L80">
-        <v>13.29</v>
+        <v>9.4944000000000006</v>
       </c>
       <c r="M80">
-        <v>9.4944000000000006</v>
-      </c>
-      <c r="N80">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5243,19 +5001,16 @@
         <v>12.044</v>
       </c>
       <c r="K81" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="L81">
-        <v>13.29</v>
+        <v>9.1057000000000006</v>
       </c>
       <c r="M81">
-        <v>9.1057000000000006</v>
-      </c>
-      <c r="N81">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5287,19 +5042,16 @@
         <v>8.7789999999999999</v>
       </c>
       <c r="K82" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="L82">
-        <v>13.29</v>
+        <v>9.0036000000000005</v>
       </c>
       <c r="M82">
-        <v>9.0036000000000005</v>
-      </c>
-      <c r="N82">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5331,19 +5083,16 @@
         <v>9.6579999999999995</v>
       </c>
       <c r="K83" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L83">
-        <v>13.29</v>
+        <v>8.82</v>
       </c>
       <c r="M83">
-        <v>8.82</v>
-      </c>
-      <c r="N83">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5375,19 +5124,16 @@
         <v>9.3379999999999992</v>
       </c>
       <c r="K84" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L84">
-        <v>13.29</v>
+        <v>8.8564000000000007</v>
       </c>
       <c r="M84">
-        <v>8.8564000000000007</v>
-      </c>
-      <c r="N84">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5419,19 +5165,16 @@
         <v>8.4359999999999999</v>
       </c>
       <c r="K85" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L85">
-        <v>13.29</v>
+        <v>8.7265999999999995</v>
       </c>
       <c r="M85">
-        <v>8.7265999999999995</v>
-      </c>
-      <c r="N85">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5463,19 +5206,16 @@
         <v>8.3759999999999994</v>
       </c>
       <c r="K86" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L86">
-        <v>13.29</v>
+        <v>8.6908999999999992</v>
       </c>
       <c r="M86">
-        <v>8.6908999999999992</v>
-      </c>
-      <c r="N86">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5507,19 +5247,16 @@
         <v>34.829000000000001</v>
       </c>
       <c r="K87" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L87">
-        <v>13.29</v>
+        <v>9.3066999999999993</v>
       </c>
       <c r="M87">
-        <v>9.3066999999999993</v>
-      </c>
-      <c r="N87">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5551,19 +5288,16 @@
         <v>38.756</v>
       </c>
       <c r="K88" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L88">
-        <v>13.29</v>
+        <v>9.4048999999999996</v>
       </c>
       <c r="M88">
-        <v>9.4048999999999996</v>
-      </c>
-      <c r="N88">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5595,19 +5329,16 @@
         <v>37.752000000000002</v>
       </c>
       <c r="K89" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L89">
-        <v>13.29</v>
+        <v>9.4594000000000005</v>
       </c>
       <c r="M89">
-        <v>9.4594000000000005</v>
-      </c>
-      <c r="N89">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5639,19 +5370,16 @@
         <v>27.361999999999998</v>
       </c>
       <c r="K90" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="L90">
-        <v>13.29</v>
+        <v>9.5521999999999991</v>
       </c>
       <c r="M90">
-        <v>9.5521999999999991</v>
-      </c>
-      <c r="N90">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5683,19 +5411,16 @@
         <v>40.136000000000003</v>
       </c>
       <c r="K91" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L91">
-        <v>13.29</v>
+        <v>8.8773999999999997</v>
       </c>
       <c r="M91">
-        <v>8.8773999999999997</v>
-      </c>
-      <c r="N91">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5727,19 +5452,16 @@
         <v>7.7350000000000003</v>
       </c>
       <c r="K92" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L92">
-        <v>13.29</v>
+        <v>8.7820999999999998</v>
       </c>
       <c r="M92">
-        <v>8.7820999999999998</v>
-      </c>
-      <c r="N92">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5771,19 +5493,16 @@
         <v>8.2720000000000002</v>
       </c>
       <c r="K93" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L93">
-        <v>13.29</v>
+        <v>8.6329999999999991</v>
       </c>
       <c r="M93">
-        <v>8.6329999999999991</v>
-      </c>
-      <c r="N93">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5815,19 +5534,16 @@
         <v>8.3780000000000001</v>
       </c>
       <c r="K94" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L94">
-        <v>13.29</v>
+        <v>8.5892999999999997</v>
       </c>
       <c r="M94">
-        <v>8.5892999999999997</v>
-      </c>
-      <c r="N94">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5859,19 +5575,16 @@
         <v>8.0960000000000001</v>
       </c>
       <c r="K95" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L95">
-        <v>13.29</v>
+        <v>8.6798000000000002</v>
       </c>
       <c r="M95">
-        <v>8.6798000000000002</v>
-      </c>
-      <c r="N95">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5903,19 +5616,16 @@
         <v>47.176000000000002</v>
       </c>
       <c r="K96" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L96">
-        <v>13.29</v>
+        <v>8.9077999999999999</v>
       </c>
       <c r="M96">
-        <v>8.9077999999999999</v>
-      </c>
-      <c r="N96">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5947,19 +5657,16 @@
         <v>70.381</v>
       </c>
       <c r="K97" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L97">
-        <v>13.29</v>
+        <v>8.5473999999999997</v>
       </c>
       <c r="M97">
-        <v>8.5473999999999997</v>
-      </c>
-      <c r="N97">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5991,19 +5698,16 @@
         <v>64.856999999999999</v>
       </c>
       <c r="K98" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L98">
-        <v>13.29</v>
+        <v>8.7873999999999999</v>
       </c>
       <c r="M98">
-        <v>8.7873999999999999</v>
-      </c>
-      <c r="N98">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -6035,19 +5739,16 @@
         <v>8.9260000000000002</v>
       </c>
       <c r="K99" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L99">
-        <v>13.29</v>
+        <v>8.7263000000000002</v>
       </c>
       <c r="M99">
-        <v>8.7263000000000002</v>
-      </c>
-      <c r="N99">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>100</v>
       </c>
@@ -6079,19 +5780,16 @@
         <v>23.966999999999999</v>
       </c>
       <c r="K100" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L100">
-        <v>13.29</v>
+        <v>9.1720000000000006</v>
       </c>
       <c r="M100">
-        <v>9.1720000000000006</v>
-      </c>
-      <c r="N100">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>101</v>
       </c>
@@ -6123,19 +5821,16 @@
         <v>25.442</v>
       </c>
       <c r="K101" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L101">
-        <v>13.29</v>
+        <v>9.0852000000000004</v>
       </c>
       <c r="M101">
-        <v>9.0852000000000004</v>
-      </c>
-      <c r="N101">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>102</v>
       </c>
@@ -6167,19 +5862,16 @@
         <v>25.503</v>
       </c>
       <c r="K102" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L102">
-        <v>13.29</v>
+        <v>9.1880000000000006</v>
       </c>
       <c r="M102">
-        <v>9.1880000000000006</v>
-      </c>
-      <c r="N102">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>103</v>
       </c>
@@ -6211,15 +5903,12 @@
         <v>26.507999999999999</v>
       </c>
       <c r="K103" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L103">
-        <v>13.29</v>
+        <v>9.2014999999999993</v>
       </c>
       <c r="M103">
-        <v>9.2014999999999993</v>
-      </c>
-      <c r="N103">
         <v>7.75</v>
       </c>
     </row>
@@ -6252,16 +5941,16 @@
   <sheetData>
     <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>153</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>24</v>
@@ -8350,71 +8039,71 @@
     <col min="13" max="13" width="13.19921875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.19921875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="47.59765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="51.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>214</v>
-      </c>
       <c r="L1" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>158</v>
-      </c>
       <c r="P1" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -8422,16 +8111,16 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -8443,10 +8132,10 @@
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -8458,10 +8147,10 @@
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -8469,16 +8158,16 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -8486,16 +8175,16 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -8503,16 +8192,16 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -8520,16 +8209,16 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -8537,16 +8226,16 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -8554,14 +8243,14 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -8569,14 +8258,14 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -8584,16 +8273,16 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C13" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -8601,16 +8290,16 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D14" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -8618,19 +8307,19 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C15" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
@@ -8642,95 +8331,90 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E16" t="s">
         <v>187</v>
+      </c>
+      <c r="F16" t="s">
+        <v>35</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="L16" t="s">
         <v>33</v>
       </c>
-      <c r="M16" t="s">
-        <v>33</v>
-      </c>
-      <c r="N16" t="s">
-        <v>33</v>
-      </c>
-      <c r="O16" t="s">
-        <v>33</v>
-      </c>
-      <c r="P16" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
         <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="L17" t="s">
         <v>33</v>
       </c>
+      <c r="O17" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E18" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F18" t="s">
         <v>34</v>
       </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+      <c r="I18" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="J18" s="2">
+        <v>60</v>
+      </c>
       <c r="K18" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="L18" t="s">
-        <v>33</v>
+        <v>160</v>
       </c>
       <c r="O18" t="s">
         <v>33</v>
@@ -8738,127 +8422,133 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
         <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E19" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F19" t="s">
-        <v>34</v>
-      </c>
-      <c r="I19" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="J19" s="2">
-        <v>60</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>162</v>
+        <v>35</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="J19" s="1">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="O19" t="s">
         <v>33</v>
       </c>
+      <c r="P19" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E20" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F20" t="s">
-        <v>35</v>
-      </c>
-      <c r="I20" s="1">
-        <v>1.4999999999999999E-4</v>
-      </c>
-      <c r="J20" s="1">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="O20" t="s">
-        <v>33</v>
-      </c>
-      <c r="P20" t="s">
-        <v>61</v>
+        <v>34</v>
+      </c>
+      <c r="I20" s="2">
+        <v>10</v>
+      </c>
+      <c r="J20" s="2">
+        <v>22</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I21" s="2">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="J21" s="2">
-        <v>22</v>
+        <v>4000</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
+      </c>
+      <c r="L21" t="s">
+        <v>33</v>
+      </c>
+      <c r="M21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N21" t="s">
+        <v>33</v>
+      </c>
+      <c r="O21" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E22" t="s">
-        <v>189</v>
-      </c>
-      <c r="F22" t="s">
-        <v>35</v>
+        <v>185</v>
       </c>
       <c r="I22" s="2">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>162</v>
+        <v>36</v>
       </c>
       <c r="L22" t="s">
         <v>33</v>
@@ -8869,34 +8559,29 @@
       <c r="N22" t="s">
         <v>33</v>
       </c>
-      <c r="O22" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" t="s">
         <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E23" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I23" s="2">
         <v>0</v>
       </c>
-      <c r="J23" s="2">
-        <v>5000</v>
-      </c>
+      <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>36</v>
+        <v>158</v>
       </c>
       <c r="L23" t="s">
         <v>33</v>
@@ -8910,26 +8595,26 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
         <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E24" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I24" s="2">
         <v>0</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L24" t="s">
         <v>33</v>
@@ -8940,29 +8625,34 @@
       <c r="N24" t="s">
         <v>33</v>
       </c>
+      <c r="O24" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C25" t="s">
         <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E25" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="J25" s="2">
+        <v>2000</v>
+      </c>
       <c r="K25" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L25" t="s">
         <v>33</v>
@@ -8979,88 +8669,84 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>169</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E26" t="s">
-        <v>187</v>
-      </c>
-      <c r="I26" s="2">
-        <v>5</v>
-      </c>
-      <c r="J26" s="2">
-        <v>2000</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="L26" t="s">
-        <v>33</v>
-      </c>
-      <c r="M26" t="s">
-        <v>33</v>
-      </c>
-      <c r="N26" t="s">
-        <v>33</v>
-      </c>
-      <c r="O26" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>163</v>
       </c>
       <c r="C27" t="s">
         <v>37</v>
       </c>
       <c r="D27" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E27" t="s">
-        <v>187</v>
-      </c>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="I27" s="2">
+        <v>-4</v>
+      </c>
+      <c r="J27" s="2">
+        <v>15</v>
+      </c>
       <c r="K27" s="2" t="s">
-        <v>36</v>
+        <v>158</v>
+      </c>
+      <c r="O27" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C28" t="s">
         <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E28" t="s">
-        <v>187</v>
-      </c>
-      <c r="I28" s="2">
-        <v>-4</v>
-      </c>
-      <c r="J28" s="2">
-        <v>15</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
+      </c>
+      <c r="L28" t="s">
+        <v>33</v>
+      </c>
+      <c r="M28" t="s">
+        <v>33</v>
+      </c>
+      <c r="N28" t="s">
+        <v>33</v>
       </c>
       <c r="O28" t="s">
         <v>33</v>
@@ -9068,65 +8754,60 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>164</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
         <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E29" t="s">
-        <v>187</v>
-      </c>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="F29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" s="2">
+        <v>-18</v>
+      </c>
+      <c r="J29" s="2">
+        <v>15</v>
+      </c>
       <c r="K29" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="L29" t="s">
-        <v>33</v>
-      </c>
-      <c r="M29" t="s">
-        <v>33</v>
-      </c>
-      <c r="N29" t="s">
-        <v>33</v>
-      </c>
       <c r="O29" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E30" t="s">
-        <v>41</v>
-      </c>
-      <c r="F30" t="s">
-        <v>34</v>
-      </c>
-      <c r="I30" s="2">
-        <v>-18</v>
-      </c>
-      <c r="J30" s="2">
-        <v>15</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2.0799999999999999E-4</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="O30" t="s">
         <v>33</v>
@@ -9134,77 +8815,77 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E31" t="s">
-        <v>187</v>
-      </c>
-      <c r="G31" s="1">
-        <v>2.0799999999999999E-4</v>
-      </c>
-      <c r="H31" s="1"/>
+        <v>185</v>
+      </c>
+      <c r="G31">
+        <v>0.25</v>
+      </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="O31" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="D32" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E32" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G32">
-        <v>0.25</v>
+        <v>9.81</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
         <v>75</v>
       </c>
+      <c r="O32" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E33" t="s">
-        <v>187</v>
-      </c>
-      <c r="G33">
-        <v>9.81</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="G33" s="2">
+        <v>26</v>
+      </c>
+      <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
@@ -9216,113 +8897,110 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
         <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E34" t="s">
-        <v>187</v>
-      </c>
-      <c r="G34" s="2">
-        <v>26</v>
-      </c>
-      <c r="H34" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="G34">
+        <v>9.81</v>
+      </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="O34" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D35" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E35" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G35">
-        <v>9.81</v>
-      </c>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
+        <v>1.5</v>
+      </c>
       <c r="K35" s="2" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="D36" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E36" t="s">
         <v>187</v>
       </c>
-      <c r="G36">
-        <v>1.5</v>
-      </c>
+      <c r="F36" t="s">
+        <v>34</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H36" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
         <v>75</v>
       </c>
+      <c r="N36" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="C37" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D37" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E37" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F37" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="H37" s="2">
+      <c r="G37">
         <v>0.1</v>
       </c>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="N37" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
@@ -9336,16 +9014,16 @@
         <v>58</v>
       </c>
       <c r="D38" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E38" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F38" t="s">
         <v>34</v>
       </c>
       <c r="G38">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>75</v>
@@ -9353,48 +9031,51 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="B39" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D39" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E39" t="s">
-        <v>189</v>
-      </c>
-      <c r="F39" t="s">
-        <v>34</v>
-      </c>
-      <c r="G39">
-        <v>0.01</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="G39" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
         <v>75</v>
       </c>
+      <c r="O39" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="D40" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E40" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G40" s="2">
-        <v>0.3</v>
+        <v>37</v>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
@@ -9408,24 +9089,24 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
+        <v>215</v>
       </c>
       <c r="D41" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E41" t="s">
-        <v>187</v>
-      </c>
-      <c r="G41" s="2">
-        <v>37</v>
-      </c>
-      <c r="H41" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1.33E-6</v>
+      </c>
+      <c r="H41" s="1"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
@@ -9437,48 +9118,53 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="B42" t="s">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="C42" t="s">
-        <v>217</v>
+        <v>69</v>
       </c>
       <c r="D42" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E42" t="s">
         <v>187</v>
       </c>
-      <c r="G42" s="1">
-        <v>1.33E-6</v>
-      </c>
-      <c r="H42" s="1"/>
+      <c r="F42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G42" s="3">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>0.1</v>
+      </c>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="O42" t="s">
+        <v>158</v>
+      </c>
+      <c r="N42" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B43" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="C43" t="s">
         <v>69</v>
       </c>
       <c r="D43" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E43" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -9487,32 +9173,32 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="N43" t="s">
+        <v>158</v>
+      </c>
+      <c r="O43" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C44" t="s">
         <v>69</v>
       </c>
       <c r="D44" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E44" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F44" t="s">
         <v>34</v>
@@ -9521,49 +9207,40 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="O44" t="s">
+        <v>158</v>
+      </c>
+      <c r="M44" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="B45" t="s">
-        <v>68</v>
+        <v>232</v>
       </c>
       <c r="C45" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="D45" t="s">
-        <v>205</v>
-      </c>
-      <c r="E45" t="s">
-        <v>189</v>
-      </c>
-      <c r="F45" t="s">
-        <v>34</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1</v>
-      </c>
-      <c r="H45">
-        <v>0.1</v>
+        <v>85</v>
       </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="M45" t="s">
-        <v>33</v>
+        <v>184</v>
+      </c>
+      <c r="L45" t="s">
+        <v>85</v>
+      </c>
+      <c r="P45" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
@@ -9577,15 +9254,15 @@
         <v>32</v>
       </c>
       <c r="D46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P46" t="s">
         <v>186</v>
-      </c>
-      <c r="P46" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
@@ -9599,191 +9276,191 @@
         <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="P47" t="s">
         <v>186</v>
-      </c>
-      <c r="P47" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
       </c>
       <c r="D48" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="O48" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
       </c>
       <c r="D49" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="O49" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B50" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C50" t="s">
         <v>32</v>
       </c>
       <c r="D50" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M50" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B51" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C51" t="s">
         <v>69</v>
       </c>
       <c r="D51" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="N51" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B52" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C52" t="s">
         <v>69</v>
       </c>
       <c r="D52" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="O52" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B53" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C53" t="s">
         <v>69</v>
       </c>
       <c r="D53" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M53" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B54" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C54" t="s">
         <v>37</v>
       </c>
       <c r="D54" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="O54" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B55" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C55" t="s">
         <v>69</v>
       </c>
       <c r="D55" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="N55" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.2">
@@ -9797,144 +9474,144 @@
         <v>58</v>
       </c>
       <c r="D56" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B57" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
       </c>
       <c r="D57" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L57" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B58" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
       </c>
       <c r="D58" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="O58" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B59" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L59" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B60" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
       </c>
       <c r="D60" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L60" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B61" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
       </c>
       <c r="D61" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L61" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B62" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C62" t="s">
         <v>37</v>
       </c>
       <c r="D62" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L62" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M62" t="s">
         <v>33</v>
@@ -9945,87 +9622,87 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B63" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C63" t="s">
         <v>69</v>
       </c>
       <c r="D63" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L63" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C64" t="s">
         <v>32</v>
       </c>
       <c r="D64" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L64" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B65" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C65" t="s">
         <v>32</v>
       </c>
       <c r="D65" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L65" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B66" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C66" t="s">
         <v>69</v>
       </c>
       <c r="D66" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M66" t="s">
         <v>33</v>
@@ -10039,68 +9716,68 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B67" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C67" t="s">
         <v>69</v>
       </c>
       <c r="D67" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="N67" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B68" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C68" t="s">
         <v>69</v>
       </c>
       <c r="D68" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="O68" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B69" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C69" t="s">
         <v>69</v>
       </c>
       <c r="D69" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M69" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -10154,68 +9831,68 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B3" s="7">
         <v>0.75</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B4" s="7">
         <v>0.01</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B5" s="7">
         <v>100</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B6" s="7" t="b">
         <v>1</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/example_new_calculations/input/input.xlsx
+++ b/workspaces/example_new_calculations/input/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKL\Documents\Github\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098B7AA6-A806-47C5-9754-45A47EB3D239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E084F0-FBA1-44B9-8FA5-0B77B38F63AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
+    <workbookView xWindow="28680" yWindow="-240" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
   </bookViews>
   <sheets>
     <sheet name="Vakken" sheetId="1" r:id="rId1"/>
@@ -1296,21 +1296,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C253AA-AAA1-47E5-9332-CA169F978D7A}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8.19921875" customWidth="1"/>
-    <col min="2" max="2" width="32.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.19921875" customWidth="1"/>
-    <col min="5" max="5" width="16.59765625" customWidth="1"/>
-    <col min="6" max="6" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.25" customWidth="1"/>
+    <col min="2" max="2" width="32.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.25" customWidth="1"/>
+    <col min="5" max="5" width="16.625" customWidth="1"/>
+    <col min="6" max="6" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.3984375" customWidth="1"/>
+    <col min="9" max="9" width="17.375" customWidth="1"/>
     <col min="10" max="10" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.59765625" customWidth="1"/>
+    <col min="11" max="11" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>140</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>c_achterland_vc</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1673,23 +1673,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB77777-746E-45C0-BE11-D138C11C003A}">
   <dimension ref="A1:M103"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.3984375" customWidth="1"/>
-    <col min="3" max="4" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.375" customWidth="1"/>
+    <col min="3" max="4" width="19.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.8984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.8984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.19921875" customWidth="1"/>
-    <col min="11" max="11" width="23.8984375" customWidth="1"/>
-    <col min="12" max="12" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.25" customWidth="1"/>
+    <col min="11" max="11" width="23.875" customWidth="1"/>
+    <col min="12" max="12" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>146</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2550,7 +2550,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2714,7 +2714,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3247,7 +3247,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3780,7 +3780,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3944,7 +3944,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4149,7 +4149,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4436,7 +4436,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4518,7 +4518,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4764,7 +4764,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4805,7 +4805,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4846,7 +4846,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5010,7 +5010,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5051,7 +5051,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5174,7 +5174,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5256,7 +5256,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5297,7 +5297,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5379,7 +5379,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5420,7 +5420,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5461,7 +5461,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5543,7 +5543,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5584,7 +5584,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5625,7 +5625,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5666,7 +5666,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5707,7 +5707,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5748,7 +5748,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A100">
         <v>100</v>
       </c>
@@ -5789,7 +5789,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A101">
         <v>101</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A102">
         <v>102</v>
       </c>
@@ -5871,7 +5871,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A103">
         <v>103</v>
       </c>
@@ -5924,22 +5924,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3ED9FF6-8968-4FA6-BAEC-B95365AA2886}">
   <dimension ref="A1:N55"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.19921875" customWidth="1"/>
-    <col min="3" max="3" width="21.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="21.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.8984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="23.09765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.3984375" customWidth="1"/>
-    <col min="13" max="13" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.19921875" customWidth="1"/>
+    <col min="12" max="12" width="11.375" customWidth="1"/>
+    <col min="13" max="13" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>149</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>d70_vc</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6147,7 +6147,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6180,7 +6180,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6213,7 +6213,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -6257,7 +6257,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6301,7 +6301,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -6339,7 +6339,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6372,7 +6372,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6438,7 +6438,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6482,7 +6482,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6526,7 +6526,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6564,7 +6564,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6597,7 +6597,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6630,7 +6630,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6663,7 +6663,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6707,7 +6707,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6751,7 +6751,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>21</v>
       </c>
@@ -6789,7 +6789,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>22</v>
       </c>
@@ -6822,7 +6822,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>23</v>
       </c>
@@ -6855,7 +6855,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -6888,7 +6888,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>25</v>
       </c>
@@ -6932,7 +6932,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>26</v>
       </c>
@@ -6976,7 +6976,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>27</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>28</v>
       </c>
@@ -7047,7 +7047,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>29</v>
       </c>
@@ -7080,7 +7080,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>30</v>
       </c>
@@ -7113,7 +7113,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>31</v>
       </c>
@@ -7157,7 +7157,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>32</v>
       </c>
@@ -7201,7 +7201,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>33</v>
       </c>
@@ -7239,7 +7239,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>34</v>
       </c>
@@ -7272,7 +7272,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>35</v>
       </c>
@@ -7305,7 +7305,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>36</v>
       </c>
@@ -7338,7 +7338,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>37</v>
       </c>
@@ -7382,7 +7382,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>38</v>
       </c>
@@ -7426,7 +7426,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>39</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>40</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>41</v>
       </c>
@@ -7530,7 +7530,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>42</v>
       </c>
@@ -7563,7 +7563,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>43</v>
       </c>
@@ -7607,7 +7607,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>44</v>
       </c>
@@ -7651,7 +7651,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>45</v>
       </c>
@@ -7689,7 +7689,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>46</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>47</v>
       </c>
@@ -7755,7 +7755,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>48</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>49</v>
       </c>
@@ -7832,7 +7832,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>50</v>
       </c>
@@ -7876,7 +7876,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>51</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>52</v>
       </c>
@@ -7947,7 +7947,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>53</v>
       </c>
@@ -7980,7 +7980,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>54</v>
       </c>
@@ -8024,25 +8024,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B7A8CE-63DA-4EEA-9A88-5E62FD2B5E40}">
   <dimension ref="A1:P69"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.8984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.25" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="17.25" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.19921875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="51.09765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="51.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>213</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>140</v>
       </c>
@@ -8109,7 +8109,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>141</v>
       </c>
@@ -8126,7 +8126,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -8141,7 +8141,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -8156,7 +8156,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>142</v>
       </c>
@@ -8173,7 +8173,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -8190,7 +8190,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>147</v>
       </c>
@@ -8207,7 +8207,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>148</v>
       </c>
@@ -8224,7 +8224,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>143</v>
       </c>
@@ -8241,7 +8241,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>144</v>
       </c>
@@ -8256,7 +8256,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>145</v>
       </c>
@@ -8271,7 +8271,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>149</v>
       </c>
@@ -8288,7 +8288,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>150</v>
       </c>
@@ -8305,7 +8305,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>151</v>
       </c>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>65</v>
       </c>
@@ -8357,7 +8357,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>62</v>
       </c>
@@ -8388,7 +8388,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -8420,7 +8420,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>59</v>
       </c>
@@ -8455,7 +8455,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -8484,7 +8484,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -8525,7 +8525,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -8560,7 +8560,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -8593,7 +8593,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -8629,7 +8629,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -8667,7 +8667,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>2</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>19</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>20</v>
       </c>
@@ -8752,7 +8752,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -8784,7 +8784,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>91</v>
       </c>
@@ -8813,7 +8813,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>78</v>
       </c>
@@ -8838,7 +8838,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>93</v>
       </c>
@@ -8866,7 +8866,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>98</v>
       </c>
@@ -8895,7 +8895,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>49</v>
       </c>
@@ -8920,7 +8920,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>138</v>
       </c>
@@ -8943,7 +8943,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>134</v>
       </c>
@@ -9003,7 +9003,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>136</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>76</v>
       </c>
@@ -9058,7 +9058,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
         <v>88</v>
       </c>
@@ -9087,7 +9087,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -9116,7 +9116,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -9150,7 +9150,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -9184,7 +9184,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
         <v>67</v>
       </c>
@@ -9218,7 +9218,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -9243,7 +9243,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -9265,7 +9265,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -9287,7 +9287,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
         <v>106</v>
       </c>
@@ -9309,7 +9309,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
         <v>102</v>
       </c>
@@ -9331,7 +9331,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
         <v>100</v>
       </c>
@@ -9353,7 +9353,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
         <v>130</v>
       </c>
@@ -9375,7 +9375,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
         <v>132</v>
       </c>
@@ -9397,7 +9397,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
         <v>128</v>
       </c>
@@ -9419,7 +9419,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -9441,7 +9441,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
         <v>104</v>
       </c>
@@ -9463,7 +9463,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A56" t="s">
         <v>56</v>
       </c>
@@ -9482,7 +9482,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A57" t="s">
         <v>118</v>
       </c>
@@ -9504,7 +9504,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
         <v>86</v>
       </c>
@@ -9526,7 +9526,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
         <v>116</v>
       </c>
@@ -9548,7 +9548,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A60" t="s">
         <v>122</v>
       </c>
@@ -9570,7 +9570,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A61" t="s">
         <v>120</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A62" t="s">
         <v>82</v>
       </c>
@@ -9620,7 +9620,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A63" t="s">
         <v>80</v>
       </c>
@@ -9642,7 +9642,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A64" t="s">
         <v>126</v>
       </c>
@@ -9664,7 +9664,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A65" t="s">
         <v>124</v>
       </c>
@@ -9686,7 +9686,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A66" t="s">
         <v>114</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A67" t="s">
         <v>110</v>
       </c>
@@ -9736,7 +9736,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A68" t="s">
         <v>112</v>
       </c>
@@ -9758,7 +9758,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A69" t="s">
         <v>108</v>
       </c>
@@ -9823,13 +9823,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7FD5E8-359B-4F56-B38E-FCA72B85D698}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.69921875" style="7"/>
+    <col min="1" max="1" width="23.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.75" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>200</v>
       </c>
@@ -9840,7 +9840,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>197</v>
       </c>
@@ -9851,7 +9851,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>194</v>
       </c>
@@ -9862,7 +9862,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>193</v>
       </c>
@@ -9873,7 +9873,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>191</v>
       </c>
@@ -9884,7 +9884,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>189</v>
       </c>

--- a/workspaces/example_new_calculations/input/input.xlsx
+++ b/workspaces/example_new_calculations/input/input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKL\Documents\Github\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oscop\Documents\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E084F0-FBA1-44B9-8FA5-0B77B38F63AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB427C6-6B29-41A0-A209-FAFB22771210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-240" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
   </bookViews>
   <sheets>
     <sheet name="Vakken" sheetId="1" r:id="rId1"/>
@@ -825,8 +825,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{11010186-4FF4-48E2-AD4E-93BC10A29908}"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
     <dxf>
@@ -929,8 +929,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9844274D-7B34-420F-9662-89C5C9A298BD}" name="Tabel10" displayName="Tabel10" ref="A2:N55" headerRowCount="0" totalsRowShown="0">
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9844274D-7B34-420F-9662-89C5C9A298BD}" name="Tabel10" displayName="Tabel10" ref="A2:P55" headerRowCount="0" totalsRowShown="0">
+  <tableColumns count="16">
     <tableColumn id="2" xr3:uid="{E80206AD-C5FD-4475-B5E4-08A08DA66E4A}" name="Kolom2"/>
     <tableColumn id="13" xr3:uid="{39F38892-EB92-4E2D-A4CE-461B1DC8B27E}" name="Column1"/>
     <tableColumn id="3" xr3:uid="{1769008F-0E39-48C3-B6C5-959D62F52592}" name="Kolom3"/>
@@ -945,6 +945,8 @@
     <tableColumn id="12" xr3:uid="{FF7176FB-923E-4ECE-83AA-046E768AD06C}" name="Kolom12"/>
     <tableColumn id="14" xr3:uid="{4E1A767E-8059-4EF5-B52B-A1637577AFDF}" name="Kolom14" headerRowDxfId="9" dataDxfId="8"/>
     <tableColumn id="15" xr3:uid="{E12738E9-E3E4-4A5D-81C1-E333D11489B2}" name="Kolom15"/>
+    <tableColumn id="1" xr3:uid="{91551BCD-3114-41AE-9A7A-4845F967A1F2}" name="Kolom1"/>
+    <tableColumn id="16" xr3:uid="{5F264CE0-A1C7-48AF-B549-08E4BC8DFD75}" name="Kolom13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -979,7 +981,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1295,22 +1297,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C253AA-AAA1-47E5-9332-CA169F978D7A}">
-  <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.25" customWidth="1"/>
-    <col min="2" max="2" width="32.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.25" customWidth="1"/>
-    <col min="5" max="5" width="16.625" customWidth="1"/>
-    <col min="6" max="6" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.19921875" customWidth="1"/>
+    <col min="2" max="2" width="32.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.19921875" customWidth="1"/>
+    <col min="5" max="5" width="16.59765625" customWidth="1"/>
+    <col min="6" max="6" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.09765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.375" customWidth="1"/>
-    <col min="10" max="10" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.625" customWidth="1"/>
+    <col min="9" max="9" width="17.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>140</v>
       </c>
@@ -1339,15 +1339,8 @@
         <f>LEFT(H1,LEN(H1)-5)&amp;VLOOKUP(LEFT(H1,LEN(H1)-5),Overzicht_parameters!$A$2:$F$69,6,(FALSE))</f>
         <v>c_voorland_stdev</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="4" t="str">
-        <f>LEFT(J1,LEN(J1)-5)&amp;VLOOKUP(LEFT(J1,LEN(J1)-5),Overzicht_parameters!$A$2:$F$69,6,(FALSE))</f>
-        <v>c_achterland_vc</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1375,14 +1368,8 @@
       <c r="I2">
         <v>0.15</v>
       </c>
-      <c r="J2">
-        <v>10</v>
-      </c>
-      <c r="K2">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1410,14 +1397,8 @@
       <c r="I3">
         <v>0.15</v>
       </c>
-      <c r="J3">
-        <v>10</v>
-      </c>
-      <c r="K3">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1445,14 +1426,8 @@
       <c r="I4">
         <v>0.15</v>
       </c>
-      <c r="J4">
-        <v>10</v>
-      </c>
-      <c r="K4">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1480,14 +1455,8 @@
       <c r="I5">
         <v>0.15</v>
       </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1515,14 +1484,8 @@
       <c r="I6">
         <v>0.15</v>
       </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1550,14 +1513,8 @@
       <c r="I7">
         <v>0.15</v>
       </c>
-      <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1585,14 +1542,8 @@
       <c r="I8">
         <v>0.15</v>
       </c>
-      <c r="J8">
-        <v>10</v>
-      </c>
-      <c r="K8">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1620,14 +1571,8 @@
       <c r="I9">
         <v>0.15</v>
       </c>
-      <c r="J9">
-        <v>10</v>
-      </c>
-      <c r="K9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1654,12 +1599,6 @@
       </c>
       <c r="I10">
         <v>0.15</v>
-      </c>
-      <c r="J10">
-        <v>10</v>
-      </c>
-      <c r="K10">
-        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1673,23 +1612,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB77777-746E-45C0-BE11-D138C11C003A}">
   <dimension ref="A1:M103"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.375" customWidth="1"/>
-    <col min="3" max="4" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3984375" customWidth="1"/>
+    <col min="3" max="4" width="19.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.8984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.25" customWidth="1"/>
-    <col min="11" max="11" width="23.875" customWidth="1"/>
-    <col min="12" max="12" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.19921875" customWidth="1"/>
+    <col min="11" max="11" width="23.8984375" customWidth="1"/>
+    <col min="12" max="12" width="11.8984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>146</v>
       </c>
@@ -1730,7 +1669,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1771,7 +1710,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1812,7 +1751,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1853,7 +1792,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1894,7 +1833,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1935,7 +1874,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1976,7 +1915,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2017,7 +1956,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2058,7 +1997,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2099,7 +2038,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2140,7 +2079,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2181,7 +2120,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2222,7 +2161,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2263,7 +2202,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2304,7 +2243,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2345,7 +2284,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2386,7 +2325,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2427,7 +2366,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2468,7 +2407,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2509,7 +2448,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2550,7 +2489,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2591,7 +2530,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2632,7 +2571,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2673,7 +2612,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2714,7 +2653,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2755,7 +2694,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2796,7 +2735,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2837,7 +2776,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2878,7 +2817,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2919,7 +2858,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2960,7 +2899,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3001,7 +2940,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3042,7 +2981,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3083,7 +3022,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3124,7 +3063,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3165,7 +3104,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3206,7 +3145,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3247,7 +3186,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3288,7 +3227,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3329,7 +3268,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3370,7 +3309,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3411,7 +3350,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3452,7 +3391,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3493,7 +3432,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3534,7 +3473,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3575,7 +3514,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3616,7 +3555,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3657,7 +3596,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3698,7 +3637,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3739,7 +3678,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3780,7 +3719,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3821,7 +3760,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3862,7 +3801,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3903,7 +3842,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3944,7 +3883,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3985,7 +3924,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4026,7 +3965,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4067,7 +4006,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4108,7 +4047,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4149,7 +4088,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4190,7 +4129,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4231,7 +4170,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4272,7 +4211,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4313,7 +4252,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4354,7 +4293,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4395,7 +4334,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4436,7 +4375,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4477,7 +4416,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4518,7 +4457,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4559,7 +4498,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4600,7 +4539,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4641,7 +4580,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4682,7 +4621,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4723,7 +4662,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4764,7 +4703,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4805,7 +4744,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4846,7 +4785,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4887,7 +4826,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4928,7 +4867,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4969,7 +4908,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5010,7 +4949,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5051,7 +4990,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5092,7 +5031,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5133,7 +5072,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5174,7 +5113,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5215,7 +5154,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5256,7 +5195,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5297,7 +5236,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5338,7 +5277,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5379,7 +5318,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5420,7 +5359,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5461,7 +5400,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5502,7 +5441,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5543,7 +5482,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5584,7 +5523,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5625,7 +5564,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5666,7 +5605,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5707,7 +5646,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5748,7 +5687,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>100</v>
       </c>
@@ -5789,7 +5728,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>101</v>
       </c>
@@ -5830,7 +5769,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>102</v>
       </c>
@@ -5871,7 +5810,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>103</v>
       </c>
@@ -5923,23 +5862,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3ED9FF6-8968-4FA6-BAEC-B95365AA2886}">
-  <dimension ref="A1:N55"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:P55"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.25" customWidth="1"/>
-    <col min="3" max="3" width="21.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.19921875" customWidth="1"/>
+    <col min="3" max="3" width="21.69921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="23.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.59765625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.375" customWidth="1"/>
-    <col min="13" max="13" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.25" customWidth="1"/>
+    <col min="12" max="12" width="11.3984375" customWidth="1"/>
+    <col min="13" max="13" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.19921875" customWidth="1"/>
+    <col min="15" max="15" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>149</v>
       </c>
@@ -5987,8 +5928,15 @@
         <f>LEFT(M1,LEN(M1)-5)&amp;VLOOKUP(LEFT(M1,LEN(M1)-5),Overzicht_parameters!$A$2:$F$69,6,(FALSE))</f>
         <v>d70_vc</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="4" t="str">
+        <f>LEFT(O1,LEN(O1)-5)&amp;VLOOKUP(LEFT(O1,LEN(O1)-5),Overzicht_parameters!$A$2:$F$69,6,(FALSE))</f>
+        <v>c_achterland_vc</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6031,8 +5979,14 @@
       <c r="N2">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O2">
+        <v>10</v>
+      </c>
+      <c r="P2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6075,8 +6029,14 @@
       <c r="N3">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O3">
+        <v>10</v>
+      </c>
+      <c r="P3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6113,8 +6073,14 @@
       <c r="N4">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O4">
+        <v>10</v>
+      </c>
+      <c r="P4">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6146,8 +6112,14 @@
       <c r="N5">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O5">
+        <v>10</v>
+      </c>
+      <c r="P5">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6179,8 +6151,14 @@
       <c r="N6">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O6">
+        <v>10</v>
+      </c>
+      <c r="P6">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6212,8 +6190,14 @@
       <c r="N7">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O7">
+        <v>10</v>
+      </c>
+      <c r="P7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -6256,8 +6240,14 @@
       <c r="N8">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O8">
+        <v>10</v>
+      </c>
+      <c r="P8">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6300,8 +6290,14 @@
       <c r="N9">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O9">
+        <v>10</v>
+      </c>
+      <c r="P9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -6338,8 +6334,14 @@
       <c r="N10">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O10">
+        <v>10</v>
+      </c>
+      <c r="P10">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6371,8 +6373,14 @@
       <c r="N11">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O11">
+        <v>10</v>
+      </c>
+      <c r="P11">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6404,8 +6412,14 @@
       <c r="N12">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O12">
+        <v>10</v>
+      </c>
+      <c r="P12">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6437,8 +6451,14 @@
       <c r="N13">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O13">
+        <v>10</v>
+      </c>
+      <c r="P13">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6481,8 +6501,14 @@
       <c r="N14">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O14">
+        <v>10</v>
+      </c>
+      <c r="P14">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6525,8 +6551,14 @@
       <c r="N15">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O15">
+        <v>10</v>
+      </c>
+      <c r="P15">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6563,8 +6595,14 @@
       <c r="N16">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O16">
+        <v>10</v>
+      </c>
+      <c r="P16">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6596,8 +6634,14 @@
       <c r="N17">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O17">
+        <v>10</v>
+      </c>
+      <c r="P17">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6629,8 +6673,14 @@
       <c r="N18">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O18">
+        <v>10</v>
+      </c>
+      <c r="P18">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6662,8 +6712,14 @@
       <c r="N19">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O19">
+        <v>10</v>
+      </c>
+      <c r="P19">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6706,8 +6762,14 @@
       <c r="N20">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O20">
+        <v>10</v>
+      </c>
+      <c r="P20">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6750,8 +6812,14 @@
       <c r="N21">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O21">
+        <v>10</v>
+      </c>
+      <c r="P21">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -6788,8 +6856,14 @@
       <c r="N22">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O22">
+        <v>10</v>
+      </c>
+      <c r="P22">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -6821,8 +6895,14 @@
       <c r="N23">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O23">
+        <v>10</v>
+      </c>
+      <c r="P23">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -6854,8 +6934,14 @@
       <c r="N24">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O24">
+        <v>10</v>
+      </c>
+      <c r="P24">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -6887,8 +6973,14 @@
       <c r="N25">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O25">
+        <v>10</v>
+      </c>
+      <c r="P25">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -6931,8 +7023,14 @@
       <c r="N26">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O26">
+        <v>10</v>
+      </c>
+      <c r="P26">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -6975,8 +7073,14 @@
       <c r="N27">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O27">
+        <v>10</v>
+      </c>
+      <c r="P27">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -7013,8 +7117,14 @@
       <c r="N28">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O28">
+        <v>10</v>
+      </c>
+      <c r="P28">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -7046,8 +7156,14 @@
       <c r="N29">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O29">
+        <v>10</v>
+      </c>
+      <c r="P29">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -7079,8 +7195,14 @@
       <c r="N30">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O30">
+        <v>10</v>
+      </c>
+      <c r="P30">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -7112,8 +7234,14 @@
       <c r="N31">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O31">
+        <v>10</v>
+      </c>
+      <c r="P31">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -7156,8 +7284,14 @@
       <c r="N32">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O32">
+        <v>10</v>
+      </c>
+      <c r="P32">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -7200,8 +7334,14 @@
       <c r="N33">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O33">
+        <v>10</v>
+      </c>
+      <c r="P33">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -7238,8 +7378,14 @@
       <c r="N34">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O34">
+        <v>10</v>
+      </c>
+      <c r="P34">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -7271,8 +7417,14 @@
       <c r="N35">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O35">
+        <v>10</v>
+      </c>
+      <c r="P35">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -7304,8 +7456,14 @@
       <c r="N36">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O36">
+        <v>10</v>
+      </c>
+      <c r="P36">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -7337,8 +7495,14 @@
       <c r="N37">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O37">
+        <v>10</v>
+      </c>
+      <c r="P37">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -7381,8 +7545,14 @@
       <c r="N38">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O38">
+        <v>10</v>
+      </c>
+      <c r="P38">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -7425,8 +7595,14 @@
       <c r="N39">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O39">
+        <v>10</v>
+      </c>
+      <c r="P39">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -7463,8 +7639,14 @@
       <c r="N40">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O40">
+        <v>10</v>
+      </c>
+      <c r="P40">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -7496,8 +7678,14 @@
       <c r="N41">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O41">
+        <v>10</v>
+      </c>
+      <c r="P41">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -7529,8 +7717,14 @@
       <c r="N42">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O42">
+        <v>10</v>
+      </c>
+      <c r="P42">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -7562,8 +7756,14 @@
       <c r="N43">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O43">
+        <v>10</v>
+      </c>
+      <c r="P43">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -7606,8 +7806,14 @@
       <c r="N44">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O44">
+        <v>10</v>
+      </c>
+      <c r="P44">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -7650,8 +7856,14 @@
       <c r="N45">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O45">
+        <v>10</v>
+      </c>
+      <c r="P45">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -7688,8 +7900,14 @@
       <c r="N46">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O46">
+        <v>10</v>
+      </c>
+      <c r="P46">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -7721,8 +7939,14 @@
       <c r="N47">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O47">
+        <v>10</v>
+      </c>
+      <c r="P47">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -7754,8 +7978,14 @@
       <c r="N48">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O48">
+        <v>10</v>
+      </c>
+      <c r="P48">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -7787,8 +8017,14 @@
       <c r="N49">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O49">
+        <v>10</v>
+      </c>
+      <c r="P49">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -7831,8 +8067,14 @@
       <c r="N50">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O50">
+        <v>10</v>
+      </c>
+      <c r="P50">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -7875,8 +8117,14 @@
       <c r="N51">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O51">
+        <v>10</v>
+      </c>
+      <c r="P51">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -7913,8 +8161,14 @@
       <c r="N52">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O52">
+        <v>10</v>
+      </c>
+      <c r="P52">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -7946,8 +8200,14 @@
       <c r="N53">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O53">
+        <v>10</v>
+      </c>
+      <c r="P53">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -7979,8 +8239,14 @@
       <c r="N54">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O54">
+        <v>10</v>
+      </c>
+      <c r="P54">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -8011,6 +8277,12 @@
       <c r="M55" s="1"/>
       <c r="N55">
         <v>0.12</v>
+      </c>
+      <c r="O55">
+        <v>10</v>
+      </c>
+      <c r="P55">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -8024,25 +8296,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9B7A8CE-63DA-4EEA-9A88-5E62FD2B5E40}">
   <dimension ref="A1:P69"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="17.19921875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.19921875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="51.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="51.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>213</v>
       </c>
@@ -8092,7 +8364,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>140</v>
       </c>
@@ -8109,7 +8381,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>141</v>
       </c>
@@ -8126,7 +8398,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -8141,7 +8413,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -8156,7 +8428,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>142</v>
       </c>
@@ -8173,7 +8445,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -8190,7 +8462,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>147</v>
       </c>
@@ -8207,7 +8479,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>148</v>
       </c>
@@ -8224,7 +8496,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>143</v>
       </c>
@@ -8241,7 +8513,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>144</v>
       </c>
@@ -8256,7 +8528,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>145</v>
       </c>
@@ -8271,7 +8543,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>149</v>
       </c>
@@ -8288,7 +8560,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>150</v>
       </c>
@@ -8305,7 +8577,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>151</v>
       </c>
@@ -8329,7 +8601,7 @@
       </c>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>65</v>
       </c>
@@ -8351,13 +8623,13 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="L16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>62</v>
       </c>
@@ -8388,7 +8660,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -8420,7 +8692,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>59</v>
       </c>
@@ -8455,7 +8727,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -8484,7 +8756,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -8525,7 +8797,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -8560,7 +8832,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -8593,7 +8865,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -8629,7 +8901,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -8667,7 +8939,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>2</v>
       </c>
@@ -8689,7 +8961,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>19</v>
       </c>
@@ -8718,7 +8990,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>20</v>
       </c>
@@ -8752,7 +9024,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -8784,7 +9056,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>91</v>
       </c>
@@ -8813,7 +9085,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>78</v>
       </c>
@@ -8838,7 +9110,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>93</v>
       </c>
@@ -8866,7 +9138,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>98</v>
       </c>
@@ -8895,7 +9167,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>49</v>
       </c>
@@ -8920,7 +9192,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>138</v>
       </c>
@@ -8943,7 +9215,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -8977,7 +9249,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>134</v>
       </c>
@@ -9003,7 +9275,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>136</v>
       </c>
@@ -9029,7 +9301,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>76</v>
       </c>
@@ -9058,7 +9330,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>88</v>
       </c>
@@ -9087,7 +9359,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -9116,7 +9388,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -9150,7 +9422,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -9184,7 +9456,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>67</v>
       </c>
@@ -9218,7 +9490,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -9243,7 +9515,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -9265,7 +9537,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -9287,7 +9559,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>106</v>
       </c>
@@ -9309,7 +9581,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>102</v>
       </c>
@@ -9331,7 +9603,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>100</v>
       </c>
@@ -9353,7 +9625,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>130</v>
       </c>
@@ -9375,7 +9647,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>132</v>
       </c>
@@ -9397,7 +9669,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>128</v>
       </c>
@@ -9419,7 +9691,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -9441,7 +9713,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>104</v>
       </c>
@@ -9463,7 +9735,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>56</v>
       </c>
@@ -9482,7 +9754,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>118</v>
       </c>
@@ -9504,7 +9776,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>86</v>
       </c>
@@ -9526,7 +9798,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>116</v>
       </c>
@@ -9548,7 +9820,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>122</v>
       </c>
@@ -9570,7 +9842,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>120</v>
       </c>
@@ -9592,7 +9864,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>82</v>
       </c>
@@ -9620,7 +9892,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>80</v>
       </c>
@@ -9642,7 +9914,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>126</v>
       </c>
@@ -9664,7 +9936,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>124</v>
       </c>
@@ -9686,7 +9958,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>114</v>
       </c>
@@ -9714,7 +9986,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>110</v>
       </c>
@@ -9736,7 +10008,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>112</v>
       </c>
@@ -9758,7 +10030,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>108</v>
       </c>
@@ -9823,13 +10095,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7FD5E8-359B-4F56-B38E-FCA72B85D698}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.75" style="7"/>
+    <col min="1" max="1" width="23.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.69921875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>200</v>
       </c>
@@ -9840,7 +10112,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>197</v>
       </c>
@@ -9851,7 +10123,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>194</v>
       </c>
@@ -9862,7 +10134,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>193</v>
       </c>
@@ -9873,7 +10145,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>191</v>
       </c>
@@ -9884,7 +10156,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>189</v>
       </c>

--- a/workspaces/example_new_calculations/input/input.xlsx
+++ b/workspaces/example_new_calculations/input/input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oscop\Documents\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CP\git_clones\GeoProb-Pipe\GeoProb-PipeV2\GeoProb-Pipe\workspaces\example_new_calculations\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB427C6-6B29-41A0-A209-FAFB22771210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BFE16AE-3D80-4E4F-8280-91C0922CECC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
   </bookViews>
   <sheets>
     <sheet name="Vakken" sheetId="1" r:id="rId1"/>
@@ -9271,6 +9271,9 @@
       <c r="G37">
         <v>0.1</v>
       </c>
+      <c r="H37">
+        <v>0.1</v>
+      </c>
       <c r="K37" s="2" t="s">
         <v>75</v>
       </c>
@@ -9296,6 +9299,9 @@
       </c>
       <c r="G38">
         <v>0.01</v>
+      </c>
+      <c r="H38">
+        <v>0.1</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>75</v>
